--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A4570C-CC6D-4720-87C5-C212750BA381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F8D6B2-7F0D-45D6-AC7C-D868B9EE424D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="1097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="1098">
   <si>
     <t>Prénom</t>
   </si>
@@ -94,9 +94,6 @@
     <t>Niveau</t>
   </si>
   <si>
-    <t xml:space="preserve">Doménikos </t>
-  </si>
-  <si>
     <t>LE GRECO</t>
   </si>
   <si>
@@ -3311,6 +3308,12 @@
   </si>
   <si>
     <t>1280 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominikos </t>
+  </si>
+  <si>
+    <t>THEOTOKOPOULOS</t>
   </si>
 </sst>
 </file>
@@ -3771,49 +3774,52 @@
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>28</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>29</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>30</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>31</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="Q2" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" t="s">
         <v>35</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>36</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>37</v>
-      </c>
-      <c r="W2" t="s">
-        <v>38</v>
       </c>
       <c r="X2">
         <v>1</v>
@@ -3821,49 +3827,52 @@
     </row>
     <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
       <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
         <v>39</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>40</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>41</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="Q3" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="S3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>45</v>
       </c>
-      <c r="U3" t="s">
-        <v>46</v>
-      </c>
       <c r="W3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="X3">
         <v>2</v>
@@ -3871,46 +3880,49 @@
     </row>
     <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
       <c r="H4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" t="s">
         <v>47</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>48</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>49</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="S4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T4" t="s">
         <v>51</v>
       </c>
-      <c r="S4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>52</v>
       </c>
-      <c r="U4" t="s">
-        <v>53</v>
-      </c>
       <c r="W4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -3918,49 +3930,52 @@
     </row>
     <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
       <c r="H5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" t="s">
         <v>54</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>55</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>56</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="Q5" t="s">
         <v>58</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="S5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T5" t="s">
         <v>59</v>
       </c>
-      <c r="S5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>60</v>
       </c>
-      <c r="U5" t="s">
-        <v>61</v>
-      </c>
       <c r="W5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="X5">
         <v>3</v>
@@ -3968,49 +3983,49 @@
     </row>
     <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" t="s">
         <v>62</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" t="s">
         <v>63</v>
       </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>64</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>65</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>66</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>67</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>68</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="Q6" t="s">
         <v>70</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="S6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T6" t="s">
         <v>71</v>
       </c>
-      <c r="S6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>72</v>
       </c>
-      <c r="U6" t="s">
+      <c r="W6" t="s">
         <v>73</v>
-      </c>
-      <c r="W6" t="s">
-        <v>74</v>
       </c>
       <c r="X6">
         <v>3</v>
@@ -4018,46 +4033,46 @@
     </row>
     <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
         <v>75</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F7" t="s">
         <v>76</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>77</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>78</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>79</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>80</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
         <v>81</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="Q7" t="s">
         <v>83</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="S7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="T7" t="s">
         <v>85</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>86</v>
       </c>
-      <c r="U7" t="s">
+      <c r="W7" t="s">
         <v>87</v>
-      </c>
-      <c r="W7" t="s">
-        <v>88</v>
       </c>
       <c r="X7">
         <v>3</v>
@@ -4065,43 +4080,43 @@
     </row>
     <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" t="s">
         <v>89</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" t="s">
         <v>90</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>91</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>92</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>93</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>94</v>
       </c>
-      <c r="J8" t="s">
+      <c r="M8" t="s">
         <v>95</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="S8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T8" t="s">
+        <v>45</v>
+      </c>
+      <c r="U8" t="s">
         <v>97</v>
       </c>
-      <c r="S8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T8" t="s">
-        <v>46</v>
-      </c>
-      <c r="U8" t="s">
-        <v>98</v>
-      </c>
       <c r="W8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X8">
         <v>3</v>
@@ -4109,43 +4124,43 @@
     </row>
     <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" t="s">
         <v>99</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F9" t="s">
         <v>100</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>101</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>102</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>103</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>104</v>
       </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>105</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="T9" t="s">
         <v>108</v>
       </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
         <v>109</v>
       </c>
-      <c r="U9" t="s">
+      <c r="W9" t="s">
         <v>110</v>
-      </c>
-      <c r="W9" t="s">
-        <v>111</v>
       </c>
       <c r="X9">
         <v>3</v>
@@ -4153,43 +4168,43 @@
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
         <v>99</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
         <v>100</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>101</v>
       </c>
-      <c r="G10" t="s">
-        <v>102</v>
-      </c>
       <c r="H10" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" t="s">
         <v>112</v>
       </c>
-      <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10" t="s">
+      <c r="N10" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="S10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" t="s">
         <v>114</v>
       </c>
-      <c r="S10" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
         <v>115</v>
       </c>
-      <c r="U10" t="s">
-        <v>116</v>
-      </c>
       <c r="W10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X10">
         <v>3</v>
@@ -4197,46 +4212,46 @@
     </row>
     <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" t="s">
         <v>117</v>
       </c>
-      <c r="B11" t="s">
+      <c r="F11" t="s">
         <v>118</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>119</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>120</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>121</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>122</v>
       </c>
-      <c r="J11" t="s">
+      <c r="M11" t="s">
         <v>123</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="Q11" t="s">
         <v>125</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="S11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T11" t="s">
         <v>126</v>
       </c>
-      <c r="S11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
         <v>127</v>
       </c>
-      <c r="U11" t="s">
-        <v>128</v>
-      </c>
       <c r="W11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X11">
         <v>3</v>
@@ -4244,43 +4259,43 @@
     </row>
     <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" t="s">
         <v>129</v>
       </c>
-      <c r="B12" t="s">
+      <c r="F12" t="s">
         <v>130</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>131</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>132</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" t="s">
         <v>133</v>
       </c>
-      <c r="I12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="N12" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="S12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T12" t="s">
         <v>135</v>
       </c>
-      <c r="S12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>136</v>
       </c>
-      <c r="U12" t="s">
-        <v>137</v>
-      </c>
       <c r="W12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X12">
         <v>3</v>
@@ -4288,43 +4303,43 @@
     </row>
     <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" t="s">
         <v>129</v>
       </c>
-      <c r="B13" t="s">
+      <c r="F13" t="s">
         <v>130</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>131</v>
       </c>
-      <c r="G13" t="s">
-        <v>132</v>
-      </c>
       <c r="H13" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" t="s">
         <v>138</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>139</v>
       </c>
-      <c r="J13" t="s">
+      <c r="M13" t="s">
         <v>140</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="S13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T13" t="s">
+        <v>135</v>
+      </c>
+      <c r="U13" t="s">
         <v>136</v>
       </c>
-      <c r="U13" t="s">
-        <v>137</v>
-      </c>
       <c r="W13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X13">
         <v>1</v>
@@ -4332,43 +4347,43 @@
     </row>
     <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" t="s">
         <v>129</v>
       </c>
-      <c r="B14" t="s">
+      <c r="F14" t="s">
         <v>130</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>131</v>
       </c>
-      <c r="G14" t="s">
-        <v>132</v>
-      </c>
       <c r="H14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I14" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" t="s">
         <v>40</v>
       </c>
-      <c r="J14" t="s">
-        <v>41</v>
-      </c>
       <c r="M14" t="s">
+        <v>142</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="S14" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T14" t="s">
+        <v>135</v>
+      </c>
+      <c r="U14" t="s">
         <v>136</v>
       </c>
-      <c r="U14" t="s">
-        <v>137</v>
-      </c>
       <c r="W14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X14">
         <v>3</v>
@@ -4376,43 +4391,43 @@
     </row>
     <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" t="s">
         <v>129</v>
       </c>
-      <c r="B15" t="s">
+      <c r="F15" t="s">
         <v>130</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>131</v>
       </c>
-      <c r="G15" t="s">
-        <v>132</v>
-      </c>
       <c r="H15" t="s">
+        <v>137</v>
+      </c>
+      <c r="I15" t="s">
         <v>138</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>139</v>
       </c>
-      <c r="J15" t="s">
-        <v>140</v>
-      </c>
       <c r="M15" t="s">
+        <v>144</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="S15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T15" t="s">
+        <v>135</v>
+      </c>
+      <c r="U15" t="s">
         <v>136</v>
       </c>
-      <c r="U15" t="s">
-        <v>137</v>
-      </c>
       <c r="W15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -4420,43 +4435,43 @@
     </row>
     <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" t="s">
         <v>129</v>
       </c>
-      <c r="B16" t="s">
+      <c r="F16" t="s">
         <v>130</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>131</v>
       </c>
-      <c r="G16" t="s">
-        <v>132</v>
-      </c>
       <c r="H16" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" t="s">
         <v>147</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>148</v>
       </c>
-      <c r="J16" t="s">
+      <c r="M16" t="s">
         <v>149</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="S16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T16" t="s">
         <v>151</v>
       </c>
-      <c r="S16" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
         <v>152</v>
       </c>
-      <c r="U16" t="s">
-        <v>153</v>
-      </c>
       <c r="W16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X16">
         <v>2</v>
@@ -4464,46 +4479,46 @@
     </row>
     <row r="17" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" t="s">
         <v>154</v>
       </c>
-      <c r="B17" t="s">
+      <c r="F17" t="s">
         <v>155</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>156</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>157</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>158</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>159</v>
       </c>
-      <c r="J17" t="s">
+      <c r="M17" t="s">
         <v>160</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="Q17" t="s">
         <v>162</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="S17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T17" t="s">
         <v>163</v>
       </c>
-      <c r="S17" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
         <v>164</v>
       </c>
-      <c r="U17" t="s">
-        <v>165</v>
-      </c>
       <c r="W17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X17">
         <v>2</v>
@@ -4511,52 +4526,52 @@
     </row>
     <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" t="s">
         <v>166</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>167</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" t="s">
         <v>168</v>
       </c>
-      <c r="E18" t="s">
-        <v>168</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>157</v>
+      </c>
+      <c r="H18" t="s">
         <v>169</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>158</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
+        <v>159</v>
+      </c>
+      <c r="M18" t="s">
         <v>170</v>
       </c>
-      <c r="I18" t="s">
-        <v>159</v>
-      </c>
-      <c r="J18" t="s">
-        <v>160</v>
-      </c>
-      <c r="M18" t="s">
+      <c r="N18" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="Q18" t="s">
         <v>172</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="S18" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="S18" s="1" t="s">
+      <c r="T18" t="s">
         <v>174</v>
       </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
         <v>175</v>
       </c>
-      <c r="U18" t="s">
-        <v>176</v>
-      </c>
       <c r="W18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X18">
         <v>3</v>
@@ -4564,52 +4579,52 @@
     </row>
     <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" t="s">
         <v>166</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
         <v>167</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F19" t="s">
         <v>168</v>
       </c>
-      <c r="E19" t="s">
-        <v>168</v>
-      </c>
-      <c r="F19" t="s">
-        <v>169</v>
-      </c>
       <c r="G19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H19" t="s">
+        <v>176</v>
+      </c>
+      <c r="I19" t="s">
         <v>177</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>178</v>
       </c>
-      <c r="J19" t="s">
+      <c r="M19" t="s">
         <v>179</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="Q19" t="s">
         <v>181</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="S19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T19" t="s">
         <v>182</v>
       </c>
-      <c r="S19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
         <v>183</v>
       </c>
-      <c r="U19" t="s">
-        <v>184</v>
-      </c>
       <c r="W19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X19">
         <v>1</v>
@@ -4617,52 +4632,52 @@
     </row>
     <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" t="s">
         <v>166</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>167</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>167</v>
+      </c>
+      <c r="F20" t="s">
         <v>168</v>
       </c>
-      <c r="E20" t="s">
-        <v>168</v>
-      </c>
-      <c r="F20" t="s">
-        <v>169</v>
-      </c>
       <c r="G20" t="s">
+        <v>157</v>
+      </c>
+      <c r="H20" t="s">
+        <v>184</v>
+      </c>
+      <c r="I20" t="s">
         <v>158</v>
       </c>
-      <c r="H20" t="s">
+      <c r="J20" t="s">
+        <v>159</v>
+      </c>
+      <c r="M20" t="s">
         <v>185</v>
       </c>
-      <c r="I20" t="s">
-        <v>159</v>
-      </c>
-      <c r="J20" t="s">
-        <v>160</v>
-      </c>
-      <c r="M20" t="s">
+      <c r="N20" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="Q20" t="s">
         <v>187</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="S20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T20" t="s">
         <v>188</v>
       </c>
-      <c r="S20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T20" t="s">
+      <c r="U20" t="s">
         <v>189</v>
       </c>
-      <c r="U20" t="s">
-        <v>190</v>
-      </c>
       <c r="W20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X20">
         <v>1</v>
@@ -4670,52 +4685,52 @@
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" t="s">
         <v>166</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D21" t="s">
         <v>167</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
+        <v>167</v>
+      </c>
+      <c r="F21" t="s">
         <v>168</v>
       </c>
-      <c r="E21" t="s">
-        <v>168</v>
-      </c>
-      <c r="F21" t="s">
-        <v>169</v>
-      </c>
       <c r="G21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H21" t="s">
+        <v>190</v>
+      </c>
+      <c r="I21" t="s">
         <v>191</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>192</v>
       </c>
-      <c r="J21" t="s">
+      <c r="M21" t="s">
         <v>193</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="Q21" t="s">
         <v>195</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="S21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T21" t="s">
         <v>196</v>
       </c>
-      <c r="S21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T21" t="s">
+      <c r="U21" t="s">
         <v>197</v>
       </c>
-      <c r="U21" t="s">
-        <v>198</v>
-      </c>
       <c r="W21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X21">
         <v>3</v>
@@ -4723,43 +4738,43 @@
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" t="s">
         <v>199</v>
       </c>
-      <c r="B22" t="s">
+      <c r="F22" t="s">
         <v>200</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>201</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>202</v>
       </c>
-      <c r="H22" t="s">
+      <c r="J22" t="s">
         <v>203</v>
       </c>
-      <c r="J22" t="s">
+      <c r="M22" t="s">
         <v>204</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="Q22" t="s">
         <v>206</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="S22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T22" t="s">
         <v>207</v>
       </c>
-      <c r="S22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T22" t="s">
+      <c r="U22" t="s">
         <v>208</v>
       </c>
-      <c r="U22" t="s">
-        <v>209</v>
-      </c>
       <c r="W22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X22">
         <v>3</v>
@@ -4767,46 +4782,46 @@
     </row>
     <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>198</v>
+      </c>
+      <c r="B23" t="s">
         <v>199</v>
       </c>
-      <c r="B23" t="s">
+      <c r="F23" t="s">
         <v>200</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>201</v>
       </c>
-      <c r="G23" t="s">
-        <v>202</v>
-      </c>
       <c r="H23" t="s">
+        <v>209</v>
+      </c>
+      <c r="I23" t="s">
         <v>210</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>211</v>
       </c>
-      <c r="J23" t="s">
+      <c r="M23" t="s">
         <v>212</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="Q23" t="s">
         <v>214</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="S23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T23" t="s">
         <v>215</v>
       </c>
-      <c r="S23" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T23" t="s">
+      <c r="U23" t="s">
         <v>216</v>
       </c>
-      <c r="U23" t="s">
-        <v>217</v>
-      </c>
       <c r="W23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X23">
         <v>3</v>
@@ -4814,43 +4829,43 @@
     </row>
     <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>217</v>
+      </c>
+      <c r="B24" t="s">
         <v>218</v>
       </c>
-      <c r="B24" t="s">
+      <c r="F24" t="s">
         <v>219</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>220</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>221</v>
       </c>
-      <c r="H24" t="s">
+      <c r="J24" t="s">
         <v>222</v>
       </c>
-      <c r="J24" t="s">
+      <c r="M24" t="s">
         <v>223</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="Q24" t="s">
         <v>225</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="S24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T24" t="s">
         <v>226</v>
       </c>
-      <c r="S24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T24" t="s">
+      <c r="U24" t="s">
         <v>227</v>
       </c>
-      <c r="U24" t="s">
-        <v>228</v>
-      </c>
       <c r="W24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X24">
         <v>3</v>
@@ -4858,52 +4873,52 @@
     </row>
     <row r="25" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>228</v>
+      </c>
+      <c r="B25" t="s">
         <v>229</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>230</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>231</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
+        <v>168</v>
+      </c>
+      <c r="G25" t="s">
         <v>232</v>
       </c>
-      <c r="F25" t="s">
-        <v>169</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>233</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
+        <v>54</v>
+      </c>
+      <c r="J25" t="s">
+        <v>55</v>
+      </c>
+      <c r="M25" t="s">
         <v>234</v>
       </c>
-      <c r="I25" t="s">
-        <v>55</v>
-      </c>
-      <c r="J25" t="s">
-        <v>56</v>
-      </c>
-      <c r="M25" t="s">
+      <c r="N25" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="Q25" t="s">
         <v>236</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="S25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T25" t="s">
         <v>237</v>
       </c>
-      <c r="S25" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T25" t="s">
+      <c r="U25" t="s">
         <v>238</v>
       </c>
-      <c r="U25" t="s">
-        <v>239</v>
-      </c>
       <c r="W25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X25">
         <v>3</v>
@@ -4911,43 +4926,43 @@
     </row>
     <row r="26" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>239</v>
+      </c>
+      <c r="B26" t="s">
         <v>240</v>
       </c>
-      <c r="B26" t="s">
+      <c r="F26" t="s">
         <v>241</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>242</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>243</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>244</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>245</v>
       </c>
-      <c r="J26" t="s">
+      <c r="M26" t="s">
         <v>246</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="N26" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="S26" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="U26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="W26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X26">
         <v>3</v>
@@ -4955,43 +4970,43 @@
     </row>
     <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" t="s">
         <v>249</v>
       </c>
-      <c r="B27" t="s">
+      <c r="F27" t="s">
         <v>250</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>251</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>252</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
+        <v>177</v>
+      </c>
+      <c r="J27" t="s">
+        <v>178</v>
+      </c>
+      <c r="M27" t="s">
         <v>253</v>
       </c>
-      <c r="I27" t="s">
-        <v>178</v>
-      </c>
-      <c r="J27" t="s">
-        <v>179</v>
-      </c>
-      <c r="M27" t="s">
+      <c r="N27" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="S27" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="S27" s="1" t="s">
+      <c r="T27" t="s">
         <v>256</v>
       </c>
-      <c r="T27" t="s">
+      <c r="U27" t="s">
         <v>257</v>
       </c>
-      <c r="U27" t="s">
-        <v>258</v>
-      </c>
       <c r="W27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X27">
         <v>2</v>
@@ -4999,46 +5014,46 @@
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>258</v>
+      </c>
+      <c r="B28" t="s">
+        <v>249</v>
+      </c>
+      <c r="F28" t="s">
         <v>259</v>
       </c>
-      <c r="B28" t="s">
-        <v>250</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" t="s">
         <v>260</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
         <v>103</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" t="s">
+        <v>104</v>
+      </c>
+      <c r="M28" t="s">
         <v>261</v>
       </c>
-      <c r="I28" t="s">
-        <v>104</v>
-      </c>
-      <c r="J28" t="s">
-        <v>105</v>
-      </c>
-      <c r="M28" t="s">
+      <c r="N28" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="Q28" t="s">
         <v>263</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="S28" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="S28" s="1" t="s">
+      <c r="T28" t="s">
         <v>265</v>
       </c>
-      <c r="T28" t="s">
+      <c r="U28" t="s">
         <v>266</v>
       </c>
-      <c r="U28" t="s">
-        <v>267</v>
-      </c>
       <c r="W28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X28">
         <v>1</v>
@@ -5046,43 +5061,43 @@
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>258</v>
+      </c>
+      <c r="B29" t="s">
+        <v>249</v>
+      </c>
+      <c r="F29" t="s">
         <v>259</v>
       </c>
-      <c r="B29" t="s">
-        <v>250</v>
-      </c>
-      <c r="F29" t="s">
-        <v>260</v>
-      </c>
       <c r="G29" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" t="s">
+        <v>267</v>
+      </c>
+      <c r="I29" t="s">
         <v>103</v>
       </c>
-      <c r="H29" t="s">
+      <c r="J29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M29" t="s">
         <v>268</v>
       </c>
-      <c r="I29" t="s">
-        <v>104</v>
-      </c>
-      <c r="J29" t="s">
-        <v>105</v>
-      </c>
-      <c r="M29" t="s">
+      <c r="N29" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="S29" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="S29" s="1" t="s">
+      <c r="T29" t="s">
         <v>271</v>
       </c>
-      <c r="T29" t="s">
+      <c r="U29" t="s">
         <v>272</v>
       </c>
-      <c r="U29" t="s">
-        <v>273</v>
-      </c>
       <c r="W29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X29">
         <v>1</v>
@@ -5090,43 +5105,43 @@
     </row>
     <row r="30" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>258</v>
+      </c>
+      <c r="B30" t="s">
+        <v>249</v>
+      </c>
+      <c r="F30" t="s">
         <v>259</v>
       </c>
-      <c r="B30" t="s">
-        <v>250</v>
-      </c>
-      <c r="F30" t="s">
-        <v>260</v>
-      </c>
       <c r="G30" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" t="s">
+        <v>273</v>
+      </c>
+      <c r="I30" t="s">
         <v>103</v>
       </c>
-      <c r="H30" t="s">
+      <c r="J30" t="s">
+        <v>104</v>
+      </c>
+      <c r="M30" t="s">
+        <v>268</v>
+      </c>
+      <c r="N30" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="I30" t="s">
-        <v>104</v>
-      </c>
-      <c r="J30" t="s">
-        <v>105</v>
-      </c>
-      <c r="M30" t="s">
-        <v>269</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="S30" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T30" t="s">
+        <v>271</v>
+      </c>
+      <c r="U30" t="s">
         <v>272</v>
       </c>
-      <c r="U30" t="s">
-        <v>273</v>
-      </c>
       <c r="W30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X30">
         <v>2</v>
@@ -5134,43 +5149,43 @@
     </row>
     <row r="31" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>258</v>
+      </c>
+      <c r="B31" t="s">
+        <v>249</v>
+      </c>
+      <c r="F31" t="s">
         <v>259</v>
       </c>
-      <c r="B31" t="s">
-        <v>250</v>
-      </c>
-      <c r="F31" t="s">
-        <v>260</v>
-      </c>
       <c r="G31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H31" t="s">
+        <v>275</v>
+      </c>
+      <c r="I31" t="s">
+        <v>177</v>
+      </c>
+      <c r="J31" t="s">
         <v>276</v>
       </c>
-      <c r="I31" t="s">
-        <v>178</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="M31" t="s">
         <v>277</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="S31" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="S31" s="1" t="s">
+      <c r="T31" t="s">
         <v>280</v>
       </c>
-      <c r="T31" t="s">
+      <c r="U31" t="s">
         <v>281</v>
       </c>
-      <c r="U31" t="s">
-        <v>282</v>
-      </c>
       <c r="W31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X31">
         <v>2</v>
@@ -5178,46 +5193,46 @@
     </row>
     <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>258</v>
+      </c>
+      <c r="B32" t="s">
+        <v>249</v>
+      </c>
+      <c r="F32" t="s">
         <v>259</v>
       </c>
-      <c r="B32" t="s">
-        <v>250</v>
-      </c>
-      <c r="F32" t="s">
-        <v>260</v>
-      </c>
       <c r="G32" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32" t="s">
+        <v>282</v>
+      </c>
+      <c r="I32" t="s">
         <v>103</v>
       </c>
-      <c r="H32" t="s">
+      <c r="J32" t="s">
+        <v>104</v>
+      </c>
+      <c r="M32" t="s">
         <v>283</v>
       </c>
-      <c r="I32" t="s">
-        <v>104</v>
-      </c>
-      <c r="J32" t="s">
-        <v>105</v>
-      </c>
-      <c r="M32" t="s">
+      <c r="N32" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="Q32" t="s">
         <v>285</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="S32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T32" t="s">
         <v>286</v>
       </c>
-      <c r="S32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T32" t="s">
+      <c r="U32" t="s">
         <v>287</v>
       </c>
-      <c r="U32" t="s">
-        <v>288</v>
-      </c>
       <c r="W32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X32">
         <v>2</v>
@@ -5225,43 +5240,43 @@
     </row>
     <row r="33" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" t="s">
+        <v>249</v>
+      </c>
+      <c r="F33" t="s">
         <v>259</v>
       </c>
-      <c r="B33" t="s">
-        <v>250</v>
-      </c>
-      <c r="F33" t="s">
-        <v>260</v>
-      </c>
       <c r="G33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I33" t="s">
+        <v>66</v>
+      </c>
+      <c r="J33" t="s">
         <v>67</v>
       </c>
-      <c r="J33" t="s">
-        <v>68</v>
-      </c>
       <c r="M33" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T33" t="s">
+        <v>286</v>
+      </c>
+      <c r="U33" t="s">
         <v>287</v>
       </c>
-      <c r="U33" t="s">
-        <v>288</v>
-      </c>
       <c r="W33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X33">
         <v>2</v>
@@ -5269,46 +5284,46 @@
     </row>
     <row r="34" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>289</v>
+      </c>
+      <c r="B34" t="s">
         <v>290</v>
       </c>
-      <c r="B34" t="s">
+      <c r="F34" t="s">
         <v>291</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" t="s">
         <v>292</v>
       </c>
-      <c r="G34" t="s">
-        <v>93</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
+        <v>210</v>
+      </c>
+      <c r="J34" t="s">
         <v>293</v>
       </c>
-      <c r="I34" t="s">
-        <v>211</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="M34" t="s">
         <v>294</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="Q34" t="s">
         <v>296</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="S34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T34" t="s">
         <v>297</v>
       </c>
-      <c r="S34" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T34" t="s">
+      <c r="U34" t="s">
         <v>298</v>
       </c>
-      <c r="U34" t="s">
+      <c r="W34" t="s">
         <v>299</v>
-      </c>
-      <c r="W34" t="s">
-        <v>300</v>
       </c>
       <c r="X34">
         <v>3</v>
@@ -5316,43 +5331,43 @@
     </row>
     <row r="35" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>300</v>
+      </c>
+      <c r="B35" t="s">
         <v>301</v>
       </c>
-      <c r="B35" t="s">
+      <c r="F35" t="s">
         <v>302</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>303</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>304</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
+        <v>103</v>
+      </c>
+      <c r="J35" t="s">
+        <v>104</v>
+      </c>
+      <c r="M35" t="s">
         <v>305</v>
       </c>
-      <c r="I35" t="s">
-        <v>104</v>
-      </c>
-      <c r="J35" t="s">
-        <v>105</v>
-      </c>
-      <c r="M35" t="s">
+      <c r="N35" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="S35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T35" t="s">
         <v>307</v>
       </c>
-      <c r="S35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T35" t="s">
+      <c r="U35" t="s">
         <v>308</v>
       </c>
-      <c r="U35" t="s">
+      <c r="W35" t="s">
         <v>309</v>
-      </c>
-      <c r="W35" t="s">
-        <v>310</v>
       </c>
       <c r="X35">
         <v>3</v>
@@ -5360,46 +5375,46 @@
     </row>
     <row r="36" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" t="s">
+        <v>310</v>
+      </c>
+      <c r="F36" t="s">
+        <v>252</v>
+      </c>
+      <c r="G36" t="s">
         <v>311</v>
       </c>
-      <c r="F36" t="s">
-        <v>253</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>312</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
+        <v>177</v>
+      </c>
+      <c r="J36" t="s">
+        <v>178</v>
+      </c>
+      <c r="M36" t="s">
         <v>313</v>
       </c>
-      <c r="I36" t="s">
-        <v>178</v>
-      </c>
-      <c r="J36" t="s">
-        <v>179</v>
-      </c>
-      <c r="M36" t="s">
+      <c r="N36" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="Q36" t="s">
         <v>315</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="S36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T36" t="s">
         <v>316</v>
       </c>
-      <c r="S36" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T36" t="s">
+      <c r="U36" t="s">
         <v>317</v>
       </c>
-      <c r="U36" t="s">
-        <v>318</v>
-      </c>
       <c r="W36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X36">
         <v>3</v>
@@ -5407,46 +5422,46 @@
     </row>
     <row r="37" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>318</v>
+      </c>
+      <c r="B37" t="s">
         <v>319</v>
       </c>
-      <c r="B37" t="s">
+      <c r="F37" t="s">
         <v>320</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
+        <v>102</v>
+      </c>
+      <c r="H37" t="s">
         <v>321</v>
       </c>
-      <c r="G37" t="s">
-        <v>103</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
+        <v>29</v>
+      </c>
+      <c r="J37" t="s">
+        <v>30</v>
+      </c>
+      <c r="M37" t="s">
         <v>322</v>
       </c>
-      <c r="I37" t="s">
-        <v>30</v>
-      </c>
-      <c r="J37" t="s">
-        <v>31</v>
-      </c>
-      <c r="M37" t="s">
+      <c r="N37" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="Q37" t="s">
         <v>324</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="S37" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="S37" s="1" t="s">
+      <c r="T37" t="s">
         <v>326</v>
       </c>
-      <c r="T37" t="s">
+      <c r="U37" t="s">
         <v>327</v>
       </c>
-      <c r="U37" t="s">
-        <v>328</v>
-      </c>
       <c r="W37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X37">
         <v>1</v>
@@ -5454,46 +5469,46 @@
     </row>
     <row r="38" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>318</v>
+      </c>
+      <c r="B38" t="s">
         <v>319</v>
       </c>
-      <c r="B38" t="s">
+      <c r="F38" t="s">
         <v>320</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38" t="s">
         <v>321</v>
       </c>
-      <c r="G38" t="s">
-        <v>103</v>
-      </c>
-      <c r="H38" t="s">
-        <v>322</v>
-      </c>
       <c r="I38" t="s">
+        <v>138</v>
+      </c>
+      <c r="J38" t="s">
         <v>139</v>
       </c>
-      <c r="J38" t="s">
-        <v>140</v>
-      </c>
       <c r="M38" t="s">
+        <v>328</v>
+      </c>
+      <c r="N38" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="Q38" t="s">
         <v>330</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="S38" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S38" s="1" t="s">
+      <c r="T38" t="s">
         <v>332</v>
       </c>
-      <c r="T38" t="s">
+      <c r="U38" t="s">
         <v>333</v>
       </c>
-      <c r="U38" t="s">
-        <v>334</v>
-      </c>
       <c r="W38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X38">
         <v>1</v>
@@ -5501,46 +5516,46 @@
     </row>
     <row r="39" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>318</v>
+      </c>
+      <c r="B39" t="s">
         <v>319</v>
       </c>
-      <c r="B39" t="s">
+      <c r="F39" t="s">
         <v>320</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
+        <v>102</v>
+      </c>
+      <c r="H39" t="s">
         <v>321</v>
       </c>
-      <c r="G39" t="s">
-        <v>103</v>
-      </c>
-      <c r="H39" t="s">
-        <v>322</v>
-      </c>
       <c r="I39" t="s">
+        <v>334</v>
+      </c>
+      <c r="J39" t="s">
         <v>335</v>
       </c>
-      <c r="J39" t="s">
+      <c r="M39" t="s">
         <v>336</v>
       </c>
-      <c r="M39" t="s">
+      <c r="N39" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="N39" s="1" t="s">
+      <c r="Q39" t="s">
         <v>338</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="S39" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="T39" t="s">
         <v>339</v>
       </c>
-      <c r="S39" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="T39" t="s">
+      <c r="U39" t="s">
         <v>340</v>
       </c>
-      <c r="U39" t="s">
-        <v>341</v>
-      </c>
       <c r="W39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X39">
         <v>1</v>
@@ -5548,46 +5563,46 @@
     </row>
     <row r="40" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>318</v>
+      </c>
+      <c r="B40" t="s">
         <v>319</v>
       </c>
-      <c r="B40" t="s">
+      <c r="F40" t="s">
         <v>320</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
+        <v>102</v>
+      </c>
+      <c r="H40" t="s">
         <v>321</v>
       </c>
-      <c r="G40" t="s">
-        <v>103</v>
-      </c>
-      <c r="H40" t="s">
-        <v>322</v>
-      </c>
       <c r="I40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J40" t="s">
+        <v>341</v>
+      </c>
+      <c r="M40" t="s">
         <v>342</v>
       </c>
-      <c r="M40" t="s">
+      <c r="N40" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="Q40" t="s">
         <v>344</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="S40" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="T40" t="s">
         <v>345</v>
       </c>
-      <c r="S40" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="T40" t="s">
-        <v>346</v>
-      </c>
       <c r="U40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="W40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X40">
         <v>1</v>
@@ -5595,46 +5610,46 @@
     </row>
     <row r="41" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>318</v>
+      </c>
+      <c r="B41" t="s">
         <v>319</v>
       </c>
-      <c r="B41" t="s">
+      <c r="F41" t="s">
         <v>320</v>
       </c>
-      <c r="F41" t="s">
-        <v>321</v>
-      </c>
       <c r="G41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H41" t="s">
+        <v>346</v>
+      </c>
+      <c r="I41" t="s">
+        <v>29</v>
+      </c>
+      <c r="J41" t="s">
+        <v>30</v>
+      </c>
+      <c r="M41" t="s">
+        <v>223</v>
+      </c>
+      <c r="N41" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="I41" t="s">
-        <v>30</v>
-      </c>
-      <c r="J41" t="s">
-        <v>31</v>
-      </c>
-      <c r="M41" t="s">
-        <v>224</v>
-      </c>
-      <c r="N41" s="1" t="s">
+      <c r="Q41" t="s">
         <v>348</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="S41" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="T41" t="s">
         <v>349</v>
       </c>
-      <c r="S41" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="T41" t="s">
-        <v>350</v>
-      </c>
       <c r="U41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X41">
         <v>1</v>
@@ -5642,43 +5657,43 @@
     </row>
     <row r="42" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>318</v>
+      </c>
+      <c r="B42" t="s">
         <v>319</v>
       </c>
-      <c r="B42" t="s">
+      <c r="F42" t="s">
         <v>320</v>
       </c>
-      <c r="F42" t="s">
-        <v>321</v>
-      </c>
       <c r="G42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H42" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I42" t="s">
+        <v>29</v>
+      </c>
+      <c r="J42" t="s">
         <v>30</v>
       </c>
-      <c r="J42" t="s">
-        <v>31</v>
-      </c>
       <c r="M42" t="s">
+        <v>350</v>
+      </c>
+      <c r="N42" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="N42" s="1" t="s">
+      <c r="S42" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="S42" s="1" t="s">
+      <c r="T42" t="s">
         <v>353</v>
       </c>
-      <c r="T42" t="s">
+      <c r="U42" t="s">
         <v>354</v>
       </c>
-      <c r="U42" t="s">
-        <v>355</v>
-      </c>
       <c r="W42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X42">
         <v>1</v>
@@ -5686,43 +5701,43 @@
     </row>
     <row r="43" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>318</v>
+      </c>
+      <c r="B43" t="s">
         <v>319</v>
       </c>
-      <c r="B43" t="s">
+      <c r="F43" t="s">
         <v>320</v>
       </c>
-      <c r="F43" t="s">
-        <v>321</v>
-      </c>
       <c r="G43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I43" t="s">
+        <v>29</v>
+      </c>
+      <c r="J43" t="s">
         <v>30</v>
       </c>
-      <c r="J43" t="s">
-        <v>31</v>
-      </c>
       <c r="M43" t="s">
+        <v>355</v>
+      </c>
+      <c r="N43" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="N43" s="1" t="s">
+      <c r="S43" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="S43" s="1" t="s">
+      <c r="T43" t="s">
         <v>358</v>
       </c>
-      <c r="T43" t="s">
+      <c r="U43" t="s">
         <v>359</v>
       </c>
-      <c r="U43" t="s">
-        <v>360</v>
-      </c>
       <c r="W43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X43">
         <v>1</v>
@@ -5730,43 +5745,43 @@
     </row>
     <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>318</v>
+      </c>
+      <c r="B44" t="s">
         <v>319</v>
       </c>
-      <c r="B44" t="s">
+      <c r="F44" t="s">
         <v>320</v>
       </c>
-      <c r="F44" t="s">
-        <v>321</v>
-      </c>
       <c r="G44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H44" t="s">
+        <v>360</v>
+      </c>
+      <c r="I44" t="s">
+        <v>29</v>
+      </c>
+      <c r="J44" t="s">
+        <v>30</v>
+      </c>
+      <c r="M44" t="s">
+        <v>355</v>
+      </c>
+      <c r="N44" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="I44" t="s">
-        <v>30</v>
-      </c>
-      <c r="J44" t="s">
-        <v>31</v>
-      </c>
-      <c r="M44" t="s">
-        <v>356</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="S44" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T44" t="s">
+        <v>358</v>
+      </c>
+      <c r="U44" t="s">
         <v>359</v>
       </c>
-      <c r="U44" t="s">
-        <v>360</v>
-      </c>
       <c r="W44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X44">
         <v>1</v>
@@ -5774,46 +5789,46 @@
     </row>
     <row r="45" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>362</v>
+      </c>
+      <c r="B45" t="s">
         <v>363</v>
       </c>
-      <c r="B45" t="s">
+      <c r="F45" t="s">
         <v>364</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>365</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>366</v>
       </c>
-      <c r="H45" t="s">
+      <c r="I45" t="s">
+        <v>103</v>
+      </c>
+      <c r="J45" t="s">
+        <v>104</v>
+      </c>
+      <c r="M45" t="s">
         <v>367</v>
       </c>
-      <c r="I45" t="s">
-        <v>104</v>
-      </c>
-      <c r="J45" t="s">
-        <v>105</v>
-      </c>
-      <c r="M45" t="s">
+      <c r="N45" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="N45" s="1" t="s">
+      <c r="Q45" t="s">
         <v>369</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="S45" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T45" t="s">
+        <v>227</v>
+      </c>
+      <c r="U45" t="s">
         <v>370</v>
       </c>
-      <c r="S45" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T45" t="s">
-        <v>228</v>
-      </c>
-      <c r="U45" t="s">
-        <v>371</v>
-      </c>
       <c r="W45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X45">
         <v>3</v>
@@ -5821,46 +5836,46 @@
     </row>
     <row r="46" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>362</v>
+      </c>
+      <c r="B46" t="s">
         <v>363</v>
       </c>
-      <c r="B46" t="s">
+      <c r="F46" t="s">
         <v>364</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>365</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>366</v>
       </c>
-      <c r="H46" t="s">
-        <v>367</v>
-      </c>
       <c r="I46" t="s">
+        <v>210</v>
+      </c>
+      <c r="J46" t="s">
         <v>211</v>
       </c>
-      <c r="J46" t="s">
-        <v>212</v>
-      </c>
       <c r="M46" t="s">
+        <v>371</v>
+      </c>
+      <c r="N46" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="N46" s="1" t="s">
+      <c r="Q46" t="s">
         <v>373</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="S46" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T46" t="s">
         <v>374</v>
       </c>
-      <c r="S46" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T46" t="s">
+      <c r="U46" t="s">
         <v>375</v>
       </c>
-      <c r="U46" t="s">
-        <v>376</v>
-      </c>
       <c r="W46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X46">
         <v>2</v>
@@ -5868,43 +5883,43 @@
     </row>
     <row r="47" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>362</v>
+      </c>
+      <c r="B47" t="s">
         <v>363</v>
       </c>
-      <c r="B47" t="s">
+      <c r="F47" t="s">
         <v>364</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>365</v>
       </c>
-      <c r="G47" t="s">
-        <v>366</v>
-      </c>
       <c r="H47" t="s">
+        <v>376</v>
+      </c>
+      <c r="I47" t="s">
+        <v>54</v>
+      </c>
+      <c r="J47" t="s">
         <v>377</v>
       </c>
-      <c r="I47" t="s">
-        <v>55</v>
-      </c>
-      <c r="J47" t="s">
+      <c r="M47" t="s">
         <v>378</v>
       </c>
-      <c r="M47" t="s">
+      <c r="N47" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="N47" s="1" t="s">
+      <c r="S47" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T47" t="s">
         <v>380</v>
       </c>
-      <c r="S47" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T47" t="s">
+      <c r="U47" t="s">
         <v>381</v>
       </c>
-      <c r="U47" t="s">
-        <v>382</v>
-      </c>
       <c r="W47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X47">
         <v>3</v>
@@ -5912,46 +5927,46 @@
     </row>
     <row r="48" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B48" t="s">
+        <v>382</v>
+      </c>
+      <c r="F48" t="s">
         <v>383</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
+        <v>304</v>
+      </c>
+      <c r="H48" t="s">
         <v>384</v>
       </c>
-      <c r="G48" t="s">
-        <v>305</v>
-      </c>
-      <c r="H48" t="s">
+      <c r="I48" t="s">
         <v>385</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>386</v>
       </c>
-      <c r="J48" t="s">
+      <c r="M48" t="s">
         <v>387</v>
       </c>
-      <c r="M48" t="s">
+      <c r="N48" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="N48" s="1" t="s">
+      <c r="Q48" t="s">
         <v>389</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="S48" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T48" t="s">
         <v>390</v>
       </c>
-      <c r="S48" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T48" t="s">
+      <c r="U48" t="s">
         <v>391</v>
       </c>
-      <c r="U48" t="s">
-        <v>392</v>
-      </c>
       <c r="W48" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X48">
         <v>1</v>
@@ -5959,46 +5974,46 @@
     </row>
     <row r="49" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B49" t="s">
+        <v>382</v>
+      </c>
+      <c r="F49" t="s">
         <v>383</v>
       </c>
-      <c r="F49" t="s">
-        <v>384</v>
-      </c>
       <c r="G49" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H49" t="s">
+        <v>392</v>
+      </c>
+      <c r="I49" t="s">
+        <v>158</v>
+      </c>
+      <c r="J49" t="s">
+        <v>159</v>
+      </c>
+      <c r="M49" t="s">
         <v>393</v>
       </c>
-      <c r="I49" t="s">
-        <v>159</v>
-      </c>
-      <c r="J49" t="s">
-        <v>160</v>
-      </c>
-      <c r="M49" t="s">
+      <c r="N49" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="N49" s="1" t="s">
+      <c r="Q49" t="s">
         <v>395</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="S49" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T49" t="s">
         <v>396</v>
       </c>
-      <c r="S49" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T49" t="s">
+      <c r="U49" t="s">
         <v>397</v>
       </c>
-      <c r="U49" t="s">
-        <v>398</v>
-      </c>
       <c r="W49" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X49">
         <v>2</v>
@@ -6006,49 +6021,49 @@
     </row>
     <row r="50" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>398</v>
+      </c>
+      <c r="B50" t="s">
         <v>399</v>
       </c>
-      <c r="B50" t="s">
+      <c r="D50" t="s">
         <v>400</v>
       </c>
-      <c r="D50" t="s">
+      <c r="F50" t="s">
         <v>401</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>402</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>403</v>
       </c>
-      <c r="H50" t="s">
+      <c r="I50" t="s">
+        <v>210</v>
+      </c>
+      <c r="J50" t="s">
+        <v>211</v>
+      </c>
+      <c r="M50" t="s">
         <v>404</v>
       </c>
-      <c r="I50" t="s">
-        <v>211</v>
-      </c>
-      <c r="J50" t="s">
-        <v>212</v>
-      </c>
-      <c r="M50" t="s">
+      <c r="N50" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="N50" s="1" t="s">
+      <c r="Q50" t="s">
         <v>406</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="S50" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="S50" s="1" t="s">
+      <c r="T50" t="s">
         <v>408</v>
       </c>
-      <c r="T50" t="s">
-        <v>409</v>
-      </c>
       <c r="U50" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="W50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X50">
         <v>2</v>
@@ -6056,43 +6071,43 @@
     </row>
     <row r="51" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>398</v>
+      </c>
+      <c r="B51" t="s">
         <v>399</v>
       </c>
-      <c r="B51" t="s">
+      <c r="D51" t="s">
         <v>400</v>
       </c>
-      <c r="D51" t="s">
+      <c r="F51" t="s">
         <v>401</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>402</v>
       </c>
-      <c r="G51" t="s">
-        <v>403</v>
-      </c>
       <c r="H51" t="s">
+        <v>409</v>
+      </c>
+      <c r="I51" t="s">
         <v>410</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>411</v>
       </c>
-      <c r="J51" t="s">
+      <c r="M51" t="s">
         <v>412</v>
       </c>
-      <c r="M51" t="s">
+      <c r="N51" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="N51" s="1" t="s">
+      <c r="Q51" t="s">
         <v>414</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="S51" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="S51" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="W51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X51">
         <v>3</v>
@@ -6100,46 +6115,46 @@
     </row>
     <row r="52" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>398</v>
+      </c>
+      <c r="B52" t="s">
         <v>399</v>
       </c>
-      <c r="B52" t="s">
+      <c r="D52" t="s">
         <v>400</v>
       </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
         <v>401</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>402</v>
       </c>
-      <c r="G52" t="s">
-        <v>403</v>
-      </c>
       <c r="H52" t="s">
+        <v>409</v>
+      </c>
+      <c r="I52" t="s">
         <v>410</v>
       </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
         <v>411</v>
       </c>
-      <c r="J52" t="s">
-        <v>412</v>
-      </c>
       <c r="M52" t="s">
+        <v>416</v>
+      </c>
+      <c r="N52" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="N52" s="1" t="s">
+      <c r="S52" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="T52" t="s">
         <v>418</v>
       </c>
-      <c r="S52" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="T52" t="s">
+      <c r="U52" t="s">
         <v>419</v>
       </c>
-      <c r="U52" t="s">
-        <v>420</v>
-      </c>
       <c r="W52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -6147,46 +6162,46 @@
     </row>
     <row r="53" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>398</v>
+      </c>
+      <c r="B53" t="s">
         <v>399</v>
       </c>
-      <c r="B53" t="s">
+      <c r="D53" t="s">
         <v>400</v>
       </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
         <v>401</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>402</v>
       </c>
-      <c r="G53" t="s">
-        <v>403</v>
-      </c>
       <c r="H53" t="s">
+        <v>420</v>
+      </c>
+      <c r="I53" t="s">
+        <v>410</v>
+      </c>
+      <c r="J53" t="s">
+        <v>411</v>
+      </c>
+      <c r="M53" t="s">
         <v>421</v>
       </c>
-      <c r="I53" t="s">
-        <v>411</v>
-      </c>
-      <c r="J53" t="s">
-        <v>412</v>
-      </c>
-      <c r="M53" t="s">
+      <c r="N53" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="N53" s="1" t="s">
+      <c r="S53" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="T53" t="s">
         <v>423</v>
       </c>
-      <c r="S53" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="T53" t="s">
+      <c r="U53" t="s">
         <v>424</v>
       </c>
-      <c r="U53" t="s">
-        <v>425</v>
-      </c>
       <c r="W53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X53">
         <v>1</v>
@@ -6194,49 +6209,49 @@
     </row>
     <row r="54" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>398</v>
+      </c>
+      <c r="B54" t="s">
         <v>399</v>
       </c>
-      <c r="B54" t="s">
+      <c r="D54" t="s">
         <v>400</v>
       </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
         <v>401</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>402</v>
       </c>
-      <c r="G54" t="s">
-        <v>403</v>
-      </c>
       <c r="H54" t="s">
+        <v>425</v>
+      </c>
+      <c r="I54" t="s">
+        <v>410</v>
+      </c>
+      <c r="J54" t="s">
         <v>426</v>
       </c>
-      <c r="I54" t="s">
-        <v>411</v>
-      </c>
-      <c r="J54" t="s">
+      <c r="M54" t="s">
         <v>427</v>
       </c>
-      <c r="M54" t="s">
+      <c r="N54" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="N54" s="1" t="s">
+      <c r="Q54" t="s">
         <v>429</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="S54" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="T54" t="s">
         <v>430</v>
       </c>
-      <c r="S54" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="T54" t="s">
+      <c r="U54" t="s">
         <v>431</v>
       </c>
-      <c r="U54" t="s">
-        <v>432</v>
-      </c>
       <c r="W54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X54">
         <v>2</v>
@@ -6244,49 +6259,49 @@
     </row>
     <row r="55" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>432</v>
+      </c>
+      <c r="B55" t="s">
         <v>433</v>
       </c>
-      <c r="B55" t="s">
+      <c r="D55" t="s">
         <v>434</v>
       </c>
-      <c r="D55" t="s">
+      <c r="F55" t="s">
         <v>435</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>436</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
+        <v>38</v>
+      </c>
+      <c r="I55" t="s">
         <v>437</v>
       </c>
-      <c r="H55" t="s">
-        <v>39</v>
-      </c>
-      <c r="I55" t="s">
+      <c r="J55" t="s">
         <v>438</v>
       </c>
-      <c r="J55" t="s">
+      <c r="M55" t="s">
         <v>439</v>
       </c>
-      <c r="M55" t="s">
+      <c r="N55" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="N55" s="1" t="s">
+      <c r="Q55" t="s">
         <v>441</v>
       </c>
-      <c r="Q55" t="s">
+      <c r="S55" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T55" t="s">
         <v>442</v>
       </c>
-      <c r="S55" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T55" t="s">
+      <c r="U55" t="s">
         <v>443</v>
       </c>
-      <c r="U55" t="s">
-        <v>444</v>
-      </c>
       <c r="W55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X55">
         <v>3</v>
@@ -6294,46 +6309,46 @@
     </row>
     <row r="56" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>432</v>
+      </c>
+      <c r="B56" t="s">
         <v>433</v>
       </c>
-      <c r="B56" t="s">
+      <c r="D56" t="s">
         <v>434</v>
       </c>
-      <c r="D56" t="s">
+      <c r="F56" t="s">
         <v>435</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>436</v>
       </c>
-      <c r="G56" t="s">
-        <v>437</v>
-      </c>
       <c r="H56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J56" t="s">
+        <v>444</v>
+      </c>
+      <c r="M56" t="s">
         <v>445</v>
       </c>
-      <c r="M56" t="s">
+      <c r="N56" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="N56" s="1" t="s">
+      <c r="Q56" t="s">
         <v>447</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="S56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T56" t="s">
         <v>448</v>
       </c>
-      <c r="S56" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T56" t="s">
-        <v>449</v>
-      </c>
       <c r="U56" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="W56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X56">
         <v>2</v>
@@ -6341,49 +6356,49 @@
     </row>
     <row r="57" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>432</v>
+      </c>
+      <c r="B57" t="s">
         <v>433</v>
       </c>
-      <c r="B57" t="s">
+      <c r="D57" t="s">
         <v>434</v>
       </c>
-      <c r="D57" t="s">
+      <c r="F57" t="s">
         <v>435</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>436</v>
       </c>
-      <c r="G57" t="s">
-        <v>437</v>
-      </c>
       <c r="H57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I57" t="s">
+        <v>138</v>
+      </c>
+      <c r="J57" t="s">
         <v>139</v>
       </c>
-      <c r="J57" t="s">
-        <v>140</v>
-      </c>
       <c r="M57" t="s">
+        <v>449</v>
+      </c>
+      <c r="N57" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="N57" s="1" t="s">
+      <c r="Q57" t="s">
         <v>451</v>
       </c>
-      <c r="Q57" t="s">
-        <v>452</v>
-      </c>
       <c r="S57" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T57" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="U57" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X57">
         <v>3</v>
@@ -6391,43 +6406,43 @@
     </row>
     <row r="58" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>452</v>
+      </c>
+      <c r="B58" t="s">
         <v>453</v>
       </c>
-      <c r="B58" t="s">
+      <c r="F58" t="s">
+        <v>219</v>
+      </c>
+      <c r="G58" t="s">
+        <v>365</v>
+      </c>
+      <c r="H58" t="s">
+        <v>311</v>
+      </c>
+      <c r="I58" t="s">
+        <v>66</v>
+      </c>
+      <c r="J58" t="s">
+        <v>67</v>
+      </c>
+      <c r="M58" t="s">
         <v>454</v>
       </c>
-      <c r="F58" t="s">
-        <v>220</v>
-      </c>
-      <c r="G58" t="s">
-        <v>366</v>
-      </c>
-      <c r="H58" t="s">
-        <v>312</v>
-      </c>
-      <c r="I58" t="s">
-        <v>67</v>
-      </c>
-      <c r="J58" t="s">
-        <v>68</v>
-      </c>
-      <c r="M58" t="s">
+      <c r="N58" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="N58" s="1" t="s">
+      <c r="S58" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T58" t="s">
+        <v>358</v>
+      </c>
+      <c r="U58" t="s">
         <v>456</v>
       </c>
-      <c r="S58" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T58" t="s">
-        <v>359</v>
-      </c>
-      <c r="U58" t="s">
+      <c r="W58" t="s">
         <v>457</v>
-      </c>
-      <c r="W58" t="s">
-        <v>458</v>
       </c>
       <c r="X58">
         <v>2</v>
@@ -6435,43 +6450,43 @@
     </row>
     <row r="59" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>458</v>
+      </c>
+      <c r="B59" t="s">
+        <v>453</v>
+      </c>
+      <c r="F59" t="s">
         <v>459</v>
       </c>
-      <c r="B59" t="s">
-        <v>454</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
+        <v>26</v>
+      </c>
+      <c r="H59" t="s">
         <v>460</v>
       </c>
-      <c r="G59" t="s">
-        <v>27</v>
-      </c>
-      <c r="H59" t="s">
+      <c r="I59" t="s">
+        <v>138</v>
+      </c>
+      <c r="J59" t="s">
+        <v>139</v>
+      </c>
+      <c r="M59" t="s">
         <v>461</v>
       </c>
-      <c r="I59" t="s">
-        <v>139</v>
-      </c>
-      <c r="J59" t="s">
-        <v>140</v>
-      </c>
-      <c r="M59" t="s">
+      <c r="N59" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="N59" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="S59" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T59" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="W59" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="X59">
         <v>1</v>
@@ -6479,43 +6494,43 @@
     </row>
     <row r="60" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B60" t="s">
+        <v>463</v>
+      </c>
+      <c r="F60" t="s">
+        <v>63</v>
+      </c>
+      <c r="G60" t="s">
         <v>464</v>
       </c>
-      <c r="F60" t="s">
-        <v>64</v>
-      </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>465</v>
       </c>
-      <c r="H60" t="s">
+      <c r="I60" t="s">
+        <v>138</v>
+      </c>
+      <c r="J60" t="s">
+        <v>139</v>
+      </c>
+      <c r="M60" t="s">
         <v>466</v>
       </c>
-      <c r="I60" t="s">
-        <v>139</v>
-      </c>
-      <c r="J60" t="s">
-        <v>140</v>
-      </c>
-      <c r="M60" t="s">
+      <c r="N60" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="N60" s="1" t="s">
+      <c r="S60" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T60" t="s">
         <v>468</v>
       </c>
-      <c r="S60" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T60" t="s">
+      <c r="U60" t="s">
         <v>469</v>
       </c>
-      <c r="U60" t="s">
-        <v>470</v>
-      </c>
       <c r="W60" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="X60">
         <v>3</v>
@@ -6523,43 +6538,43 @@
     </row>
     <row r="61" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>470</v>
+      </c>
+      <c r="B61" t="s">
         <v>471</v>
       </c>
-      <c r="B61" t="s">
+      <c r="F61" t="s">
         <v>472</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>473</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
+        <v>130</v>
+      </c>
+      <c r="I61" t="s">
+        <v>103</v>
+      </c>
+      <c r="J61" t="s">
         <v>474</v>
       </c>
-      <c r="H61" t="s">
-        <v>131</v>
-      </c>
-      <c r="I61" t="s">
-        <v>104</v>
-      </c>
-      <c r="J61" t="s">
+      <c r="M61" t="s">
         <v>475</v>
       </c>
-      <c r="M61" t="s">
+      <c r="N61" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="N61" s="1" t="s">
+      <c r="S61" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T61" t="s">
+        <v>396</v>
+      </c>
+      <c r="U61" t="s">
         <v>477</v>
       </c>
-      <c r="S61" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T61" t="s">
-        <v>397</v>
-      </c>
-      <c r="U61" t="s">
-        <v>478</v>
-      </c>
       <c r="W61" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X61">
         <v>1</v>
@@ -6567,46 +6582,46 @@
     </row>
     <row r="62" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s">
+        <v>478</v>
+      </c>
+      <c r="F62" t="s">
         <v>479</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>480</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
+        <v>304</v>
+      </c>
+      <c r="I62" t="s">
         <v>481</v>
       </c>
-      <c r="H62" t="s">
-        <v>305</v>
-      </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>482</v>
       </c>
-      <c r="J62" t="s">
+      <c r="M62" t="s">
         <v>483</v>
       </c>
-      <c r="M62" t="s">
+      <c r="N62" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="N62" s="1" t="s">
+      <c r="Q62" t="s">
         <v>485</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="S62" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T62" t="s">
         <v>486</v>
       </c>
-      <c r="S62" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T62" t="s">
+      <c r="U62" t="s">
         <v>487</v>
       </c>
-      <c r="U62" t="s">
-        <v>488</v>
-      </c>
       <c r="W62" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X62">
         <v>3</v>
@@ -6614,37 +6629,37 @@
     </row>
     <row r="63" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>488</v>
+      </c>
+      <c r="B63" t="s">
         <v>489</v>
       </c>
-      <c r="B63" t="s">
+      <c r="D63" t="s">
         <v>490</v>
       </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
         <v>491</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>492</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>493</v>
       </c>
-      <c r="H63" t="s">
+      <c r="J63" t="s">
         <v>494</v>
       </c>
-      <c r="J63" t="s">
+      <c r="M63" t="s">
         <v>495</v>
       </c>
-      <c r="M63" t="s">
+      <c r="N63" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="N63" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="S63" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="W63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X63">
         <v>2</v>
@@ -6652,49 +6667,49 @@
     </row>
     <row r="64" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>488</v>
+      </c>
+      <c r="B64" t="s">
         <v>489</v>
       </c>
-      <c r="B64" t="s">
+      <c r="D64" t="s">
         <v>490</v>
       </c>
-      <c r="D64" t="s">
+      <c r="F64" t="s">
         <v>491</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>492</v>
       </c>
-      <c r="G64" t="s">
-        <v>493</v>
-      </c>
       <c r="H64" t="s">
+        <v>497</v>
+      </c>
+      <c r="I64" t="s">
+        <v>79</v>
+      </c>
+      <c r="J64" t="s">
+        <v>80</v>
+      </c>
+      <c r="M64" t="s">
         <v>498</v>
       </c>
-      <c r="I64" t="s">
-        <v>80</v>
-      </c>
-      <c r="J64" t="s">
-        <v>81</v>
-      </c>
-      <c r="M64" t="s">
+      <c r="N64" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="N64" s="1" t="s">
+      <c r="Q64" t="s">
         <v>500</v>
       </c>
-      <c r="Q64" t="s">
+      <c r="S64" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T64" t="s">
         <v>501</v>
       </c>
-      <c r="S64" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T64" t="s">
-        <v>502</v>
-      </c>
       <c r="U64" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="W64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X64">
         <v>3</v>
@@ -6702,46 +6717,46 @@
     </row>
     <row r="65" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>502</v>
+      </c>
+      <c r="B65" t="s">
         <v>503</v>
       </c>
-      <c r="B65" t="s">
+      <c r="F65" t="s">
         <v>504</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>505</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
+        <v>366</v>
+      </c>
+      <c r="I65" t="s">
         <v>506</v>
       </c>
-      <c r="H65" t="s">
-        <v>367</v>
-      </c>
-      <c r="I65" t="s">
+      <c r="J65" t="s">
         <v>507</v>
       </c>
-      <c r="J65" t="s">
+      <c r="M65" t="s">
+        <v>204</v>
+      </c>
+      <c r="N65" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="M65" t="s">
-        <v>205</v>
-      </c>
-      <c r="N65" s="1" t="s">
+      <c r="Q65" t="s">
+        <v>206</v>
+      </c>
+      <c r="S65" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T65" t="s">
         <v>509</v>
       </c>
-      <c r="Q65" t="s">
-        <v>207</v>
-      </c>
-      <c r="S65" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T65" t="s">
-        <v>510</v>
-      </c>
       <c r="U65" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="W65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X65">
         <v>3</v>
@@ -6749,43 +6764,43 @@
     </row>
     <row r="66" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>510</v>
+      </c>
+      <c r="B66" t="s">
         <v>511</v>
       </c>
-      <c r="B66" t="s">
+      <c r="F66" t="s">
         <v>512</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>513</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>514</v>
       </c>
-      <c r="H66" t="s">
+      <c r="I66" t="s">
+        <v>103</v>
+      </c>
+      <c r="J66" t="s">
+        <v>104</v>
+      </c>
+      <c r="M66" t="s">
         <v>515</v>
       </c>
-      <c r="I66" t="s">
-        <v>104</v>
-      </c>
-      <c r="J66" t="s">
-        <v>105</v>
-      </c>
-      <c r="M66" t="s">
+      <c r="N66" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="N66" s="1" t="s">
+      <c r="S66" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T66" t="s">
         <v>517</v>
       </c>
-      <c r="S66" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T66" t="s">
+      <c r="U66" t="s">
         <v>518</v>
       </c>
-      <c r="U66" t="s">
-        <v>519</v>
-      </c>
       <c r="W66" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X66">
         <v>2</v>
@@ -6793,43 +6808,43 @@
     </row>
     <row r="67" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>510</v>
+      </c>
+      <c r="B67" t="s">
         <v>511</v>
       </c>
-      <c r="B67" t="s">
+      <c r="F67" t="s">
         <v>512</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>513</v>
       </c>
-      <c r="G67" t="s">
-        <v>514</v>
-      </c>
       <c r="H67" t="s">
+        <v>519</v>
+      </c>
+      <c r="I67" t="s">
         <v>520</v>
       </c>
-      <c r="I67" t="s">
+      <c r="J67" t="s">
         <v>521</v>
       </c>
-      <c r="J67" t="s">
+      <c r="M67" t="s">
         <v>522</v>
       </c>
-      <c r="M67" t="s">
+      <c r="N67" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="N67" s="1" t="s">
+      <c r="S67" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="S67" s="1" t="s">
+      <c r="T67" t="s">
         <v>525</v>
       </c>
-      <c r="T67" t="s">
+      <c r="U67" t="s">
         <v>526</v>
       </c>
-      <c r="U67" t="s">
-        <v>527</v>
-      </c>
       <c r="W67" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X67">
         <v>2</v>
@@ -6837,43 +6852,43 @@
     </row>
     <row r="68" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>510</v>
+      </c>
+      <c r="B68" t="s">
         <v>511</v>
       </c>
-      <c r="B68" t="s">
+      <c r="F68" t="s">
         <v>512</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>513</v>
       </c>
-      <c r="G68" t="s">
-        <v>514</v>
-      </c>
       <c r="H68" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I68" t="s">
+        <v>54</v>
+      </c>
+      <c r="J68" t="s">
         <v>55</v>
       </c>
-      <c r="J68" t="s">
-        <v>56</v>
-      </c>
       <c r="M68" t="s">
+        <v>527</v>
+      </c>
+      <c r="N68" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="N68" s="1" t="s">
+      <c r="S68" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T68" t="s">
         <v>529</v>
       </c>
-      <c r="S68" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T68" t="s">
-        <v>530</v>
-      </c>
       <c r="U68" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="W68" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X68">
         <v>2</v>
@@ -6881,43 +6896,43 @@
     </row>
     <row r="69" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>510</v>
+      </c>
+      <c r="B69" t="s">
         <v>511</v>
       </c>
-      <c r="B69" t="s">
+      <c r="F69" t="s">
         <v>512</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>513</v>
       </c>
-      <c r="G69" t="s">
-        <v>514</v>
-      </c>
       <c r="H69" t="s">
+        <v>530</v>
+      </c>
+      <c r="I69" t="s">
         <v>531</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
         <v>532</v>
       </c>
-      <c r="J69" t="s">
+      <c r="M69" t="s">
         <v>533</v>
       </c>
-      <c r="M69" t="s">
+      <c r="N69" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="N69" s="1" t="s">
+      <c r="S69" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T69" t="s">
         <v>535</v>
       </c>
-      <c r="S69" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T69" t="s">
+      <c r="U69" t="s">
         <v>536</v>
       </c>
-      <c r="U69" t="s">
-        <v>537</v>
-      </c>
       <c r="W69" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X69">
         <v>2</v>
@@ -6925,43 +6940,43 @@
     </row>
     <row r="70" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>510</v>
+      </c>
+      <c r="B70" t="s">
         <v>511</v>
       </c>
-      <c r="B70" t="s">
+      <c r="F70" t="s">
         <v>512</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>513</v>
       </c>
-      <c r="G70" t="s">
-        <v>514</v>
-      </c>
       <c r="H70" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I70" t="s">
+        <v>66</v>
+      </c>
+      <c r="J70" t="s">
         <v>67</v>
       </c>
-      <c r="J70" t="s">
-        <v>68</v>
-      </c>
       <c r="M70" t="s">
+        <v>537</v>
+      </c>
+      <c r="N70" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="N70" s="1" t="s">
+      <c r="S70" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T70" t="s">
         <v>539</v>
       </c>
-      <c r="S70" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T70" t="s">
+      <c r="U70" t="s">
         <v>540</v>
       </c>
-      <c r="U70" t="s">
-        <v>541</v>
-      </c>
       <c r="W70" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X70">
         <v>2</v>
@@ -6969,43 +6984,43 @@
     </row>
     <row r="71" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>510</v>
+      </c>
+      <c r="B71" t="s">
         <v>511</v>
       </c>
-      <c r="B71" t="s">
+      <c r="F71" t="s">
         <v>512</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>513</v>
       </c>
-      <c r="G71" t="s">
-        <v>514</v>
-      </c>
       <c r="H71" t="s">
+        <v>541</v>
+      </c>
+      <c r="I71" t="s">
+        <v>103</v>
+      </c>
+      <c r="J71" t="s">
+        <v>104</v>
+      </c>
+      <c r="M71" t="s">
         <v>542</v>
       </c>
-      <c r="I71" t="s">
-        <v>104</v>
-      </c>
-      <c r="J71" t="s">
-        <v>105</v>
-      </c>
-      <c r="M71" t="s">
+      <c r="N71" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="N71" s="1" t="s">
+      <c r="S71" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T71" t="s">
+        <v>237</v>
+      </c>
+      <c r="U71" t="s">
         <v>544</v>
       </c>
-      <c r="S71" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T71" t="s">
-        <v>238</v>
-      </c>
-      <c r="U71" t="s">
-        <v>545</v>
-      </c>
       <c r="W71" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X71">
         <v>2</v>
@@ -7013,46 +7028,46 @@
     </row>
     <row r="72" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>545</v>
+      </c>
+      <c r="B72" t="s">
         <v>546</v>
       </c>
-      <c r="B72" t="s">
+      <c r="F72" t="s">
+        <v>512</v>
+      </c>
+      <c r="G72" t="s">
         <v>547</v>
       </c>
-      <c r="F72" t="s">
-        <v>513</v>
-      </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>548</v>
       </c>
-      <c r="H72" t="s">
+      <c r="I72" t="s">
+        <v>29</v>
+      </c>
+      <c r="J72" t="s">
+        <v>30</v>
+      </c>
+      <c r="M72" t="s">
         <v>549</v>
       </c>
-      <c r="I72" t="s">
-        <v>30</v>
-      </c>
-      <c r="J72" t="s">
-        <v>31</v>
-      </c>
-      <c r="M72" t="s">
+      <c r="N72" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="N72" s="1" t="s">
+      <c r="Q72" t="s">
         <v>551</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="S72" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T72" t="s">
         <v>552</v>
       </c>
-      <c r="S72" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T72" t="s">
+      <c r="U72" t="s">
         <v>553</v>
       </c>
-      <c r="U72" t="s">
-        <v>554</v>
-      </c>
       <c r="W72" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="X72">
         <v>3</v>
@@ -7060,46 +7075,46 @@
     </row>
     <row r="73" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>554</v>
+      </c>
+      <c r="B73" t="s">
         <v>555</v>
       </c>
-      <c r="B73" t="s">
+      <c r="F73" t="s">
+        <v>530</v>
+      </c>
+      <c r="G73" t="s">
+        <v>480</v>
+      </c>
+      <c r="H73" t="s">
         <v>556</v>
       </c>
-      <c r="F73" t="s">
-        <v>531</v>
-      </c>
-      <c r="G73" t="s">
-        <v>481</v>
-      </c>
-      <c r="H73" t="s">
+      <c r="I73" t="s">
+        <v>29</v>
+      </c>
+      <c r="J73" t="s">
         <v>557</v>
       </c>
-      <c r="I73" t="s">
-        <v>30</v>
-      </c>
-      <c r="J73" t="s">
+      <c r="M73" t="s">
         <v>558</v>
       </c>
-      <c r="M73" t="s">
+      <c r="N73" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="N73" s="1" t="s">
+      <c r="Q73" t="s">
         <v>560</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="S73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T73" t="s">
         <v>561</v>
       </c>
-      <c r="S73" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T73" t="s">
-        <v>562</v>
-      </c>
       <c r="U73" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="W73" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="X73">
         <v>3</v>
@@ -7107,40 +7122,40 @@
     </row>
     <row r="74" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>562</v>
+      </c>
+      <c r="B74" t="s">
         <v>563</v>
       </c>
-      <c r="B74" t="s">
+      <c r="F74" t="s">
         <v>564</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
+        <v>547</v>
+      </c>
+      <c r="H74" t="s">
+        <v>273</v>
+      </c>
+      <c r="J74" t="s">
+        <v>222</v>
+      </c>
+      <c r="M74" t="s">
         <v>565</v>
       </c>
-      <c r="G74" t="s">
-        <v>548</v>
-      </c>
-      <c r="H74" t="s">
-        <v>274</v>
-      </c>
-      <c r="J74" t="s">
-        <v>223</v>
-      </c>
-      <c r="M74" t="s">
+      <c r="N74" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="N74" s="1" t="s">
+      <c r="S74" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T74" t="s">
         <v>567</v>
       </c>
-      <c r="S74" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T74" t="s">
+      <c r="U74" t="s">
         <v>568</v>
       </c>
-      <c r="U74" t="s">
-        <v>569</v>
-      </c>
       <c r="W74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X74">
         <v>1</v>
@@ -7148,43 +7163,43 @@
     </row>
     <row r="75" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>562</v>
+      </c>
+      <c r="B75" t="s">
         <v>563</v>
       </c>
-      <c r="B75" t="s">
+      <c r="F75" t="s">
         <v>564</v>
       </c>
-      <c r="F75" t="s">
-        <v>565</v>
-      </c>
       <c r="G75" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H75" t="s">
+        <v>569</v>
+      </c>
+      <c r="I75" t="s">
+        <v>138</v>
+      </c>
+      <c r="J75" t="s">
+        <v>139</v>
+      </c>
+      <c r="M75" t="s">
         <v>570</v>
       </c>
-      <c r="I75" t="s">
-        <v>139</v>
-      </c>
-      <c r="J75" t="s">
-        <v>140</v>
-      </c>
-      <c r="M75" t="s">
+      <c r="N75" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="N75" s="1" t="s">
+      <c r="S75" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="S75" s="1" t="s">
+      <c r="T75" t="s">
         <v>573</v>
       </c>
-      <c r="T75" t="s">
+      <c r="U75" t="s">
         <v>574</v>
       </c>
-      <c r="U75" t="s">
-        <v>575</v>
-      </c>
       <c r="W75" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X75">
         <v>1</v>
@@ -7192,43 +7207,43 @@
     </row>
     <row r="76" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>562</v>
+      </c>
+      <c r="B76" t="s">
         <v>563</v>
       </c>
-      <c r="B76" t="s">
+      <c r="F76" t="s">
         <v>564</v>
       </c>
-      <c r="F76" t="s">
-        <v>565</v>
-      </c>
       <c r="G76" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H76" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I76" t="s">
+        <v>138</v>
+      </c>
+      <c r="J76" t="s">
         <v>139</v>
       </c>
-      <c r="J76" t="s">
-        <v>140</v>
-      </c>
       <c r="M76" t="s">
+        <v>575</v>
+      </c>
+      <c r="N76" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="N76" s="1" t="s">
+      <c r="S76" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T76" t="s">
         <v>577</v>
       </c>
-      <c r="S76" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T76" t="s">
+      <c r="U76" t="s">
         <v>578</v>
       </c>
-      <c r="U76" t="s">
-        <v>579</v>
-      </c>
       <c r="W76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X76">
         <v>1</v>
@@ -7236,52 +7251,52 @@
     </row>
     <row r="77" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>562</v>
+      </c>
+      <c r="B77" t="s">
         <v>563</v>
       </c>
-      <c r="B77" t="s">
+      <c r="F77" t="s">
         <v>564</v>
       </c>
-      <c r="F77" t="s">
-        <v>565</v>
-      </c>
       <c r="G77" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H77" t="s">
+        <v>579</v>
+      </c>
+      <c r="I77" t="s">
         <v>580</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>581</v>
       </c>
-      <c r="J77" t="s">
+      <c r="L77" t="s">
         <v>582</v>
       </c>
-      <c r="L77" t="s">
+      <c r="M77" t="s">
         <v>583</v>
       </c>
-      <c r="M77" t="s">
+      <c r="N77" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="N77" s="1" t="s">
+      <c r="O77" t="s">
         <v>585</v>
       </c>
-      <c r="O77" t="s">
+      <c r="Q77" t="s">
         <v>586</v>
       </c>
-      <c r="Q77" t="s">
+      <c r="S77" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="S77" s="1" t="s">
+      <c r="T77" t="s">
         <v>588</v>
       </c>
-      <c r="T77" t="s">
+      <c r="U77" t="s">
         <v>589</v>
       </c>
-      <c r="U77" t="s">
-        <v>590</v>
-      </c>
       <c r="W77" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X77">
         <v>2</v>
@@ -7289,43 +7304,43 @@
     </row>
     <row r="78" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>562</v>
+      </c>
+      <c r="B78" t="s">
         <v>563</v>
       </c>
-      <c r="B78" t="s">
+      <c r="F78" t="s">
         <v>564</v>
       </c>
-      <c r="F78" t="s">
-        <v>565</v>
-      </c>
       <c r="G78" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H78" t="s">
+        <v>590</v>
+      </c>
+      <c r="I78" t="s">
+        <v>138</v>
+      </c>
+      <c r="J78" t="s">
+        <v>139</v>
+      </c>
+      <c r="M78" t="s">
         <v>591</v>
       </c>
-      <c r="I78" t="s">
-        <v>139</v>
-      </c>
-      <c r="J78" t="s">
-        <v>140</v>
-      </c>
-      <c r="M78" t="s">
+      <c r="N78" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="N78" s="1" t="s">
+      <c r="S78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T78" t="s">
         <v>593</v>
       </c>
-      <c r="S78" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T78" t="s">
+      <c r="U78" t="s">
         <v>594</v>
       </c>
-      <c r="U78" t="s">
-        <v>595</v>
-      </c>
       <c r="W78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X78">
         <v>1</v>
@@ -7333,46 +7348,46 @@
     </row>
     <row r="79" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>595</v>
+      </c>
+      <c r="B79" t="s">
         <v>596</v>
       </c>
-      <c r="B79" t="s">
+      <c r="F79" t="s">
+        <v>459</v>
+      </c>
+      <c r="G79" t="s">
         <v>597</v>
       </c>
-      <c r="F79" t="s">
-        <v>460</v>
-      </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>598</v>
       </c>
-      <c r="H79" t="s">
+      <c r="I79" t="s">
+        <v>103</v>
+      </c>
+      <c r="J79" t="s">
+        <v>104</v>
+      </c>
+      <c r="M79" t="s">
+        <v>549</v>
+      </c>
+      <c r="N79" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="I79" t="s">
-        <v>104</v>
-      </c>
-      <c r="J79" t="s">
-        <v>105</v>
-      </c>
-      <c r="M79" t="s">
-        <v>550</v>
-      </c>
-      <c r="N79" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="Q79" t="s">
+        <v>551</v>
+      </c>
+      <c r="S79" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T79" t="s">
         <v>552</v>
       </c>
-      <c r="S79" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T79" t="s">
+      <c r="U79" t="s">
         <v>553</v>
       </c>
-      <c r="U79" t="s">
-        <v>554</v>
-      </c>
       <c r="W79" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X79">
         <v>3</v>
@@ -7380,46 +7395,46 @@
     </row>
     <row r="80" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>600</v>
+      </c>
+      <c r="B80" t="s">
         <v>601</v>
       </c>
-      <c r="B80" t="s">
+      <c r="F80" t="s">
+        <v>241</v>
+      </c>
+      <c r="G80" t="s">
         <v>602</v>
       </c>
-      <c r="F80" t="s">
-        <v>242</v>
-      </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>603</v>
       </c>
-      <c r="H80" t="s">
+      <c r="I80" t="s">
+        <v>210</v>
+      </c>
+      <c r="J80" t="s">
+        <v>211</v>
+      </c>
+      <c r="M80" t="s">
         <v>604</v>
       </c>
-      <c r="I80" t="s">
-        <v>211</v>
-      </c>
-      <c r="J80" t="s">
-        <v>212</v>
-      </c>
-      <c r="M80" t="s">
+      <c r="N80" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="N80" s="1" t="s">
+      <c r="Q80" t="s">
         <v>606</v>
       </c>
-      <c r="Q80" t="s">
+      <c r="S80" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T80" t="s">
         <v>607</v>
       </c>
-      <c r="S80" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T80" t="s">
+      <c r="U80" t="s">
         <v>608</v>
       </c>
-      <c r="U80" t="s">
-        <v>609</v>
-      </c>
       <c r="W80" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X80">
         <v>2</v>
@@ -7427,37 +7442,37 @@
     </row>
     <row r="81" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>609</v>
+      </c>
+      <c r="B81" t="s">
         <v>610</v>
       </c>
-      <c r="B81" t="s">
+      <c r="F81" t="s">
         <v>611</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>612</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>613</v>
       </c>
-      <c r="H81" t="s">
+      <c r="I81" t="s">
+        <v>244</v>
+      </c>
+      <c r="J81" t="s">
         <v>614</v>
       </c>
-      <c r="I81" t="s">
-        <v>245</v>
-      </c>
-      <c r="J81" t="s">
+      <c r="M81" t="s">
         <v>615</v>
       </c>
-      <c r="M81" t="s">
+      <c r="N81" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="N81" s="1" t="s">
-        <v>617</v>
-      </c>
       <c r="S81" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="W81" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X81">
         <v>3</v>
@@ -7465,52 +7480,52 @@
     </row>
     <row r="82" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>617</v>
+      </c>
+      <c r="B82" t="s">
         <v>618</v>
       </c>
-      <c r="B82" t="s">
+      <c r="D82" t="s">
         <v>619</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
+        <v>619</v>
+      </c>
+      <c r="F82" t="s">
         <v>620</v>
       </c>
-      <c r="E82" t="s">
-        <v>620</v>
-      </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>621</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>622</v>
       </c>
-      <c r="H82" t="s">
+      <c r="I82" t="s">
         <v>623</v>
       </c>
-      <c r="I82" t="s">
+      <c r="J82" t="s">
         <v>624</v>
       </c>
-      <c r="J82" t="s">
+      <c r="M82" t="s">
+        <v>204</v>
+      </c>
+      <c r="N82" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="M82" t="s">
-        <v>205</v>
-      </c>
-      <c r="N82" s="1" t="s">
+      <c r="Q82" t="s">
+        <v>206</v>
+      </c>
+      <c r="S82" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T82" t="s">
         <v>626</v>
       </c>
-      <c r="Q82" t="s">
-        <v>207</v>
-      </c>
-      <c r="S82" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T82" t="s">
+      <c r="U82" t="s">
         <v>627</v>
       </c>
-      <c r="U82" t="s">
-        <v>628</v>
-      </c>
       <c r="W82" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X82">
         <v>3</v>
@@ -7518,46 +7533,46 @@
     </row>
     <row r="83" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B83" t="s">
+        <v>628</v>
+      </c>
+      <c r="F83" t="s">
         <v>629</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>630</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
+        <v>252</v>
+      </c>
+      <c r="I83" t="s">
+        <v>39</v>
+      </c>
+      <c r="J83" t="s">
+        <v>40</v>
+      </c>
+      <c r="M83" t="s">
         <v>631</v>
       </c>
-      <c r="H83" t="s">
-        <v>253</v>
-      </c>
-      <c r="I83" t="s">
-        <v>40</v>
-      </c>
-      <c r="J83" t="s">
-        <v>41</v>
-      </c>
-      <c r="M83" t="s">
+      <c r="N83" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="N83" s="1" t="s">
+      <c r="Q83" t="s">
         <v>633</v>
       </c>
-      <c r="Q83" t="s">
+      <c r="S83" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="S83" s="1" t="s">
+      <c r="T83" t="s">
         <v>635</v>
       </c>
-      <c r="T83" t="s">
+      <c r="U83" t="s">
         <v>636</v>
       </c>
-      <c r="U83" t="s">
-        <v>637</v>
-      </c>
       <c r="W83" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X83">
         <v>1</v>
@@ -7565,43 +7580,43 @@
     </row>
     <row r="84" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B84" t="s">
+        <v>628</v>
+      </c>
+      <c r="F84" t="s">
         <v>629</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>630</v>
       </c>
-      <c r="G84" t="s">
-        <v>631</v>
-      </c>
       <c r="H84" t="s">
+        <v>637</v>
+      </c>
+      <c r="I84" t="s">
+        <v>210</v>
+      </c>
+      <c r="J84" t="s">
+        <v>211</v>
+      </c>
+      <c r="M84" t="s">
+        <v>542</v>
+      </c>
+      <c r="N84" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="I84" t="s">
-        <v>211</v>
-      </c>
-      <c r="J84" t="s">
-        <v>212</v>
-      </c>
-      <c r="M84" t="s">
-        <v>543</v>
-      </c>
-      <c r="N84" s="1" t="s">
+      <c r="S84" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="T84" t="s">
         <v>639</v>
       </c>
-      <c r="S84" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="T84" t="s">
-        <v>640</v>
-      </c>
       <c r="U84" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="W84" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X84">
         <v>2</v>
@@ -7609,52 +7624,52 @@
     </row>
     <row r="85" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B85" t="s">
+        <v>628</v>
+      </c>
+      <c r="F85" t="s">
         <v>629</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>630</v>
-      </c>
-      <c r="G85" t="s">
-        <v>631</v>
       </c>
       <c r="H85">
         <v>1506</v>
       </c>
       <c r="I85" t="s">
+        <v>640</v>
+      </c>
+      <c r="J85" t="s">
         <v>641</v>
       </c>
-      <c r="J85" t="s">
+      <c r="L85" t="s">
         <v>642</v>
       </c>
-      <c r="L85" t="s">
+      <c r="M85" t="s">
         <v>643</v>
       </c>
-      <c r="M85" t="s">
+      <c r="N85" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="N85" s="1" t="s">
+      <c r="O85" t="s">
+        <v>585</v>
+      </c>
+      <c r="Q85" t="s">
         <v>645</v>
       </c>
-      <c r="O85" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q85" t="s">
+      <c r="S85" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="S85" s="1" t="s">
+      <c r="T85" t="s">
+        <v>397</v>
+      </c>
+      <c r="U85" t="s">
         <v>647</v>
       </c>
-      <c r="T85" t="s">
-        <v>398</v>
-      </c>
-      <c r="U85" t="s">
-        <v>648</v>
-      </c>
       <c r="W85" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X85">
         <v>2</v>
@@ -7662,52 +7677,52 @@
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B86" t="s">
+        <v>628</v>
+      </c>
+      <c r="F86" t="s">
         <v>629</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>630</v>
-      </c>
-      <c r="G86" t="s">
-        <v>631</v>
       </c>
       <c r="H86">
         <v>1506</v>
       </c>
       <c r="I86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J86" t="s">
+        <v>648</v>
+      </c>
+      <c r="L86" t="s">
         <v>649</v>
       </c>
-      <c r="L86" t="s">
+      <c r="M86" t="s">
         <v>650</v>
       </c>
-      <c r="M86" t="s">
+      <c r="N86" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="N86" s="1" t="s">
+      <c r="O86" t="s">
+        <v>585</v>
+      </c>
+      <c r="Q86" t="s">
         <v>652</v>
       </c>
-      <c r="O86" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q86" t="s">
+      <c r="S86" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="T86" t="s">
         <v>653</v>
       </c>
-      <c r="S86" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="T86" t="s">
+      <c r="U86" t="s">
         <v>654</v>
       </c>
-      <c r="U86" t="s">
-        <v>655</v>
-      </c>
       <c r="W86" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X86">
         <v>2</v>
@@ -7715,40 +7730,40 @@
     </row>
     <row r="87" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B87" t="s">
+        <v>628</v>
+      </c>
+      <c r="F87" t="s">
         <v>629</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>630</v>
       </c>
-      <c r="G87" t="s">
-        <v>631</v>
-      </c>
       <c r="H87" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J87" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="M87" t="s">
+        <v>655</v>
+      </c>
+      <c r="N87" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="N87" s="1" t="s">
+      <c r="S87" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T87" t="s">
+        <v>397</v>
+      </c>
+      <c r="U87" t="s">
         <v>657</v>
       </c>
-      <c r="S87" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T87" t="s">
-        <v>398</v>
-      </c>
-      <c r="U87" t="s">
-        <v>658</v>
-      </c>
       <c r="W87" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X87">
         <v>3</v>
@@ -7756,52 +7771,52 @@
     </row>
     <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B88" t="s">
+        <v>628</v>
+      </c>
+      <c r="F88" t="s">
         <v>629</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>630</v>
-      </c>
-      <c r="G88" t="s">
-        <v>631</v>
       </c>
       <c r="H88">
         <v>1507</v>
       </c>
       <c r="I88" t="s">
+        <v>29</v>
+      </c>
+      <c r="J88" t="s">
         <v>30</v>
       </c>
-      <c r="J88" t="s">
-        <v>31</v>
-      </c>
       <c r="L88" t="s">
+        <v>658</v>
+      </c>
+      <c r="M88" t="s">
         <v>659</v>
       </c>
-      <c r="M88" t="s">
+      <c r="N88" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="N88" s="1" t="s">
+      <c r="O88" t="s">
         <v>661</v>
       </c>
-      <c r="O88" t="s">
+      <c r="Q88" t="s">
+        <v>659</v>
+      </c>
+      <c r="S88" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="Q88" t="s">
-        <v>660</v>
-      </c>
-      <c r="S88" s="1" t="s">
+      <c r="T88" t="s">
         <v>663</v>
       </c>
-      <c r="T88" t="s">
-        <v>664</v>
-      </c>
       <c r="U88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="W88" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X88">
         <v>2</v>
@@ -7809,52 +7824,52 @@
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B89" t="s">
+        <v>628</v>
+      </c>
+      <c r="F89" t="s">
         <v>629</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>630</v>
-      </c>
-      <c r="G89" t="s">
-        <v>631</v>
       </c>
       <c r="H89">
         <v>1507</v>
       </c>
       <c r="I89" t="s">
+        <v>29</v>
+      </c>
+      <c r="J89" t="s">
         <v>30</v>
       </c>
-      <c r="J89" t="s">
-        <v>31</v>
-      </c>
       <c r="L89" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="M89" t="s">
+        <v>664</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="O89" t="s">
         <v>665</v>
       </c>
-      <c r="N89" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="O89" t="s">
+      <c r="Q89" t="s">
         <v>666</v>
       </c>
-      <c r="Q89" t="s">
+      <c r="S89" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="T89" t="s">
         <v>667</v>
       </c>
-      <c r="S89" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="T89" t="s">
-        <v>668</v>
-      </c>
       <c r="U89" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="W89" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X89">
         <v>2</v>
@@ -7862,52 +7877,52 @@
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B90" t="s">
+        <v>628</v>
+      </c>
+      <c r="F90" t="s">
         <v>629</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>630</v>
-      </c>
-      <c r="G90" t="s">
-        <v>631</v>
       </c>
       <c r="H90">
         <v>1508</v>
       </c>
       <c r="I90" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J90" t="s">
+        <v>668</v>
+      </c>
+      <c r="L90" t="s">
         <v>669</v>
       </c>
-      <c r="L90" t="s">
+      <c r="M90" t="s">
         <v>670</v>
       </c>
-      <c r="M90" t="s">
+      <c r="N90" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="N90" s="1" t="s">
+      <c r="O90" t="s">
+        <v>585</v>
+      </c>
+      <c r="Q90" t="s">
         <v>672</v>
       </c>
-      <c r="O90" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q90" t="s">
+      <c r="S90" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="S90" s="1" t="s">
+      <c r="T90" t="s">
         <v>674</v>
       </c>
-      <c r="T90" t="s">
+      <c r="U90" t="s">
         <v>675</v>
       </c>
-      <c r="U90" t="s">
-        <v>676</v>
-      </c>
       <c r="W90" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X90">
         <v>2</v>
@@ -7915,52 +7930,52 @@
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B91" t="s">
+        <v>628</v>
+      </c>
+      <c r="F91" t="s">
         <v>629</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>630</v>
-      </c>
-      <c r="G91" t="s">
-        <v>631</v>
       </c>
       <c r="H91">
         <v>1511</v>
       </c>
       <c r="I91" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J91" t="s">
+        <v>668</v>
+      </c>
+      <c r="L91" t="s">
         <v>669</v>
       </c>
-      <c r="L91" t="s">
-        <v>670</v>
-      </c>
       <c r="M91" t="s">
+        <v>676</v>
+      </c>
+      <c r="N91" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="N91" s="1" t="s">
+      <c r="O91" t="s">
+        <v>585</v>
+      </c>
+      <c r="Q91" t="s">
         <v>678</v>
       </c>
-      <c r="O91" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q91" t="s">
+      <c r="S91" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="S91" s="1" t="s">
+      <c r="T91" t="s">
+        <v>358</v>
+      </c>
+      <c r="U91" t="s">
         <v>680</v>
       </c>
-      <c r="T91" t="s">
-        <v>359</v>
-      </c>
-      <c r="U91" t="s">
-        <v>681</v>
-      </c>
       <c r="W91" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X91">
         <v>2</v>
@@ -7968,43 +7983,43 @@
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B92" t="s">
+        <v>628</v>
+      </c>
+      <c r="F92" t="s">
         <v>629</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>630</v>
       </c>
-      <c r="G92" t="s">
-        <v>631</v>
-      </c>
       <c r="H92" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I92" t="s">
+        <v>39</v>
+      </c>
+      <c r="J92" t="s">
         <v>40</v>
       </c>
-      <c r="J92" t="s">
-        <v>41</v>
-      </c>
       <c r="M92" t="s">
+        <v>681</v>
+      </c>
+      <c r="N92" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="N92" s="1" t="s">
+      <c r="S92" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T92" t="s">
         <v>683</v>
       </c>
-      <c r="S92" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T92" t="s">
-        <v>684</v>
-      </c>
       <c r="U92" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W92" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X92">
         <v>2</v>
@@ -8012,43 +8027,43 @@
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B93" t="s">
+        <v>684</v>
+      </c>
+      <c r="F93" t="s">
         <v>685</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>686</v>
       </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>687</v>
       </c>
-      <c r="H93" t="s">
+      <c r="I93" t="s">
+        <v>103</v>
+      </c>
+      <c r="J93" t="s">
         <v>688</v>
       </c>
-      <c r="I93" t="s">
-        <v>104</v>
-      </c>
-      <c r="J93" t="s">
+      <c r="M93" t="s">
         <v>689</v>
       </c>
-      <c r="M93" t="s">
+      <c r="N93" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="N93" s="1" t="s">
+      <c r="S93" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T93" t="s">
         <v>691</v>
       </c>
-      <c r="S93" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T93" t="s">
+      <c r="U93" t="s">
         <v>692</v>
       </c>
-      <c r="U93" t="s">
-        <v>693</v>
-      </c>
       <c r="W93" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X93">
         <v>3</v>
@@ -8056,43 +8071,43 @@
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>693</v>
+      </c>
+      <c r="B94" t="s">
         <v>694</v>
       </c>
-      <c r="B94" t="s">
+      <c r="F94" t="s">
+        <v>547</v>
+      </c>
+      <c r="G94" t="s">
         <v>695</v>
       </c>
-      <c r="F94" t="s">
-        <v>548</v>
-      </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
+        <v>687</v>
+      </c>
+      <c r="I94" t="s">
         <v>696</v>
       </c>
-      <c r="H94" t="s">
-        <v>688</v>
-      </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>697</v>
       </c>
-      <c r="J94" t="s">
+      <c r="M94" t="s">
         <v>698</v>
       </c>
-      <c r="M94" t="s">
+      <c r="N94" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="N94" s="1" t="s">
+      <c r="S94" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T94" t="s">
         <v>700</v>
       </c>
-      <c r="S94" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T94" t="s">
+      <c r="U94" t="s">
         <v>701</v>
       </c>
-      <c r="U94" t="s">
-        <v>702</v>
-      </c>
       <c r="W94" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X94">
         <v>3</v>
@@ -8100,46 +8115,46 @@
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>702</v>
+      </c>
+      <c r="B95" t="s">
         <v>703</v>
       </c>
-      <c r="B95" t="s">
+      <c r="F95" t="s">
         <v>704</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
+        <v>27</v>
+      </c>
+      <c r="H95" t="s">
         <v>705</v>
       </c>
-      <c r="G95" t="s">
-        <v>28</v>
-      </c>
-      <c r="H95" t="s">
+      <c r="I95" t="s">
+        <v>506</v>
+      </c>
+      <c r="J95" t="s">
         <v>706</v>
       </c>
-      <c r="I95" t="s">
-        <v>507</v>
-      </c>
-      <c r="J95" t="s">
+      <c r="M95" t="s">
         <v>707</v>
       </c>
-      <c r="M95" t="s">
+      <c r="N95" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="N95" s="1" t="s">
+      <c r="Q95" t="s">
         <v>709</v>
       </c>
-      <c r="Q95" t="s">
+      <c r="S95" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T95" t="s">
         <v>710</v>
       </c>
-      <c r="S95" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T95" t="s">
+      <c r="U95" t="s">
         <v>711</v>
       </c>
-      <c r="U95" t="s">
-        <v>712</v>
-      </c>
       <c r="W95" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X95">
         <v>3</v>
@@ -8147,43 +8162,43 @@
     </row>
     <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>712</v>
+      </c>
+      <c r="B96" t="s">
         <v>713</v>
       </c>
-      <c r="B96" t="s">
+      <c r="F96" t="s">
         <v>714</v>
       </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
+        <v>479</v>
+      </c>
+      <c r="H96" t="s">
+        <v>514</v>
+      </c>
+      <c r="I96" t="s">
+        <v>103</v>
+      </c>
+      <c r="J96" t="s">
+        <v>104</v>
+      </c>
+      <c r="M96" t="s">
+        <v>223</v>
+      </c>
+      <c r="N96" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="G96" t="s">
-        <v>480</v>
-      </c>
-      <c r="H96" t="s">
-        <v>515</v>
-      </c>
-      <c r="I96" t="s">
-        <v>104</v>
-      </c>
-      <c r="J96" t="s">
-        <v>105</v>
-      </c>
-      <c r="M96" t="s">
-        <v>224</v>
-      </c>
-      <c r="N96" s="1" t="s">
+      <c r="S96" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="S96" s="1" t="s">
+      <c r="T96" t="s">
         <v>717</v>
       </c>
-      <c r="T96" t="s">
+      <c r="U96" t="s">
         <v>718</v>
       </c>
-      <c r="U96" t="s">
-        <v>719</v>
-      </c>
       <c r="W96" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X96">
         <v>3</v>
@@ -8191,46 +8206,46 @@
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>719</v>
+      </c>
+      <c r="B97" t="s">
         <v>720</v>
       </c>
-      <c r="B97" t="s">
+      <c r="F97" t="s">
         <v>721</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>722</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
+        <v>220</v>
+      </c>
+      <c r="I97" t="s">
+        <v>103</v>
+      </c>
+      <c r="J97" t="s">
+        <v>688</v>
+      </c>
+      <c r="M97" t="s">
         <v>723</v>
       </c>
-      <c r="H97" t="s">
-        <v>221</v>
-      </c>
-      <c r="I97" t="s">
-        <v>104</v>
-      </c>
-      <c r="J97" t="s">
-        <v>689</v>
-      </c>
-      <c r="M97" t="s">
+      <c r="N97" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="N97" s="1" t="s">
+      <c r="Q97" t="s">
         <v>725</v>
       </c>
-      <c r="Q97" t="s">
+      <c r="S97" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T97" t="s">
         <v>726</v>
       </c>
-      <c r="S97" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T97" t="s">
+      <c r="U97" t="s">
         <v>727</v>
       </c>
-      <c r="U97" t="s">
-        <v>728</v>
-      </c>
       <c r="W97" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X97">
         <v>3</v>
@@ -8238,52 +8253,52 @@
     </row>
     <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>728</v>
+      </c>
+      <c r="B98" t="s">
         <v>729</v>
       </c>
-      <c r="B98" t="s">
+      <c r="D98" t="s">
         <v>730</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
+        <v>730</v>
+      </c>
+      <c r="F98" t="s">
         <v>731</v>
       </c>
-      <c r="E98" t="s">
-        <v>731</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
+        <v>497</v>
+      </c>
+      <c r="H98" t="s">
+        <v>102</v>
+      </c>
+      <c r="I98" t="s">
+        <v>79</v>
+      </c>
+      <c r="J98" t="s">
+        <v>80</v>
+      </c>
+      <c r="M98" t="s">
         <v>732</v>
       </c>
-      <c r="G98" t="s">
-        <v>498</v>
-      </c>
-      <c r="H98" t="s">
-        <v>103</v>
-      </c>
-      <c r="I98" t="s">
-        <v>80</v>
-      </c>
-      <c r="J98" t="s">
-        <v>81</v>
-      </c>
-      <c r="M98" t="s">
+      <c r="N98" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="N98" s="1" t="s">
+      <c r="Q98" t="s">
         <v>734</v>
       </c>
-      <c r="Q98" t="s">
+      <c r="S98" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T98" t="s">
+        <v>287</v>
+      </c>
+      <c r="U98" t="s">
         <v>735</v>
       </c>
-      <c r="S98" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T98" t="s">
-        <v>288</v>
-      </c>
-      <c r="U98" t="s">
-        <v>736</v>
-      </c>
       <c r="W98" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X98">
         <v>3</v>
@@ -8291,43 +8306,43 @@
     </row>
     <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>736</v>
+      </c>
+      <c r="B99" t="s">
         <v>737</v>
       </c>
-      <c r="B99" t="s">
+      <c r="F99" t="s">
         <v>738</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
+        <v>630</v>
+      </c>
+      <c r="H99" t="s">
+        <v>479</v>
+      </c>
+      <c r="I99" t="s">
         <v>739</v>
       </c>
-      <c r="G99" t="s">
-        <v>631</v>
-      </c>
-      <c r="H99" t="s">
-        <v>480</v>
-      </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>740</v>
       </c>
-      <c r="J99" t="s">
+      <c r="M99" t="s">
         <v>741</v>
       </c>
-      <c r="M99" t="s">
+      <c r="N99" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="N99" s="1" t="s">
+      <c r="S99" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="S99" s="1" t="s">
+      <c r="T99" t="s">
         <v>744</v>
       </c>
-      <c r="T99" t="s">
+      <c r="U99" t="s">
         <v>745</v>
       </c>
-      <c r="U99" t="s">
-        <v>746</v>
-      </c>
       <c r="W99" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X99">
         <v>3</v>
@@ -8335,43 +8350,43 @@
     </row>
     <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>746</v>
+      </c>
+      <c r="B100" t="s">
         <v>747</v>
       </c>
-      <c r="B100" t="s">
+      <c r="F100" t="s">
+        <v>597</v>
+      </c>
+      <c r="G100" t="s">
         <v>748</v>
       </c>
-      <c r="F100" t="s">
-        <v>598</v>
-      </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
         <v>749</v>
       </c>
-      <c r="H100" t="s">
+      <c r="I100" t="s">
+        <v>103</v>
+      </c>
+      <c r="J100" t="s">
         <v>750</v>
       </c>
-      <c r="I100" t="s">
-        <v>104</v>
-      </c>
-      <c r="J100" t="s">
+      <c r="M100" t="s">
         <v>751</v>
       </c>
-      <c r="M100" t="s">
+      <c r="N100" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="N100" s="1" t="s">
+      <c r="S100" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="S100" s="1" t="s">
+      <c r="T100" t="s">
         <v>754</v>
       </c>
-      <c r="T100" t="s">
+      <c r="U100" t="s">
         <v>755</v>
       </c>
-      <c r="U100" t="s">
+      <c r="W100" t="s">
         <v>756</v>
-      </c>
-      <c r="W100" t="s">
-        <v>757</v>
       </c>
       <c r="X100">
         <v>3</v>
@@ -8379,46 +8394,46 @@
     </row>
     <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B101" t="s">
+        <v>757</v>
+      </c>
+      <c r="F101" t="s">
         <v>758</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>759</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>760</v>
       </c>
-      <c r="H101" t="s">
+      <c r="I101" t="s">
         <v>761</v>
       </c>
-      <c r="I101" t="s">
+      <c r="J101" t="s">
         <v>762</v>
       </c>
-      <c r="J101" t="s">
+      <c r="M101" t="s">
         <v>763</v>
       </c>
-      <c r="M101" t="s">
+      <c r="N101" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="N101" s="1" t="s">
+      <c r="Q101" t="s">
         <v>765</v>
       </c>
-      <c r="Q101" t="s">
+      <c r="S101" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="S101" s="1" t="s">
+      <c r="T101" t="s">
         <v>767</v>
       </c>
-      <c r="T101" t="s">
-        <v>768</v>
-      </c>
       <c r="U101" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="W101" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X101">
         <v>2</v>
@@ -8426,46 +8441,46 @@
     </row>
     <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B102" t="s">
+        <v>757</v>
+      </c>
+      <c r="F102" t="s">
         <v>758</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>759</v>
       </c>
-      <c r="G102" t="s">
-        <v>760</v>
-      </c>
       <c r="H102" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I102" t="s">
+        <v>761</v>
+      </c>
+      <c r="J102" t="s">
         <v>762</v>
       </c>
-      <c r="J102" t="s">
-        <v>763</v>
-      </c>
       <c r="M102" t="s">
+        <v>768</v>
+      </c>
+      <c r="N102" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="N102" s="1" t="s">
+      <c r="Q102" t="s">
         <v>770</v>
       </c>
-      <c r="Q102" t="s">
+      <c r="S102" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T102" t="s">
         <v>771</v>
       </c>
-      <c r="S102" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T102" t="s">
-        <v>772</v>
-      </c>
       <c r="U102" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="W102" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X102">
         <v>2</v>
@@ -8473,46 +8488,46 @@
     </row>
     <row r="103" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B103" t="s">
+        <v>757</v>
+      </c>
+      <c r="F103" t="s">
         <v>758</v>
       </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
         <v>759</v>
       </c>
-      <c r="G103" t="s">
-        <v>760</v>
-      </c>
       <c r="H103" t="s">
+        <v>772</v>
+      </c>
+      <c r="I103" t="s">
+        <v>103</v>
+      </c>
+      <c r="J103" t="s">
+        <v>104</v>
+      </c>
+      <c r="M103" t="s">
         <v>773</v>
       </c>
-      <c r="I103" t="s">
-        <v>104</v>
-      </c>
-      <c r="J103" t="s">
-        <v>105</v>
-      </c>
-      <c r="M103" t="s">
+      <c r="N103" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="N103" s="1" t="s">
+      <c r="Q103" t="s">
         <v>775</v>
       </c>
-      <c r="Q103" t="s">
+      <c r="S103" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="S103" s="1" t="s">
+      <c r="T103" t="s">
+        <v>607</v>
+      </c>
+      <c r="U103" t="s">
         <v>777</v>
       </c>
-      <c r="T103" t="s">
-        <v>608</v>
-      </c>
-      <c r="U103" t="s">
-        <v>778</v>
-      </c>
       <c r="W103" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X103">
         <v>1</v>
@@ -8520,46 +8535,46 @@
     </row>
     <row r="104" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B104" t="s">
+        <v>757</v>
+      </c>
+      <c r="F104" t="s">
         <v>758</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>759</v>
       </c>
-      <c r="G104" t="s">
-        <v>760</v>
-      </c>
       <c r="H104" t="s">
+        <v>778</v>
+      </c>
+      <c r="I104" t="s">
+        <v>158</v>
+      </c>
+      <c r="J104" t="s">
+        <v>159</v>
+      </c>
+      <c r="M104" t="s">
         <v>779</v>
       </c>
-      <c r="I104" t="s">
-        <v>159</v>
-      </c>
-      <c r="J104" t="s">
-        <v>160</v>
-      </c>
-      <c r="M104" t="s">
+      <c r="N104" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="N104" s="1" t="s">
+      <c r="Q104" t="s">
         <v>781</v>
       </c>
-      <c r="Q104" t="s">
+      <c r="S104" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T104" t="s">
+        <v>653</v>
+      </c>
+      <c r="U104" t="s">
         <v>782</v>
       </c>
-      <c r="S104" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T104" t="s">
-        <v>654</v>
-      </c>
-      <c r="U104" t="s">
-        <v>783</v>
-      </c>
       <c r="W104" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X104">
         <v>3</v>
@@ -8567,46 +8582,46 @@
     </row>
     <row r="105" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B105" t="s">
+        <v>757</v>
+      </c>
+      <c r="F105" t="s">
         <v>758</v>
       </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>759</v>
       </c>
-      <c r="G105" t="s">
-        <v>760</v>
-      </c>
       <c r="H105" t="s">
+        <v>783</v>
+      </c>
+      <c r="I105" t="s">
         <v>784</v>
       </c>
-      <c r="I105" t="s">
+      <c r="J105" t="s">
         <v>785</v>
       </c>
-      <c r="J105" t="s">
+      <c r="M105" t="s">
         <v>786</v>
       </c>
-      <c r="M105" t="s">
+      <c r="N105" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="N105" s="1" t="s">
+      <c r="Q105" t="s">
         <v>788</v>
       </c>
-      <c r="Q105" t="s">
+      <c r="S105" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T105" t="s">
         <v>789</v>
       </c>
-      <c r="S105" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T105" t="s">
+      <c r="U105" t="s">
         <v>790</v>
       </c>
-      <c r="U105" t="s">
-        <v>791</v>
-      </c>
       <c r="W105" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X105">
         <v>2</v>
@@ -8614,43 +8629,43 @@
     </row>
     <row r="106" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B106" t="s">
+        <v>791</v>
+      </c>
+      <c r="F106" t="s">
+        <v>63</v>
+      </c>
+      <c r="G106" t="s">
         <v>792</v>
       </c>
-      <c r="F106" t="s">
-        <v>64</v>
-      </c>
-      <c r="G106" t="s">
+      <c r="H106" t="s">
         <v>793</v>
       </c>
-      <c r="H106" t="s">
+      <c r="I106" t="s">
         <v>794</v>
       </c>
-      <c r="I106" t="s">
+      <c r="J106" t="s">
         <v>795</v>
       </c>
-      <c r="J106" t="s">
+      <c r="M106" t="s">
         <v>796</v>
       </c>
-      <c r="M106" t="s">
+      <c r="N106" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="N106" s="1" t="s">
+      <c r="S106" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="S106" s="1" t="s">
+      <c r="T106" t="s">
         <v>799</v>
       </c>
-      <c r="T106" t="s">
-        <v>800</v>
-      </c>
       <c r="U106" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="W106" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X106">
         <v>3</v>
@@ -8658,46 +8673,46 @@
     </row>
     <row r="107" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>800</v>
+      </c>
+      <c r="B107" t="s">
         <v>801</v>
       </c>
-      <c r="B107" t="s">
+      <c r="F107" t="s">
+        <v>100</v>
+      </c>
+      <c r="G107" t="s">
         <v>802</v>
       </c>
-      <c r="F107" t="s">
-        <v>101</v>
-      </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>803</v>
       </c>
-      <c r="H107" t="s">
+      <c r="I107" t="s">
+        <v>66</v>
+      </c>
+      <c r="J107" t="s">
+        <v>67</v>
+      </c>
+      <c r="M107" t="s">
         <v>804</v>
       </c>
-      <c r="I107" t="s">
-        <v>67</v>
-      </c>
-      <c r="J107" t="s">
-        <v>68</v>
-      </c>
-      <c r="M107" t="s">
+      <c r="N107" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="N107" s="1" t="s">
+      <c r="Q107" t="s">
         <v>806</v>
       </c>
-      <c r="Q107" t="s">
+      <c r="S107" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T107" t="s">
         <v>807</v>
       </c>
-      <c r="S107" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T107" t="s">
-        <v>808</v>
-      </c>
       <c r="U107" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="W107" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X107">
         <v>3</v>
@@ -8705,46 +8720,46 @@
     </row>
     <row r="108" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>800</v>
+      </c>
+      <c r="B108" t="s">
         <v>801</v>
       </c>
-      <c r="B108" t="s">
+      <c r="F108" t="s">
+        <v>100</v>
+      </c>
+      <c r="G108" t="s">
         <v>802</v>
       </c>
-      <c r="F108" t="s">
-        <v>101</v>
-      </c>
-      <c r="G108" t="s">
-        <v>803</v>
-      </c>
       <c r="H108" t="s">
+        <v>808</v>
+      </c>
+      <c r="I108" t="s">
         <v>809</v>
       </c>
-      <c r="I108" t="s">
+      <c r="J108" t="s">
         <v>810</v>
       </c>
-      <c r="J108" t="s">
+      <c r="M108" t="s">
         <v>811</v>
       </c>
-      <c r="M108" t="s">
+      <c r="N108" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="N108" s="1" t="s">
+      <c r="Q108" t="s">
         <v>813</v>
       </c>
-      <c r="Q108" t="s">
+      <c r="S108" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T108" t="s">
+        <v>36</v>
+      </c>
+      <c r="U108" t="s">
         <v>814</v>
       </c>
-      <c r="S108" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T108" t="s">
-        <v>37</v>
-      </c>
-      <c r="U108" t="s">
-        <v>815</v>
-      </c>
       <c r="W108" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X108">
         <v>2</v>
@@ -8752,46 +8767,46 @@
     </row>
     <row r="109" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B109" t="s">
+        <v>815</v>
+      </c>
+      <c r="F109" t="s">
+        <v>100</v>
+      </c>
+      <c r="G109" t="s">
+        <v>497</v>
+      </c>
+      <c r="H109" t="s">
         <v>816</v>
       </c>
-      <c r="F109" t="s">
-        <v>101</v>
-      </c>
-      <c r="G109" t="s">
-        <v>498</v>
-      </c>
-      <c r="H109" t="s">
+      <c r="I109" t="s">
+        <v>506</v>
+      </c>
+      <c r="J109" t="s">
+        <v>706</v>
+      </c>
+      <c r="M109" t="s">
         <v>817</v>
       </c>
-      <c r="I109" t="s">
-        <v>507</v>
-      </c>
-      <c r="J109" t="s">
-        <v>707</v>
-      </c>
-      <c r="M109" t="s">
+      <c r="N109" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="N109" s="1" t="s">
+      <c r="Q109" t="s">
+        <v>296</v>
+      </c>
+      <c r="S109" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T109" t="s">
         <v>819</v>
       </c>
-      <c r="Q109" t="s">
-        <v>297</v>
-      </c>
-      <c r="S109" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T109" t="s">
+      <c r="U109" t="s">
         <v>820</v>
       </c>
-      <c r="U109" t="s">
-        <v>821</v>
-      </c>
       <c r="W109" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X109">
         <v>3</v>
@@ -8799,52 +8814,52 @@
     </row>
     <row r="110" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>821</v>
+      </c>
+      <c r="B110" t="s">
         <v>822</v>
       </c>
-      <c r="B110" t="s">
+      <c r="D110" t="s">
         <v>823</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>824</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
+        <v>364</v>
+      </c>
+      <c r="G110" t="s">
+        <v>621</v>
+      </c>
+      <c r="H110" t="s">
         <v>825</v>
       </c>
-      <c r="F110" t="s">
-        <v>365</v>
-      </c>
-      <c r="G110" t="s">
-        <v>622</v>
-      </c>
-      <c r="H110" t="s">
+      <c r="I110" t="s">
+        <v>158</v>
+      </c>
+      <c r="J110" t="s">
+        <v>159</v>
+      </c>
+      <c r="M110" t="s">
         <v>826</v>
       </c>
-      <c r="I110" t="s">
-        <v>159</v>
-      </c>
-      <c r="J110" t="s">
-        <v>160</v>
-      </c>
-      <c r="M110" t="s">
+      <c r="N110" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="N110" s="1" t="s">
+      <c r="Q110" t="s">
         <v>828</v>
       </c>
-      <c r="Q110" t="s">
+      <c r="S110" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="S110" s="1" t="s">
+      <c r="T110" t="s">
         <v>830</v>
       </c>
-      <c r="T110" t="s">
-        <v>831</v>
-      </c>
       <c r="U110" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="W110" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X110">
         <v>2</v>
@@ -8852,52 +8867,52 @@
     </row>
     <row r="111" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>821</v>
+      </c>
+      <c r="B111" t="s">
         <v>822</v>
       </c>
-      <c r="B111" t="s">
+      <c r="D111" t="s">
         <v>823</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>824</v>
       </c>
-      <c r="E111" t="s">
-        <v>825</v>
-      </c>
       <c r="F111" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G111" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H111" t="s">
+        <v>831</v>
+      </c>
+      <c r="I111" t="s">
         <v>832</v>
       </c>
-      <c r="I111" t="s">
+      <c r="J111" t="s">
         <v>833</v>
       </c>
-      <c r="J111" t="s">
+      <c r="M111" t="s">
         <v>834</v>
       </c>
-      <c r="M111" t="s">
+      <c r="N111" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="N111" s="1" t="s">
+      <c r="Q111" t="s">
+        <v>834</v>
+      </c>
+      <c r="S111" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T111" t="s">
         <v>836</v>
       </c>
-      <c r="Q111" t="s">
-        <v>835</v>
-      </c>
-      <c r="S111" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T111" t="s">
+      <c r="U111" t="s">
         <v>837</v>
       </c>
-      <c r="U111" t="s">
-        <v>838</v>
-      </c>
       <c r="W111" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X111">
         <v>3</v>
@@ -8905,52 +8920,52 @@
     </row>
     <row r="112" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>821</v>
+      </c>
+      <c r="B112" t="s">
         <v>822</v>
       </c>
-      <c r="B112" t="s">
+      <c r="D112" t="s">
         <v>823</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>824</v>
       </c>
-      <c r="E112" t="s">
-        <v>825</v>
-      </c>
       <c r="F112" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G112" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H112" t="s">
+        <v>838</v>
+      </c>
+      <c r="I112" t="s">
+        <v>210</v>
+      </c>
+      <c r="J112" t="s">
+        <v>211</v>
+      </c>
+      <c r="M112" t="s">
         <v>839</v>
       </c>
-      <c r="I112" t="s">
-        <v>211</v>
-      </c>
-      <c r="J112" t="s">
-        <v>212</v>
-      </c>
-      <c r="M112" t="s">
+      <c r="N112" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="N112" s="1" t="s">
+      <c r="Q112" t="s">
         <v>841</v>
       </c>
-      <c r="Q112" t="s">
+      <c r="S112" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T112" t="s">
         <v>842</v>
       </c>
-      <c r="S112" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T112" t="s">
-        <v>843</v>
-      </c>
       <c r="U112" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="W112" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X112">
         <v>1</v>
@@ -8958,52 +8973,52 @@
     </row>
     <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B113" t="s">
+        <v>843</v>
+      </c>
+      <c r="D113" t="s">
         <v>844</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
         <v>845</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
+        <v>311</v>
+      </c>
+      <c r="G113" t="s">
         <v>846</v>
       </c>
-      <c r="F113" t="s">
-        <v>312</v>
-      </c>
-      <c r="G113" t="s">
+      <c r="H113" t="s">
         <v>847</v>
       </c>
-      <c r="H113" t="s">
+      <c r="I113" t="s">
+        <v>506</v>
+      </c>
+      <c r="J113" t="s">
         <v>848</v>
       </c>
-      <c r="I113" t="s">
-        <v>507</v>
-      </c>
-      <c r="J113" t="s">
+      <c r="M113" t="s">
         <v>849</v>
       </c>
-      <c r="M113" t="s">
+      <c r="N113" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="N113" s="1" t="s">
+      <c r="Q113" t="s">
         <v>851</v>
       </c>
-      <c r="Q113" t="s">
+      <c r="S113" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T113" t="s">
+        <v>674</v>
+      </c>
+      <c r="U113" t="s">
         <v>852</v>
       </c>
-      <c r="S113" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T113" t="s">
-        <v>675</v>
-      </c>
-      <c r="U113" t="s">
-        <v>853</v>
-      </c>
       <c r="W113" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X113">
         <v>2</v>
@@ -9011,52 +9026,52 @@
     </row>
     <row r="114" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B114" t="s">
+        <v>843</v>
+      </c>
+      <c r="D114" t="s">
         <v>844</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>845</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
+        <v>311</v>
+      </c>
+      <c r="G114" t="s">
         <v>846</v>
       </c>
-      <c r="F114" t="s">
-        <v>312</v>
-      </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>847</v>
       </c>
-      <c r="H114" t="s">
-        <v>848</v>
-      </c>
       <c r="I114" t="s">
+        <v>853</v>
+      </c>
+      <c r="J114" t="s">
         <v>854</v>
       </c>
-      <c r="J114" t="s">
+      <c r="M114" t="s">
         <v>855</v>
       </c>
-      <c r="M114" t="s">
+      <c r="N114" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="N114" s="1" t="s">
+      <c r="Q114" t="s">
         <v>857</v>
       </c>
-      <c r="Q114" t="s">
+      <c r="S114" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T114" t="s">
         <v>858</v>
       </c>
-      <c r="S114" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T114" t="s">
+      <c r="U114" t="s">
         <v>859</v>
       </c>
-      <c r="U114" t="s">
-        <v>860</v>
-      </c>
       <c r="W114" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X114">
         <v>3</v>
@@ -9064,52 +9079,52 @@
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B115" t="s">
+        <v>843</v>
+      </c>
+      <c r="D115" t="s">
         <v>844</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>845</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
+        <v>311</v>
+      </c>
+      <c r="G115" t="s">
         <v>846</v>
       </c>
-      <c r="F115" t="s">
-        <v>312</v>
-      </c>
-      <c r="G115" t="s">
-        <v>847</v>
-      </c>
       <c r="H115" t="s">
+        <v>860</v>
+      </c>
+      <c r="I115" t="s">
+        <v>210</v>
+      </c>
+      <c r="J115" t="s">
+        <v>211</v>
+      </c>
+      <c r="M115" t="s">
         <v>861</v>
       </c>
-      <c r="I115" t="s">
-        <v>211</v>
-      </c>
-      <c r="J115" t="s">
-        <v>212</v>
-      </c>
-      <c r="M115" t="s">
+      <c r="N115" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="N115" s="1" t="s">
+      <c r="Q115" t="s">
         <v>863</v>
       </c>
-      <c r="Q115" t="s">
+      <c r="S115" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T115" t="s">
         <v>864</v>
       </c>
-      <c r="S115" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T115" t="s">
+      <c r="U115" t="s">
         <v>865</v>
       </c>
-      <c r="U115" t="s">
-        <v>866</v>
-      </c>
       <c r="W115" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X115">
         <v>1</v>
@@ -9117,52 +9132,52 @@
     </row>
     <row r="116" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B116" t="s">
+        <v>843</v>
+      </c>
+      <c r="D116" t="s">
         <v>844</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>845</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
+        <v>311</v>
+      </c>
+      <c r="G116" t="s">
         <v>846</v>
       </c>
-      <c r="F116" t="s">
-        <v>312</v>
-      </c>
-      <c r="G116" t="s">
-        <v>847</v>
-      </c>
       <c r="H116" t="s">
+        <v>866</v>
+      </c>
+      <c r="I116" t="s">
+        <v>506</v>
+      </c>
+      <c r="J116" t="s">
         <v>867</v>
       </c>
-      <c r="I116" t="s">
-        <v>507</v>
-      </c>
-      <c r="J116" t="s">
+      <c r="M116" t="s">
         <v>868</v>
       </c>
-      <c r="M116" t="s">
+      <c r="N116" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="N116" s="1" t="s">
+      <c r="Q116" t="s">
         <v>870</v>
       </c>
-      <c r="Q116" t="s">
-        <v>871</v>
-      </c>
       <c r="S116" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T116" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="U116" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="W116" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X116">
         <v>1</v>
@@ -9170,46 +9185,46 @@
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>871</v>
+      </c>
+      <c r="B117" t="s">
         <v>872</v>
       </c>
-      <c r="B117" t="s">
+      <c r="F117" t="s">
         <v>873</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
+        <v>602</v>
+      </c>
+      <c r="H117" t="s">
+        <v>243</v>
+      </c>
+      <c r="I117" t="s">
+        <v>138</v>
+      </c>
+      <c r="J117" t="s">
+        <v>139</v>
+      </c>
+      <c r="M117" t="s">
         <v>874</v>
       </c>
-      <c r="G117" t="s">
-        <v>603</v>
-      </c>
-      <c r="H117" t="s">
-        <v>244</v>
-      </c>
-      <c r="I117" t="s">
-        <v>139</v>
-      </c>
-      <c r="J117" t="s">
-        <v>140</v>
-      </c>
-      <c r="M117" t="s">
+      <c r="N117" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="N117" s="1" t="s">
+      <c r="Q117" t="s">
         <v>876</v>
       </c>
-      <c r="Q117" t="s">
+      <c r="S117" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T117" t="s">
         <v>877</v>
       </c>
-      <c r="S117" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T117" t="s">
-        <v>878</v>
-      </c>
       <c r="U117" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="W117" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X117">
         <v>3</v>
@@ -9217,40 +9232,40 @@
     </row>
     <row r="118" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>878</v>
+      </c>
+      <c r="B118" t="s">
         <v>879</v>
       </c>
-      <c r="B118" t="s">
+      <c r="F118" t="s">
         <v>880</v>
       </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>881</v>
       </c>
-      <c r="G118" t="s">
+      <c r="I118" t="s">
+        <v>29</v>
+      </c>
+      <c r="J118" t="s">
+        <v>30</v>
+      </c>
+      <c r="M118" t="s">
         <v>882</v>
       </c>
-      <c r="I118" t="s">
-        <v>30</v>
-      </c>
-      <c r="J118" t="s">
-        <v>31</v>
-      </c>
-      <c r="M118" t="s">
+      <c r="N118" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="N118" s="1" t="s">
+      <c r="S118" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T118" t="s">
         <v>884</v>
       </c>
-      <c r="S118" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T118" t="s">
+      <c r="U118" t="s">
         <v>885</v>
       </c>
-      <c r="U118" t="s">
-        <v>886</v>
-      </c>
       <c r="W118" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X118">
         <v>3</v>
@@ -9258,46 +9273,46 @@
     </row>
     <row r="119" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B119" t="s">
+        <v>886</v>
+      </c>
+      <c r="F119" t="s">
+        <v>685</v>
+      </c>
+      <c r="G119" t="s">
         <v>887</v>
       </c>
-      <c r="F119" t="s">
-        <v>686</v>
-      </c>
-      <c r="G119" t="s">
+      <c r="H119" t="s">
         <v>888</v>
       </c>
-      <c r="H119" t="s">
+      <c r="I119" t="s">
+        <v>103</v>
+      </c>
+      <c r="J119" t="s">
+        <v>104</v>
+      </c>
+      <c r="M119" t="s">
         <v>889</v>
       </c>
-      <c r="I119" t="s">
-        <v>104</v>
-      </c>
-      <c r="J119" t="s">
-        <v>105</v>
-      </c>
-      <c r="M119" t="s">
+      <c r="N119" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="N119" s="1" t="s">
+      <c r="Q119" t="s">
         <v>891</v>
       </c>
-      <c r="Q119" t="s">
+      <c r="S119" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T119" t="s">
         <v>892</v>
       </c>
-      <c r="S119" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T119" t="s">
-        <v>893</v>
-      </c>
       <c r="U119" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="W119" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X119">
         <v>3</v>
@@ -9305,52 +9320,52 @@
     </row>
     <row r="120" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B120" t="s">
+        <v>893</v>
+      </c>
+      <c r="D120" t="s">
         <v>894</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
         <v>895</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
+        <v>100</v>
+      </c>
+      <c r="G120" t="s">
+        <v>630</v>
+      </c>
+      <c r="H120" t="s">
         <v>896</v>
       </c>
-      <c r="F120" t="s">
-        <v>101</v>
-      </c>
-      <c r="G120" t="s">
-        <v>631</v>
-      </c>
-      <c r="H120" t="s">
+      <c r="I120" t="s">
+        <v>177</v>
+      </c>
+      <c r="J120" t="s">
         <v>897</v>
       </c>
-      <c r="I120" t="s">
-        <v>178</v>
-      </c>
-      <c r="J120" t="s">
+      <c r="M120" t="s">
         <v>898</v>
       </c>
-      <c r="M120" t="s">
+      <c r="N120" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="N120" s="1" t="s">
+      <c r="Q120" t="s">
         <v>900</v>
       </c>
-      <c r="Q120" t="s">
+      <c r="S120" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T120" t="s">
         <v>901</v>
       </c>
-      <c r="S120" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T120" t="s">
+      <c r="U120" t="s">
         <v>902</v>
       </c>
-      <c r="U120" t="s">
-        <v>903</v>
-      </c>
       <c r="W120" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X120">
         <v>3</v>
@@ -9358,46 +9373,46 @@
     </row>
     <row r="121" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B121" t="s">
+        <v>903</v>
+      </c>
+      <c r="F121" t="s">
+        <v>473</v>
+      </c>
+      <c r="G121" t="s">
         <v>904</v>
       </c>
-      <c r="F121" t="s">
-        <v>474</v>
-      </c>
-      <c r="G121" t="s">
+      <c r="H121" t="s">
         <v>905</v>
       </c>
-      <c r="H121" t="s">
+      <c r="I121" t="s">
+        <v>29</v>
+      </c>
+      <c r="J121" t="s">
+        <v>30</v>
+      </c>
+      <c r="M121" t="s">
         <v>906</v>
       </c>
-      <c r="I121" t="s">
-        <v>30</v>
-      </c>
-      <c r="J121" t="s">
-        <v>31</v>
-      </c>
-      <c r="M121" t="s">
+      <c r="N121" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="N121" s="1" t="s">
+      <c r="Q121" t="s">
         <v>908</v>
       </c>
-      <c r="Q121" t="s">
+      <c r="S121" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T121" t="s">
         <v>909</v>
       </c>
-      <c r="S121" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T121" t="s">
+      <c r="U121" t="s">
         <v>910</v>
       </c>
-      <c r="U121" t="s">
-        <v>911</v>
-      </c>
       <c r="W121" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="X121">
         <v>3</v>
@@ -9405,46 +9420,46 @@
     </row>
     <row r="122" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B122" t="s">
+        <v>911</v>
+      </c>
+      <c r="F122" t="s">
+        <v>100</v>
+      </c>
+      <c r="G122" t="s">
         <v>912</v>
       </c>
-      <c r="F122" t="s">
-        <v>101</v>
-      </c>
-      <c r="G122" t="s">
+      <c r="H122" t="s">
         <v>913</v>
       </c>
-      <c r="H122" t="s">
+      <c r="I122" t="s">
+        <v>29</v>
+      </c>
+      <c r="J122" t="s">
+        <v>30</v>
+      </c>
+      <c r="M122" t="s">
         <v>914</v>
       </c>
-      <c r="I122" t="s">
-        <v>30</v>
-      </c>
-      <c r="J122" t="s">
-        <v>31</v>
-      </c>
-      <c r="M122" t="s">
+      <c r="N122" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="N122" s="1" t="s">
+      <c r="Q122" t="s">
         <v>916</v>
       </c>
-      <c r="Q122" t="s">
+      <c r="S122" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T122" t="s">
         <v>917</v>
       </c>
-      <c r="S122" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T122" t="s">
+      <c r="U122" t="s">
         <v>918</v>
       </c>
-      <c r="U122" t="s">
-        <v>919</v>
-      </c>
       <c r="W122" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X122">
         <v>2</v>
@@ -9452,46 +9467,46 @@
     </row>
     <row r="123" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B123" t="s">
+        <v>919</v>
+      </c>
+      <c r="F123" t="s">
+        <v>620</v>
+      </c>
+      <c r="G123" t="s">
         <v>920</v>
       </c>
-      <c r="F123" t="s">
-        <v>621</v>
-      </c>
-      <c r="G123" t="s">
+      <c r="H123" t="s">
         <v>921</v>
       </c>
-      <c r="H123" t="s">
+      <c r="I123" t="s">
+        <v>210</v>
+      </c>
+      <c r="J123" t="s">
         <v>922</v>
       </c>
-      <c r="I123" t="s">
-        <v>211</v>
-      </c>
-      <c r="J123" t="s">
+      <c r="M123" t="s">
+        <v>204</v>
+      </c>
+      <c r="N123" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="M123" t="s">
-        <v>205</v>
-      </c>
-      <c r="N123" s="1" t="s">
+      <c r="Q123" t="s">
+        <v>206</v>
+      </c>
+      <c r="S123" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T123" t="s">
         <v>924</v>
       </c>
-      <c r="Q123" t="s">
-        <v>207</v>
-      </c>
-      <c r="S123" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T123" t="s">
+      <c r="U123" t="s">
         <v>925</v>
       </c>
-      <c r="U123" t="s">
-        <v>926</v>
-      </c>
       <c r="W123" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X123">
         <v>3</v>
@@ -9499,46 +9514,46 @@
     </row>
     <row r="124" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B124" t="s">
+        <v>926</v>
+      </c>
+      <c r="F124" t="s">
         <v>927</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>928</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
+        <v>514</v>
+      </c>
+      <c r="I124" t="s">
+        <v>54</v>
+      </c>
+      <c r="J124" t="s">
         <v>929</v>
       </c>
-      <c r="H124" t="s">
-        <v>515</v>
-      </c>
-      <c r="I124" t="s">
-        <v>55</v>
-      </c>
-      <c r="J124" t="s">
+      <c r="M124" t="s">
+        <v>223</v>
+      </c>
+      <c r="N124" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="M124" t="s">
-        <v>224</v>
-      </c>
-      <c r="N124" s="1" t="s">
+      <c r="Q124" t="s">
         <v>931</v>
       </c>
-      <c r="Q124" t="s">
+      <c r="S124" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="S124" s="1" t="s">
+      <c r="T124" t="s">
         <v>933</v>
       </c>
-      <c r="T124" t="s">
+      <c r="U124" t="s">
         <v>934</v>
       </c>
-      <c r="U124" t="s">
-        <v>935</v>
-      </c>
       <c r="W124" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="X124">
         <v>3</v>
@@ -9546,34 +9561,34 @@
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>935</v>
+      </c>
+      <c r="B125" t="s">
         <v>936</v>
       </c>
-      <c r="B125" t="s">
+      <c r="F125" t="s">
+        <v>637</v>
+      </c>
+      <c r="G125" t="s">
+        <v>695</v>
+      </c>
+      <c r="H125" t="s">
         <v>937</v>
       </c>
-      <c r="F125" t="s">
-        <v>638</v>
-      </c>
-      <c r="G125" t="s">
-        <v>696</v>
-      </c>
-      <c r="H125" t="s">
+      <c r="J125" t="s">
         <v>938</v>
       </c>
-      <c r="J125" t="s">
+      <c r="M125" t="s">
         <v>939</v>
       </c>
-      <c r="M125" t="s">
+      <c r="N125" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="N125" s="1" t="s">
+      <c r="S125" s="1" t="s">
         <v>941</v>
       </c>
-      <c r="S125" s="1" t="s">
-        <v>942</v>
-      </c>
       <c r="W125" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X125">
         <v>3</v>
@@ -9581,52 +9596,52 @@
     </row>
     <row r="126" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B126" t="s">
+        <v>942</v>
+      </c>
+      <c r="D126" t="s">
         <v>943</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
         <v>944</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>945</v>
       </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
+        <v>847</v>
+      </c>
+      <c r="H126" t="s">
         <v>946</v>
       </c>
-      <c r="G126" t="s">
-        <v>848</v>
-      </c>
-      <c r="H126" t="s">
+      <c r="I126" t="s">
+        <v>177</v>
+      </c>
+      <c r="J126" t="s">
+        <v>178</v>
+      </c>
+      <c r="M126" t="s">
         <v>947</v>
       </c>
-      <c r="I126" t="s">
-        <v>178</v>
-      </c>
-      <c r="J126" t="s">
-        <v>179</v>
-      </c>
-      <c r="M126" t="s">
+      <c r="N126" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="N126" s="1" t="s">
+      <c r="Q126" t="s">
         <v>949</v>
       </c>
-      <c r="Q126" t="s">
+      <c r="S126" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T126" t="s">
         <v>950</v>
       </c>
-      <c r="S126" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T126" t="s">
+      <c r="U126" t="s">
         <v>951</v>
       </c>
-      <c r="U126" t="s">
-        <v>952</v>
-      </c>
       <c r="W126" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X126">
         <v>2</v>
@@ -9634,52 +9649,52 @@
     </row>
     <row r="127" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B127" t="s">
+        <v>942</v>
+      </c>
+      <c r="D127" t="s">
         <v>943</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
         <v>944</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>945</v>
       </c>
-      <c r="F127" t="s">
-        <v>946</v>
-      </c>
       <c r="G127" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H127" t="s">
+        <v>952</v>
+      </c>
+      <c r="I127" t="s">
+        <v>29</v>
+      </c>
+      <c r="J127" t="s">
+        <v>30</v>
+      </c>
+      <c r="M127" t="s">
         <v>953</v>
       </c>
-      <c r="I127" t="s">
-        <v>30</v>
-      </c>
-      <c r="J127" t="s">
-        <v>31</v>
-      </c>
-      <c r="M127" t="s">
+      <c r="N127" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="N127" s="1" t="s">
+      <c r="Q127" t="s">
         <v>955</v>
       </c>
-      <c r="Q127" t="s">
+      <c r="S127" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T127" t="s">
+        <v>561</v>
+      </c>
+      <c r="U127" t="s">
         <v>956</v>
       </c>
-      <c r="S127" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T127" t="s">
-        <v>562</v>
-      </c>
-      <c r="U127" t="s">
-        <v>957</v>
-      </c>
       <c r="W127" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X127">
         <v>2</v>
@@ -9687,49 +9702,49 @@
     </row>
     <row r="128" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B128" t="s">
+        <v>942</v>
+      </c>
+      <c r="D128" t="s">
         <v>943</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>944</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>945</v>
       </c>
-      <c r="F128" t="s">
-        <v>946</v>
-      </c>
       <c r="G128" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H128" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J128" t="s">
+        <v>957</v>
+      </c>
+      <c r="M128" t="s">
         <v>958</v>
       </c>
-      <c r="M128" t="s">
+      <c r="N128" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="N128" s="1" t="s">
+      <c r="Q128" t="s">
         <v>960</v>
       </c>
-      <c r="Q128" t="s">
+      <c r="S128" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T128" t="s">
         <v>961</v>
       </c>
-      <c r="S128" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T128" t="s">
+      <c r="U128" t="s">
         <v>962</v>
       </c>
-      <c r="U128" t="s">
-        <v>963</v>
-      </c>
       <c r="W128" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X128">
         <v>2</v>
@@ -9737,52 +9752,52 @@
     </row>
     <row r="129" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B129" t="s">
+        <v>942</v>
+      </c>
+      <c r="D129" t="s">
         <v>943</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
         <v>944</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>945</v>
       </c>
-      <c r="F129" t="s">
-        <v>946</v>
-      </c>
       <c r="G129" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H129" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I129" t="s">
+        <v>103</v>
+      </c>
+      <c r="J129" t="s">
         <v>104</v>
       </c>
-      <c r="J129" t="s">
-        <v>105</v>
-      </c>
       <c r="M129" t="s">
+        <v>963</v>
+      </c>
+      <c r="N129" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="N129" s="1" t="s">
+      <c r="Q129" t="s">
         <v>965</v>
       </c>
-      <c r="Q129" t="s">
+      <c r="S129" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T129" t="s">
         <v>966</v>
       </c>
-      <c r="S129" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T129" t="s">
-        <v>967</v>
-      </c>
       <c r="U129" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="W129" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X129">
         <v>2</v>
@@ -9790,52 +9805,52 @@
     </row>
     <row r="130" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B130" t="s">
+        <v>942</v>
+      </c>
+      <c r="D130" t="s">
         <v>943</v>
       </c>
-      <c r="D130" t="s">
+      <c r="E130" t="s">
         <v>944</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>945</v>
       </c>
-      <c r="F130" t="s">
-        <v>946</v>
-      </c>
       <c r="G130" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H130" t="s">
+        <v>967</v>
+      </c>
+      <c r="I130" t="s">
+        <v>177</v>
+      </c>
+      <c r="J130" t="s">
         <v>968</v>
       </c>
-      <c r="I130" t="s">
-        <v>178</v>
-      </c>
-      <c r="J130" t="s">
+      <c r="M130" t="s">
         <v>969</v>
       </c>
-      <c r="M130" t="s">
+      <c r="N130" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="N130" s="1" t="s">
+      <c r="Q130" t="s">
         <v>971</v>
       </c>
-      <c r="Q130" t="s">
+      <c r="S130" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T130" t="s">
         <v>972</v>
       </c>
-      <c r="S130" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T130" t="s">
+      <c r="U130" t="s">
         <v>973</v>
       </c>
-      <c r="U130" t="s">
-        <v>974</v>
-      </c>
       <c r="W130" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X130">
         <v>2</v>
@@ -9843,40 +9858,40 @@
     </row>
     <row r="131" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>974</v>
+      </c>
+      <c r="B131" t="s">
         <v>975</v>
       </c>
-      <c r="B131" t="s">
+      <c r="F131" t="s">
         <v>976</v>
       </c>
-      <c r="F131" t="s">
+      <c r="G131" t="s">
+        <v>556</v>
+      </c>
+      <c r="H131" t="s">
         <v>977</v>
       </c>
-      <c r="G131" t="s">
-        <v>557</v>
-      </c>
-      <c r="H131" t="s">
+      <c r="I131" t="s">
         <v>978</v>
       </c>
-      <c r="I131" t="s">
+      <c r="J131" t="s">
         <v>979</v>
       </c>
-      <c r="J131" t="s">
+      <c r="M131" t="s">
         <v>980</v>
       </c>
-      <c r="M131" t="s">
+      <c r="N131" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="N131" s="1" t="s">
+      <c r="Q131" t="s">
         <v>982</v>
       </c>
-      <c r="Q131" t="s">
-        <v>983</v>
-      </c>
       <c r="S131" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="W131" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X131">
         <v>3</v>
@@ -9884,43 +9899,43 @@
     </row>
     <row r="132" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B132" t="s">
+        <v>983</v>
+      </c>
+      <c r="F132" t="s">
         <v>984</v>
       </c>
-      <c r="F132" t="s">
+      <c r="G132" t="s">
         <v>985</v>
       </c>
-      <c r="G132" t="s">
+      <c r="H132" t="s">
         <v>986</v>
       </c>
-      <c r="H132" t="s">
+      <c r="I132" t="s">
+        <v>29</v>
+      </c>
+      <c r="J132" t="s">
+        <v>30</v>
+      </c>
+      <c r="M132" t="s">
         <v>987</v>
       </c>
-      <c r="I132" t="s">
-        <v>30</v>
-      </c>
-      <c r="J132" t="s">
-        <v>31</v>
-      </c>
-      <c r="M132" t="s">
+      <c r="N132" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="N132" s="1" t="s">
+      <c r="S132" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T132" t="s">
+        <v>370</v>
+      </c>
+      <c r="U132" t="s">
         <v>989</v>
       </c>
-      <c r="S132" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T132" t="s">
-        <v>371</v>
-      </c>
-      <c r="U132" t="s">
-        <v>990</v>
-      </c>
       <c r="W132" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="X132">
         <v>3</v>
@@ -9928,49 +9943,49 @@
     </row>
     <row r="133" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>990</v>
+      </c>
+      <c r="B133" t="s">
         <v>991</v>
       </c>
-      <c r="B133" t="s">
+      <c r="D133" t="s">
         <v>992</v>
       </c>
-      <c r="D133" t="s">
+      <c r="F133" t="s">
         <v>993</v>
       </c>
-      <c r="F133" t="s">
+      <c r="G133" t="s">
         <v>994</v>
       </c>
-      <c r="G133" t="s">
+      <c r="H133" t="s">
         <v>995</v>
       </c>
-      <c r="H133" t="s">
+      <c r="I133" t="s">
+        <v>210</v>
+      </c>
+      <c r="J133" t="s">
+        <v>211</v>
+      </c>
+      <c r="M133" t="s">
         <v>996</v>
       </c>
-      <c r="I133" t="s">
-        <v>211</v>
-      </c>
-      <c r="J133" t="s">
-        <v>212</v>
-      </c>
-      <c r="M133" t="s">
+      <c r="N133" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="N133" s="1" t="s">
+      <c r="Q133" t="s">
         <v>998</v>
       </c>
-      <c r="Q133" t="s">
+      <c r="S133" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T133" t="s">
         <v>999</v>
       </c>
-      <c r="S133" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T133" t="s">
-        <v>1000</v>
-      </c>
       <c r="U133" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="W133" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X133">
         <v>2</v>
@@ -9978,49 +9993,49 @@
     </row>
     <row r="134" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>990</v>
+      </c>
+      <c r="B134" t="s">
         <v>991</v>
       </c>
-      <c r="B134" t="s">
+      <c r="D134" t="s">
         <v>992</v>
       </c>
-      <c r="D134" t="s">
+      <c r="F134" t="s">
         <v>993</v>
       </c>
-      <c r="F134" t="s">
+      <c r="G134" t="s">
         <v>994</v>
       </c>
-      <c r="G134" t="s">
-        <v>995</v>
-      </c>
       <c r="H134" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I134" t="s">
+        <v>410</v>
+      </c>
+      <c r="J134" t="s">
         <v>1001</v>
       </c>
-      <c r="I134" t="s">
-        <v>411</v>
-      </c>
-      <c r="J134" t="s">
+      <c r="M134" t="s">
         <v>1002</v>
       </c>
-      <c r="M134" t="s">
+      <c r="N134" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="N134" s="1" t="s">
+      <c r="Q134" t="s">
         <v>1004</v>
       </c>
-      <c r="Q134" t="s">
+      <c r="S134" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="T134" t="s">
         <v>1005</v>
       </c>
-      <c r="S134" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="T134" t="s">
+      <c r="U134" t="s">
         <v>1006</v>
       </c>
-      <c r="U134" t="s">
-        <v>1007</v>
-      </c>
       <c r="W134" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X134">
         <v>2</v>
@@ -10028,49 +10043,49 @@
     </row>
     <row r="135" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>990</v>
+      </c>
+      <c r="B135" t="s">
         <v>991</v>
       </c>
-      <c r="B135" t="s">
+      <c r="D135" t="s">
         <v>992</v>
       </c>
-      <c r="D135" t="s">
+      <c r="F135" t="s">
         <v>993</v>
       </c>
-      <c r="F135" t="s">
+      <c r="G135" t="s">
         <v>994</v>
       </c>
-      <c r="G135" t="s">
-        <v>995</v>
-      </c>
       <c r="H135" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I135" t="s">
+        <v>138</v>
+      </c>
+      <c r="J135" t="s">
         <v>139</v>
       </c>
-      <c r="J135" t="s">
-        <v>140</v>
-      </c>
       <c r="M135" t="s">
+        <v>1007</v>
+      </c>
+      <c r="N135" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="N135" s="1" t="s">
+      <c r="Q135" t="s">
         <v>1009</v>
       </c>
-      <c r="Q135" t="s">
-        <v>1010</v>
-      </c>
       <c r="S135" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T135" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="U135" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="W135" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X135">
         <v>2</v>
@@ -10078,40 +10093,40 @@
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B136" t="s">
         <v>1011</v>
       </c>
-      <c r="B136" t="s">
+      <c r="F136" t="s">
         <v>1012</v>
       </c>
-      <c r="F136" t="s">
+      <c r="G136" t="s">
+        <v>513</v>
+      </c>
+      <c r="H136" t="s">
         <v>1013</v>
       </c>
-      <c r="G136" t="s">
-        <v>514</v>
-      </c>
-      <c r="H136" t="s">
+      <c r="J136" t="s">
         <v>1014</v>
       </c>
-      <c r="J136" t="s">
+      <c r="M136" t="s">
         <v>1015</v>
       </c>
-      <c r="M136" t="s">
+      <c r="N136" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="N136" s="1" t="s">
+      <c r="Q136" t="s">
         <v>1017</v>
       </c>
-      <c r="Q136" t="s">
+      <c r="S136" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="U136" t="s">
         <v>1018</v>
       </c>
-      <c r="S136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="U136" t="s">
-        <v>1019</v>
-      </c>
       <c r="W136" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X136">
         <v>3</v>
@@ -10119,40 +10134,40 @@
     </row>
     <row r="137" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B137" t="s">
         <v>1020</v>
       </c>
-      <c r="B137" t="s">
+      <c r="F137" t="s">
         <v>1021</v>
       </c>
-      <c r="F137" t="s">
+      <c r="G137" t="s">
         <v>1022</v>
       </c>
-      <c r="G137" t="s">
+      <c r="H137" t="s">
         <v>1023</v>
       </c>
-      <c r="H137" t="s">
+      <c r="I137" t="s">
         <v>1024</v>
       </c>
-      <c r="I137" t="s">
+      <c r="J137" t="s">
         <v>1025</v>
       </c>
-      <c r="J137" t="s">
+      <c r="M137" t="s">
         <v>1026</v>
       </c>
-      <c r="M137" t="s">
+      <c r="N137" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="N137" s="1" t="s">
+      <c r="Q137" t="s">
         <v>1028</v>
       </c>
-      <c r="Q137" t="s">
-        <v>1029</v>
-      </c>
       <c r="S137" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="W137" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X137">
         <v>3</v>
@@ -10160,43 +10175,43 @@
     </row>
     <row r="138" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B138" t="s">
         <v>1030</v>
       </c>
-      <c r="B138" t="s">
+      <c r="F138" t="s">
+        <v>792</v>
+      </c>
+      <c r="G138" t="s">
+        <v>91</v>
+      </c>
+      <c r="H138" t="s">
         <v>1031</v>
       </c>
-      <c r="F138" t="s">
-        <v>793</v>
-      </c>
-      <c r="G138" t="s">
-        <v>92</v>
-      </c>
-      <c r="H138" t="s">
+      <c r="I138" t="s">
         <v>1032</v>
       </c>
-      <c r="I138" t="s">
+      <c r="J138" t="s">
         <v>1033</v>
       </c>
-      <c r="J138" t="s">
+      <c r="M138" t="s">
         <v>1034</v>
       </c>
-      <c r="M138" t="s">
+      <c r="N138" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="N138" s="1" t="s">
-        <v>1036</v>
-      </c>
       <c r="S138" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T138" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="U138" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="W138" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X138">
         <v>3</v>
@@ -10204,43 +10219,43 @@
     </row>
     <row r="139" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B139" t="s">
         <v>1037</v>
       </c>
-      <c r="B139" t="s">
+      <c r="F139" t="s">
         <v>1038</v>
       </c>
-      <c r="F139" t="s">
+      <c r="G139" t="s">
+        <v>303</v>
+      </c>
+      <c r="H139" t="s">
+        <v>473</v>
+      </c>
+      <c r="I139" t="s">
+        <v>794</v>
+      </c>
+      <c r="J139" t="s">
         <v>1039</v>
       </c>
-      <c r="G139" t="s">
-        <v>304</v>
-      </c>
-      <c r="H139" t="s">
-        <v>474</v>
-      </c>
-      <c r="I139" t="s">
-        <v>795</v>
-      </c>
-      <c r="J139" t="s">
+      <c r="M139" t="s">
         <v>1040</v>
       </c>
-      <c r="M139" t="s">
+      <c r="N139" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="N139" s="1" t="s">
+      <c r="S139" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T139" t="s">
+        <v>540</v>
+      </c>
+      <c r="U139" t="s">
         <v>1042</v>
       </c>
-      <c r="S139" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T139" t="s">
-        <v>541</v>
-      </c>
-      <c r="U139" t="s">
-        <v>1043</v>
-      </c>
       <c r="W139" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X139">
         <v>3</v>
@@ -10248,43 +10263,43 @@
     </row>
     <row r="140" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B140" t="s">
         <v>1044</v>
       </c>
-      <c r="B140" t="s">
+      <c r="F140" t="s">
+        <v>630</v>
+      </c>
+      <c r="G140" t="s">
         <v>1045</v>
       </c>
-      <c r="F140" t="s">
-        <v>631</v>
-      </c>
-      <c r="G140" t="s">
+      <c r="H140" t="s">
+        <v>946</v>
+      </c>
+      <c r="I140" t="s">
+        <v>761</v>
+      </c>
+      <c r="J140" t="s">
         <v>1046</v>
       </c>
-      <c r="H140" t="s">
-        <v>947</v>
-      </c>
-      <c r="I140" t="s">
-        <v>762</v>
-      </c>
-      <c r="J140" t="s">
+      <c r="M140" t="s">
         <v>1047</v>
       </c>
-      <c r="M140" t="s">
+      <c r="N140" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="N140" s="1" t="s">
+      <c r="S140" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T140" t="s">
         <v>1049</v>
       </c>
-      <c r="S140" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T140" t="s">
+      <c r="U140" t="s">
         <v>1050</v>
       </c>
-      <c r="U140" t="s">
-        <v>1051</v>
-      </c>
       <c r="W140" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X140">
         <v>3</v>
@@ -10292,46 +10307,46 @@
     </row>
     <row r="141" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F141" t="s">
+        <v>514</v>
+      </c>
+      <c r="G141" t="s">
         <v>1052</v>
       </c>
-      <c r="B141" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F141" t="s">
-        <v>515</v>
-      </c>
-      <c r="G141" t="s">
+      <c r="H141" t="s">
+        <v>946</v>
+      </c>
+      <c r="I141" t="s">
+        <v>158</v>
+      </c>
+      <c r="J141" t="s">
+        <v>159</v>
+      </c>
+      <c r="M141" t="s">
         <v>1053</v>
       </c>
-      <c r="H141" t="s">
-        <v>947</v>
-      </c>
-      <c r="I141" t="s">
-        <v>159</v>
-      </c>
-      <c r="J141" t="s">
-        <v>160</v>
-      </c>
-      <c r="M141" t="s">
+      <c r="N141" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="N141" s="1" t="s">
+      <c r="Q141" t="s">
         <v>1055</v>
       </c>
-      <c r="Q141" t="s">
-        <v>1056</v>
-      </c>
       <c r="S141" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T141" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="U141" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="W141" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X141">
         <v>3</v>
@@ -10339,46 +10354,46 @@
     </row>
     <row r="142" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B142" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F142" t="s">
+        <v>620</v>
+      </c>
+      <c r="G142" t="s">
+        <v>772</v>
+      </c>
+      <c r="H142" t="s">
         <v>1057</v>
       </c>
-      <c r="F142" t="s">
-        <v>621</v>
-      </c>
-      <c r="G142" t="s">
-        <v>773</v>
-      </c>
-      <c r="H142" t="s">
+      <c r="I142" t="s">
         <v>1058</v>
       </c>
-      <c r="I142" t="s">
+      <c r="J142" t="s">
         <v>1059</v>
       </c>
-      <c r="J142" t="s">
+      <c r="M142" t="s">
         <v>1060</v>
       </c>
-      <c r="M142" t="s">
+      <c r="N142" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="N142" s="1" t="s">
+      <c r="Q142" t="s">
         <v>1062</v>
       </c>
-      <c r="Q142" t="s">
+      <c r="S142" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T142" t="s">
         <v>1063</v>
       </c>
-      <c r="S142" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T142" t="s">
+      <c r="U142" t="s">
         <v>1064</v>
       </c>
-      <c r="U142" t="s">
-        <v>1065</v>
-      </c>
       <c r="W142" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X142">
         <v>3</v>
@@ -10386,49 +10401,49 @@
     </row>
     <row r="143" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B143" t="s">
         <v>1066</v>
       </c>
-      <c r="B143" t="s">
+      <c r="D143" t="s">
         <v>1067</v>
       </c>
-      <c r="D143" t="s">
+      <c r="F143" t="s">
+        <v>291</v>
+      </c>
+      <c r="G143" t="s">
+        <v>881</v>
+      </c>
+      <c r="H143" t="s">
+        <v>243</v>
+      </c>
+      <c r="I143" t="s">
+        <v>506</v>
+      </c>
+      <c r="J143" t="s">
+        <v>706</v>
+      </c>
+      <c r="M143" t="s">
         <v>1068</v>
       </c>
-      <c r="F143" t="s">
-        <v>292</v>
-      </c>
-      <c r="G143" t="s">
-        <v>882</v>
-      </c>
-      <c r="H143" t="s">
-        <v>244</v>
-      </c>
-      <c r="I143" t="s">
-        <v>507</v>
-      </c>
-      <c r="J143" t="s">
-        <v>707</v>
-      </c>
-      <c r="M143" t="s">
+      <c r="N143" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="N143" s="1" t="s">
+      <c r="Q143" t="s">
         <v>1070</v>
       </c>
-      <c r="Q143" t="s">
+      <c r="S143" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T143" t="s">
+        <v>535</v>
+      </c>
+      <c r="U143" t="s">
         <v>1071</v>
       </c>
-      <c r="S143" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T143" t="s">
-        <v>536</v>
-      </c>
-      <c r="U143" t="s">
-        <v>1072</v>
-      </c>
       <c r="W143" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X143">
         <v>1</v>
@@ -10436,49 +10451,49 @@
     </row>
     <row r="144" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B144" t="s">
         <v>1066</v>
       </c>
-      <c r="B144" t="s">
+      <c r="D144" t="s">
         <v>1067</v>
       </c>
-      <c r="D144" t="s">
-        <v>1068</v>
-      </c>
       <c r="F144" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G144" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H144" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I144" t="s">
+        <v>177</v>
+      </c>
+      <c r="J144" t="s">
         <v>1073</v>
       </c>
-      <c r="I144" t="s">
-        <v>178</v>
-      </c>
-      <c r="J144" t="s">
+      <c r="M144" t="s">
+        <v>445</v>
+      </c>
+      <c r="N144" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="M144" t="s">
-        <v>446</v>
-      </c>
-      <c r="N144" s="1" t="s">
-        <v>1075</v>
-      </c>
       <c r="Q144" t="s">
+        <v>447</v>
+      </c>
+      <c r="S144" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T144" t="s">
         <v>448</v>
       </c>
-      <c r="S144" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T144" t="s">
-        <v>449</v>
-      </c>
       <c r="U144" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="W144" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X144">
         <v>2</v>
@@ -10486,49 +10501,49 @@
     </row>
     <row r="145" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B145" t="s">
         <v>1066</v>
       </c>
-      <c r="B145" t="s">
+      <c r="D145" t="s">
         <v>1067</v>
       </c>
-      <c r="D145" t="s">
-        <v>1068</v>
-      </c>
       <c r="F145" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G145" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H145" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I145" t="s">
+        <v>210</v>
+      </c>
+      <c r="J145" t="s">
         <v>211</v>
       </c>
-      <c r="J145" t="s">
-        <v>212</v>
-      </c>
       <c r="M145" t="s">
+        <v>1075</v>
+      </c>
+      <c r="N145" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="N145" s="1" t="s">
+      <c r="Q145" t="s">
         <v>1077</v>
       </c>
-      <c r="Q145" t="s">
+      <c r="S145" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T145" t="s">
+        <v>354</v>
+      </c>
+      <c r="U145" t="s">
         <v>1078</v>
       </c>
-      <c r="S145" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T145" t="s">
-        <v>355</v>
-      </c>
-      <c r="U145" t="s">
-        <v>1079</v>
-      </c>
       <c r="W145" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X145">
         <v>2</v>
@@ -10536,46 +10551,46 @@
     </row>
     <row r="146" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B146" t="s">
         <v>1080</v>
       </c>
-      <c r="B146" t="s">
+      <c r="F146" t="s">
+        <v>630</v>
+      </c>
+      <c r="G146" t="s">
+        <v>985</v>
+      </c>
+      <c r="H146" t="s">
+        <v>435</v>
+      </c>
+      <c r="I146" t="s">
+        <v>54</v>
+      </c>
+      <c r="J146" t="s">
+        <v>55</v>
+      </c>
+      <c r="M146" t="s">
         <v>1081</v>
       </c>
-      <c r="F146" t="s">
-        <v>631</v>
-      </c>
-      <c r="G146" t="s">
-        <v>986</v>
-      </c>
-      <c r="H146" t="s">
-        <v>436</v>
-      </c>
-      <c r="I146" t="s">
-        <v>55</v>
-      </c>
-      <c r="J146" t="s">
-        <v>56</v>
-      </c>
-      <c r="M146" t="s">
+      <c r="N146" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="N146" s="1" t="s">
+      <c r="Q146" t="s">
         <v>1083</v>
       </c>
-      <c r="Q146" t="s">
+      <c r="S146" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T146" t="s">
         <v>1084</v>
       </c>
-      <c r="S146" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T146" t="s">
+      <c r="U146" t="s">
         <v>1085</v>
       </c>
-      <c r="U146" t="s">
-        <v>1086</v>
-      </c>
       <c r="W146" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X146">
         <v>2</v>
@@ -10583,46 +10598,46 @@
     </row>
     <row r="147" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B147" t="s">
         <v>1080</v>
       </c>
-      <c r="B147" t="s">
-        <v>1081</v>
-      </c>
       <c r="F147" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G147" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H147" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I147" t="s">
+        <v>138</v>
+      </c>
+      <c r="J147" t="s">
         <v>139</v>
       </c>
-      <c r="J147" t="s">
-        <v>140</v>
-      </c>
       <c r="M147" t="s">
+        <v>1086</v>
+      </c>
+      <c r="N147" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="N147" s="1" t="s">
+      <c r="Q147" t="s">
         <v>1088</v>
       </c>
-      <c r="Q147" t="s">
+      <c r="S147" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T147" t="s">
         <v>1089</v>
       </c>
-      <c r="S147" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T147" t="s">
+      <c r="U147" t="s">
         <v>1090</v>
       </c>
-      <c r="U147" t="s">
-        <v>1091</v>
-      </c>
       <c r="W147" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X147">
         <v>1</v>
@@ -10630,46 +10645,46 @@
     </row>
     <row r="148" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B148" t="s">
         <v>1080</v>
       </c>
-      <c r="B148" t="s">
-        <v>1081</v>
-      </c>
       <c r="F148" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G148" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H148" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I148" t="s">
+        <v>177</v>
+      </c>
+      <c r="J148" t="s">
         <v>178</v>
       </c>
-      <c r="J148" t="s">
-        <v>179</v>
-      </c>
       <c r="M148" t="s">
+        <v>1091</v>
+      </c>
+      <c r="N148" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="N148" s="1" t="s">
+      <c r="Q148" t="s">
         <v>1093</v>
       </c>
-      <c r="Q148" t="s">
+      <c r="S148" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T148" t="s">
         <v>1094</v>
       </c>
-      <c r="S148" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T148" t="s">
+      <c r="U148" t="s">
         <v>1095</v>
       </c>
-      <c r="U148" t="s">
-        <v>1096</v>
-      </c>
       <c r="W148" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X148">
         <v>2</v>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70216180-76AB-4C85-B099-3A342DAF9A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1288,9 +1294,6 @@
     <t>Galerie des Offices</t>
   </si>
   <si>
-    <t>Musée des Beaux-Arts (MSK)</t>
-  </si>
-  <si>
     <t>Académie des Beaux-Arts</t>
   </si>
   <si>
@@ -1522,9 +1525,6 @@
     <t>"Ecce Homo"</t>
   </si>
   <si>
-    <t>"Vierge à l"Enfant"</t>
-  </si>
-  <si>
     <t>"Miracle de la relique de la Vraie Croix au pont de San Lorenzo"</t>
   </si>
   <si>
@@ -3209,13 +3209,19 @@
   </si>
   <si>
     <t>anglaise (Royaume-Uni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musée des Beaux-Arts </t>
+  </si>
+  <si>
+    <t>"Vierge à l'Enfant"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3260,18 +3266,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3309,7 +3323,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -3343,6 +3357,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3377,9 +3392,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3552,11 +3568,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X148"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3630,7 +3646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -3659,31 +3675,31 @@
         <v>404</v>
       </c>
       <c r="M2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="Q2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="S2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="U2" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="W2" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="X2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -3712,31 +3728,31 @@
         <v>405</v>
       </c>
       <c r="M3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="Q3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="S3" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="U3" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="W3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="X3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -3765,28 +3781,28 @@
         <v>406</v>
       </c>
       <c r="M4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="S4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="U4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="W4" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="X4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -3815,31 +3831,31 @@
         <v>407</v>
       </c>
       <c r="M5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Q5" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="S5" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T5" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="U5" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="W5" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="X5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -3865,31 +3881,31 @@
         <v>408</v>
       </c>
       <c r="M6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="Q6" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="S6" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T6" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="U6" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="W6" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -3912,31 +3928,31 @@
         <v>409</v>
       </c>
       <c r="M7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="Q7" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="S7" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T7" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="U7" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="W7" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -3959,28 +3975,28 @@
         <v>410</v>
       </c>
       <c r="M8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="S8" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T8" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="U8" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="W8" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X8">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -4003,28 +4019,28 @@
         <v>411</v>
       </c>
       <c r="M9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="S9" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="T9" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="U9" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="W9" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X9">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -4047,28 +4063,28 @@
         <v>405</v>
       </c>
       <c r="M10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="S10" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T10" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="U10" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="W10" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X10">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -4091,31 +4107,31 @@
         <v>412</v>
       </c>
       <c r="M11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="Q11" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="S11" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T11" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="U11" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="W11" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -4138,28 +4154,28 @@
         <v>405</v>
       </c>
       <c r="M12" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="S12" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T12" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="U12" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="W12" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -4182,28 +4198,28 @@
         <v>413</v>
       </c>
       <c r="M13" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="S13" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T13" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="U13" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="W13" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -4226,28 +4242,28 @@
         <v>405</v>
       </c>
       <c r="M14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="S14" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T14" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="U14" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="W14" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -4270,28 +4286,28 @@
         <v>413</v>
       </c>
       <c r="M15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="S15" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T15" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="U15" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="W15" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -4314,28 +4330,28 @@
         <v>414</v>
       </c>
       <c r="M16" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="S16" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T16" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="U16" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="W16" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -4358,31 +4374,31 @@
         <v>415</v>
       </c>
       <c r="M17" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="Q17" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="S17" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T17" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="U17" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="W17" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -4411,31 +4427,31 @@
         <v>415</v>
       </c>
       <c r="M18" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="Q18" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="S18" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="T18" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="U18" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="W18" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X18">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -4464,31 +4480,31 @@
         <v>416</v>
       </c>
       <c r="M19" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="Q19" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="S19" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T19" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="U19" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="W19" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -4517,31 +4533,31 @@
         <v>415</v>
       </c>
       <c r="M20" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="Q20" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="S20" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T20" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="U20" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="W20" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -4570,31 +4586,31 @@
         <v>417</v>
       </c>
       <c r="M21" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="Q21" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="S21" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T21" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="U21" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="W21" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X21">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -4614,31 +4630,31 @@
         <v>418</v>
       </c>
       <c r="M22" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="Q22" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="S22" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T22" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="U22" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="W22" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X22">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -4661,31 +4677,31 @@
         <v>419</v>
       </c>
       <c r="M23" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="Q23" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="S23" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T23" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="U23" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="W23" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X23">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -4705,31 +4721,31 @@
         <v>420</v>
       </c>
       <c r="M24" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="Q24" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="S24" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T24" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="U24" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="W24" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X24">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -4758,31 +4774,31 @@
         <v>407</v>
       </c>
       <c r="M25" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="Q25" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="S25" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T25" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="U25" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="W25" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X25">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -4805,28 +4821,28 @@
         <v>421</v>
       </c>
       <c r="M26" t="s">
-        <v>502</v>
+        <v>1064</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="S26" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T26" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="U26" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="W26" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X26">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -4849,28 +4865,28 @@
         <v>416</v>
       </c>
       <c r="M27" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="S27" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="T27" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="U27" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="W27" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -4893,31 +4909,31 @@
         <v>411</v>
       </c>
       <c r="M28" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="Q28" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="S28" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="T28" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="U28" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="W28" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -4940,28 +4956,28 @@
         <v>411</v>
       </c>
       <c r="M29" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="S29" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="T29" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="U29" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="W29" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -4984,28 +5000,28 @@
         <v>411</v>
       </c>
       <c r="M30" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="S30" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T30" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="U30" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="W30" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -5028,28 +5044,28 @@
         <v>422</v>
       </c>
       <c r="M31" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="S31" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="T31" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="U31" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="W31" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -5072,31 +5088,31 @@
         <v>411</v>
       </c>
       <c r="M32" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="Q32" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="S32" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T32" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="U32" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="W32" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -5119,28 +5135,28 @@
         <v>408</v>
       </c>
       <c r="M33" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S33" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T33" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="U33" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="W33" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -5163,31 +5179,31 @@
         <v>423</v>
       </c>
       <c r="M34" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="Q34" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="S34" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T34" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="U34" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="W34" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="X34">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -5210,28 +5226,28 @@
         <v>411</v>
       </c>
       <c r="M35" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="S35" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T35" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="U35" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="W35" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X35">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -5254,31 +5270,31 @@
         <v>416</v>
       </c>
       <c r="M36" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="Q36" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="S36" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T36" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="U36" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="W36" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X36">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -5301,31 +5317,31 @@
         <v>404</v>
       </c>
       <c r="M37" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="Q37" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="S37" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="T37" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="U37" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="W37" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -5348,31 +5364,31 @@
         <v>413</v>
       </c>
       <c r="M38" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="Q38" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="S38" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="T38" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="U38" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="W38" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -5392,34 +5408,34 @@
         <v>381</v>
       </c>
       <c r="J39" t="s">
-        <v>424</v>
+        <v>1063</v>
       </c>
       <c r="M39" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="Q39" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="S39" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="T39" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="U39" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="W39" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -5439,34 +5455,34 @@
         <v>376</v>
       </c>
       <c r="J40" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M40" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="Q40" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="S40" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="T40" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="U40" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="W40" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -5489,31 +5505,31 @@
         <v>404</v>
       </c>
       <c r="M41" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="Q41" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="S41" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="T41" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="U41" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="W41" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -5536,28 +5552,28 @@
         <v>404</v>
       </c>
       <c r="M42" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="S42" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="T42" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="U42" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="W42" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -5580,28 +5596,28 @@
         <v>404</v>
       </c>
       <c r="M43" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="S43" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="T43" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="U43" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="W43" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -5624,28 +5640,28 @@
         <v>404</v>
       </c>
       <c r="M44" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="S44" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T44" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="U44" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="W44" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -5668,31 +5684,31 @@
         <v>411</v>
       </c>
       <c r="M45" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="Q45" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="S45" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T45" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="U45" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="W45" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X45">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>43</v>
       </c>
@@ -5715,31 +5731,31 @@
         <v>419</v>
       </c>
       <c r="M46" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="Q46" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="S46" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T46" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="U46" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="W46" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X46">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -5759,31 +5775,31 @@
         <v>369</v>
       </c>
       <c r="J47" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M47" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="S47" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T47" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="U47" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="W47" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X47">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>26</v>
       </c>
@@ -5803,34 +5819,34 @@
         <v>382</v>
       </c>
       <c r="J48" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="M48" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="Q48" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="S48" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T48" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="U48" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="W48" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>26</v>
       </c>
@@ -5853,31 +5869,31 @@
         <v>415</v>
       </c>
       <c r="M49" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="Q49" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="S49" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T49" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="U49" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="W49" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X49">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>44</v>
       </c>
@@ -5903,31 +5919,31 @@
         <v>419</v>
       </c>
       <c r="M50" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="Q50" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="S50" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="T50" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="U50" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="W50" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X50">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -5950,28 +5966,28 @@
         <v>383</v>
       </c>
       <c r="J51" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M51" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="Q51" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="S51" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="W51" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X51">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>44</v>
       </c>
@@ -5994,31 +6010,31 @@
         <v>383</v>
       </c>
       <c r="J52" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M52" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="S52" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="T52" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="U52" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="W52" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>44</v>
       </c>
@@ -6041,31 +6057,31 @@
         <v>383</v>
       </c>
       <c r="J53" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M53" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="S53" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="T53" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="U53" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="W53" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X53">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>44</v>
       </c>
@@ -6088,34 +6104,34 @@
         <v>383</v>
       </c>
       <c r="J54" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="M54" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="Q54" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="S54" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="T54" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="U54" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="W54" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X54">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>45</v>
       </c>
@@ -6138,34 +6154,34 @@
         <v>384</v>
       </c>
       <c r="J55" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M55" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="Q55" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="S55" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T55" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="U55" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="W55" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X55">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>45</v>
       </c>
@@ -6185,34 +6201,34 @@
         <v>241</v>
       </c>
       <c r="J56" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M56" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="Q56" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="S56" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T56" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="U56" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="W56" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X56">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -6238,31 +6254,31 @@
         <v>413</v>
       </c>
       <c r="M57" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="Q57" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="S57" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T57" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="U57" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="W57" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X57">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>46</v>
       </c>
@@ -6285,28 +6301,28 @@
         <v>408</v>
       </c>
       <c r="M58" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="S58" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T58" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="U58" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="W58" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="X58">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>47</v>
       </c>
@@ -6329,28 +6345,28 @@
         <v>413</v>
       </c>
       <c r="M59" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="S59" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T59" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="U59" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="W59" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="X59">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>47</v>
       </c>
@@ -6373,28 +6389,28 @@
         <v>413</v>
       </c>
       <c r="M60" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="S60" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T60" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="U60" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="W60" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="X60">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>48</v>
       </c>
@@ -6414,31 +6430,31 @@
         <v>373</v>
       </c>
       <c r="J61" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M61" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="S61" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T61" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="U61" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="W61" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X61">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>48</v>
       </c>
@@ -6458,34 +6474,34 @@
         <v>385</v>
       </c>
       <c r="J62" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M62" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="Q62" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="S62" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T62" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="U62" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="W62" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X62">
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>49</v>
       </c>
@@ -6505,25 +6521,25 @@
         <v>322</v>
       </c>
       <c r="J63" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M63" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="S63" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="W63" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X63">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>49</v>
       </c>
@@ -6549,31 +6565,31 @@
         <v>409</v>
       </c>
       <c r="M64" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="Q64" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="S64" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T64" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="U64" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="W64" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X64">
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:24">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>50</v>
       </c>
@@ -6593,34 +6609,34 @@
         <v>386</v>
       </c>
       <c r="J65" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="Q65" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="S65" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T65" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="U65" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="W65" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X65">
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:24">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>51</v>
       </c>
@@ -6643,28 +6659,28 @@
         <v>411</v>
       </c>
       <c r="M66" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="S66" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T66" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="U66" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="W66" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X66">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:24">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>51</v>
       </c>
@@ -6684,31 +6700,31 @@
         <v>387</v>
       </c>
       <c r="J67" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M67" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="S67" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="T67" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="U67" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="W67" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X67">
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>51</v>
       </c>
@@ -6731,28 +6747,28 @@
         <v>407</v>
       </c>
       <c r="M68" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="S68" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T68" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="U68" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="W68" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X68">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>51</v>
       </c>
@@ -6772,31 +6788,31 @@
         <v>388</v>
       </c>
       <c r="J69" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M69" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="S69" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T69" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="U69" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="W69" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X69">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>51</v>
       </c>
@@ -6819,28 +6835,28 @@
         <v>408</v>
       </c>
       <c r="M70" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="S70" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T70" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="U70" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="W70" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X70">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>51</v>
       </c>
@@ -6863,28 +6879,28 @@
         <v>411</v>
       </c>
       <c r="M71" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="S71" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T71" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="U71" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="W71" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X71">
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>52</v>
       </c>
@@ -6907,31 +6923,31 @@
         <v>404</v>
       </c>
       <c r="M72" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="Q72" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="S72" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T72" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="U72" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="W72" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="X72">
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>53</v>
       </c>
@@ -6951,34 +6967,34 @@
         <v>366</v>
       </c>
       <c r="J73" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M73" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="Q73" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="S73" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T73" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="U73" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="W73" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="X73">
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>54</v>
       </c>
@@ -6998,28 +7014,28 @@
         <v>420</v>
       </c>
       <c r="M74" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="S74" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T74" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="U74" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="W74" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>54</v>
       </c>
@@ -7042,28 +7058,28 @@
         <v>413</v>
       </c>
       <c r="M75" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="S75" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="T75" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="U75" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="W75" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X75">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>54</v>
       </c>
@@ -7086,28 +7102,28 @@
         <v>413</v>
       </c>
       <c r="M76" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="S76" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T76" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="U76" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="W76" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X76">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>54</v>
       </c>
@@ -7127,37 +7143,37 @@
         <v>389</v>
       </c>
       <c r="J77" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L77" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M77" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="Q77" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="S77" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="T77" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="U77" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="W77" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X77">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>54</v>
       </c>
@@ -7180,28 +7196,28 @@
         <v>413</v>
       </c>
       <c r="M78" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="S78" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T78" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="U78" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="W78" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -7224,31 +7240,31 @@
         <v>411</v>
       </c>
       <c r="M79" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="Q79" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="S79" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T79" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="U79" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="W79" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X79">
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:24">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>56</v>
       </c>
@@ -7271,31 +7287,31 @@
         <v>419</v>
       </c>
       <c r="M80" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="Q80" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="S80" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T80" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="U80" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="W80" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X80">
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:24">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>57</v>
       </c>
@@ -7315,25 +7331,25 @@
         <v>380</v>
       </c>
       <c r="J81" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M81" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="S81" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="W81" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X81">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:24">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -7359,34 +7375,34 @@
         <v>390</v>
       </c>
       <c r="J82" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M82" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="Q82" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="S82" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T82" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="U82" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="W82" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X82">
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:24">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>28</v>
       </c>
@@ -7409,31 +7425,31 @@
         <v>405</v>
       </c>
       <c r="M83" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="Q83" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="S83" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="T83" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="U83" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="W83" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X83">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:24">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>28</v>
       </c>
@@ -7456,28 +7472,28 @@
         <v>419</v>
       </c>
       <c r="M84" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="S84" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="T84" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="U84" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="W84" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X84">
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:24">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>28</v>
       </c>
@@ -7497,37 +7513,37 @@
         <v>391</v>
       </c>
       <c r="J85" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L85" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="M85" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="Q85" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="S85" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="T85" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="U85" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="W85" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X85">
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:24">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>28</v>
       </c>
@@ -7547,37 +7563,37 @@
         <v>377</v>
       </c>
       <c r="J86" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L86" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M86" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="Q86" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="S86" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="T86" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="U86" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="W86" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X86">
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:24">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>28</v>
       </c>
@@ -7594,31 +7610,31 @@
         <v>293</v>
       </c>
       <c r="J87" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M87" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="S87" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T87" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="U87" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="W87" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X87">
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:24">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>28</v>
       </c>
@@ -7641,37 +7657,37 @@
         <v>404</v>
       </c>
       <c r="L88" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M88" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="O88" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="Q88" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="S88" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="T88" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="U88" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="W88" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X88">
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:24">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>28</v>
       </c>
@@ -7694,37 +7710,37 @@
         <v>404</v>
       </c>
       <c r="L89" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M89" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="O89" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="Q89" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="S89" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="T89" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="U89" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="W89" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X89">
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:24">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>28</v>
       </c>
@@ -7744,37 +7760,37 @@
         <v>376</v>
       </c>
       <c r="J90" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L90" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M90" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="Q90" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="S90" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="T90" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="U90" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="W90" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X90">
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:24">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>28</v>
       </c>
@@ -7794,37 +7810,37 @@
         <v>376</v>
       </c>
       <c r="J91" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L91" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M91" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="Q91" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="S91" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="T91" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="U91" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="W91" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X91">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:24">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>28</v>
       </c>
@@ -7847,28 +7863,28 @@
         <v>405</v>
       </c>
       <c r="M92" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="S92" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T92" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="U92" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="W92" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X92">
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:24">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>31</v>
       </c>
@@ -7888,31 +7904,31 @@
         <v>373</v>
       </c>
       <c r="J93" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M93" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="S93" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T93" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="U93" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="W93" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X93">
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:24">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>59</v>
       </c>
@@ -7932,31 +7948,31 @@
         <v>392</v>
       </c>
       <c r="J94" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M94" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="S94" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T94" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="U94" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="W94" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X94">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:24">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>60</v>
       </c>
@@ -7976,34 +7992,34 @@
         <v>386</v>
       </c>
       <c r="J95" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="M95" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="Q95" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="S95" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T95" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="U95" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="W95" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X95">
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:24">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>61</v>
       </c>
@@ -8026,28 +8042,28 @@
         <v>411</v>
       </c>
       <c r="M96" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="S96" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="T96" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="U96" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="W96" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X96">
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:24">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>62</v>
       </c>
@@ -8067,34 +8083,34 @@
         <v>373</v>
       </c>
       <c r="J97" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M97" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="Q97" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="S97" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T97" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="U97" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="W97" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X97">
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:24">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>63</v>
       </c>
@@ -8123,31 +8139,31 @@
         <v>409</v>
       </c>
       <c r="M98" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="Q98" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="S98" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T98" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="U98" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="W98" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X98">
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:24">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>64</v>
       </c>
@@ -8167,31 +8183,31 @@
         <v>393</v>
       </c>
       <c r="J99" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M99" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="S99" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="T99" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="U99" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="W99" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X99">
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:24">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>65</v>
       </c>
@@ -8211,31 +8227,31 @@
         <v>373</v>
       </c>
       <c r="J100" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M100" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="S100" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="T100" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="U100" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="W100" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="X100">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:24">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>31</v>
       </c>
@@ -8255,34 +8271,34 @@
         <v>394</v>
       </c>
       <c r="J101" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M101" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="Q101" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="S101" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="T101" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="U101" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="W101" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X101">
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:24">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>31</v>
       </c>
@@ -8302,34 +8318,34 @@
         <v>394</v>
       </c>
       <c r="J102" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M102" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="Q102" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="S102" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T102" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="U102" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="W102" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X102">
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:24">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>31</v>
       </c>
@@ -8352,31 +8368,31 @@
         <v>411</v>
       </c>
       <c r="M103" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="Q103" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="S103" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="T103" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="U103" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="W103" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:24">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>31</v>
       </c>
@@ -8399,31 +8415,31 @@
         <v>415</v>
       </c>
       <c r="M104" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="Q104" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="S104" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T104" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="U104" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="W104" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X104">
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:24">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>31</v>
       </c>
@@ -8443,34 +8459,34 @@
         <v>395</v>
       </c>
       <c r="J105" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M105" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="Q105" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="S105" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T105" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="U105" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="W105" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="X105">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:24">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>48</v>
       </c>
@@ -8490,31 +8506,31 @@
         <v>396</v>
       </c>
       <c r="J106" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M106" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="S106" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="T106" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="U106" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="W106" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X106">
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:24">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>66</v>
       </c>
@@ -8537,31 +8553,31 @@
         <v>408</v>
       </c>
       <c r="M107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="Q107" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S107" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T107" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="U107" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="W107" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X107">
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:24">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>66</v>
       </c>
@@ -8581,34 +8597,34 @@
         <v>397</v>
       </c>
       <c r="J108" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M108" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="Q108" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="S108" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T108" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="U108" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="W108" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X108">
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:24">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>57</v>
       </c>
@@ -8628,34 +8644,34 @@
         <v>386</v>
       </c>
       <c r="J109" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="M109" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="Q109" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="S109" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T109" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="U109" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="W109" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X109">
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:24">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>67</v>
       </c>
@@ -8684,31 +8700,31 @@
         <v>415</v>
       </c>
       <c r="M110" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="Q110" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="S110" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="T110" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="U110" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="W110" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X110">
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:24">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>67</v>
       </c>
@@ -8734,34 +8750,34 @@
         <v>398</v>
       </c>
       <c r="J111" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="M111" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="Q111" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="S111" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T111" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="U111" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="W111" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X111">
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:24">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>67</v>
       </c>
@@ -8790,31 +8806,31 @@
         <v>419</v>
       </c>
       <c r="M112" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="Q112" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="S112" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T112" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="U112" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="W112" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X112">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:24">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>44</v>
       </c>
@@ -8840,34 +8856,34 @@
         <v>386</v>
       </c>
       <c r="J113" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M113" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="Q113" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="S113" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T113" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="U113" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="W113" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X113">
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:24">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>44</v>
       </c>
@@ -8893,34 +8909,34 @@
         <v>399</v>
       </c>
       <c r="J114" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M114" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="Q114" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="S114" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T114" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="U114" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="W114" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X114">
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:24">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>44</v>
       </c>
@@ -8949,31 +8965,31 @@
         <v>419</v>
       </c>
       <c r="M115" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="Q115" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="S115" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T115" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="U115" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="W115" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X115">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:24">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>44</v>
       </c>
@@ -8999,34 +9015,34 @@
         <v>386</v>
       </c>
       <c r="J116" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="M116" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="Q116" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="S116" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T116" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="U116" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="W116" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:24">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>68</v>
       </c>
@@ -9049,31 +9065,31 @@
         <v>413</v>
       </c>
       <c r="M117" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="Q117" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="S117" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T117" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="U117" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="W117" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X117">
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:24">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>69</v>
       </c>
@@ -9093,28 +9109,28 @@
         <v>404</v>
       </c>
       <c r="M118" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="S118" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T118" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="U118" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="W118" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X118">
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:24">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>58</v>
       </c>
@@ -9137,31 +9153,31 @@
         <v>411</v>
       </c>
       <c r="M119" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="Q119" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="S119" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T119" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="U119" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="W119" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X119">
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:24">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>34</v>
       </c>
@@ -9187,34 +9203,34 @@
         <v>377</v>
       </c>
       <c r="J120" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M120" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="Q120" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="S120" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T120" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="U120" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="W120" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X120">
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:24">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>52</v>
       </c>
@@ -9237,31 +9253,31 @@
         <v>404</v>
       </c>
       <c r="M121" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="Q121" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="S121" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T121" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="U121" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="W121" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="X121">
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:24">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>40</v>
       </c>
@@ -9284,31 +9300,31 @@
         <v>404</v>
       </c>
       <c r="M122" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="Q122" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="S122" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T122" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="U122" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="W122" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X122">
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:24">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>34</v>
       </c>
@@ -9328,34 +9344,34 @@
         <v>379</v>
       </c>
       <c r="J123" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M123" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="Q123" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="S123" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T123" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="U123" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="W123" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X123">
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:24">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>47</v>
       </c>
@@ -9375,34 +9391,34 @@
         <v>369</v>
       </c>
       <c r="J124" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M124" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="N124" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="Q124" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="S124" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="T124" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="U124" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="W124" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="X124">
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:24">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>70</v>
       </c>
@@ -9419,25 +9435,25 @@
         <v>353</v>
       </c>
       <c r="J125" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M125" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="S125" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="W125" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X125">
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:24">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>34</v>
       </c>
@@ -9466,31 +9482,31 @@
         <v>416</v>
       </c>
       <c r="M126" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="N126" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="Q126" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="S126" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T126" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="U126" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="W126" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X126">
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:24">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>34</v>
       </c>
@@ -9519,31 +9535,31 @@
         <v>404</v>
       </c>
       <c r="M127" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="N127" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="Q127" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="S127" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T127" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="U127" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="W127" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X127">
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:24">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>34</v>
       </c>
@@ -9566,34 +9582,34 @@
         <v>314</v>
       </c>
       <c r="J128" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M128" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Q128" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="S128" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T128" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="U128" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="W128" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X128">
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:24">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>34</v>
       </c>
@@ -9622,31 +9638,31 @@
         <v>411</v>
       </c>
       <c r="M129" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="N129" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Q129" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="S129" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T129" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="U129" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="W129" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X129">
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:24">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>34</v>
       </c>
@@ -9672,34 +9688,34 @@
         <v>377</v>
       </c>
       <c r="J130" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="M130" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="N130" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Q130" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="S130" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T130" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="U130" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="W130" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X130">
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:24">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>71</v>
       </c>
@@ -9719,28 +9735,28 @@
         <v>400</v>
       </c>
       <c r="J131" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M131" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="N131" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Q131" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="S131" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="W131" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X131">
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:24">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>39</v>
       </c>
@@ -9763,28 +9779,28 @@
         <v>404</v>
       </c>
       <c r="M132" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N132" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="S132" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T132" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="U132" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="W132" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="X132">
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:24">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>72</v>
       </c>
@@ -9810,31 +9826,31 @@
         <v>419</v>
       </c>
       <c r="M133" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="Q133" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="S133" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T133" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="U133" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="W133" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X133">
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:24">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>72</v>
       </c>
@@ -9857,34 +9873,34 @@
         <v>383</v>
       </c>
       <c r="J134" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M134" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="Q134" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="S134" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="T134" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="U134" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="W134" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X134">
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:24">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>72</v>
       </c>
@@ -9910,31 +9926,31 @@
         <v>413</v>
       </c>
       <c r="M135" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="Q135" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="S135" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T135" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="U135" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="W135" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X135">
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:24">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>73</v>
       </c>
@@ -9951,31 +9967,31 @@
         <v>361</v>
       </c>
       <c r="J136" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M136" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="N136" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="Q136" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="S136" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="U136" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="W136" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X136">
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:24">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>74</v>
       </c>
@@ -9995,28 +10011,28 @@
         <v>401</v>
       </c>
       <c r="J137" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M137" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="Q137" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="S137" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="W137" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X137">
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:24">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>75</v>
       </c>
@@ -10036,31 +10052,31 @@
         <v>402</v>
       </c>
       <c r="J138" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="M138" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="S138" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T138" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="U138" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="W138" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X138">
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:24">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>76</v>
       </c>
@@ -10080,31 +10096,31 @@
         <v>396</v>
       </c>
       <c r="J139" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M139" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="S139" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T139" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="U139" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="W139" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X139">
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:24">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>77</v>
       </c>
@@ -10124,31 +10140,31 @@
         <v>394</v>
       </c>
       <c r="J140" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="M140" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="S140" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T140" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="U140" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="W140" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X140">
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:24">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>78</v>
       </c>
@@ -10171,31 +10187,31 @@
         <v>415</v>
       </c>
       <c r="M141" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="Q141" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="S141" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T141" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="U141" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="W141" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="X141">
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:24">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>48</v>
       </c>
@@ -10215,34 +10231,34 @@
         <v>403</v>
       </c>
       <c r="J142" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M142" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="Q142" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="S142" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="T142" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="U142" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="W142" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="X142">
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:24">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>79</v>
       </c>
@@ -10265,34 +10281,34 @@
         <v>386</v>
       </c>
       <c r="J143" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="M143" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="Q143" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="S143" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T143" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="U143" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="W143" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X143">
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:24">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>79</v>
       </c>
@@ -10315,34 +10331,34 @@
         <v>377</v>
       </c>
       <c r="J144" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M144" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="Q144" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="S144" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T144" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="U144" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="W144" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X144">
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:24">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>79</v>
       </c>
@@ -10368,31 +10384,31 @@
         <v>419</v>
       </c>
       <c r="M145" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="Q145" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="S145" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T145" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="U145" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="W145" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X145">
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:24">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>80</v>
       </c>
@@ -10415,31 +10431,31 @@
         <v>407</v>
       </c>
       <c r="M146" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="Q146" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="S146" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T146" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="U146" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="W146" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X146">
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:24">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>80</v>
       </c>
@@ -10462,31 +10478,31 @@
         <v>413</v>
       </c>
       <c r="M147" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="N147" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="Q147" t="s">
+        <v>843</v>
+      </c>
+      <c r="S147" t="s">
         <v>845</v>
       </c>
-      <c r="S147" t="s">
-        <v>847</v>
-      </c>
       <c r="T147" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="U147" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="W147" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="X147">
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:24">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>80</v>
       </c>
@@ -10509,25 +10525,25 @@
         <v>416</v>
       </c>
       <c r="M148" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="Q148" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="S148" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T148" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="U148" t="s">
+        <v>1054</v>
+      </c>
+      <c r="W148" t="s">
         <v>1056</v>
-      </c>
-      <c r="W148" t="s">
-        <v>1058</v>
       </c>
       <c r="X148">
         <v>2</v>
@@ -10535,153 +10551,153 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2"/>
-    <hyperlink ref="N4" r:id="rId3"/>
-    <hyperlink ref="N5" r:id="rId4"/>
-    <hyperlink ref="N6" r:id="rId5"/>
-    <hyperlink ref="N7" r:id="rId6"/>
-    <hyperlink ref="N8" r:id="rId7"/>
-    <hyperlink ref="N9" r:id="rId8"/>
-    <hyperlink ref="N10" r:id="rId9"/>
-    <hyperlink ref="N11" r:id="rId10"/>
-    <hyperlink ref="N12" r:id="rId11"/>
-    <hyperlink ref="N13" r:id="rId12"/>
-    <hyperlink ref="N14" r:id="rId13"/>
-    <hyperlink ref="N15" r:id="rId14"/>
-    <hyperlink ref="N16" r:id="rId15"/>
-    <hyperlink ref="N17" r:id="rId16"/>
-    <hyperlink ref="N18" r:id="rId17"/>
-    <hyperlink ref="N19" r:id="rId18"/>
-    <hyperlink ref="N20" r:id="rId19"/>
-    <hyperlink ref="N21" r:id="rId20"/>
-    <hyperlink ref="N22" r:id="rId21"/>
-    <hyperlink ref="N23" r:id="rId22"/>
-    <hyperlink ref="N24" r:id="rId23"/>
-    <hyperlink ref="N25" r:id="rId24"/>
-    <hyperlink ref="N26" r:id="rId25"/>
-    <hyperlink ref="N27" r:id="rId26"/>
-    <hyperlink ref="N28" r:id="rId27"/>
-    <hyperlink ref="N29" r:id="rId28"/>
-    <hyperlink ref="N30" r:id="rId29"/>
-    <hyperlink ref="N31" r:id="rId30"/>
-    <hyperlink ref="N32" r:id="rId31"/>
-    <hyperlink ref="N33" r:id="rId32"/>
-    <hyperlink ref="N34" r:id="rId33"/>
-    <hyperlink ref="N35" r:id="rId34"/>
-    <hyperlink ref="N36" r:id="rId35"/>
-    <hyperlink ref="N37" r:id="rId36"/>
-    <hyperlink ref="N38" r:id="rId37"/>
-    <hyperlink ref="N39" r:id="rId38"/>
-    <hyperlink ref="N40" r:id="rId39"/>
-    <hyperlink ref="N41" r:id="rId40"/>
-    <hyperlink ref="N42" r:id="rId41"/>
-    <hyperlink ref="N43" r:id="rId42"/>
-    <hyperlink ref="N44" r:id="rId43"/>
-    <hyperlink ref="N45" r:id="rId44"/>
-    <hyperlink ref="N46" r:id="rId45"/>
-    <hyperlink ref="N47" r:id="rId46"/>
-    <hyperlink ref="N48" r:id="rId47"/>
-    <hyperlink ref="N49" r:id="rId48"/>
-    <hyperlink ref="N50" r:id="rId49"/>
-    <hyperlink ref="N51" r:id="rId50"/>
-    <hyperlink ref="N52" r:id="rId51"/>
-    <hyperlink ref="N53" r:id="rId52"/>
-    <hyperlink ref="N54" r:id="rId53"/>
-    <hyperlink ref="N55" r:id="rId54"/>
-    <hyperlink ref="N56" r:id="rId55"/>
-    <hyperlink ref="N57" r:id="rId56"/>
-    <hyperlink ref="N58" r:id="rId57"/>
-    <hyperlink ref="N59" r:id="rId58"/>
-    <hyperlink ref="N60" r:id="rId59"/>
-    <hyperlink ref="N61" r:id="rId60"/>
-    <hyperlink ref="N62" r:id="rId61"/>
-    <hyperlink ref="N63" r:id="rId62"/>
-    <hyperlink ref="N64" r:id="rId63"/>
-    <hyperlink ref="N65" r:id="rId64"/>
-    <hyperlink ref="N66" r:id="rId65"/>
-    <hyperlink ref="N67" r:id="rId66"/>
-    <hyperlink ref="N68" r:id="rId67"/>
-    <hyperlink ref="N69" r:id="rId68"/>
-    <hyperlink ref="N70" r:id="rId69"/>
-    <hyperlink ref="N71" r:id="rId70"/>
-    <hyperlink ref="N72" r:id="rId71"/>
-    <hyperlink ref="N73" r:id="rId72"/>
-    <hyperlink ref="N74" r:id="rId73"/>
-    <hyperlink ref="N75" r:id="rId74"/>
-    <hyperlink ref="N76" r:id="rId75"/>
-    <hyperlink ref="N77" r:id="rId76"/>
-    <hyperlink ref="N78" r:id="rId77"/>
-    <hyperlink ref="N79" r:id="rId78"/>
-    <hyperlink ref="N80" r:id="rId79"/>
-    <hyperlink ref="N81" r:id="rId80"/>
-    <hyperlink ref="N82" r:id="rId81"/>
-    <hyperlink ref="N83" r:id="rId82"/>
-    <hyperlink ref="N84" r:id="rId83"/>
-    <hyperlink ref="N85" r:id="rId84"/>
-    <hyperlink ref="N86" r:id="rId85"/>
-    <hyperlink ref="N87" r:id="rId86"/>
-    <hyperlink ref="N88" r:id="rId87"/>
-    <hyperlink ref="N89" r:id="rId88"/>
-    <hyperlink ref="N90" r:id="rId89"/>
-    <hyperlink ref="N91" r:id="rId90"/>
-    <hyperlink ref="N92" r:id="rId91"/>
-    <hyperlink ref="N93" r:id="rId92"/>
-    <hyperlink ref="N94" r:id="rId93"/>
-    <hyperlink ref="N95" r:id="rId94"/>
-    <hyperlink ref="N96" r:id="rId95"/>
-    <hyperlink ref="N97" r:id="rId96"/>
-    <hyperlink ref="N98" r:id="rId97"/>
-    <hyperlink ref="N99" r:id="rId98"/>
-    <hyperlink ref="N100" r:id="rId99"/>
-    <hyperlink ref="N101" r:id="rId100"/>
-    <hyperlink ref="N102" r:id="rId101"/>
-    <hyperlink ref="N103" r:id="rId102"/>
-    <hyperlink ref="N104" r:id="rId103"/>
-    <hyperlink ref="N105" r:id="rId104"/>
-    <hyperlink ref="N106" r:id="rId105"/>
-    <hyperlink ref="N107" r:id="rId106"/>
-    <hyperlink ref="N108" r:id="rId107"/>
-    <hyperlink ref="N109" r:id="rId108"/>
-    <hyperlink ref="N110" r:id="rId109"/>
-    <hyperlink ref="N111" r:id="rId110"/>
-    <hyperlink ref="N112" r:id="rId111"/>
-    <hyperlink ref="N113" r:id="rId112"/>
-    <hyperlink ref="N114" r:id="rId113"/>
-    <hyperlink ref="N115" r:id="rId114"/>
-    <hyperlink ref="N116" r:id="rId115"/>
-    <hyperlink ref="N117" r:id="rId116"/>
-    <hyperlink ref="N118" r:id="rId117"/>
-    <hyperlink ref="N119" r:id="rId118"/>
-    <hyperlink ref="N120" r:id="rId119"/>
-    <hyperlink ref="N121" r:id="rId120"/>
-    <hyperlink ref="N122" r:id="rId121"/>
-    <hyperlink ref="N123" r:id="rId122"/>
-    <hyperlink ref="N124" r:id="rId123"/>
-    <hyperlink ref="N125" r:id="rId124"/>
-    <hyperlink ref="N126" r:id="rId125"/>
-    <hyperlink ref="N127" r:id="rId126"/>
-    <hyperlink ref="N128" r:id="rId127"/>
-    <hyperlink ref="N129" r:id="rId128"/>
-    <hyperlink ref="N130" r:id="rId129"/>
-    <hyperlink ref="N131" r:id="rId130"/>
-    <hyperlink ref="N132" r:id="rId131"/>
-    <hyperlink ref="N133" r:id="rId132"/>
-    <hyperlink ref="N134" r:id="rId133"/>
-    <hyperlink ref="N135" r:id="rId134"/>
-    <hyperlink ref="N136" r:id="rId135"/>
-    <hyperlink ref="N137" r:id="rId136"/>
-    <hyperlink ref="N138" r:id="rId137"/>
-    <hyperlink ref="N139" r:id="rId138"/>
-    <hyperlink ref="N140" r:id="rId139"/>
-    <hyperlink ref="N141" r:id="rId140"/>
-    <hyperlink ref="N142" r:id="rId141"/>
-    <hyperlink ref="N143" r:id="rId142"/>
-    <hyperlink ref="N144" r:id="rId143"/>
-    <hyperlink ref="N145" r:id="rId144"/>
-    <hyperlink ref="N146" r:id="rId145"/>
-    <hyperlink ref="N147" r:id="rId146"/>
-    <hyperlink ref="N148" r:id="rId147"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="N42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="N45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="N46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="N47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="N49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="N50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="N52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="N53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="N55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="N56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="N57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="N58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="N59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="N60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="N61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="N62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="N63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="N64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="N65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="N66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="N67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="N68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="N69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="N70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="N71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="N72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="N73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="N74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="N75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="N76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="N77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="N78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="N79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="N80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="N81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="N82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="N83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="N84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="N85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="N86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="N87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="N88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="N89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="N90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="N91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="N92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="N93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="N94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="N95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="N96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="N97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="N98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="N99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="N100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="N101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="N102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="N103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="N104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="N105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="N106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="N107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="N108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="N109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="N110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="N111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="N112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="N113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="N114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="N115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="N116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="N117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="N118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="N119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="N120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="N121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="N122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="N123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="N124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="N125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="N126" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="N127" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="N128" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="N129" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="N130" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="N131" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="N132" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="N133" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="N134" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="N135" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="N136" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="N137" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="N138" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="N139" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="N140" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="N141" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="N142" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="N143" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="N144" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="N145" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="N146" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="N147" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="N148" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70216180-76AB-4C85-B099-3A342DAF9A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7FD1F4-782A-48EA-84FC-B0DFFD543A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4674,7 +4674,7 @@
         <v>379</v>
       </c>
       <c r="J23" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="M23" t="s">
         <v>498</v>
@@ -5728,7 +5728,7 @@
         <v>379</v>
       </c>
       <c r="J46" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="M46" t="s">
         <v>516</v>
@@ -5916,7 +5916,7 @@
         <v>379</v>
       </c>
       <c r="J50" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="M50" t="s">
         <v>520</v>
@@ -7284,7 +7284,7 @@
         <v>379</v>
       </c>
       <c r="J80" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="M80" t="s">
         <v>548</v>
@@ -10381,7 +10381,7 @@
         <v>379</v>
       </c>
       <c r="J145" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="M145" t="s">
         <v>607</v>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7FD1F4-782A-48EA-84FC-B0DFFD543A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D0789D-154C-4457-9C19-CAF05A69A3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="1066">
   <si>
     <t>Prénom</t>
   </si>
@@ -3215,6 +3215,9 @@
   </si>
   <si>
     <t>"Vierge à l'Enfant"</t>
+  </si>
+  <si>
+    <t>202 cm</t>
   </si>
 </sst>
 </file>
@@ -3984,10 +3987,10 @@
         <v>845</v>
       </c>
       <c r="T8" t="s">
-        <v>882</v>
+        <v>1065</v>
       </c>
       <c r="U8" t="s">
-        <v>986</v>
+        <v>912</v>
       </c>
       <c r="W8" t="s">
         <v>1056</v>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89464A75-B8E3-41B7-9C9B-BCD2E0645934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="1030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="1054">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1624,12 +1630,6 @@
     <t>Portrait d'Élisabeth d'Autriche, reine de France</t>
   </si>
   <si>
-    <t>"Portrait de François Ier"</t>
-  </si>
-  <si>
-    <t>"Eva Prima Pandora"</t>
-  </si>
-  <si>
     <t>"Adam et Ève"</t>
   </si>
   <si>
@@ -3104,13 +3104,91 @@
   </si>
   <si>
     <t>500  environ</t>
+  </si>
+  <si>
+    <t>Portrait de François Ier</t>
+  </si>
+  <si>
+    <t>1536 environ</t>
+  </si>
+  <si>
+    <t>Portrait de Guillaume Budé</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/8d/Guillaume_Bud%C3%A9_by_Jean_Clouet.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>1525 environ</t>
+  </si>
+  <si>
+    <t>National Gallery of Scotland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portrait de Marie de Canaples </t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/96/Madame_de_Canaples_%28Marie_d%27Assigny%29_by_Jean_Clouet.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>1530 environ</t>
+  </si>
+  <si>
+    <t>Windsor</t>
+  </si>
+  <si>
+    <t>Royal Collection, Windsor Castle</t>
+  </si>
+  <si>
+    <t>Portrait d'un homme tenant un volume de Pétrarque</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Jean_Clouet_-_Homme_au_P%C3%A9trarque_-_Royal_Collection.jpg/960px-Jean_Clouet_-_Homme_au_P%C3%A9trarque_-_Royal_Collection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Eva Prima Pandora</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Musée Fabre</t>
+  </si>
+  <si>
+    <t>La Charité</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f1/Jean_Cousin_%28I%29_-_Charity_-_WGA05536.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Blois</t>
+  </si>
+  <si>
+    <t>L'Enlèvement d'Europe</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/1f/Jean_Cousin_%28I%29_-_The_Rape_of_Europa_-_WGA05539.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>1550 environ</t>
+  </si>
+  <si>
+    <t>Suzanne et les vieillards</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d1/HCAM_-_Chaste_Suzanne.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Heures du connétable Anne de Montmorency</t>
+  </si>
+  <si>
+    <t>Enluminure sur parchemin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3122,6 +3200,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3150,23 +3235,38 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3204,7 +3304,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -3238,6 +3338,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3272,9 +3373,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3447,11 +3549,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V367"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="31.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" customWidth="1"/>
+    <col min="15" max="15" width="7.5703125" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="7.28515625" customWidth="1"/>
+    <col min="20" max="21" width="7.42578125" customWidth="1"/>
+    <col min="22" max="22" width="6.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3470,7 +3595,7 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -3482,7 +3607,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -3519,7 +3644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -3539,13 +3664,13 @@
         <v>426</v>
       </c>
       <c r="J2" t="s">
-        <v>619</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>774</v>
+        <v>617</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>772</v>
       </c>
       <c r="R2" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S2">
         <v>81</v>
@@ -3557,7 +3682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -3577,13 +3702,13 @@
         <v>427</v>
       </c>
       <c r="J3" t="s">
-        <v>620</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>775</v>
+        <v>618</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>773</v>
       </c>
       <c r="R3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S3">
         <v>165</v>
@@ -3595,7 +3720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3615,13 +3740,13 @@
         <v>428</v>
       </c>
       <c r="J4" t="s">
-        <v>621</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>776</v>
+        <v>619</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>774</v>
       </c>
       <c r="R4" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S4">
         <v>480</v>
@@ -3633,7 +3758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -3653,13 +3778,13 @@
         <v>429</v>
       </c>
       <c r="J5" t="s">
-        <v>622</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>777</v>
+        <v>620</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>775</v>
       </c>
       <c r="R5" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S5">
         <v>121</v>
@@ -3671,7 +3796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3691,13 +3816,13 @@
         <v>430</v>
       </c>
       <c r="J6" t="s">
-        <v>623</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>778</v>
+        <v>621</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>776</v>
       </c>
       <c r="R6" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S6">
         <v>448</v>
@@ -3709,7 +3834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3729,13 +3854,13 @@
         <v>431</v>
       </c>
       <c r="J7" t="s">
-        <v>624</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>779</v>
+        <v>622</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>777</v>
       </c>
       <c r="R7" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S7">
         <v>346</v>
@@ -3747,7 +3872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -3767,13 +3892,13 @@
         <v>432</v>
       </c>
       <c r="J8" t="s">
-        <v>625</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>780</v>
+        <v>623</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>778</v>
       </c>
       <c r="R8" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S8">
         <v>275</v>
@@ -3785,7 +3910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3805,13 +3930,13 @@
         <v>433</v>
       </c>
       <c r="J9" t="s">
-        <v>626</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>781</v>
+        <v>624</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>779</v>
       </c>
       <c r="R9" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S9">
         <v>171</v>
@@ -3823,7 +3948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -3843,13 +3968,13 @@
         <v>434</v>
       </c>
       <c r="J10" t="s">
-        <v>627</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>782</v>
+        <v>625</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>780</v>
       </c>
       <c r="R10" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S10">
         <v>137</v>
@@ -3861,7 +3986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -3881,13 +4006,13 @@
         <v>435</v>
       </c>
       <c r="J11" t="s">
-        <v>628</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>783</v>
+        <v>626</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>781</v>
       </c>
       <c r="R11" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S11">
         <v>106</v>
@@ -3899,7 +4024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3919,16 +4044,16 @@
         <v>436</v>
       </c>
       <c r="J12" t="s">
-        <v>629</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>784</v>
+        <v>627</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>782</v>
       </c>
       <c r="R12" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S12" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="T12">
         <v>103</v>
@@ -3937,7 +4062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -3957,13 +4082,13 @@
         <v>437</v>
       </c>
       <c r="J13" t="s">
-        <v>630</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>785</v>
+        <v>628</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>783</v>
       </c>
       <c r="R13" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S13">
         <v>224</v>
@@ -3975,7 +4100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -3995,13 +4120,13 @@
         <v>438</v>
       </c>
       <c r="J14" t="s">
-        <v>631</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>786</v>
+        <v>629</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>784</v>
       </c>
       <c r="R14" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S14">
         <v>100.8</v>
@@ -4013,7 +4138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -4033,13 +4158,13 @@
         <v>439</v>
       </c>
       <c r="J15" t="s">
-        <v>632</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>787</v>
+        <v>630</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>785</v>
       </c>
       <c r="R15" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S15">
         <v>176</v>
@@ -4051,7 +4176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -4071,13 +4196,13 @@
         <v>440</v>
       </c>
       <c r="J16" t="s">
-        <v>633</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>788</v>
+        <v>631</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>786</v>
       </c>
       <c r="R16" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S16">
         <v>191</v>
@@ -4089,7 +4214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -4109,13 +4234,13 @@
         <v>441</v>
       </c>
       <c r="J17" t="s">
-        <v>634</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>789</v>
+        <v>632</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>787</v>
       </c>
       <c r="R17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S17">
         <v>58.7</v>
@@ -4127,7 +4252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -4147,13 +4272,13 @@
         <v>442</v>
       </c>
       <c r="J18" t="s">
-        <v>635</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>790</v>
+        <v>633</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>788</v>
       </c>
       <c r="R18" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S18">
         <v>111</v>
@@ -4165,7 +4290,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -4185,13 +4310,13 @@
         <v>443</v>
       </c>
       <c r="J19" t="s">
-        <v>636</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>791</v>
+        <v>634</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>789</v>
       </c>
       <c r="R19" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S19">
         <v>124</v>
@@ -4203,7 +4328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -4223,13 +4348,13 @@
         <v>444</v>
       </c>
       <c r="J20" t="s">
-        <v>637</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>792</v>
+        <v>635</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>790</v>
       </c>
       <c r="R20" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S20">
         <v>84</v>
@@ -4241,7 +4366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -4261,13 +4386,13 @@
         <v>445</v>
       </c>
       <c r="J21" t="s">
-        <v>638</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>793</v>
+        <v>636</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>791</v>
       </c>
       <c r="R21" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S21">
         <v>112</v>
@@ -4279,7 +4404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -4298,11 +4423,11 @@
       <c r="I22" t="s">
         <v>446</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>794</v>
+      <c r="K22" s="3" t="s">
+        <v>792</v>
       </c>
       <c r="R22" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S22">
         <v>202</v>
@@ -4314,7 +4439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -4334,13 +4459,13 @@
         <v>447</v>
       </c>
       <c r="J23" t="s">
-        <v>639</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>795</v>
+        <v>637</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>793</v>
       </c>
       <c r="R23" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S23">
         <v>146</v>
@@ -4352,7 +4477,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -4372,13 +4497,13 @@
         <v>448</v>
       </c>
       <c r="J24" t="s">
-        <v>640</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>796</v>
+        <v>638</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>794</v>
       </c>
       <c r="R24" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S24">
         <v>115</v>
@@ -4390,7 +4515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -4409,11 +4534,11 @@
       <c r="I25" t="s">
         <v>449</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>797</v>
+      <c r="K25" s="3" t="s">
+        <v>795</v>
       </c>
       <c r="R25" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S25">
         <v>117</v>
@@ -4425,7 +4550,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -4445,13 +4570,13 @@
         <v>450</v>
       </c>
       <c r="J26" t="s">
-        <v>641</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>798</v>
+        <v>639</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>796</v>
       </c>
       <c r="R26" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="S26">
         <v>42</v>
@@ -4463,7 +4588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -4483,13 +4608,13 @@
         <v>451</v>
       </c>
       <c r="J27" t="s">
-        <v>642</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>799</v>
+        <v>640</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>797</v>
       </c>
       <c r="R27" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S27">
         <v>158</v>
@@ -4501,7 +4626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -4521,13 +4646,13 @@
         <v>452</v>
       </c>
       <c r="J28" t="s">
-        <v>643</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>800</v>
+        <v>641</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>798</v>
       </c>
       <c r="R28" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="S28">
         <v>28</v>
@@ -4539,7 +4664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -4559,13 +4684,13 @@
         <v>453</v>
       </c>
       <c r="J29" t="s">
-        <v>644</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>801</v>
+        <v>642</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>799</v>
       </c>
       <c r="R29" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S29">
         <v>57</v>
@@ -4577,7 +4702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -4593,20 +4718,20 @@
       <c r="E30" t="s">
         <v>352</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="2" t="s">
         <v>423</v>
       </c>
       <c r="I30" t="s">
         <v>454</v>
       </c>
       <c r="J30" t="s">
-        <v>645</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>802</v>
+        <v>643</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>800</v>
       </c>
       <c r="R30" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S30">
         <v>72</v>
@@ -4618,7 +4743,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -4638,13 +4763,13 @@
         <v>455</v>
       </c>
       <c r="J31" t="s">
-        <v>646</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>803</v>
+        <v>644</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>801</v>
       </c>
       <c r="R31" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S31">
         <v>66</v>
@@ -4656,7 +4781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -4676,13 +4801,13 @@
         <v>456</v>
       </c>
       <c r="J32" t="s">
-        <v>647</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>804</v>
+        <v>645</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>802</v>
       </c>
       <c r="R32" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S32">
         <v>157</v>
@@ -4694,7 +4819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -4714,13 +4839,13 @@
         <v>457</v>
       </c>
       <c r="J33" t="s">
-        <v>648</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>805</v>
+        <v>646</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>803</v>
       </c>
       <c r="R33" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S33">
         <v>88</v>
@@ -4732,7 +4857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -4752,19 +4877,19 @@
         <v>458</v>
       </c>
       <c r="J34" t="s">
-        <v>649</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>806</v>
+        <v>647</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>804</v>
       </c>
       <c r="L34" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="R34" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S34">
         <v>76</v>
@@ -4776,7 +4901,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -4796,19 +4921,19 @@
         <v>459</v>
       </c>
       <c r="J35" t="s">
-        <v>650</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>807</v>
+        <v>648</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>805</v>
       </c>
       <c r="L35" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="R35" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S35">
         <v>76</v>
@@ -4820,7 +4945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -4840,19 +4965,19 @@
         <v>460</v>
       </c>
       <c r="J36" t="s">
-        <v>651</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>808</v>
+        <v>649</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>806</v>
       </c>
       <c r="L36" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="R36" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S36">
         <v>76</v>
@@ -4864,7 +4989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -4884,19 +5009,19 @@
         <v>461</v>
       </c>
       <c r="J37" t="s">
-        <v>652</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>809</v>
+        <v>650</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>807</v>
       </c>
       <c r="L37" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="R37" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S37">
         <v>76</v>
@@ -4908,7 +5033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -4928,19 +5053,19 @@
         <v>462</v>
       </c>
       <c r="J38" t="s">
-        <v>653</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>810</v>
+        <v>651</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>808</v>
       </c>
       <c r="L38" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="R38" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S38">
         <v>67</v>
@@ -4952,7 +5077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -4972,19 +5097,19 @@
         <v>463</v>
       </c>
       <c r="J39" t="s">
-        <v>654</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>811</v>
+        <v>652</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>809</v>
       </c>
       <c r="L39" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="R39" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S39">
         <v>67</v>
@@ -4996,7 +5121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>28</v>
       </c>
@@ -5016,19 +5141,19 @@
         <v>464</v>
       </c>
       <c r="J40" t="s">
-        <v>655</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>812</v>
+        <v>653</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>810</v>
       </c>
       <c r="L40" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="R40" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S40">
         <v>64</v>
@@ -5040,7 +5165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -5060,19 +5185,19 @@
         <v>465</v>
       </c>
       <c r="J41" t="s">
-        <v>656</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>813</v>
+        <v>654</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>811</v>
       </c>
       <c r="L41" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="R41" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S41">
         <v>74</v>
@@ -5084,7 +5209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -5104,19 +5229,19 @@
         <v>466</v>
       </c>
       <c r="J42" t="s">
-        <v>657</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>814</v>
+        <v>655</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>812</v>
       </c>
       <c r="L42" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="R42" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S42">
         <v>48</v>
@@ -5128,7 +5253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -5148,19 +5273,19 @@
         <v>467</v>
       </c>
       <c r="J43" t="s">
-        <v>658</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>815</v>
+        <v>656</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>813</v>
       </c>
       <c r="L43" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="R43" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S43">
         <v>151</v>
@@ -5172,7 +5297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>29</v>
       </c>
@@ -5192,22 +5317,22 @@
         <v>468</v>
       </c>
       <c r="J44" t="s">
-        <v>659</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>816</v>
+        <v>657</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>814</v>
       </c>
       <c r="L44" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="O44" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="R44" t="s">
         <v>993</v>
-      </c>
-      <c r="R44" t="s">
-        <v>995</v>
       </c>
       <c r="S44">
         <v>270</v>
@@ -5219,7 +5344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -5239,13 +5364,13 @@
         <v>469</v>
       </c>
       <c r="J45" t="s">
-        <v>660</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>817</v>
+        <v>658</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>815</v>
       </c>
       <c r="R45" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="S45">
         <v>31</v>
@@ -5257,7 +5382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>30</v>
       </c>
@@ -5277,13 +5402,13 @@
         <v>470</v>
       </c>
       <c r="J46" t="s">
-        <v>661</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>818</v>
+        <v>659</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>816</v>
       </c>
       <c r="R46" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S46">
         <v>83</v>
@@ -5295,7 +5420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>30</v>
       </c>
@@ -5315,13 +5440,13 @@
         <v>471</v>
       </c>
       <c r="J47" t="s">
-        <v>662</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>819</v>
+        <v>660</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>817</v>
       </c>
       <c r="R47" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S47">
         <v>124</v>
@@ -5333,7 +5458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -5353,13 +5478,13 @@
         <v>472</v>
       </c>
       <c r="J48" t="s">
-        <v>663</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>820</v>
+        <v>661</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>818</v>
       </c>
       <c r="R48" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S48">
         <v>109</v>
@@ -5371,7 +5496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>30</v>
       </c>
@@ -5391,13 +5516,13 @@
         <v>473</v>
       </c>
       <c r="J49" t="s">
-        <v>664</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>821</v>
+        <v>662</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>819</v>
       </c>
       <c r="R49" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S49">
         <v>200</v>
@@ -5409,7 +5534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -5429,13 +5554,13 @@
         <v>474</v>
       </c>
       <c r="J50" t="s">
-        <v>665</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>822</v>
+        <v>663</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>820</v>
       </c>
       <c r="R50" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S50">
         <v>105</v>
@@ -5447,7 +5572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>30</v>
       </c>
@@ -5467,13 +5592,13 @@
         <v>475</v>
       </c>
       <c r="J51" t="s">
-        <v>666</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>823</v>
+        <v>664</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>821</v>
       </c>
       <c r="R51" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S51">
         <v>48</v>
@@ -5485,7 +5610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>30</v>
       </c>
@@ -5505,13 +5630,13 @@
         <v>476</v>
       </c>
       <c r="J52" t="s">
-        <v>667</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>824</v>
+        <v>665</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>822</v>
       </c>
       <c r="R52" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S52">
         <v>58</v>
@@ -5523,7 +5648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>31</v>
       </c>
@@ -5543,13 +5668,13 @@
         <v>477</v>
       </c>
       <c r="J53" t="s">
-        <v>668</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>825</v>
+        <v>666</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>823</v>
       </c>
       <c r="R53" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S53">
         <v>412</v>
@@ -5561,7 +5686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>31</v>
       </c>
@@ -5581,13 +5706,13 @@
         <v>478</v>
       </c>
       <c r="J54" t="s">
-        <v>669</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>826</v>
+        <v>667</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>824</v>
       </c>
       <c r="R54" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S54">
         <v>359</v>
@@ -5599,7 +5724,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>31</v>
       </c>
@@ -5619,13 +5744,13 @@
         <v>479</v>
       </c>
       <c r="J55" t="s">
-        <v>670</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>827</v>
+        <v>668</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>825</v>
       </c>
       <c r="R55" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S55">
         <v>179</v>
@@ -5637,7 +5762,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -5657,13 +5782,13 @@
         <v>480</v>
       </c>
       <c r="J56" t="s">
-        <v>671</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>828</v>
+        <v>669</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>826</v>
       </c>
       <c r="R56" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S56">
         <v>134</v>
@@ -5675,7 +5800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>32</v>
       </c>
@@ -5695,13 +5820,13 @@
         <v>481</v>
       </c>
       <c r="J57" t="s">
-        <v>672</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>829</v>
+        <v>670</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>827</v>
       </c>
       <c r="R57" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S57">
         <v>183</v>
@@ -5713,7 +5838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -5733,13 +5858,13 @@
         <v>482</v>
       </c>
       <c r="J58" t="s">
-        <v>673</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>830</v>
+        <v>671</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>828</v>
       </c>
       <c r="R58" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S58">
         <v>168</v>
@@ -5751,7 +5876,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -5771,13 +5896,13 @@
         <v>483</v>
       </c>
       <c r="J59" t="s">
-        <v>674</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>831</v>
+        <v>672</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>829</v>
       </c>
       <c r="R59" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S59">
         <v>102</v>
@@ -5789,7 +5914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>32</v>
       </c>
@@ -5809,13 +5934,13 @@
         <v>484</v>
       </c>
       <c r="J60" t="s">
-        <v>675</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>832</v>
+        <v>673</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>830</v>
       </c>
       <c r="R60" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S60">
         <v>123</v>
@@ -5827,7 +5952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>33</v>
       </c>
@@ -5847,13 +5972,13 @@
         <v>485</v>
       </c>
       <c r="J61" t="s">
-        <v>676</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>833</v>
+        <v>674</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>831</v>
       </c>
       <c r="R61" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S61">
         <v>60</v>
@@ -5865,7 +5990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>33</v>
       </c>
@@ -5885,13 +6010,13 @@
         <v>486</v>
       </c>
       <c r="J62" t="s">
-        <v>677</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>834</v>
+        <v>675</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>832</v>
       </c>
       <c r="R62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S62">
         <v>206</v>
@@ -5903,7 +6028,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>33</v>
       </c>
@@ -5923,13 +6048,13 @@
         <v>487</v>
       </c>
       <c r="J63" t="s">
-        <v>678</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>835</v>
+        <v>676</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>833</v>
       </c>
       <c r="R63" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="S63">
         <v>370</v>
@@ -5941,7 +6066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>33</v>
       </c>
@@ -5958,19 +6083,19 @@
         <v>488</v>
       </c>
       <c r="J64" t="s">
-        <v>679</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>836</v>
+        <v>677</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>834</v>
       </c>
       <c r="L64" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="R64" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="S64">
         <v>300</v>
@@ -5982,7 +6107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:22">
+    <row r="65" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>34</v>
       </c>
@@ -6002,13 +6127,13 @@
         <v>489</v>
       </c>
       <c r="J65" t="s">
-        <v>680</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>837</v>
+        <v>678</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>835</v>
       </c>
       <c r="R65" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S65">
         <v>61</v>
@@ -6020,7 +6145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:22">
+    <row r="66" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>34</v>
       </c>
@@ -6040,13 +6165,13 @@
         <v>490</v>
       </c>
       <c r="J66" t="s">
-        <v>681</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>838</v>
+        <v>679</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>836</v>
       </c>
       <c r="R66" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S66">
         <v>347</v>
@@ -6058,7 +6183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:22">
+    <row r="67" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>34</v>
       </c>
@@ -6074,32 +6199,32 @@
       <c r="E67" t="s">
         <v>369</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G67" s="2" t="s">
         <v>424</v>
       </c>
       <c r="I67" t="s">
         <v>491</v>
       </c>
       <c r="J67" t="s">
-        <v>682</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>839</v>
+        <v>680</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>837</v>
       </c>
       <c r="L67" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="R67" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="V67">
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:22">
+    <row r="68" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>34</v>
       </c>
@@ -6119,13 +6244,13 @@
         <v>492</v>
       </c>
       <c r="J68" t="s">
-        <v>683</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>840</v>
+        <v>681</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>838</v>
       </c>
       <c r="R68" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S68">
         <v>398</v>
@@ -6137,7 +6262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:22">
+    <row r="69" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>35</v>
       </c>
@@ -6156,11 +6281,11 @@
       <c r="I69" t="s">
         <v>493</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>841</v>
+      <c r="K69" s="3" t="s">
+        <v>839</v>
       </c>
       <c r="R69" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="S69">
         <v>323</v>
@@ -6172,7 +6297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:22">
+    <row r="70" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>35</v>
       </c>
@@ -6188,11 +6313,11 @@
       <c r="I70" t="s">
         <v>494</v>
       </c>
-      <c r="K70" s="1" t="s">
-        <v>842</v>
+      <c r="K70" s="3" t="s">
+        <v>840</v>
       </c>
       <c r="R70" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S70">
         <v>347</v>
@@ -6204,7 +6329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:22">
+    <row r="71" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>36</v>
       </c>
@@ -6224,13 +6349,13 @@
         <v>495</v>
       </c>
       <c r="J71" t="s">
-        <v>684</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>843</v>
+        <v>682</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>841</v>
       </c>
       <c r="R71" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="S71">
         <v>67</v>
@@ -6242,7 +6367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:22">
+    <row r="72" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>36</v>
       </c>
@@ -6261,11 +6386,11 @@
       <c r="I72" t="s">
         <v>496</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>844</v>
+      <c r="K72" s="3" t="s">
+        <v>842</v>
       </c>
       <c r="R72" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="S72">
         <v>62</v>
@@ -6277,7 +6402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:22">
+    <row r="73" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>36</v>
       </c>
@@ -6297,13 +6422,13 @@
         <v>497</v>
       </c>
       <c r="J73" t="s">
-        <v>685</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>845</v>
+        <v>683</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>843</v>
       </c>
       <c r="R73" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S73">
         <v>170</v>
@@ -6315,7 +6440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:22">
+    <row r="74" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>37</v>
       </c>
@@ -6335,13 +6460,13 @@
         <v>498</v>
       </c>
       <c r="J74" t="s">
-        <v>686</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>846</v>
+        <v>684</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>844</v>
       </c>
       <c r="R74" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S74">
         <v>88</v>
@@ -6353,7 +6478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:22">
+    <row r="75" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>37</v>
       </c>
@@ -6373,13 +6498,13 @@
         <v>489</v>
       </c>
       <c r="J75" t="s">
-        <v>680</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>847</v>
+        <v>678</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>845</v>
       </c>
       <c r="R75" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S75">
         <v>89</v>
@@ -6391,7 +6516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:22">
+    <row r="76" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>38</v>
       </c>
@@ -6411,13 +6536,13 @@
         <v>499</v>
       </c>
       <c r="J76" t="s">
-        <v>687</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>848</v>
+        <v>685</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>846</v>
       </c>
       <c r="R76" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S76">
         <v>158</v>
@@ -6429,7 +6554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:22">
+    <row r="77" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>38</v>
       </c>
@@ -6449,13 +6574,13 @@
         <v>500</v>
       </c>
       <c r="J77" t="s">
-        <v>688</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>849</v>
+        <v>686</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>847</v>
       </c>
       <c r="R77" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S77">
         <v>158</v>
@@ -6467,7 +6592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:22">
+    <row r="78" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>38</v>
       </c>
@@ -6487,13 +6612,13 @@
         <v>501</v>
       </c>
       <c r="J78" t="s">
-        <v>689</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>850</v>
+        <v>687</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>848</v>
       </c>
       <c r="R78" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S78">
         <v>158</v>
@@ -6505,7 +6630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:22">
+    <row r="79" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>38</v>
       </c>
@@ -6525,13 +6650,13 @@
         <v>502</v>
       </c>
       <c r="J79" t="s">
-        <v>690</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>851</v>
+        <v>688</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>849</v>
       </c>
       <c r="R79" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S79">
         <v>158</v>
@@ -6543,7 +6668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:22">
+    <row r="80" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>39</v>
       </c>
@@ -6563,13 +6688,13 @@
         <v>503</v>
       </c>
       <c r="J80" t="s">
-        <v>691</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>852</v>
+        <v>689</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>850</v>
       </c>
       <c r="R80" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S80">
         <v>370</v>
@@ -6581,7 +6706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:22">
+    <row r="81" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>39</v>
       </c>
@@ -6601,13 +6726,13 @@
         <v>504</v>
       </c>
       <c r="J81" t="s">
-        <v>692</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>853</v>
+        <v>690</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>851</v>
       </c>
       <c r="R81" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S81">
         <v>234</v>
@@ -6619,7 +6744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:22">
+    <row r="82" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>39</v>
       </c>
@@ -6639,13 +6764,13 @@
         <v>505</v>
       </c>
       <c r="J82" t="s">
-        <v>693</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>854</v>
+        <v>691</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>852</v>
       </c>
       <c r="R82" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S82">
         <v>112</v>
@@ -6657,7 +6782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>39</v>
       </c>
@@ -6677,13 +6802,13 @@
         <v>506</v>
       </c>
       <c r="J83" t="s">
-        <v>694</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>855</v>
+        <v>692</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>853</v>
       </c>
       <c r="R83" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S83">
         <v>105</v>
@@ -6695,7 +6820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:22">
+    <row r="84" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>40</v>
       </c>
@@ -6715,13 +6840,13 @@
         <v>507</v>
       </c>
       <c r="J84" t="s">
-        <v>695</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>856</v>
+        <v>693</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>854</v>
       </c>
       <c r="R84" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="S84">
         <v>220</v>
@@ -6733,7 +6858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:22">
+    <row r="85" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>40</v>
       </c>
@@ -6753,13 +6878,13 @@
         <v>508</v>
       </c>
       <c r="J85" t="s">
-        <v>696</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>857</v>
+        <v>694</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>855</v>
       </c>
       <c r="R85" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="S85">
         <v>58</v>
@@ -6771,7 +6896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:22">
+    <row r="86" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>40</v>
       </c>
@@ -6791,13 +6916,13 @@
         <v>509</v>
       </c>
       <c r="J86" t="s">
-        <v>697</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>858</v>
+        <v>695</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>856</v>
       </c>
       <c r="R86" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="S86">
         <v>74</v>
@@ -6809,7 +6934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:22">
+    <row r="87" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>40</v>
       </c>
@@ -6829,13 +6954,13 @@
         <v>510</v>
       </c>
       <c r="J87" t="s">
-        <v>698</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>859</v>
+        <v>696</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>857</v>
       </c>
       <c r="R87" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="S87">
         <v>164</v>
@@ -6847,7 +6972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:22">
+    <row r="88" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>40</v>
       </c>
@@ -6867,13 +6992,13 @@
         <v>511</v>
       </c>
       <c r="J88" t="s">
-        <v>699</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>860</v>
+        <v>697</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>858</v>
       </c>
       <c r="R88" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="S88">
         <v>138</v>
@@ -6885,7 +7010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:22">
+    <row r="89" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>40</v>
       </c>
@@ -6904,11 +7029,11 @@
       <c r="I89" t="s">
         <v>512</v>
       </c>
-      <c r="K89" s="1" t="s">
-        <v>861</v>
+      <c r="K89" s="3" t="s">
+        <v>859</v>
       </c>
       <c r="R89" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="S89">
         <v>132</v>
@@ -6920,7 +7045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:22">
+    <row r="90" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>40</v>
       </c>
@@ -6939,11 +7064,11 @@
       <c r="I90" t="s">
         <v>513</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>862</v>
+      <c r="K90" s="3" t="s">
+        <v>860</v>
       </c>
       <c r="R90" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="S90">
         <v>135</v>
@@ -6955,7 +7080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:22">
+    <row r="91" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>40</v>
       </c>
@@ -6974,11 +7099,11 @@
       <c r="I91" t="s">
         <v>513</v>
       </c>
-      <c r="K91" s="1" t="s">
-        <v>863</v>
+      <c r="K91" s="3" t="s">
+        <v>861</v>
       </c>
       <c r="R91" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S91">
         <v>135</v>
@@ -6990,7 +7115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:22">
+    <row r="92" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>24</v>
       </c>
@@ -7010,25 +7135,25 @@
         <v>514</v>
       </c>
       <c r="J92" t="s">
-        <v>700</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>864</v>
+        <v>698</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>862</v>
       </c>
       <c r="R92" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S92">
         <v>60</v>
       </c>
       <c r="T92" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="V92">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:22">
+    <row r="93" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>24</v>
       </c>
@@ -7048,16 +7173,16 @@
         <v>515</v>
       </c>
       <c r="J93" t="s">
-        <v>701</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>865</v>
+        <v>699</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>863</v>
       </c>
       <c r="L93" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="R93" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S93">
         <v>117</v>
@@ -7069,7 +7194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:22">
+    <row r="94" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>24</v>
       </c>
@@ -7089,13 +7214,13 @@
         <v>516</v>
       </c>
       <c r="J94" t="s">
-        <v>702</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>866</v>
+        <v>700</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>864</v>
       </c>
       <c r="R94" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S94">
         <v>114</v>
@@ -7107,7 +7232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:22">
+    <row r="95" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>24</v>
       </c>
@@ -7127,13 +7252,13 @@
         <v>517</v>
       </c>
       <c r="J95" t="s">
-        <v>703</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>867</v>
+        <v>701</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>865</v>
       </c>
       <c r="R95" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S95">
         <v>118</v>
@@ -7145,7 +7270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:22">
+    <row r="96" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>24</v>
       </c>
@@ -7165,13 +7290,13 @@
         <v>518</v>
       </c>
       <c r="J96" t="s">
-        <v>704</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>868</v>
+        <v>702</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>866</v>
       </c>
       <c r="R96" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S96">
         <v>117</v>
@@ -7183,7 +7308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:22">
+    <row r="97" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>24</v>
       </c>
@@ -7203,13 +7328,13 @@
         <v>519</v>
       </c>
       <c r="J97" t="s">
-        <v>705</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>869</v>
+        <v>703</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>867</v>
       </c>
       <c r="R97" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S97">
         <v>118</v>
@@ -7221,7 +7346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:22">
+    <row r="98" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>24</v>
       </c>
@@ -7241,13 +7366,13 @@
         <v>490</v>
       </c>
       <c r="J98" t="s">
-        <v>706</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>870</v>
+        <v>704</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>868</v>
       </c>
       <c r="R98" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S98">
         <v>117</v>
@@ -7259,7 +7384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:22">
+    <row r="99" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>24</v>
       </c>
@@ -7279,13 +7404,13 @@
         <v>520</v>
       </c>
       <c r="J99" t="s">
-        <v>707</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>871</v>
+        <v>705</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>869</v>
       </c>
       <c r="R99" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S99">
         <v>117</v>
@@ -7297,7 +7422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:22">
+    <row r="100" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>24</v>
       </c>
@@ -7317,13 +7442,13 @@
         <v>481</v>
       </c>
       <c r="J100" t="s">
-        <v>708</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>872</v>
+        <v>706</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>870</v>
       </c>
       <c r="R100" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S100">
         <v>111</v>
@@ -7335,7 +7460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:22">
+    <row r="101" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>24</v>
       </c>
@@ -7355,13 +7480,13 @@
         <v>521</v>
       </c>
       <c r="J101" t="s">
-        <v>709</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>873</v>
+        <v>707</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>871</v>
       </c>
       <c r="R101" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S101">
         <v>114</v>
@@ -7373,7 +7498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:22">
+    <row r="102" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>24</v>
       </c>
@@ -7393,13 +7518,13 @@
         <v>522</v>
       </c>
       <c r="J102" t="s">
-        <v>710</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>874</v>
+        <v>708</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>872</v>
       </c>
       <c r="R102" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S102">
         <v>114</v>
@@ -7411,7 +7536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:22">
+    <row r="103" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>24</v>
       </c>
@@ -7431,25 +7556,25 @@
         <v>523</v>
       </c>
       <c r="J103" t="s">
-        <v>711</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>875</v>
+        <v>709</v>
+      </c>
+      <c r="K103" s="3" t="s">
+        <v>873</v>
       </c>
       <c r="R103" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S103" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="T103" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="V103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:22">
+    <row r="104" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>41</v>
       </c>
@@ -7469,13 +7594,13 @@
         <v>524</v>
       </c>
       <c r="J104" t="s">
-        <v>712</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>876</v>
+        <v>710</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>874</v>
       </c>
       <c r="R104" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="S104">
         <v>120</v>
@@ -7487,7 +7612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:22">
+    <row r="105" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>41</v>
       </c>
@@ -7507,19 +7632,19 @@
         <v>525</v>
       </c>
       <c r="J105" t="s">
-        <v>713</v>
-      </c>
-      <c r="K105" s="1" t="s">
-        <v>877</v>
+        <v>711</v>
+      </c>
+      <c r="K105" s="3" t="s">
+        <v>875</v>
       </c>
       <c r="R105" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="V105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:22">
+    <row r="106" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>41</v>
       </c>
@@ -7538,11 +7663,11 @@
       <c r="I106" t="s">
         <v>526</v>
       </c>
-      <c r="K106" s="1" t="s">
-        <v>878</v>
+      <c r="K106" s="3" t="s">
+        <v>876</v>
       </c>
       <c r="R106" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="S106">
         <v>280</v>
@@ -7554,7 +7679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:22">
+    <row r="107" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>41</v>
       </c>
@@ -7573,11 +7698,11 @@
       <c r="I107" t="s">
         <v>527</v>
       </c>
-      <c r="K107" s="1" t="s">
-        <v>879</v>
+      <c r="K107" s="3" t="s">
+        <v>877</v>
       </c>
       <c r="R107" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="S107">
         <v>1370</v>
@@ -7589,7 +7714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:22">
+    <row r="108" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>41</v>
       </c>
@@ -7609,13 +7734,13 @@
         <v>528</v>
       </c>
       <c r="J108" t="s">
-        <v>714</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>880</v>
+        <v>712</v>
+      </c>
+      <c r="K108" s="3" t="s">
+        <v>878</v>
       </c>
       <c r="R108" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="S108">
         <v>625</v>
@@ -7627,7 +7752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:22">
+    <row r="109" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>42</v>
       </c>
@@ -7647,13 +7772,13 @@
         <v>529</v>
       </c>
       <c r="J109" t="s">
-        <v>715</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>881</v>
+        <v>713</v>
+      </c>
+      <c r="K109" s="3" t="s">
+        <v>879</v>
       </c>
       <c r="R109" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S109">
         <v>185</v>
@@ -7665,7 +7790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:22">
+    <row r="110" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>42</v>
       </c>
@@ -7685,13 +7810,13 @@
         <v>530</v>
       </c>
       <c r="J110" t="s">
-        <v>716</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>882</v>
+        <v>714</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>880</v>
       </c>
       <c r="R110" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S110">
         <v>245</v>
@@ -7703,7 +7828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:22">
+    <row r="111" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>42</v>
       </c>
@@ -7723,13 +7848,13 @@
         <v>531</v>
       </c>
       <c r="J111" t="s">
-        <v>717</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>883</v>
+        <v>715</v>
+      </c>
+      <c r="K111" s="3" t="s">
+        <v>881</v>
       </c>
       <c r="R111" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S111">
         <v>120</v>
@@ -7741,7 +7866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:22">
+    <row r="112" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>43</v>
       </c>
@@ -7761,13 +7886,13 @@
         <v>532</v>
       </c>
       <c r="J112" t="s">
-        <v>718</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>884</v>
+        <v>716</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>882</v>
       </c>
       <c r="R112" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S112">
         <v>92</v>
@@ -7779,7 +7904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:22">
+    <row r="113" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>43</v>
       </c>
@@ -7801,11 +7926,11 @@
       <c r="J113" t="s">
         <v>533</v>
       </c>
-      <c r="K113" s="1" t="s">
-        <v>885</v>
+      <c r="K113" s="3" t="s">
+        <v>883</v>
       </c>
       <c r="R113" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S113">
         <v>133</v>
@@ -7817,7 +7942,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:22">
+    <row r="114" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>43</v>
       </c>
@@ -7839,11 +7964,11 @@
       <c r="J114" t="s">
         <v>534</v>
       </c>
-      <c r="K114" s="1" t="s">
-        <v>886</v>
+      <c r="K114" s="3" t="s">
+        <v>884</v>
       </c>
       <c r="R114" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S114">
         <v>91</v>
@@ -7855,7 +7980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:22">
+    <row r="115" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>43</v>
       </c>
@@ -7875,13 +8000,13 @@
         <v>535</v>
       </c>
       <c r="J115" t="s">
-        <v>719</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>887</v>
+        <v>717</v>
+      </c>
+      <c r="K115" s="3" t="s">
+        <v>885</v>
       </c>
       <c r="R115" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S115">
         <v>35</v>
@@ -7893,7 +8018,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:22">
+    <row r="116" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>44</v>
       </c>
@@ -7907,16 +8032,19 @@
         <v>39</v>
       </c>
       <c r="E116" t="s">
+        <v>39</v>
+      </c>
+      <c r="F116" t="s">
         <v>355</v>
       </c>
       <c r="I116" t="s">
-        <v>536</v>
+        <v>1028</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="R116" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S116">
         <v>96</v>
@@ -7928,7 +8056,94 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:22">
+    <row r="117" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C117" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E117" t="s">
+        <v>289</v>
+      </c>
+      <c r="F117" t="s">
+        <v>340</v>
+      </c>
+      <c r="I117" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="R117" t="s">
+        <v>993</v>
+      </c>
+      <c r="S117">
+        <v>40</v>
+      </c>
+      <c r="T117">
+        <v>34</v>
+      </c>
+      <c r="V117">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C118" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E118" t="s">
+        <v>310</v>
+      </c>
+      <c r="F118" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I118" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="R118" t="s">
+        <v>993</v>
+      </c>
+      <c r="S118">
+        <v>36</v>
+      </c>
+      <c r="T118">
+        <v>29</v>
+      </c>
+      <c r="V118">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C119" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E119" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F119" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I119" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="R119" t="s">
+        <v>993</v>
+      </c>
+      <c r="S119">
+        <v>38</v>
+      </c>
+      <c r="T119">
+        <v>33</v>
+      </c>
+      <c r="V119">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>44</v>
       </c>
@@ -7944,14 +8159,15 @@
       <c r="E120" t="s">
         <v>355</v>
       </c>
+      <c r="G120"/>
       <c r="I120" t="s">
-        <v>537</v>
-      </c>
-      <c r="K120" s="1" t="s">
-        <v>889</v>
+        <v>1041</v>
+      </c>
+      <c r="K120" s="4" t="s">
+        <v>887</v>
       </c>
       <c r="R120" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S120">
         <v>97</v>
@@ -7963,7 +8179,118 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:22">
+    <row r="121" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>44</v>
+      </c>
+      <c r="B121" t="s">
+        <v>100</v>
+      </c>
+      <c r="C121">
+        <v>1540</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E121" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G121"/>
+      <c r="I121" t="s">
+        <v>1044</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="R121" t="s">
+        <v>993</v>
+      </c>
+      <c r="S121">
+        <v>100</v>
+      </c>
+      <c r="T121">
+        <v>81</v>
+      </c>
+      <c r="V121">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>44</v>
+      </c>
+      <c r="B122" t="s">
+        <v>100</v>
+      </c>
+      <c r="C122" t="s">
+        <v>169</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E122" t="s">
+        <v>380</v>
+      </c>
+      <c r="G122"/>
+      <c r="I122" t="s">
+        <v>1047</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="R122" t="s">
+        <v>993</v>
+      </c>
+      <c r="S122">
+        <v>88</v>
+      </c>
+      <c r="T122">
+        <v>140</v>
+      </c>
+      <c r="V122">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>44</v>
+      </c>
+      <c r="B123" t="s">
+        <v>100</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D123" t="s">
+        <v>322</v>
+      </c>
+      <c r="E123" t="s">
+        <v>381</v>
+      </c>
+      <c r="G123"/>
+      <c r="I123" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L123" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R123" t="s">
+        <v>1053</v>
+      </c>
+      <c r="S123">
+        <v>21</v>
+      </c>
+      <c r="T123">
+        <v>14</v>
+      </c>
+      <c r="V123">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>45</v>
       </c>
@@ -7980,13 +8307,13 @@
         <v>382</v>
       </c>
       <c r="I124" t="s">
-        <v>538</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>890</v>
+        <v>536</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>888</v>
       </c>
       <c r="R124" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S124">
         <v>117</v>
@@ -7998,7 +8325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:22">
+    <row r="128" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>45</v>
       </c>
@@ -8015,16 +8342,16 @@
         <v>383</v>
       </c>
       <c r="I128" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="J128" t="s">
-        <v>720</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>891</v>
+        <v>718</v>
+      </c>
+      <c r="K128" s="3" t="s">
+        <v>889</v>
       </c>
       <c r="R128" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S128">
         <v>127</v>
@@ -8036,7 +8363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:22">
+    <row r="132" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>46</v>
       </c>
@@ -8053,19 +8380,19 @@
         <v>362</v>
       </c>
       <c r="I132" t="s">
-        <v>540</v>
-      </c>
-      <c r="K132" s="1" t="s">
-        <v>892</v>
+        <v>538</v>
+      </c>
+      <c r="K132" s="3" t="s">
+        <v>890</v>
       </c>
       <c r="R132" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="V132">
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:22">
+    <row r="133" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>46</v>
       </c>
@@ -8082,16 +8409,16 @@
         <v>345</v>
       </c>
       <c r="I133" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J133" t="s">
-        <v>721</v>
-      </c>
-      <c r="K133" s="1" t="s">
-        <v>893</v>
+        <v>719</v>
+      </c>
+      <c r="K133" s="3" t="s">
+        <v>891</v>
       </c>
       <c r="R133" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S133">
         <v>156</v>
@@ -8103,7 +8430,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:22">
+    <row r="136" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>47</v>
       </c>
@@ -8120,16 +8447,16 @@
         <v>384</v>
       </c>
       <c r="I136" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J136" t="s">
-        <v>722</v>
-      </c>
-      <c r="K136" s="1" t="s">
-        <v>894</v>
+        <v>720</v>
+      </c>
+      <c r="K136" s="3" t="s">
+        <v>892</v>
       </c>
       <c r="R136" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S136">
         <v>260</v>
@@ -8141,7 +8468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:22">
+    <row r="140" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>48</v>
       </c>
@@ -8158,13 +8485,13 @@
         <v>343</v>
       </c>
       <c r="I140" t="s">
-        <v>543</v>
-      </c>
-      <c r="K140" s="1" t="s">
-        <v>895</v>
+        <v>541</v>
+      </c>
+      <c r="K140" s="3" t="s">
+        <v>893</v>
       </c>
       <c r="R140" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S140">
         <v>106</v>
@@ -8176,7 +8503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:22">
+    <row r="141" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>48</v>
       </c>
@@ -8193,13 +8520,13 @@
         <v>385</v>
       </c>
       <c r="I141" t="s">
-        <v>544</v>
-      </c>
-      <c r="K141" s="1" t="s">
-        <v>896</v>
+        <v>542</v>
+      </c>
+      <c r="K141" s="3" t="s">
+        <v>894</v>
       </c>
       <c r="R141" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="S141">
         <v>132</v>
@@ -8211,7 +8538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:22">
+    <row r="142" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>48</v>
       </c>
@@ -8228,13 +8555,13 @@
         <v>340</v>
       </c>
       <c r="I142" t="s">
-        <v>545</v>
-      </c>
-      <c r="K142" s="1" t="s">
-        <v>897</v>
+        <v>543</v>
+      </c>
+      <c r="K142" s="3" t="s">
+        <v>895</v>
       </c>
       <c r="R142" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S142">
         <v>79</v>
@@ -8246,7 +8573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:22">
+    <row r="143" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>48</v>
       </c>
@@ -8263,13 +8590,13 @@
         <v>380</v>
       </c>
       <c r="I143" t="s">
-        <v>546</v>
-      </c>
-      <c r="K143" s="1" t="s">
-        <v>898</v>
+        <v>544</v>
+      </c>
+      <c r="K143" s="3" t="s">
+        <v>896</v>
       </c>
       <c r="R143" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S143">
         <v>118</v>
@@ -8281,7 +8608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:22">
+    <row r="144" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>48</v>
       </c>
@@ -8298,13 +8625,13 @@
         <v>342</v>
       </c>
       <c r="I144" t="s">
-        <v>547</v>
-      </c>
-      <c r="K144" s="1" t="s">
-        <v>899</v>
+        <v>545</v>
+      </c>
+      <c r="K144" s="3" t="s">
+        <v>897</v>
       </c>
       <c r="R144" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S144">
         <v>42</v>
@@ -8316,7 +8643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:22">
+    <row r="145" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>48</v>
       </c>
@@ -8333,13 +8660,13 @@
         <v>343</v>
       </c>
       <c r="I145" t="s">
-        <v>548</v>
-      </c>
-      <c r="K145" s="1" t="s">
-        <v>900</v>
+        <v>546</v>
+      </c>
+      <c r="K145" s="3" t="s">
+        <v>898</v>
       </c>
       <c r="R145" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S145">
         <v>60</v>
@@ -8351,7 +8678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:22">
+    <row r="149" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>49</v>
       </c>
@@ -8368,16 +8695,16 @@
         <v>337</v>
       </c>
       <c r="I149" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="J149" t="s">
-        <v>723</v>
-      </c>
-      <c r="K149" s="1" t="s">
-        <v>901</v>
+        <v>721</v>
+      </c>
+      <c r="K149" s="3" t="s">
+        <v>899</v>
       </c>
       <c r="R149" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S149">
         <v>381</v>
@@ -8389,7 +8716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:22">
+    <row r="153" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>50</v>
       </c>
@@ -8406,16 +8733,16 @@
         <v>386</v>
       </c>
       <c r="I153" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="J153" t="s">
-        <v>724</v>
-      </c>
-      <c r="K153" s="1" t="s">
-        <v>902</v>
+        <v>722</v>
+      </c>
+      <c r="K153" s="3" t="s">
+        <v>900</v>
       </c>
       <c r="R153" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S153">
         <v>210</v>
@@ -8427,7 +8754,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:22">
+    <row r="157" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>51</v>
       </c>
@@ -8441,13 +8768,13 @@
         <v>387</v>
       </c>
       <c r="I157" t="s">
-        <v>551</v>
-      </c>
-      <c r="K157" s="1" t="s">
-        <v>903</v>
+        <v>549</v>
+      </c>
+      <c r="K157" s="3" t="s">
+        <v>901</v>
       </c>
       <c r="R157" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S157">
         <v>48</v>
@@ -8459,7 +8786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:22">
+    <row r="158" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>51</v>
       </c>
@@ -8476,13 +8803,13 @@
         <v>355</v>
       </c>
       <c r="I158" t="s">
-        <v>552</v>
-      </c>
-      <c r="K158" s="1" t="s">
-        <v>904</v>
+        <v>550</v>
+      </c>
+      <c r="K158" s="3" t="s">
+        <v>902</v>
       </c>
       <c r="R158" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="S158">
         <v>77</v>
@@ -8494,7 +8821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:22">
+    <row r="159" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>51</v>
       </c>
@@ -8511,13 +8838,13 @@
         <v>355</v>
       </c>
       <c r="I159" t="s">
-        <v>553</v>
-      </c>
-      <c r="K159" s="1" t="s">
-        <v>905</v>
+        <v>551</v>
+      </c>
+      <c r="K159" s="3" t="s">
+        <v>903</v>
       </c>
       <c r="R159" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S159">
         <v>168</v>
@@ -8529,7 +8856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:22">
+    <row r="160" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>51</v>
       </c>
@@ -8545,20 +8872,20 @@
       <c r="E160" t="s">
         <v>388</v>
       </c>
-      <c r="G160" t="s">
+      <c r="G160" s="2" t="s">
         <v>425</v>
       </c>
       <c r="I160" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="J160" t="s">
-        <v>725</v>
-      </c>
-      <c r="K160" s="1" t="s">
-        <v>906</v>
+        <v>723</v>
+      </c>
+      <c r="K160" s="3" t="s">
+        <v>904</v>
       </c>
       <c r="R160" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="S160">
         <v>25</v>
@@ -8570,7 +8897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:22">
+    <row r="161" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>51</v>
       </c>
@@ -8587,13 +8914,13 @@
         <v>355</v>
       </c>
       <c r="I161" t="s">
-        <v>555</v>
-      </c>
-      <c r="K161" s="1" t="s">
-        <v>907</v>
+        <v>553</v>
+      </c>
+      <c r="K161" s="3" t="s">
+        <v>905</v>
       </c>
       <c r="R161" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S161">
         <v>69</v>
@@ -8605,7 +8932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:22">
+    <row r="163" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>52</v>
       </c>
@@ -8622,16 +8949,16 @@
         <v>343</v>
       </c>
       <c r="I163" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="J163" t="s">
-        <v>723</v>
-      </c>
-      <c r="K163" s="1" t="s">
-        <v>908</v>
+        <v>721</v>
+      </c>
+      <c r="K163" s="3" t="s">
+        <v>906</v>
       </c>
       <c r="R163" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S163">
         <v>381</v>
@@ -8643,7 +8970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:22">
+    <row r="167" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>53</v>
       </c>
@@ -8660,16 +8987,16 @@
         <v>350</v>
       </c>
       <c r="I167" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="J167" t="s">
-        <v>726</v>
-      </c>
-      <c r="K167" s="1" t="s">
-        <v>909</v>
+        <v>724</v>
+      </c>
+      <c r="K167" s="3" t="s">
+        <v>907</v>
       </c>
       <c r="R167" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S167">
         <v>207</v>
@@ -8681,7 +9008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:22">
+    <row r="171" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>54</v>
       </c>
@@ -8698,19 +9025,19 @@
         <v>389</v>
       </c>
       <c r="I171" t="s">
-        <v>557</v>
-      </c>
-      <c r="K171" s="1" t="s">
-        <v>910</v>
+        <v>555</v>
+      </c>
+      <c r="K171" s="3" t="s">
+        <v>908</v>
       </c>
       <c r="R171" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="V171">
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:22">
+    <row r="175" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>55</v>
       </c>
@@ -8727,16 +9054,16 @@
         <v>390</v>
       </c>
       <c r="I175" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J175" t="s">
-        <v>722</v>
-      </c>
-      <c r="K175" s="1" t="s">
-        <v>911</v>
+        <v>720</v>
+      </c>
+      <c r="K175" s="3" t="s">
+        <v>909</v>
       </c>
       <c r="R175" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S175">
         <v>375</v>
@@ -8748,7 +9075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:22">
+    <row r="179" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>26</v>
       </c>
@@ -8765,16 +9092,16 @@
         <v>338</v>
       </c>
       <c r="I179" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="J179" t="s">
-        <v>727</v>
-      </c>
-      <c r="K179" s="1" t="s">
-        <v>912</v>
+        <v>725</v>
+      </c>
+      <c r="K179" s="3" t="s">
+        <v>910</v>
       </c>
       <c r="R179" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="S179">
         <v>67</v>
@@ -8786,7 +9113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:22">
+    <row r="180" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>26</v>
       </c>
@@ -8803,13 +9130,13 @@
         <v>391</v>
       </c>
       <c r="I180" t="s">
-        <v>548</v>
-      </c>
-      <c r="K180" s="1" t="s">
-        <v>913</v>
+        <v>546</v>
+      </c>
+      <c r="K180" s="3" t="s">
+        <v>911</v>
       </c>
       <c r="R180" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="S180">
         <v>100</v>
@@ -8821,7 +9148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:22">
+    <row r="181" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>26</v>
       </c>
@@ -8838,16 +9165,16 @@
         <v>392</v>
       </c>
       <c r="I181" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="J181" t="s">
-        <v>728</v>
-      </c>
-      <c r="K181" s="1" t="s">
-        <v>914</v>
+        <v>726</v>
+      </c>
+      <c r="K181" s="3" t="s">
+        <v>912</v>
       </c>
       <c r="R181" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="S181">
         <v>162</v>
@@ -8859,7 +9186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:22">
+    <row r="182" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>26</v>
       </c>
@@ -8876,16 +9203,16 @@
         <v>393</v>
       </c>
       <c r="I182" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="J182" t="s">
-        <v>729</v>
-      </c>
-      <c r="K182" s="1" t="s">
-        <v>915</v>
+        <v>727</v>
+      </c>
+      <c r="K182" s="3" t="s">
+        <v>913</v>
       </c>
       <c r="R182" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="S182">
         <v>65</v>
@@ -8897,7 +9224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:22">
+    <row r="183" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>26</v>
       </c>
@@ -8914,13 +9241,13 @@
         <v>394</v>
       </c>
       <c r="I183" t="s">
-        <v>561</v>
-      </c>
-      <c r="K183" s="1" t="s">
-        <v>916</v>
+        <v>559</v>
+      </c>
+      <c r="K183" s="3" t="s">
+        <v>914</v>
       </c>
       <c r="R183" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S183">
         <v>162</v>
@@ -8932,7 +9259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:22">
+    <row r="184" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>26</v>
       </c>
@@ -8949,19 +9276,19 @@
         <v>337</v>
       </c>
       <c r="I184" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J184" t="s">
-        <v>562</v>
-      </c>
-      <c r="K184" s="1" t="s">
-        <v>917</v>
+        <v>560</v>
+      </c>
+      <c r="K184" s="3" t="s">
+        <v>915</v>
       </c>
       <c r="L184" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="R184" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="S184">
         <v>209</v>
@@ -8973,7 +9300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:22">
+    <row r="185" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>26</v>
       </c>
@@ -8990,19 +9317,19 @@
         <v>337</v>
       </c>
       <c r="I185" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J185" t="s">
-        <v>730</v>
-      </c>
-      <c r="K185" s="1" t="s">
-        <v>917</v>
+        <v>728</v>
+      </c>
+      <c r="K185" s="3" t="s">
+        <v>915</v>
       </c>
       <c r="L185" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="R185" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="S185">
         <v>211</v>
@@ -9014,7 +9341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:22">
+    <row r="186" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>26</v>
       </c>
@@ -9031,16 +9358,16 @@
         <v>395</v>
       </c>
       <c r="I186" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J186" t="s">
-        <v>731</v>
-      </c>
-      <c r="K186" s="1" t="s">
-        <v>918</v>
+        <v>729</v>
+      </c>
+      <c r="K186" s="3" t="s">
+        <v>916</v>
       </c>
       <c r="R186" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="S186">
         <v>99</v>
@@ -9052,7 +9379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:22">
+    <row r="187" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>26</v>
       </c>
@@ -9069,16 +9396,16 @@
         <v>395</v>
       </c>
       <c r="I187" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J187" t="s">
-        <v>732</v>
-      </c>
-      <c r="K187" s="1" t="s">
-        <v>919</v>
+        <v>730</v>
+      </c>
+      <c r="K187" s="3" t="s">
+        <v>917</v>
       </c>
       <c r="R187" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="S187">
         <v>135</v>
@@ -9090,7 +9417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:22">
+    <row r="188" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>26</v>
       </c>
@@ -9107,13 +9434,13 @@
         <v>338</v>
       </c>
       <c r="I188" t="s">
-        <v>566</v>
-      </c>
-      <c r="K188" s="1" t="s">
-        <v>920</v>
+        <v>564</v>
+      </c>
+      <c r="K188" s="3" t="s">
+        <v>918</v>
       </c>
       <c r="R188" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S188">
         <v>215</v>
@@ -9125,7 +9452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:22">
+    <row r="189" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>29</v>
       </c>
@@ -9142,13 +9469,13 @@
         <v>396</v>
       </c>
       <c r="I189" t="s">
-        <v>567</v>
-      </c>
-      <c r="K189" s="1" t="s">
-        <v>921</v>
+        <v>565</v>
+      </c>
+      <c r="K189" s="3" t="s">
+        <v>919</v>
       </c>
       <c r="R189" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S189">
         <v>22</v>
@@ -9160,7 +9487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:22">
+    <row r="193" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>56</v>
       </c>
@@ -9177,13 +9504,13 @@
         <v>397</v>
       </c>
       <c r="I193" t="s">
-        <v>568</v>
-      </c>
-      <c r="K193" s="1" t="s">
-        <v>922</v>
+        <v>566</v>
+      </c>
+      <c r="K193" s="3" t="s">
+        <v>920</v>
       </c>
       <c r="R193" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S193">
         <v>302</v>
@@ -9195,7 +9522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:22">
+    <row r="197" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>57</v>
       </c>
@@ -9212,16 +9539,16 @@
         <v>398</v>
       </c>
       <c r="I197" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J197" t="s">
-        <v>733</v>
-      </c>
-      <c r="K197" s="1" t="s">
-        <v>923</v>
+        <v>731</v>
+      </c>
+      <c r="K197" s="3" t="s">
+        <v>921</v>
       </c>
       <c r="R197" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S197">
         <v>133</v>
@@ -9233,7 +9560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="1:22">
+    <row r="201" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>58</v>
       </c>
@@ -9252,11 +9579,11 @@
       <c r="I201" t="s">
         <v>511</v>
       </c>
-      <c r="K201" s="1" t="s">
-        <v>924</v>
+      <c r="K201" s="3" t="s">
+        <v>922</v>
       </c>
       <c r="R201" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="S201">
         <v>239</v>
@@ -9268,7 +9595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:22">
+    <row r="205" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>59</v>
       </c>
@@ -9285,16 +9612,16 @@
         <v>396</v>
       </c>
       <c r="I205" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="J205" t="s">
-        <v>734</v>
-      </c>
-      <c r="K205" s="1" t="s">
-        <v>925</v>
+        <v>732</v>
+      </c>
+      <c r="K205" s="3" t="s">
+        <v>923</v>
       </c>
       <c r="R205" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S205">
         <v>241</v>
@@ -9306,7 +9633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:22">
+    <row r="208" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>60</v>
       </c>
@@ -9323,16 +9650,16 @@
         <v>345</v>
       </c>
       <c r="I208" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="J208" t="s">
-        <v>735</v>
-      </c>
-      <c r="K208" s="1" t="s">
-        <v>926</v>
+        <v>733</v>
+      </c>
+      <c r="K208" s="3" t="s">
+        <v>924</v>
       </c>
       <c r="R208" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S208">
         <v>188</v>
@@ -9344,7 +9671,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:22">
+    <row r="212" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>61</v>
       </c>
@@ -9361,13 +9688,13 @@
         <v>399</v>
       </c>
       <c r="I212" t="s">
-        <v>572</v>
-      </c>
-      <c r="K212" s="1" t="s">
-        <v>927</v>
+        <v>570</v>
+      </c>
+      <c r="K212" s="3" t="s">
+        <v>925</v>
       </c>
       <c r="R212" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="S212">
         <v>376</v>
@@ -9379,7 +9706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:22">
+    <row r="216" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>62</v>
       </c>
@@ -9396,13 +9723,13 @@
         <v>400</v>
       </c>
       <c r="I216" t="s">
-        <v>573</v>
-      </c>
-      <c r="K216" s="1" t="s">
-        <v>928</v>
+        <v>571</v>
+      </c>
+      <c r="K216" s="3" t="s">
+        <v>926</v>
       </c>
       <c r="R216" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="S216">
         <v>14</v>
@@ -9414,7 +9741,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:22">
+    <row r="220" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>29</v>
       </c>
@@ -9431,16 +9758,16 @@
         <v>358</v>
       </c>
       <c r="I220" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J220" t="s">
-        <v>736</v>
-      </c>
-      <c r="K220" s="1" t="s">
-        <v>929</v>
+        <v>734</v>
+      </c>
+      <c r="K220" s="3" t="s">
+        <v>927</v>
       </c>
       <c r="R220" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="S220">
         <v>31</v>
@@ -9452,7 +9779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:22">
+    <row r="221" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>29</v>
       </c>
@@ -9469,16 +9796,16 @@
         <v>358</v>
       </c>
       <c r="I221" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="J221" t="s">
-        <v>737</v>
-      </c>
-      <c r="K221" s="1" t="s">
-        <v>930</v>
+        <v>735</v>
+      </c>
+      <c r="K221" s="3" t="s">
+        <v>928</v>
       </c>
       <c r="R221" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S221">
         <v>43</v>
@@ -9490,7 +9817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:22">
+    <row r="222" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>29</v>
       </c>
@@ -9507,16 +9834,16 @@
         <v>343</v>
       </c>
       <c r="I222" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="J222" t="s">
-        <v>738</v>
-      </c>
-      <c r="K222" s="1" t="s">
-        <v>931</v>
+        <v>736</v>
+      </c>
+      <c r="K222" s="3" t="s">
+        <v>929</v>
       </c>
       <c r="R222" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="S222">
         <v>207</v>
@@ -9528,7 +9855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:22">
+    <row r="223" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>29</v>
       </c>
@@ -9545,16 +9872,16 @@
         <v>356</v>
       </c>
       <c r="I223" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="J223" t="s">
-        <v>739</v>
-      </c>
-      <c r="K223" s="1" t="s">
-        <v>932</v>
+        <v>737</v>
+      </c>
+      <c r="K223" s="3" t="s">
+        <v>930</v>
       </c>
       <c r="R223" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S223">
         <v>65</v>
@@ -9566,7 +9893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:22">
+    <row r="224" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>29</v>
       </c>
@@ -9583,16 +9910,16 @@
         <v>401</v>
       </c>
       <c r="I224" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="J224" t="s">
-        <v>740</v>
-      </c>
-      <c r="K224" s="1" t="s">
-        <v>933</v>
+        <v>738</v>
+      </c>
+      <c r="K224" s="3" t="s">
+        <v>931</v>
       </c>
       <c r="R224" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S224">
         <v>89</v>
@@ -9604,7 +9931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:22">
+    <row r="225" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>45</v>
       </c>
@@ -9621,13 +9948,13 @@
         <v>402</v>
       </c>
       <c r="I225" t="s">
-        <v>579</v>
-      </c>
-      <c r="K225" s="1" t="s">
-        <v>934</v>
+        <v>577</v>
+      </c>
+      <c r="K225" s="3" t="s">
+        <v>932</v>
       </c>
       <c r="R225" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="S225">
         <v>6</v>
@@ -9639,7 +9966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:22">
+    <row r="229" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>63</v>
       </c>
@@ -9656,16 +9983,16 @@
         <v>342</v>
       </c>
       <c r="I229" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="J229" t="s">
-        <v>741</v>
-      </c>
-      <c r="K229" s="1" t="s">
-        <v>935</v>
+        <v>739</v>
+      </c>
+      <c r="K229" s="3" t="s">
+        <v>933</v>
       </c>
       <c r="R229" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S229">
         <v>57</v>
@@ -9677,7 +10004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="1:22">
+    <row r="230" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>63</v>
       </c>
@@ -9694,16 +10021,16 @@
         <v>403</v>
       </c>
       <c r="I230" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J230" t="s">
-        <v>742</v>
-      </c>
-      <c r="K230" s="1" t="s">
-        <v>936</v>
+        <v>740</v>
+      </c>
+      <c r="K230" s="3" t="s">
+        <v>934</v>
       </c>
       <c r="R230" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S230">
         <v>66</v>
@@ -9715,7 +10042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:22">
+    <row r="233" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>54</v>
       </c>
@@ -9732,16 +10059,16 @@
         <v>404</v>
       </c>
       <c r="I233" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="J233" t="s">
-        <v>743</v>
-      </c>
-      <c r="K233" s="1" t="s">
-        <v>937</v>
+        <v>741</v>
+      </c>
+      <c r="K233" s="3" t="s">
+        <v>935</v>
       </c>
       <c r="R233" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S233">
         <v>63</v>
@@ -9753,7 +10080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="237" spans="1:22">
+    <row r="237" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>64</v>
       </c>
@@ -9770,16 +10097,16 @@
         <v>356</v>
       </c>
       <c r="I237" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="J237" t="s">
-        <v>744</v>
-      </c>
-      <c r="K237" s="1" t="s">
-        <v>938</v>
+        <v>742</v>
+      </c>
+      <c r="K237" s="3" t="s">
+        <v>936</v>
       </c>
       <c r="R237" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="S237">
         <v>24</v>
@@ -9791,7 +10118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:22">
+    <row r="238" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>64</v>
       </c>
@@ -9808,16 +10135,16 @@
         <v>405</v>
       </c>
       <c r="I238" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="J238" t="s">
-        <v>584</v>
-      </c>
-      <c r="K238" s="1" t="s">
-        <v>939</v>
+        <v>582</v>
+      </c>
+      <c r="K238" s="3" t="s">
+        <v>937</v>
       </c>
       <c r="R238" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S238">
         <v>136</v>
@@ -9829,7 +10156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:22">
+    <row r="239" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>64</v>
       </c>
@@ -9846,16 +10173,16 @@
         <v>391</v>
       </c>
       <c r="I239" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J239" t="s">
-        <v>745</v>
-      </c>
-      <c r="K239" s="1" t="s">
-        <v>940</v>
+        <v>743</v>
+      </c>
+      <c r="K239" s="3" t="s">
+        <v>938</v>
       </c>
       <c r="R239" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S239">
         <v>216</v>
@@ -9867,7 +10194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:22">
+    <row r="241" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>41</v>
       </c>
@@ -9884,16 +10211,16 @@
         <v>406</v>
       </c>
       <c r="I241" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="J241" t="s">
-        <v>746</v>
-      </c>
-      <c r="K241" s="1" t="s">
-        <v>941</v>
+        <v>744</v>
+      </c>
+      <c r="K241" s="3" t="s">
+        <v>939</v>
       </c>
       <c r="R241" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S241">
         <v>99</v>
@@ -9905,7 +10232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:22">
+    <row r="242" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>41</v>
       </c>
@@ -9922,16 +10249,16 @@
         <v>407</v>
       </c>
       <c r="I242" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="J242" t="s">
-        <v>747</v>
-      </c>
-      <c r="K242" s="1" t="s">
-        <v>942</v>
+        <v>745</v>
+      </c>
+      <c r="K242" s="3" t="s">
+        <v>940</v>
       </c>
       <c r="R242" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S242">
         <v>94</v>
@@ -9943,7 +10270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="243" spans="1:22">
+    <row r="243" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>41</v>
       </c>
@@ -9960,16 +10287,16 @@
         <v>391</v>
       </c>
       <c r="I243" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="J243" t="s">
-        <v>748</v>
-      </c>
-      <c r="K243" s="1" t="s">
-        <v>943</v>
+        <v>746</v>
+      </c>
+      <c r="K243" s="3" t="s">
+        <v>941</v>
       </c>
       <c r="R243" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S243">
         <v>95</v>
@@ -9981,7 +10308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:22">
+    <row r="244" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>41</v>
       </c>
@@ -9998,16 +10325,16 @@
         <v>408</v>
       </c>
       <c r="I244" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="J244" t="s">
-        <v>749</v>
-      </c>
-      <c r="K244" s="1" t="s">
-        <v>944</v>
+        <v>747</v>
+      </c>
+      <c r="K244" s="3" t="s">
+        <v>942</v>
       </c>
       <c r="R244" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S244">
         <v>145</v>
@@ -10019,7 +10346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:22">
+    <row r="245" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>65</v>
       </c>
@@ -10036,16 +10363,16 @@
         <v>355</v>
       </c>
       <c r="I245" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="J245" t="s">
-        <v>750</v>
-      </c>
-      <c r="K245" s="1" t="s">
-        <v>945</v>
+        <v>748</v>
+      </c>
+      <c r="K245" s="3" t="s">
+        <v>943</v>
       </c>
       <c r="R245" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S245">
         <v>71</v>
@@ -10057,7 +10384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="249" spans="1:22">
+    <row r="249" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>66</v>
       </c>
@@ -10071,13 +10398,13 @@
         <v>337</v>
       </c>
       <c r="I249" t="s">
-        <v>591</v>
-      </c>
-      <c r="K249" s="1" t="s">
-        <v>946</v>
+        <v>589</v>
+      </c>
+      <c r="K249" s="3" t="s">
+        <v>944</v>
       </c>
       <c r="R249" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S249">
         <v>109</v>
@@ -10089,7 +10416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="253" spans="1:22">
+    <row r="253" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>55</v>
       </c>
@@ -10106,16 +10433,16 @@
         <v>343</v>
       </c>
       <c r="I253" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="J253" t="s">
-        <v>751</v>
-      </c>
-      <c r="K253" s="1" t="s">
-        <v>947</v>
+        <v>749</v>
+      </c>
+      <c r="K253" s="3" t="s">
+        <v>945</v>
       </c>
       <c r="R253" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S253">
         <v>100</v>
@@ -10127,7 +10454,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="257" spans="1:22">
+    <row r="257" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>32</v>
       </c>
@@ -10144,16 +10471,16 @@
         <v>409</v>
       </c>
       <c r="I257" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J257" t="s">
-        <v>752</v>
-      </c>
-      <c r="K257" s="1" t="s">
-        <v>948</v>
+        <v>750</v>
+      </c>
+      <c r="K257" s="3" t="s">
+        <v>946</v>
       </c>
       <c r="R257" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S257">
         <v>340</v>
@@ -10165,7 +10492,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:22">
+    <row r="261" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>49</v>
       </c>
@@ -10182,16 +10509,16 @@
         <v>337</v>
       </c>
       <c r="I261" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="J261" t="s">
-        <v>753</v>
-      </c>
-      <c r="K261" s="1" t="s">
-        <v>949</v>
+        <v>751</v>
+      </c>
+      <c r="K261" s="3" t="s">
+        <v>947</v>
       </c>
       <c r="R261" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S261">
         <v>204</v>
@@ -10203,7 +10530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:22">
+    <row r="265" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>38</v>
       </c>
@@ -10220,16 +10547,16 @@
         <v>337</v>
       </c>
       <c r="I265" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="J265" t="s">
-        <v>754</v>
-      </c>
-      <c r="K265" s="1" t="s">
-        <v>950</v>
+        <v>752</v>
+      </c>
+      <c r="K265" s="3" t="s">
+        <v>948</v>
       </c>
       <c r="R265" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S265">
         <v>64</v>
@@ -10241,7 +10568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:22">
+    <row r="269" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>32</v>
       </c>
@@ -10258,16 +10585,16 @@
         <v>410</v>
       </c>
       <c r="I269" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J269" t="s">
-        <v>722</v>
-      </c>
-      <c r="K269" s="1" t="s">
-        <v>951</v>
+        <v>720</v>
+      </c>
+      <c r="K269" s="3" t="s">
+        <v>949</v>
       </c>
       <c r="R269" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S269">
         <v>313</v>
@@ -10279,7 +10606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="273" spans="1:22">
+    <row r="273" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>44</v>
       </c>
@@ -10299,13 +10626,13 @@
         <v>511</v>
       </c>
       <c r="J273" t="s">
-        <v>755</v>
-      </c>
-      <c r="K273" s="1" t="s">
-        <v>952</v>
+        <v>753</v>
+      </c>
+      <c r="K273" s="3" t="s">
+        <v>950</v>
       </c>
       <c r="R273" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="S273">
         <v>26</v>
@@ -10317,7 +10644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="277" spans="1:22">
+    <row r="277" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>67</v>
       </c>
@@ -10331,19 +10658,19 @@
         <v>412</v>
       </c>
       <c r="I277" t="s">
-        <v>596</v>
-      </c>
-      <c r="K277" s="1" t="s">
-        <v>953</v>
+        <v>594</v>
+      </c>
+      <c r="K277" s="3" t="s">
+        <v>951</v>
       </c>
       <c r="R277" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="V277">
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:22">
+    <row r="281" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>32</v>
       </c>
@@ -10360,16 +10687,16 @@
         <v>359</v>
       </c>
       <c r="I281" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="J281" t="s">
-        <v>756</v>
-      </c>
-      <c r="K281" s="1" t="s">
-        <v>954</v>
+        <v>754</v>
+      </c>
+      <c r="K281" s="3" t="s">
+        <v>952</v>
       </c>
       <c r="R281" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S281">
         <v>416</v>
@@ -10381,7 +10708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:22">
+    <row r="282" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>32</v>
       </c>
@@ -10398,16 +10725,16 @@
         <v>337</v>
       </c>
       <c r="I282" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="J282" t="s">
-        <v>757</v>
-      </c>
-      <c r="K282" s="1" t="s">
-        <v>955</v>
+        <v>755</v>
+      </c>
+      <c r="K282" s="3" t="s">
+        <v>953</v>
       </c>
       <c r="R282" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S282">
         <v>210</v>
@@ -10419,7 +10746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:22">
+    <row r="283" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>32</v>
       </c>
@@ -10433,28 +10760,28 @@
         <v>413</v>
       </c>
       <c r="I283" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="J283" t="s">
-        <v>758</v>
-      </c>
-      <c r="K283" s="1" t="s">
-        <v>956</v>
+        <v>756</v>
+      </c>
+      <c r="K283" s="3" t="s">
+        <v>954</v>
       </c>
       <c r="R283" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S283" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="T283" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="V283">
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:22">
+    <row r="284" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>32</v>
       </c>
@@ -10471,16 +10798,16 @@
         <v>343</v>
       </c>
       <c r="I284" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="J284" t="s">
-        <v>759</v>
-      </c>
-      <c r="K284" s="1" t="s">
-        <v>957</v>
+        <v>757</v>
+      </c>
+      <c r="K284" s="3" t="s">
+        <v>955</v>
       </c>
       <c r="R284" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S284">
         <v>149</v>
@@ -10492,7 +10819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:22">
+    <row r="285" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>32</v>
       </c>
@@ -10509,16 +10836,16 @@
         <v>414</v>
       </c>
       <c r="I285" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="J285" t="s">
-        <v>760</v>
-      </c>
-      <c r="K285" s="1" t="s">
-        <v>958</v>
+        <v>758</v>
+      </c>
+      <c r="K285" s="3" t="s">
+        <v>956</v>
       </c>
       <c r="R285" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S285">
         <v>365</v>
@@ -10530,7 +10857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:22">
+    <row r="298" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>68</v>
       </c>
@@ -10547,22 +10874,22 @@
         <v>415</v>
       </c>
       <c r="I298" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J298" t="s">
-        <v>761</v>
-      </c>
-      <c r="K298" s="1" t="s">
-        <v>959</v>
+        <v>759</v>
+      </c>
+      <c r="K298" s="3" t="s">
+        <v>957</v>
       </c>
       <c r="R298" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="V298">
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:22">
+    <row r="306" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>37</v>
       </c>
@@ -10579,13 +10906,13 @@
         <v>337</v>
       </c>
       <c r="I306" t="s">
-        <v>603</v>
-      </c>
-      <c r="K306" s="1" t="s">
-        <v>960</v>
+        <v>601</v>
+      </c>
+      <c r="K306" s="3" t="s">
+        <v>958</v>
       </c>
       <c r="R306" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S306">
         <v>116</v>
@@ -10597,7 +10924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:22">
+    <row r="310" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>69</v>
       </c>
@@ -10614,16 +10941,16 @@
         <v>391</v>
       </c>
       <c r="I310" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="J310" t="s">
-        <v>762</v>
-      </c>
-      <c r="K310" s="1" t="s">
-        <v>961</v>
+        <v>760</v>
+      </c>
+      <c r="K310" s="3" t="s">
+        <v>959</v>
       </c>
       <c r="R310" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S310">
         <v>107</v>
@@ -10635,7 +10962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:22">
+    <row r="311" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>69</v>
       </c>
@@ -10652,16 +10979,16 @@
         <v>416</v>
       </c>
       <c r="I311" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J311" t="s">
-        <v>763</v>
-      </c>
-      <c r="K311" s="1" t="s">
-        <v>962</v>
+        <v>761</v>
+      </c>
+      <c r="K311" s="3" t="s">
+        <v>960</v>
       </c>
       <c r="R311" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="S311">
         <v>500</v>
@@ -10673,7 +11000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:22">
+    <row r="312" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>69</v>
       </c>
@@ -10690,16 +11017,16 @@
         <v>355</v>
       </c>
       <c r="I312" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="J312" t="s">
-        <v>764</v>
-      </c>
-      <c r="K312" s="1" t="s">
-        <v>963</v>
+        <v>762</v>
+      </c>
+      <c r="K312" s="3" t="s">
+        <v>961</v>
       </c>
       <c r="R312" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S312">
         <v>82</v>
@@ -10711,7 +11038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:22">
+    <row r="322" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>70</v>
       </c>
@@ -10725,16 +11052,16 @@
         <v>417</v>
       </c>
       <c r="I322" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="J322" t="s">
-        <v>765</v>
-      </c>
-      <c r="K322" s="1" t="s">
-        <v>964</v>
+        <v>763</v>
+      </c>
+      <c r="K322" s="3" t="s">
+        <v>962</v>
       </c>
       <c r="R322" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="T322">
         <v>700</v>
@@ -10743,7 +11070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="330" spans="1:22">
+    <row r="330" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>71</v>
       </c>
@@ -10760,22 +11087,22 @@
         <v>418</v>
       </c>
       <c r="I330" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="J330" t="s">
-        <v>766</v>
-      </c>
-      <c r="K330" s="1" t="s">
-        <v>965</v>
+        <v>764</v>
+      </c>
+      <c r="K330" s="3" t="s">
+        <v>963</v>
       </c>
       <c r="R330" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="V330">
         <v>3</v>
       </c>
     </row>
-    <row r="334" spans="1:22">
+    <row r="334" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>72</v>
       </c>
@@ -10792,13 +11119,13 @@
         <v>376</v>
       </c>
       <c r="I334" t="s">
-        <v>609</v>
-      </c>
-      <c r="K334" s="1" t="s">
-        <v>966</v>
+        <v>607</v>
+      </c>
+      <c r="K334" s="3" t="s">
+        <v>964</v>
       </c>
       <c r="R334" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S334">
         <v>115</v>
@@ -10810,7 +11137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="338" spans="1:22">
+    <row r="338" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>73</v>
       </c>
@@ -10827,13 +11154,13 @@
         <v>419</v>
       </c>
       <c r="I338" t="s">
-        <v>610</v>
-      </c>
-      <c r="K338" s="1" t="s">
-        <v>967</v>
+        <v>608</v>
+      </c>
+      <c r="K338" s="3" t="s">
+        <v>965</v>
       </c>
       <c r="R338" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S338">
         <v>42</v>
@@ -10845,7 +11172,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="342" spans="1:22">
+    <row r="342" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>74</v>
       </c>
@@ -10862,13 +11189,13 @@
         <v>420</v>
       </c>
       <c r="I342" t="s">
-        <v>611</v>
-      </c>
-      <c r="K342" s="1" t="s">
-        <v>968</v>
+        <v>609</v>
+      </c>
+      <c r="K342" s="3" t="s">
+        <v>966</v>
       </c>
       <c r="R342" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S342">
         <v>32</v>
@@ -10880,7 +11207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="346" spans="1:22">
+    <row r="346" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>75</v>
       </c>
@@ -10897,16 +11224,16 @@
         <v>356</v>
       </c>
       <c r="I346" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="J346" t="s">
-        <v>767</v>
-      </c>
-      <c r="K346" s="1" t="s">
-        <v>969</v>
+        <v>765</v>
+      </c>
+      <c r="K346" s="3" t="s">
+        <v>967</v>
       </c>
       <c r="R346" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S346">
         <v>85</v>
@@ -10918,7 +11245,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:22">
+    <row r="350" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>45</v>
       </c>
@@ -10935,16 +11262,16 @@
         <v>421</v>
       </c>
       <c r="I350" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J350" t="s">
-        <v>768</v>
-      </c>
-      <c r="K350" s="1" t="s">
-        <v>970</v>
+        <v>766</v>
+      </c>
+      <c r="K350" s="3" t="s">
+        <v>968</v>
       </c>
       <c r="R350" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="S350">
         <v>301</v>
@@ -10956,7 +11283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="354" spans="1:22">
+    <row r="354" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>76</v>
       </c>
@@ -10973,16 +11300,16 @@
         <v>404</v>
       </c>
       <c r="I354" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="J354" t="s">
-        <v>769</v>
-      </c>
-      <c r="K354" s="1" t="s">
-        <v>971</v>
+        <v>767</v>
+      </c>
+      <c r="K354" s="3" t="s">
+        <v>969</v>
       </c>
       <c r="R354" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S354">
         <v>118</v>
@@ -10994,7 +11321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:22">
+    <row r="355" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>76</v>
       </c>
@@ -11014,13 +11341,13 @@
         <v>530</v>
       </c>
       <c r="J355" t="s">
-        <v>716</v>
-      </c>
-      <c r="K355" s="1" t="s">
-        <v>972</v>
+        <v>714</v>
+      </c>
+      <c r="K355" s="3" t="s">
+        <v>970</v>
       </c>
       <c r="R355" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S355">
         <v>245</v>
@@ -11032,7 +11359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:22">
+    <row r="356" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>76</v>
       </c>
@@ -11049,16 +11376,16 @@
         <v>350</v>
       </c>
       <c r="I356" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="J356" t="s">
-        <v>770</v>
-      </c>
-      <c r="K356" s="1" t="s">
-        <v>973</v>
+        <v>768</v>
+      </c>
+      <c r="K356" s="3" t="s">
+        <v>971</v>
       </c>
       <c r="R356" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S356">
         <v>119</v>
@@ -11070,7 +11397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:22">
+    <row r="365" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>77</v>
       </c>
@@ -11087,16 +11414,16 @@
         <v>340</v>
       </c>
       <c r="I365" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="J365" t="s">
-        <v>771</v>
-      </c>
-      <c r="K365" s="1" t="s">
-        <v>974</v>
+        <v>769</v>
+      </c>
+      <c r="K365" s="3" t="s">
+        <v>972</v>
       </c>
       <c r="R365" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S365">
         <v>206</v>
@@ -11108,7 +11435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:22">
+    <row r="366" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>77</v>
       </c>
@@ -11125,16 +11452,16 @@
         <v>355</v>
       </c>
       <c r="I366" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="J366" t="s">
-        <v>772</v>
-      </c>
-      <c r="K366" s="1" t="s">
-        <v>975</v>
+        <v>770</v>
+      </c>
+      <c r="K366" s="3" t="s">
+        <v>973</v>
       </c>
       <c r="R366" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S366">
         <v>677</v>
@@ -11146,7 +11473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:22">
+    <row r="367" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>77</v>
       </c>
@@ -11163,16 +11490,16 @@
         <v>359</v>
       </c>
       <c r="I367" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="J367" t="s">
-        <v>773</v>
-      </c>
-      <c r="K367" s="1" t="s">
-        <v>976</v>
+        <v>771</v>
+      </c>
+      <c r="K367" s="3" t="s">
+        <v>974</v>
       </c>
       <c r="R367" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="S367">
         <v>555</v>
@@ -11186,224 +11513,230 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1"/>
-    <hyperlink ref="K3" r:id="rId2"/>
-    <hyperlink ref="K4" r:id="rId3"/>
-    <hyperlink ref="K5" r:id="rId4"/>
-    <hyperlink ref="K6" r:id="rId5"/>
-    <hyperlink ref="K7" r:id="rId6"/>
-    <hyperlink ref="K8" r:id="rId7"/>
-    <hyperlink ref="K9" r:id="rId8"/>
-    <hyperlink ref="K10" r:id="rId9"/>
-    <hyperlink ref="K11" r:id="rId10"/>
-    <hyperlink ref="K12" r:id="rId11"/>
-    <hyperlink ref="K13" r:id="rId12"/>
-    <hyperlink ref="K14" r:id="rId13"/>
-    <hyperlink ref="K15" r:id="rId14"/>
-    <hyperlink ref="K16" r:id="rId15"/>
-    <hyperlink ref="K17" r:id="rId16"/>
-    <hyperlink ref="K18" r:id="rId17"/>
-    <hyperlink ref="K19" r:id="rId18"/>
-    <hyperlink ref="K20" r:id="rId19"/>
-    <hyperlink ref="K21" r:id="rId20"/>
-    <hyperlink ref="K22" r:id="rId21"/>
-    <hyperlink ref="K23" r:id="rId22"/>
-    <hyperlink ref="K24" r:id="rId23"/>
-    <hyperlink ref="K25" r:id="rId24"/>
-    <hyperlink ref="K26" r:id="rId25"/>
-    <hyperlink ref="K27" r:id="rId26"/>
-    <hyperlink ref="K28" r:id="rId27"/>
-    <hyperlink ref="K29" r:id="rId28"/>
-    <hyperlink ref="K30" r:id="rId29"/>
-    <hyperlink ref="K31" r:id="rId30"/>
-    <hyperlink ref="K32" r:id="rId31"/>
-    <hyperlink ref="K33" r:id="rId32"/>
-    <hyperlink ref="K34" r:id="rId33"/>
-    <hyperlink ref="M34" r:id="rId34"/>
-    <hyperlink ref="K35" r:id="rId35"/>
-    <hyperlink ref="M35" r:id="rId36"/>
-    <hyperlink ref="K36" r:id="rId37"/>
-    <hyperlink ref="M36" r:id="rId38"/>
-    <hyperlink ref="K37" r:id="rId39"/>
-    <hyperlink ref="M37" r:id="rId40"/>
-    <hyperlink ref="K38" r:id="rId41"/>
-    <hyperlink ref="M38" r:id="rId42"/>
-    <hyperlink ref="K39" r:id="rId43"/>
-    <hyperlink ref="M39" r:id="rId44"/>
-    <hyperlink ref="K40" r:id="rId45"/>
-    <hyperlink ref="M40" r:id="rId46"/>
-    <hyperlink ref="K41" r:id="rId47"/>
-    <hyperlink ref="M41" r:id="rId48"/>
-    <hyperlink ref="K42" r:id="rId49"/>
-    <hyperlink ref="M42" r:id="rId50"/>
-    <hyperlink ref="K43" r:id="rId51"/>
-    <hyperlink ref="M43" r:id="rId52"/>
-    <hyperlink ref="K44" r:id="rId53"/>
-    <hyperlink ref="M44" r:id="rId54"/>
-    <hyperlink ref="O44" r:id="rId55"/>
-    <hyperlink ref="K45" r:id="rId56"/>
-    <hyperlink ref="K46" r:id="rId57"/>
-    <hyperlink ref="K47" r:id="rId58"/>
-    <hyperlink ref="K48" r:id="rId59"/>
-    <hyperlink ref="K49" r:id="rId60"/>
-    <hyperlink ref="K50" r:id="rId61"/>
-    <hyperlink ref="K51" r:id="rId62"/>
-    <hyperlink ref="K52" r:id="rId63"/>
-    <hyperlink ref="K53" r:id="rId64"/>
-    <hyperlink ref="K54" r:id="rId65"/>
-    <hyperlink ref="K55" r:id="rId66"/>
-    <hyperlink ref="K56" r:id="rId67"/>
-    <hyperlink ref="K57" r:id="rId68"/>
-    <hyperlink ref="K58" r:id="rId69"/>
-    <hyperlink ref="K59" r:id="rId70"/>
-    <hyperlink ref="K60" r:id="rId71"/>
-    <hyperlink ref="K61" r:id="rId72"/>
-    <hyperlink ref="K62" r:id="rId73"/>
-    <hyperlink ref="K63" r:id="rId74"/>
-    <hyperlink ref="K64" r:id="rId75"/>
-    <hyperlink ref="M64" r:id="rId76"/>
-    <hyperlink ref="K65" r:id="rId77"/>
-    <hyperlink ref="K66" r:id="rId78"/>
-    <hyperlink ref="K67" r:id="rId79"/>
-    <hyperlink ref="M67" r:id="rId80"/>
-    <hyperlink ref="K68" r:id="rId81"/>
-    <hyperlink ref="K69" r:id="rId82"/>
-    <hyperlink ref="K70" r:id="rId83"/>
-    <hyperlink ref="K71" r:id="rId84"/>
-    <hyperlink ref="K72" r:id="rId85"/>
-    <hyperlink ref="K73" r:id="rId86"/>
-    <hyperlink ref="K74" r:id="rId87"/>
-    <hyperlink ref="K75" r:id="rId88"/>
-    <hyperlink ref="K76" r:id="rId89"/>
-    <hyperlink ref="K77" r:id="rId90"/>
-    <hyperlink ref="K78" r:id="rId91"/>
-    <hyperlink ref="K79" r:id="rId92"/>
-    <hyperlink ref="K80" r:id="rId93"/>
-    <hyperlink ref="K81" r:id="rId94"/>
-    <hyperlink ref="K82" r:id="rId95"/>
-    <hyperlink ref="K83" r:id="rId96"/>
-    <hyperlink ref="K84" r:id="rId97"/>
-    <hyperlink ref="K85" r:id="rId98"/>
-    <hyperlink ref="K86" r:id="rId99"/>
-    <hyperlink ref="K87" r:id="rId100"/>
-    <hyperlink ref="K88" r:id="rId101"/>
-    <hyperlink ref="K89" r:id="rId102"/>
-    <hyperlink ref="K90" r:id="rId103"/>
-    <hyperlink ref="K91" r:id="rId104"/>
-    <hyperlink ref="K92" r:id="rId105"/>
-    <hyperlink ref="K93" r:id="rId106"/>
-    <hyperlink ref="K94" r:id="rId107"/>
-    <hyperlink ref="K95" r:id="rId108"/>
-    <hyperlink ref="K96" r:id="rId109"/>
-    <hyperlink ref="K97" r:id="rId110"/>
-    <hyperlink ref="K98" r:id="rId111"/>
-    <hyperlink ref="K99" r:id="rId112"/>
-    <hyperlink ref="K100" r:id="rId113"/>
-    <hyperlink ref="K101" r:id="rId114"/>
-    <hyperlink ref="K102" r:id="rId115"/>
-    <hyperlink ref="K103" r:id="rId116"/>
-    <hyperlink ref="K104" r:id="rId117"/>
-    <hyperlink ref="K105" r:id="rId118"/>
-    <hyperlink ref="K106" r:id="rId119"/>
-    <hyperlink ref="K107" r:id="rId120"/>
-    <hyperlink ref="K108" r:id="rId121"/>
-    <hyperlink ref="K109" r:id="rId122"/>
-    <hyperlink ref="K110" r:id="rId123"/>
-    <hyperlink ref="K111" r:id="rId124"/>
-    <hyperlink ref="K112" r:id="rId125"/>
-    <hyperlink ref="K113" r:id="rId126"/>
-    <hyperlink ref="K114" r:id="rId127"/>
-    <hyperlink ref="K115" r:id="rId128"/>
-    <hyperlink ref="K116" r:id="rId129"/>
-    <hyperlink ref="K120" r:id="rId130"/>
-    <hyperlink ref="K124" r:id="rId131"/>
-    <hyperlink ref="K128" r:id="rId132"/>
-    <hyperlink ref="K132" r:id="rId133"/>
-    <hyperlink ref="K133" r:id="rId134"/>
-    <hyperlink ref="K136" r:id="rId135"/>
-    <hyperlink ref="K140" r:id="rId136"/>
-    <hyperlink ref="K141" r:id="rId137"/>
-    <hyperlink ref="K142" r:id="rId138"/>
-    <hyperlink ref="K143" r:id="rId139"/>
-    <hyperlink ref="K144" r:id="rId140"/>
-    <hyperlink ref="K145" r:id="rId141"/>
-    <hyperlink ref="K149" r:id="rId142"/>
-    <hyperlink ref="K153" r:id="rId143"/>
-    <hyperlink ref="K157" r:id="rId144"/>
-    <hyperlink ref="K158" r:id="rId145"/>
-    <hyperlink ref="K159" r:id="rId146"/>
-    <hyperlink ref="K160" r:id="rId147"/>
-    <hyperlink ref="K161" r:id="rId148"/>
-    <hyperlink ref="K163" r:id="rId149"/>
-    <hyperlink ref="K167" r:id="rId150"/>
-    <hyperlink ref="K171" r:id="rId151"/>
-    <hyperlink ref="K175" r:id="rId152"/>
-    <hyperlink ref="K179" r:id="rId153"/>
-    <hyperlink ref="K180" r:id="rId154"/>
-    <hyperlink ref="K181" r:id="rId155"/>
-    <hyperlink ref="K182" r:id="rId156"/>
-    <hyperlink ref="K183" r:id="rId157"/>
-    <hyperlink ref="K184" r:id="rId158"/>
-    <hyperlink ref="K185" r:id="rId159"/>
-    <hyperlink ref="K186" r:id="rId160"/>
-    <hyperlink ref="K187" r:id="rId161"/>
-    <hyperlink ref="K188" r:id="rId162"/>
-    <hyperlink ref="K189" r:id="rId163"/>
-    <hyperlink ref="K193" r:id="rId164"/>
-    <hyperlink ref="K197" r:id="rId165"/>
-    <hyperlink ref="K201" r:id="rId166"/>
-    <hyperlink ref="K205" r:id="rId167"/>
-    <hyperlink ref="K208" r:id="rId168"/>
-    <hyperlink ref="K212" r:id="rId169"/>
-    <hyperlink ref="K216" r:id="rId170"/>
-    <hyperlink ref="K220" r:id="rId171"/>
-    <hyperlink ref="K221" r:id="rId172"/>
-    <hyperlink ref="K222" r:id="rId173"/>
-    <hyperlink ref="K223" r:id="rId174"/>
-    <hyperlink ref="K224" r:id="rId175"/>
-    <hyperlink ref="K225" r:id="rId176"/>
-    <hyperlink ref="K229" r:id="rId177"/>
-    <hyperlink ref="K230" r:id="rId178"/>
-    <hyperlink ref="K233" r:id="rId179"/>
-    <hyperlink ref="K237" r:id="rId180"/>
-    <hyperlink ref="K238" r:id="rId181"/>
-    <hyperlink ref="K239" r:id="rId182"/>
-    <hyperlink ref="K241" r:id="rId183"/>
-    <hyperlink ref="K242" r:id="rId184"/>
-    <hyperlink ref="K243" r:id="rId185"/>
-    <hyperlink ref="K244" r:id="rId186"/>
-    <hyperlink ref="K245" r:id="rId187"/>
-    <hyperlink ref="K249" r:id="rId188"/>
-    <hyperlink ref="K253" r:id="rId189"/>
-    <hyperlink ref="K257" r:id="rId190"/>
-    <hyperlink ref="K261" r:id="rId191"/>
-    <hyperlink ref="K265" r:id="rId192"/>
-    <hyperlink ref="K269" r:id="rId193"/>
-    <hyperlink ref="K273" r:id="rId194"/>
-    <hyperlink ref="K277" r:id="rId195"/>
-    <hyperlink ref="K281" r:id="rId196"/>
-    <hyperlink ref="K282" r:id="rId197"/>
-    <hyperlink ref="K283" r:id="rId198"/>
-    <hyperlink ref="K284" r:id="rId199"/>
-    <hyperlink ref="K285" r:id="rId200"/>
-    <hyperlink ref="K298" r:id="rId201"/>
-    <hyperlink ref="K306" r:id="rId202"/>
-    <hyperlink ref="K310" r:id="rId203"/>
-    <hyperlink ref="K311" r:id="rId204"/>
-    <hyperlink ref="K312" r:id="rId205"/>
-    <hyperlink ref="K322" r:id="rId206"/>
-    <hyperlink ref="K330" r:id="rId207"/>
-    <hyperlink ref="K334" r:id="rId208"/>
-    <hyperlink ref="K338" r:id="rId209"/>
-    <hyperlink ref="K342" r:id="rId210"/>
-    <hyperlink ref="K346" r:id="rId211"/>
-    <hyperlink ref="K350" r:id="rId212"/>
-    <hyperlink ref="K354" r:id="rId213"/>
-    <hyperlink ref="K355" r:id="rId214"/>
-    <hyperlink ref="K356" r:id="rId215"/>
-    <hyperlink ref="K365" r:id="rId216"/>
-    <hyperlink ref="K366" r:id="rId217"/>
-    <hyperlink ref="K367" r:id="rId218"/>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="K5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="K7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="K8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="K9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="K10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="K11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="K12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="K13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="K14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="K15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="K16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="K17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="K18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="K20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="K21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="K22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="K23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="K24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="K25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="K27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="K30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="K32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="K33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="K34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="M34" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="K35" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="M35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="K36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="M36" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="K37" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="M37" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="K38" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="M38" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="K39" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="M39" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="K40" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="M40" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="K41" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="M41" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="K42" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="M42" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="K43" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="M43" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="K44" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="M44" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="O44" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="K45" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="K46" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="K47" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="K48" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="K49" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="K50" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="K51" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="K52" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="K53" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="K54" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="K55" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="K56" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="K57" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="K58" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="K59" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="K60" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="K61" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="K62" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="K63" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="K64" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="M64" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="K65" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="K66" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="K67" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="M67" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="K68" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="K69" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="K70" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="K71" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="K72" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="K73" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="K74" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="K75" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="K76" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="K77" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="K78" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="K79" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="K80" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="K81" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="K82" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="K83" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="K84" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="K85" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="K86" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="K87" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="K88" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="K89" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="K90" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="K91" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="K92" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="K93" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="K94" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="K95" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="K96" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="K97" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="K98" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="K99" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="K100" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="K101" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="K102" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="K103" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="K104" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="K105" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="K106" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="K107" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="K108" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="K109" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="K110" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="K111" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="K112" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="K113" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="K114" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="K115" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="K124" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="K128" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="K132" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="K133" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="K136" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="K140" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="K141" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="K142" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="K143" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="K144" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="K145" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="K149" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="K153" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="K157" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="K158" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="K159" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="K160" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="K161" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="K163" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="K167" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="K171" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="K175" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="K179" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="K180" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="K181" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="K182" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="K183" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="K184" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="K185" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="K186" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="K187" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="K188" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="K189" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="K193" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="K197" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="K201" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="K205" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="K208" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="K212" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="K216" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="K220" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="K221" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="K222" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="K223" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="K224" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="K225" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="K229" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="K230" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="K233" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="K237" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="K238" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="K239" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="K241" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="K242" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="K243" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="K244" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="K245" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="K249" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="K253" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="K257" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="K261" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="K265" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="K269" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="K273" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="K277" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="K281" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="K282" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="K283" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="K284" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="K285" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="K298" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="K306" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="K310" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="K311" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="K312" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="K322" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="K330" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="K334" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="K338" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="K342" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="K346" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="K350" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="K354" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="K355" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="K356" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="K365" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="K366" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="K367" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="K116" r:id="rId217" xr:uid="{02662092-E6C0-454A-8489-C97E5956E980}"/>
+    <hyperlink ref="K117" r:id="rId218" xr:uid="{FE70B001-8889-4AB8-9D4D-839ABB365E11}"/>
+    <hyperlink ref="K118" r:id="rId219" xr:uid="{66ED02C8-B796-4F9B-AC1C-81DC93F9F63E}"/>
+    <hyperlink ref="K119" r:id="rId220" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Jean_Clouet_-_Homme_au_P%C3%A9trarque_-_Royal_Collection.jpg/960px-Jean_Clouet_-_Homme_au_P%C3%A9trarque_-_Royal_Collection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9FEF5F6E-A8F1-45AC-95BC-DF3E82B41AB8}"/>
+    <hyperlink ref="K120" r:id="rId221" xr:uid="{E91CBA31-66A1-42A0-B75D-026F69F47838}"/>
+    <hyperlink ref="K121" r:id="rId222" xr:uid="{6F6B6D57-B58A-4E2A-80AF-D4A48207B5E8}"/>
+    <hyperlink ref="K122" r:id="rId223" xr:uid="{C16EBAE4-5B88-42A7-9D43-716CE6FA6944}"/>
+    <hyperlink ref="K123" r:id="rId224" xr:uid="{DB845F8C-A74D-4614-9577-F6D44008AC95}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89464A75-B8E3-41B7-9C9B-BCD2E0645934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E8B687-4653-45A6-9106-5A1CD38F2237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="1103">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1630,18 +1630,6 @@
     <t>Portrait d'Élisabeth d'Autriche, reine de France</t>
   </si>
   <si>
-    <t>"Adam et Ève"</t>
-  </si>
-  <si>
-    <t>"Le Vignoble du Seigneur (épitaphe pour Paul Eber)"</t>
-  </si>
-  <si>
-    <t>"L'Assomption de la Vierge (coupole, fresque)"</t>
-  </si>
-  <si>
-    <t>"Léda et le cygne"</t>
-  </si>
-  <si>
     <t>"La Déposition de croix"</t>
   </si>
   <si>
@@ -2176,12 +2164,6 @@
     <t>Portrait d'Élisabeth d'Autriche</t>
   </si>
   <si>
-    <t>"Weinberg des Herrn"</t>
-  </si>
-  <si>
-    <t>"Leda e il cigno"</t>
-  </si>
-  <si>
     <t>"Deposizione"</t>
   </si>
   <si>
@@ -3182,6 +3164,171 @@
   </si>
   <si>
     <t>Enluminure sur parchemin</t>
+  </si>
+  <si>
+    <t>Adam et Ève</t>
+  </si>
+  <si>
+    <t>Die drei Grazien</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Lucas_Cranach_d.%C3%84._-_Drei_Grazien%2C_1531_%28Mus%C3%A9e_du_Louvre%29.jpg/960px-Lucas_Cranach_d.%C3%84._-_Drei_Grazien%2C_1531_%28Mus%C3%A9e_du_Louvre%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam et Ève </t>
+  </si>
+  <si>
+    <t>Adam und Eva</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Cranach%2C_adamo_ed_eva%2C_uffizi.jpg/960px-Cranach%2C_adamo_ed_eva%2C_uffizi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cène </t>
+  </si>
+  <si>
+    <t>Wittenberger Reformationsaltar</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/Lucas_Cranach_d.%C3%84._-_Reformationsaltar%2C_St._Marien_zu_Wittenberg%2C_Mitteltafel.jpg/1280px-Lucas_Cranach_d.%C3%84._-_Reformationsaltar%2C_St._Marien_zu_Wittenberg%2C_Mitteltafel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Le Retable de Wittenberg</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/00_3420_Wittenberg_-_Lutherstadt_%28Stadtkirche%29.jpg/960px-00_3420_Wittenberg_-_Lutherstadt_%28Stadtkirche%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Arrière du retable</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d3/Cranach_Reformationsaltar_R%C3%BCckseite.jpg/1280px-Cranach_Reformationsaltar_R%C3%BCckseite.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Le Vignoble du Seigneur (épitaphe pour Paul Eber)</t>
+  </si>
+  <si>
+    <t>Weinberg des Herrn</t>
+  </si>
+  <si>
+    <t>Weimar</t>
+  </si>
+  <si>
+    <t>Église Saints-Pierre-et-Paul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Christ en croix Weimar </t>
+  </si>
+  <si>
+    <t>Weimarer Altar</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/Herderkirche_Weimar_Cranach_Altarpiece.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Retable de Weimar </t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/04/Weimar_-_Altar_in_St._Peter_und_Paul%2C_Weimar_by_Cranachs_-_Central_piece.jpg/1280px-Weimar_-_Altar_in_St._Peter_und_Paul%2C_Weimar_by_Cranachs_-_Central_piece.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1580</t>
+  </si>
+  <si>
+    <t>Saint-Pétersbourg</t>
+  </si>
+  <si>
+    <t>Musée de l'Ermitage</t>
+  </si>
+  <si>
+    <t>Le Christ et la femme adultère</t>
+  </si>
+  <si>
+    <t>Christus und die Ehebrecherin</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9a/Cranach_the_Younger%2C_Lucas_-_Christ_and_the_adulteress.jpg/1280px-Cranach_the_Younger%2C_Lucas_-_Christ_and_the_adulteress.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Portrait du prince-électeur Auguste de Saxe</t>
+  </si>
+  <si>
+    <t>Kurfürst August von Sachsen</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Lucas_Cranach_the_Younger_-_Prince_Elector_Moritz_of_Saxony_-_Google_Art_Project.jpg/960px-Lucas_Cranach_the_Younger_-_Prince_Elector_Moritz_of_Saxony_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>L'Assomption de la Vierge (coupole, fresque)</t>
+  </si>
+  <si>
+    <t>Léda et le cygne</t>
+  </si>
+  <si>
+    <t>Leda e il cigno</t>
+  </si>
+  <si>
+    <t>1532 environ</t>
+  </si>
+  <si>
+    <t>Jupiter et Io</t>
+  </si>
+  <si>
+    <t>Giove e Io</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Antonio_Allegri%2C_called_Correggio_-_Jupiter_and_Io_-_Google_Art_Project.jpg/500px-Antonio_Allegri%2C_called_Correggio_-_Jupiter_and_Io_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>L'Éducation de l'Amour (Le Maître d'école de l'amour)</t>
+  </si>
+  <si>
+    <t>Educazione di Cupido</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d8/Correggio_-_The_Education_of_Cupid_-_WGA05340.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>1557</t>
+  </si>
+  <si>
+    <t>Le Massacre des Innocents</t>
+  </si>
+  <si>
+    <t>Strage degli innocenti</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/98/Daniele_da_Volterra_-_The_Massacre_of_the_Innocents_-_WGA05910.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>c. 1544</t>
+  </si>
+  <si>
+    <t>Portrait de Michel-Ange</t>
+  </si>
+  <si>
+    <t>Ritratto di Michelangelo Buonarroti</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/Michelangelo_Daniele_da_Volterra.jpg/960px-Michelangelo_Daniele_da_Volterra.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>c. 1550</t>
+  </si>
+  <si>
+    <t>David et Goliath (Double face sur ardoise)</t>
+  </si>
+  <si>
+    <t>David e Golia</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/David_and_Goliath_by_Daniele_da_Volterra_%28Louvre_INV_566%29_verso_02.jpg/1280px-David_and_Goliath_by_Daniele_da_Volterra_%28Louvre_INV_566%29_verso_02.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Huile sur ardoise</t>
   </si>
 </sst>
 </file>
@@ -3664,13 +3811,13 @@
         <v>426</v>
       </c>
       <c r="J2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="R2" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S2">
         <v>81</v>
@@ -3702,13 +3849,13 @@
         <v>427</v>
       </c>
       <c r="J3" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="R3" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S3">
         <v>165</v>
@@ -3740,13 +3887,13 @@
         <v>428</v>
       </c>
       <c r="J4" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="R4" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S4">
         <v>480</v>
@@ -3778,13 +3925,13 @@
         <v>429</v>
       </c>
       <c r="J5" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="R5" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S5">
         <v>121</v>
@@ -3816,13 +3963,13 @@
         <v>430</v>
       </c>
       <c r="J6" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="R6" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S6">
         <v>448</v>
@@ -3854,13 +4001,13 @@
         <v>431</v>
       </c>
       <c r="J7" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="R7" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S7">
         <v>346</v>
@@ -3892,13 +4039,13 @@
         <v>432</v>
       </c>
       <c r="J8" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="R8" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S8">
         <v>275</v>
@@ -3930,13 +4077,13 @@
         <v>433</v>
       </c>
       <c r="J9" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="R9" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S9">
         <v>171</v>
@@ -3968,13 +4115,13 @@
         <v>434</v>
       </c>
       <c r="J10" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="R10" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S10">
         <v>137</v>
@@ -4006,13 +4153,13 @@
         <v>435</v>
       </c>
       <c r="J11" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="R11" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S11">
         <v>106</v>
@@ -4044,16 +4191,16 @@
         <v>436</v>
       </c>
       <c r="J12" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="R12" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S12" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="T12">
         <v>103</v>
@@ -4082,13 +4229,13 @@
         <v>437</v>
       </c>
       <c r="J13" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="R13" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S13">
         <v>224</v>
@@ -4120,13 +4267,13 @@
         <v>438</v>
       </c>
       <c r="J14" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="R14" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S14">
         <v>100.8</v>
@@ -4158,13 +4305,13 @@
         <v>439</v>
       </c>
       <c r="J15" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="R15" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S15">
         <v>176</v>
@@ -4196,13 +4343,13 @@
         <v>440</v>
       </c>
       <c r="J16" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="R16" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S16">
         <v>191</v>
@@ -4234,13 +4381,13 @@
         <v>441</v>
       </c>
       <c r="J17" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="R17" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S17">
         <v>58.7</v>
@@ -4272,13 +4419,13 @@
         <v>442</v>
       </c>
       <c r="J18" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="R18" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S18">
         <v>111</v>
@@ -4310,13 +4457,13 @@
         <v>443</v>
       </c>
       <c r="J19" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="R19" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S19">
         <v>124</v>
@@ -4348,13 +4495,13 @@
         <v>444</v>
       </c>
       <c r="J20" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="R20" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S20">
         <v>84</v>
@@ -4386,13 +4533,13 @@
         <v>445</v>
       </c>
       <c r="J21" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="R21" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S21">
         <v>112</v>
@@ -4424,10 +4571,10 @@
         <v>446</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="R22" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S22">
         <v>202</v>
@@ -4459,13 +4606,13 @@
         <v>447</v>
       </c>
       <c r="J23" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="R23" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S23">
         <v>146</v>
@@ -4497,13 +4644,13 @@
         <v>448</v>
       </c>
       <c r="J24" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="R24" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S24">
         <v>115</v>
@@ -4535,10 +4682,10 @@
         <v>449</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="R25" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S25">
         <v>117</v>
@@ -4570,13 +4717,13 @@
         <v>450</v>
       </c>
       <c r="J26" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="R26" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="S26">
         <v>42</v>
@@ -4608,13 +4755,13 @@
         <v>451</v>
       </c>
       <c r="J27" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="R27" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S27">
         <v>158</v>
@@ -4646,13 +4793,13 @@
         <v>452</v>
       </c>
       <c r="J28" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="R28" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="S28">
         <v>28</v>
@@ -4684,13 +4831,13 @@
         <v>453</v>
       </c>
       <c r="J29" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="R29" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S29">
         <v>57</v>
@@ -4725,13 +4872,13 @@
         <v>454</v>
       </c>
       <c r="J30" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="R30" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S30">
         <v>72</v>
@@ -4763,13 +4910,13 @@
         <v>455</v>
       </c>
       <c r="J31" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="R31" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S31">
         <v>66</v>
@@ -4801,13 +4948,13 @@
         <v>456</v>
       </c>
       <c r="J32" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="R32" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S32">
         <v>157</v>
@@ -4839,13 +4986,13 @@
         <v>457</v>
       </c>
       <c r="J33" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="R33" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S33">
         <v>88</v>
@@ -4877,19 +5024,19 @@
         <v>458</v>
       </c>
       <c r="J34" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="L34" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="R34" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S34">
         <v>76</v>
@@ -4921,19 +5068,19 @@
         <v>459</v>
       </c>
       <c r="J35" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="L35" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="R35" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S35">
         <v>76</v>
@@ -4965,19 +5112,19 @@
         <v>460</v>
       </c>
       <c r="J36" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="L36" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="R36" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S36">
         <v>76</v>
@@ -5009,19 +5156,19 @@
         <v>461</v>
       </c>
       <c r="J37" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="L37" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="R37" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S37">
         <v>76</v>
@@ -5053,19 +5200,19 @@
         <v>462</v>
       </c>
       <c r="J38" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="L38" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="R38" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S38">
         <v>67</v>
@@ -5097,19 +5244,19 @@
         <v>463</v>
       </c>
       <c r="J39" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="L39" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="R39" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S39">
         <v>67</v>
@@ -5141,19 +5288,19 @@
         <v>464</v>
       </c>
       <c r="J40" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="L40" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="R40" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S40">
         <v>64</v>
@@ -5185,19 +5332,19 @@
         <v>465</v>
       </c>
       <c r="J41" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="L41" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="M41" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="R41" t="s">
         <v>986</v>
-      </c>
-      <c r="R41" t="s">
-        <v>992</v>
       </c>
       <c r="S41">
         <v>74</v>
@@ -5229,19 +5376,19 @@
         <v>466</v>
       </c>
       <c r="J42" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="L42" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="M42" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="R42" t="s">
         <v>987</v>
-      </c>
-      <c r="R42" t="s">
-        <v>993</v>
       </c>
       <c r="S42">
         <v>48</v>
@@ -5273,19 +5420,19 @@
         <v>467</v>
       </c>
       <c r="J43" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="L43" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="M43" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="R43" t="s">
         <v>987</v>
-      </c>
-      <c r="R43" t="s">
-        <v>993</v>
       </c>
       <c r="S43">
         <v>151</v>
@@ -5317,22 +5464,22 @@
         <v>468</v>
       </c>
       <c r="J44" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="L44" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="R44" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S44">
         <v>270</v>
@@ -5364,13 +5511,13 @@
         <v>469</v>
       </c>
       <c r="J45" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="R45" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="S45">
         <v>31</v>
@@ -5402,13 +5549,13 @@
         <v>470</v>
       </c>
       <c r="J46" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="R46" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S46">
         <v>83</v>
@@ -5440,13 +5587,13 @@
         <v>471</v>
       </c>
       <c r="J47" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="R47" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S47">
         <v>124</v>
@@ -5478,13 +5625,13 @@
         <v>472</v>
       </c>
       <c r="J48" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="R48" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S48">
         <v>109</v>
@@ -5516,13 +5663,13 @@
         <v>473</v>
       </c>
       <c r="J49" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="R49" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S49">
         <v>200</v>
@@ -5554,13 +5701,13 @@
         <v>474</v>
       </c>
       <c r="J50" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="R50" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S50">
         <v>105</v>
@@ -5592,13 +5739,13 @@
         <v>475</v>
       </c>
       <c r="J51" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="R51" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S51">
         <v>48</v>
@@ -5630,13 +5777,13 @@
         <v>476</v>
       </c>
       <c r="J52" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="R52" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S52">
         <v>58</v>
@@ -5668,13 +5815,13 @@
         <v>477</v>
       </c>
       <c r="J53" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="R53" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S53">
         <v>412</v>
@@ -5706,13 +5853,13 @@
         <v>478</v>
       </c>
       <c r="J54" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="R54" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S54">
         <v>359</v>
@@ -5744,13 +5891,13 @@
         <v>479</v>
       </c>
       <c r="J55" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="R55" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S55">
         <v>179</v>
@@ -5782,13 +5929,13 @@
         <v>480</v>
       </c>
       <c r="J56" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="R56" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S56">
         <v>134</v>
@@ -5820,13 +5967,13 @@
         <v>481</v>
       </c>
       <c r="J57" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="R57" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S57">
         <v>183</v>
@@ -5858,13 +6005,13 @@
         <v>482</v>
       </c>
       <c r="J58" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="R58" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S58">
         <v>168</v>
@@ -5896,13 +6043,13 @@
         <v>483</v>
       </c>
       <c r="J59" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="R59" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S59">
         <v>102</v>
@@ -5934,13 +6081,13 @@
         <v>484</v>
       </c>
       <c r="J60" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="R60" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S60">
         <v>123</v>
@@ -5972,13 +6119,13 @@
         <v>485</v>
       </c>
       <c r="J61" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="R61" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S61">
         <v>60</v>
@@ -6010,13 +6157,13 @@
         <v>486</v>
       </c>
       <c r="J62" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="R62" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S62">
         <v>206</v>
@@ -6048,13 +6195,13 @@
         <v>487</v>
       </c>
       <c r="J63" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="R63" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="S63">
         <v>370</v>
@@ -6083,19 +6230,19 @@
         <v>488</v>
       </c>
       <c r="J64" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L64" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="R64" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="S64">
         <v>300</v>
@@ -6127,13 +6274,13 @@
         <v>489</v>
       </c>
       <c r="J65" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="R65" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S65">
         <v>61</v>
@@ -6165,13 +6312,13 @@
         <v>490</v>
       </c>
       <c r="J66" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="R66" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S66">
         <v>347</v>
@@ -6206,19 +6353,19 @@
         <v>491</v>
       </c>
       <c r="J67" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="L67" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="R67" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="V67">
         <v>3</v>
@@ -6244,13 +6391,13 @@
         <v>492</v>
       </c>
       <c r="J68" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="R68" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S68">
         <v>398</v>
@@ -6282,10 +6429,10 @@
         <v>493</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="R69" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="S69">
         <v>323</v>
@@ -6314,10 +6461,10 @@
         <v>494</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="R70" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S70">
         <v>347</v>
@@ -6349,13 +6496,13 @@
         <v>495</v>
       </c>
       <c r="J71" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="R71" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="S71">
         <v>67</v>
@@ -6387,10 +6534,10 @@
         <v>496</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="R72" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="S72">
         <v>62</v>
@@ -6422,13 +6569,13 @@
         <v>497</v>
       </c>
       <c r="J73" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="R73" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S73">
         <v>170</v>
@@ -6460,13 +6607,13 @@
         <v>498</v>
       </c>
       <c r="J74" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="R74" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S74">
         <v>88</v>
@@ -6498,13 +6645,13 @@
         <v>489</v>
       </c>
       <c r="J75" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="R75" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S75">
         <v>89</v>
@@ -6536,13 +6683,13 @@
         <v>499</v>
       </c>
       <c r="J76" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="R76" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S76">
         <v>158</v>
@@ -6574,13 +6721,13 @@
         <v>500</v>
       </c>
       <c r="J77" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="R77" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S77">
         <v>158</v>
@@ -6612,13 +6759,13 @@
         <v>501</v>
       </c>
       <c r="J78" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="R78" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S78">
         <v>158</v>
@@ -6650,13 +6797,13 @@
         <v>502</v>
       </c>
       <c r="J79" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="R79" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S79">
         <v>158</v>
@@ -6688,13 +6835,13 @@
         <v>503</v>
       </c>
       <c r="J80" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="R80" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S80">
         <v>370</v>
@@ -6726,13 +6873,13 @@
         <v>504</v>
       </c>
       <c r="J81" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="R81" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S81">
         <v>234</v>
@@ -6764,13 +6911,13 @@
         <v>505</v>
       </c>
       <c r="J82" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="R82" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S82">
         <v>112</v>
@@ -6802,13 +6949,13 @@
         <v>506</v>
       </c>
       <c r="J83" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="R83" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S83">
         <v>105</v>
@@ -6840,13 +6987,13 @@
         <v>507</v>
       </c>
       <c r="J84" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="R84" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="S84">
         <v>220</v>
@@ -6878,13 +7025,13 @@
         <v>508</v>
       </c>
       <c r="J85" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="R85" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="S85">
         <v>58</v>
@@ -6916,13 +7063,13 @@
         <v>509</v>
       </c>
       <c r="J86" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="R86" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="S86">
         <v>74</v>
@@ -6954,13 +7101,13 @@
         <v>510</v>
       </c>
       <c r="J87" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="R87" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="S87">
         <v>164</v>
@@ -6992,13 +7139,13 @@
         <v>511</v>
       </c>
       <c r="J88" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="R88" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="S88">
         <v>138</v>
@@ -7030,10 +7177,10 @@
         <v>512</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="R89" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="S89">
         <v>132</v>
@@ -7065,10 +7212,10 @@
         <v>513</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="R90" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="S90">
         <v>135</v>
@@ -7100,10 +7247,10 @@
         <v>513</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="R91" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S91">
         <v>135</v>
@@ -7135,19 +7282,19 @@
         <v>514</v>
       </c>
       <c r="J92" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="R92" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S92">
         <v>60</v>
       </c>
       <c r="T92" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="V92">
         <v>1</v>
@@ -7173,16 +7320,16 @@
         <v>515</v>
       </c>
       <c r="J93" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="L93" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="R93" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S93">
         <v>117</v>
@@ -7214,13 +7361,13 @@
         <v>516</v>
       </c>
       <c r="J94" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="R94" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S94">
         <v>114</v>
@@ -7252,13 +7399,13 @@
         <v>517</v>
       </c>
       <c r="J95" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="R95" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S95">
         <v>118</v>
@@ -7290,13 +7437,13 @@
         <v>518</v>
       </c>
       <c r="J96" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="R96" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S96">
         <v>117</v>
@@ -7328,13 +7475,13 @@
         <v>519</v>
       </c>
       <c r="J97" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="R97" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S97">
         <v>118</v>
@@ -7366,13 +7513,13 @@
         <v>490</v>
       </c>
       <c r="J98" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="R98" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S98">
         <v>117</v>
@@ -7404,13 +7551,13 @@
         <v>520</v>
       </c>
       <c r="J99" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="R99" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S99">
         <v>117</v>
@@ -7442,13 +7589,13 @@
         <v>481</v>
       </c>
       <c r="J100" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="R100" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S100">
         <v>111</v>
@@ -7480,13 +7627,13 @@
         <v>521</v>
       </c>
       <c r="J101" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="R101" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S101">
         <v>114</v>
@@ -7518,13 +7665,13 @@
         <v>522</v>
       </c>
       <c r="J102" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="R102" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S102">
         <v>114</v>
@@ -7556,19 +7703,19 @@
         <v>523</v>
       </c>
       <c r="J103" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="R103" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S103" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="T103" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="V103">
         <v>1</v>
@@ -7594,13 +7741,13 @@
         <v>524</v>
       </c>
       <c r="J104" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="R104" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="S104">
         <v>120</v>
@@ -7632,13 +7779,13 @@
         <v>525</v>
       </c>
       <c r="J105" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="R105" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="V105">
         <v>1</v>
@@ -7664,10 +7811,10 @@
         <v>526</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="R106" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="S106">
         <v>280</v>
@@ -7699,10 +7846,10 @@
         <v>527</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="R107" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="S107">
         <v>1370</v>
@@ -7734,13 +7881,13 @@
         <v>528</v>
       </c>
       <c r="J108" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="R108" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="S108">
         <v>625</v>
@@ -7772,13 +7919,13 @@
         <v>529</v>
       </c>
       <c r="J109" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="R109" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S109">
         <v>185</v>
@@ -7810,13 +7957,13 @@
         <v>530</v>
       </c>
       <c r="J110" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="R110" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S110">
         <v>245</v>
@@ -7848,13 +7995,13 @@
         <v>531</v>
       </c>
       <c r="J111" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="R111" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S111">
         <v>120</v>
@@ -7886,13 +8033,13 @@
         <v>532</v>
       </c>
       <c r="J112" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="R112" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S112">
         <v>92</v>
@@ -7927,10 +8074,10 @@
         <v>533</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="R113" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S113">
         <v>133</v>
@@ -7965,10 +8112,10 @@
         <v>534</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="R114" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S114">
         <v>91</v>
@@ -8000,13 +8147,13 @@
         <v>535</v>
       </c>
       <c r="J115" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="R115" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S115">
         <v>35</v>
@@ -8038,13 +8185,13 @@
         <v>355</v>
       </c>
       <c r="I116" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="R116" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S116">
         <v>96</v>
@@ -8058,7 +8205,7 @@
     </row>
     <row r="117" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C117" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="E117" t="s">
         <v>289</v>
@@ -8067,13 +8214,13 @@
         <v>340</v>
       </c>
       <c r="I117" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="R117" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S117">
         <v>40</v>
@@ -8087,22 +8234,22 @@
     </row>
     <row r="118" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C118" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="E118" t="s">
         <v>310</v>
       </c>
       <c r="F118" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="I118" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="R118" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S118">
         <v>36</v>
@@ -8116,22 +8263,22 @@
     </row>
     <row r="119" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C119" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="E119" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="F119" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="I119" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="R119" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S119">
         <v>38</v>
@@ -8161,13 +8308,13 @@
       </c>
       <c r="G120"/>
       <c r="I120" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="R120" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S120">
         <v>97</v>
@@ -8190,20 +8337,20 @@
         <v>1540</v>
       </c>
       <c r="D121" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="E121" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="G121"/>
       <c r="I121" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="R121" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S121">
         <v>100</v>
@@ -8226,20 +8373,20 @@
         <v>169</v>
       </c>
       <c r="D122" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="E122" t="s">
         <v>380</v>
       </c>
       <c r="G122"/>
       <c r="I122" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="R122" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S122">
         <v>88</v>
@@ -8259,7 +8406,7 @@
         <v>100</v>
       </c>
       <c r="C123" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="D123" t="s">
         <v>322</v>
@@ -8269,16 +8416,16 @@
       </c>
       <c r="G123"/>
       <c r="I123" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="L123" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="R123" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="S123">
         <v>21</v>
@@ -8306,14 +8453,18 @@
       <c r="E124" t="s">
         <v>382</v>
       </c>
+      <c r="G124"/>
       <c r="I124" t="s">
-        <v>536</v>
-      </c>
+        <v>1048</v>
+      </c>
+      <c r="J124" s="2"/>
       <c r="K124" s="3" t="s">
-        <v>888</v>
-      </c>
+        <v>882</v>
+      </c>
+      <c r="M124" s="2"/>
+      <c r="O124" s="2"/>
       <c r="R124" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S124">
         <v>117</v>
@@ -8322,7 +8473,140 @@
         <v>81</v>
       </c>
       <c r="V124">
-        <v>1</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>45</v>
+      </c>
+      <c r="B125" t="s">
+        <v>101</v>
+      </c>
+      <c r="C125">
+        <v>1531</v>
+      </c>
+      <c r="D125" t="s">
+        <v>39</v>
+      </c>
+      <c r="E125" t="s">
+        <v>355</v>
+      </c>
+      <c r="G125"/>
+      <c r="I125" t="s">
+        <v>467</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="K125" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="M125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="R125" t="s">
+        <v>987</v>
+      </c>
+      <c r="S125">
+        <v>36</v>
+      </c>
+      <c r="T125">
+        <v>24</v>
+      </c>
+      <c r="V125">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>45</v>
+      </c>
+      <c r="B126" t="s">
+        <v>101</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D126" t="s">
+        <v>299</v>
+      </c>
+      <c r="E126" t="s">
+        <v>371</v>
+      </c>
+      <c r="G126"/>
+      <c r="I126" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="K126" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="R126" t="s">
+        <v>987</v>
+      </c>
+      <c r="S126">
+        <v>172</v>
+      </c>
+      <c r="T126">
+        <v>63</v>
+      </c>
+      <c r="V126">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>45</v>
+      </c>
+      <c r="B127" t="s">
+        <v>101</v>
+      </c>
+      <c r="C127">
+        <v>1547</v>
+      </c>
+      <c r="D127" t="s">
+        <v>323</v>
+      </c>
+      <c r="E127" t="s">
+        <v>383</v>
+      </c>
+      <c r="G127"/>
+      <c r="I127" t="s">
+        <v>1055</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="L127" t="s">
+        <v>1058</v>
+      </c>
+      <c r="M127" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="N127" t="s">
+        <v>1060</v>
+      </c>
+      <c r="O127" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="R127" t="s">
+        <v>987</v>
+      </c>
+      <c r="S127">
+        <v>255</v>
+      </c>
+      <c r="T127">
+        <v>240</v>
+      </c>
+      <c r="V127">
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8341,17 +8625,19 @@
       <c r="E128" t="s">
         <v>383</v>
       </c>
+      <c r="G128"/>
       <c r="I128" t="s">
-        <v>537</v>
+        <v>1062</v>
       </c>
       <c r="J128" t="s">
-        <v>718</v>
+        <v>1063</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>889</v>
-      </c>
+        <v>883</v>
+      </c>
+      <c r="M128" s="2"/>
       <c r="R128" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S128">
         <v>127</v>
@@ -8361,6 +8647,122 @@
       </c>
       <c r="V128">
         <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>45</v>
+      </c>
+      <c r="B129" t="s">
+        <v>102</v>
+      </c>
+      <c r="C129" t="s">
+        <v>172</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E129" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G129"/>
+      <c r="I129" t="s">
+        <v>1066</v>
+      </c>
+      <c r="J129" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K129" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="L129" t="s">
+        <v>1069</v>
+      </c>
+      <c r="M129" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="R129" t="s">
+        <v>987</v>
+      </c>
+      <c r="S129">
+        <v>370</v>
+      </c>
+      <c r="T129">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>45</v>
+      </c>
+      <c r="B130" t="s">
+        <v>102</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E130" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G130"/>
+      <c r="I130" t="s">
+        <v>1074</v>
+      </c>
+      <c r="J130" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K130" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="M130" s="2"/>
+      <c r="R130" t="s">
+        <v>987</v>
+      </c>
+      <c r="S130">
+        <v>84</v>
+      </c>
+      <c r="T130">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="131" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>45</v>
+      </c>
+      <c r="B131" t="s">
+        <v>102</v>
+      </c>
+      <c r="C131" t="s">
+        <v>173</v>
+      </c>
+      <c r="D131" t="s">
+        <v>303</v>
+      </c>
+      <c r="E131" t="s">
+        <v>356</v>
+      </c>
+      <c r="G131"/>
+      <c r="I131" t="s">
+        <v>1077</v>
+      </c>
+      <c r="J131" t="s">
+        <v>1078</v>
+      </c>
+      <c r="K131" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M131" s="2"/>
+      <c r="R131" t="s">
+        <v>986</v>
+      </c>
+      <c r="S131">
+        <v>122</v>
+      </c>
+      <c r="T131">
+        <v>93</v>
       </c>
     </row>
     <row r="132" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8379,17 +8781,18 @@
       <c r="E132" t="s">
         <v>362</v>
       </c>
+      <c r="G132"/>
       <c r="I132" t="s">
-        <v>538</v>
-      </c>
-      <c r="K132" s="3" t="s">
-        <v>890</v>
-      </c>
-      <c r="R132" t="s">
-        <v>997</v>
+        <v>1080</v>
+      </c>
+      <c r="K132" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>991</v>
       </c>
       <c r="V132">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8408,25 +8811,104 @@
       <c r="E133" t="s">
         <v>345</v>
       </c>
+      <c r="G133"/>
       <c r="I133" t="s">
-        <v>539</v>
+        <v>1081</v>
       </c>
       <c r="J133" t="s">
-        <v>719</v>
-      </c>
-      <c r="K133" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="R133" t="s">
-        <v>992</v>
+        <v>1082</v>
+      </c>
+      <c r="K133" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>986</v>
       </c>
       <c r="S133">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="T133">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="V133">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>46</v>
+      </c>
+      <c r="B134" t="s">
+        <v>103</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D134" t="s">
+        <v>303</v>
+      </c>
+      <c r="E134" t="s">
+        <v>356</v>
+      </c>
+      <c r="G134"/>
+      <c r="I134" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J134" t="s">
+        <v>1085</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="R134" t="s">
+        <v>986</v>
+      </c>
+      <c r="S134">
+        <v>162</v>
+      </c>
+      <c r="T134">
+        <v>73</v>
+      </c>
+      <c r="V134">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>46</v>
+      </c>
+      <c r="B135" t="s">
+        <v>103</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D135" t="s">
+        <v>292</v>
+      </c>
+      <c r="E135" t="s">
+        <v>343</v>
+      </c>
+      <c r="G135"/>
+      <c r="I135" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J135" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="R135" t="s">
+        <v>986</v>
+      </c>
+      <c r="S135">
+        <v>155</v>
+      </c>
+      <c r="T135">
+        <v>92</v>
+      </c>
+      <c r="V135">
         <v>3</v>
       </c>
     </row>
@@ -8446,17 +8928,18 @@
       <c r="E136" t="s">
         <v>384</v>
       </c>
+      <c r="G136"/>
       <c r="I136" t="s">
-        <v>540</v>
+        <v>477</v>
       </c>
       <c r="J136" t="s">
-        <v>720</v>
-      </c>
-      <c r="K136" s="3" t="s">
-        <v>892</v>
+        <v>662</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>886</v>
       </c>
       <c r="R136" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="S136">
         <v>260</v>
@@ -8465,6 +8948,123 @@
         <v>280</v>
       </c>
       <c r="V136">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>47</v>
+      </c>
+      <c r="B137" t="s">
+        <v>104</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D137" t="s">
+        <v>299</v>
+      </c>
+      <c r="E137" t="s">
+        <v>371</v>
+      </c>
+      <c r="G137"/>
+      <c r="I137" t="s">
+        <v>1091</v>
+      </c>
+      <c r="J137" t="s">
+        <v>1092</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="R137" t="s">
+        <v>987</v>
+      </c>
+      <c r="S137">
+        <v>51</v>
+      </c>
+      <c r="T137">
+        <v>42</v>
+      </c>
+      <c r="V137">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>47</v>
+      </c>
+      <c r="B138" t="s">
+        <v>104</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D138" t="s">
+        <v>289</v>
+      </c>
+      <c r="E138" t="s">
+        <v>340</v>
+      </c>
+      <c r="G138"/>
+      <c r="I138" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J138" t="s">
+        <v>1096</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="R138" t="s">
+        <v>987</v>
+      </c>
+      <c r="S138">
+        <v>89</v>
+      </c>
+      <c r="T138">
+        <v>64</v>
+      </c>
+      <c r="V138">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>47</v>
+      </c>
+      <c r="B139" t="s">
+        <v>104</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D139" t="s">
+        <v>39</v>
+      </c>
+      <c r="E139" t="s">
+        <v>355</v>
+      </c>
+      <c r="G139"/>
+      <c r="I139" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J139" t="s">
+        <v>1100</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R139" t="s">
+        <v>1102</v>
+      </c>
+      <c r="S139">
+        <v>133</v>
+      </c>
+      <c r="T139">
+        <v>172</v>
+      </c>
+      <c r="V139">
         <v>3</v>
       </c>
     </row>
@@ -8485,13 +9085,13 @@
         <v>343</v>
       </c>
       <c r="I140" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="R140" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S140">
         <v>106</v>
@@ -8520,13 +9120,13 @@
         <v>385</v>
       </c>
       <c r="I141" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="R141" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="S141">
         <v>132</v>
@@ -8555,13 +9155,13 @@
         <v>340</v>
       </c>
       <c r="I142" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="K142" s="3" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="R142" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S142">
         <v>79</v>
@@ -8590,13 +9190,13 @@
         <v>380</v>
       </c>
       <c r="I143" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="K143" s="3" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="R143" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S143">
         <v>118</v>
@@ -8625,13 +9225,13 @@
         <v>342</v>
       </c>
       <c r="I144" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="K144" s="3" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="R144" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S144">
         <v>42</v>
@@ -8660,13 +9260,13 @@
         <v>343</v>
       </c>
       <c r="I145" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="K145" s="3" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="R145" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S145">
         <v>60</v>
@@ -8695,16 +9295,16 @@
         <v>337</v>
       </c>
       <c r="I149" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="J149" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="K149" s="3" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="R149" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S149">
         <v>381</v>
@@ -8733,16 +9333,16 @@
         <v>386</v>
       </c>
       <c r="I153" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="J153" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K153" s="3" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="R153" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S153">
         <v>210</v>
@@ -8768,13 +9368,13 @@
         <v>387</v>
       </c>
       <c r="I157" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="K157" s="3" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="R157" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S157">
         <v>48</v>
@@ -8803,13 +9403,13 @@
         <v>355</v>
       </c>
       <c r="I158" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="K158" s="3" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="R158" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="S158">
         <v>77</v>
@@ -8838,13 +9438,13 @@
         <v>355</v>
       </c>
       <c r="I159" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="K159" s="3" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="R159" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S159">
         <v>168</v>
@@ -8876,16 +9476,16 @@
         <v>425</v>
       </c>
       <c r="I160" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="J160" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="K160" s="3" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="R160" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="S160">
         <v>25</v>
@@ -8914,13 +9514,13 @@
         <v>355</v>
       </c>
       <c r="I161" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="K161" s="3" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="R161" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S161">
         <v>69</v>
@@ -8949,16 +9549,16 @@
         <v>343</v>
       </c>
       <c r="I163" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="J163" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="K163" s="3" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="R163" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S163">
         <v>381</v>
@@ -8987,16 +9587,16 @@
         <v>350</v>
       </c>
       <c r="I167" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="J167" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="K167" s="3" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="R167" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S167">
         <v>207</v>
@@ -9025,13 +9625,13 @@
         <v>389</v>
       </c>
       <c r="I171" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="K171" s="3" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="R171" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="V171">
         <v>3</v>
@@ -9054,16 +9654,16 @@
         <v>390</v>
       </c>
       <c r="I175" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="J175" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="K175" s="3" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="R175" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S175">
         <v>375</v>
@@ -9092,16 +9692,16 @@
         <v>338</v>
       </c>
       <c r="I179" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="J179" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="K179" s="3" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="R179" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="S179">
         <v>67</v>
@@ -9130,13 +9730,13 @@
         <v>391</v>
       </c>
       <c r="I180" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="K180" s="3" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="R180" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="S180">
         <v>100</v>
@@ -9165,16 +9765,16 @@
         <v>392</v>
       </c>
       <c r="I181" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="J181" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="K181" s="3" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="R181" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="S181">
         <v>162</v>
@@ -9203,16 +9803,16 @@
         <v>393</v>
       </c>
       <c r="I182" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="J182" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="K182" s="3" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="R182" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="S182">
         <v>65</v>
@@ -9241,13 +9841,13 @@
         <v>394</v>
       </c>
       <c r="I183" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="K183" s="3" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="R183" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S183">
         <v>162</v>
@@ -9276,19 +9876,19 @@
         <v>337</v>
       </c>
       <c r="I184" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="J184" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="K184" s="3" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="L184" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="R184" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="S184">
         <v>209</v>
@@ -9317,19 +9917,19 @@
         <v>337</v>
       </c>
       <c r="I185" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="J185" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="K185" s="3" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="L185" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="R185" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="S185">
         <v>211</v>
@@ -9358,16 +9958,16 @@
         <v>395</v>
       </c>
       <c r="I186" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="J186" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="K186" s="3" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="R186" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="S186">
         <v>99</v>
@@ -9396,16 +9996,16 @@
         <v>395</v>
       </c>
       <c r="I187" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="J187" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="K187" s="3" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="R187" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="S187">
         <v>135</v>
@@ -9434,13 +10034,13 @@
         <v>338</v>
       </c>
       <c r="I188" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="K188" s="3" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="R188" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S188">
         <v>215</v>
@@ -9469,13 +10069,13 @@
         <v>396</v>
       </c>
       <c r="I189" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="K189" s="3" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="R189" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S189">
         <v>22</v>
@@ -9504,13 +10104,13 @@
         <v>397</v>
       </c>
       <c r="I193" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="K193" s="3" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="R193" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S193">
         <v>302</v>
@@ -9539,16 +10139,16 @@
         <v>398</v>
       </c>
       <c r="I197" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="J197" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K197" s="3" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="R197" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S197">
         <v>133</v>
@@ -9580,10 +10180,10 @@
         <v>511</v>
       </c>
       <c r="K201" s="3" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="R201" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="S201">
         <v>239</v>
@@ -9612,16 +10212,16 @@
         <v>396</v>
       </c>
       <c r="I205" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="J205" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K205" s="3" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="R205" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S205">
         <v>241</v>
@@ -9650,16 +10250,16 @@
         <v>345</v>
       </c>
       <c r="I208" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="J208" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="K208" s="3" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="R208" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S208">
         <v>188</v>
@@ -9688,13 +10288,13 @@
         <v>399</v>
       </c>
       <c r="I212" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="K212" s="3" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="R212" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="S212">
         <v>376</v>
@@ -9723,13 +10323,13 @@
         <v>400</v>
       </c>
       <c r="I216" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="K216" s="3" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="R216" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="S216">
         <v>14</v>
@@ -9758,16 +10358,16 @@
         <v>358</v>
       </c>
       <c r="I220" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="J220" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="K220" s="3" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="R220" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="S220">
         <v>31</v>
@@ -9796,16 +10396,16 @@
         <v>358</v>
       </c>
       <c r="I221" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="J221" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="K221" s="3" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="R221" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S221">
         <v>43</v>
@@ -9834,16 +10434,16 @@
         <v>343</v>
       </c>
       <c r="I222" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="J222" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="K222" s="3" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="R222" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="S222">
         <v>207</v>
@@ -9872,16 +10472,16 @@
         <v>356</v>
       </c>
       <c r="I223" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="J223" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="K223" s="3" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="R223" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S223">
         <v>65</v>
@@ -9910,16 +10510,16 @@
         <v>401</v>
       </c>
       <c r="I224" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="J224" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="K224" s="3" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="R224" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S224">
         <v>89</v>
@@ -9948,13 +10548,13 @@
         <v>402</v>
       </c>
       <c r="I225" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="K225" s="3" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="R225" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="S225">
         <v>6</v>
@@ -9983,16 +10583,16 @@
         <v>342</v>
       </c>
       <c r="I229" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="J229" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="K229" s="3" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="R229" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S229">
         <v>57</v>
@@ -10021,16 +10621,16 @@
         <v>403</v>
       </c>
       <c r="I230" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="J230" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="K230" s="3" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="R230" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S230">
         <v>66</v>
@@ -10059,16 +10659,16 @@
         <v>404</v>
       </c>
       <c r="I233" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="J233" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="K233" s="3" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="R233" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S233">
         <v>63</v>
@@ -10097,16 +10697,16 @@
         <v>356</v>
       </c>
       <c r="I237" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="J237" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="K237" s="3" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="R237" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="S237">
         <v>24</v>
@@ -10135,16 +10735,16 @@
         <v>405</v>
       </c>
       <c r="I238" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="J238" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="K238" s="3" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="R238" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S238">
         <v>136</v>
@@ -10173,16 +10773,16 @@
         <v>391</v>
       </c>
       <c r="I239" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="J239" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="K239" s="3" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="R239" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S239">
         <v>216</v>
@@ -10211,16 +10811,16 @@
         <v>406</v>
       </c>
       <c r="I241" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="J241" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="K241" s="3" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="R241" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S241">
         <v>99</v>
@@ -10249,16 +10849,16 @@
         <v>407</v>
       </c>
       <c r="I242" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="J242" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="K242" s="3" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="R242" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S242">
         <v>94</v>
@@ -10287,16 +10887,16 @@
         <v>391</v>
       </c>
       <c r="I243" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="J243" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="K243" s="3" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="R243" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S243">
         <v>95</v>
@@ -10325,16 +10925,16 @@
         <v>408</v>
       </c>
       <c r="I244" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="J244" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="K244" s="3" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="R244" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S244">
         <v>145</v>
@@ -10363,16 +10963,16 @@
         <v>355</v>
       </c>
       <c r="I245" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="J245" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="K245" s="3" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="R245" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S245">
         <v>71</v>
@@ -10398,13 +10998,13 @@
         <v>337</v>
       </c>
       <c r="I249" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="K249" s="3" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="R249" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S249">
         <v>109</v>
@@ -10433,16 +11033,16 @@
         <v>343</v>
       </c>
       <c r="I253" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="J253" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="K253" s="3" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="R253" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S253">
         <v>100</v>
@@ -10471,16 +11071,16 @@
         <v>409</v>
       </c>
       <c r="I257" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="J257" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="K257" s="3" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="R257" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S257">
         <v>340</v>
@@ -10509,16 +11109,16 @@
         <v>337</v>
       </c>
       <c r="I261" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="J261" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="K261" s="3" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="R261" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S261">
         <v>204</v>
@@ -10547,16 +11147,16 @@
         <v>337</v>
       </c>
       <c r="I265" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="J265" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="K265" s="3" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="R265" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S265">
         <v>64</v>
@@ -10585,16 +11185,16 @@
         <v>410</v>
       </c>
       <c r="I269" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="J269" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="K269" s="3" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="R269" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S269">
         <v>313</v>
@@ -10626,13 +11226,13 @@
         <v>511</v>
       </c>
       <c r="J273" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="K273" s="3" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="R273" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="S273">
         <v>26</v>
@@ -10658,13 +11258,13 @@
         <v>412</v>
       </c>
       <c r="I277" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="K277" s="3" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="R277" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="V277">
         <v>3</v>
@@ -10687,16 +11287,16 @@
         <v>359</v>
       </c>
       <c r="I281" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="J281" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="K281" s="3" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="R281" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S281">
         <v>416</v>
@@ -10725,16 +11325,16 @@
         <v>337</v>
       </c>
       <c r="I282" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="J282" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="K282" s="3" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="R282" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S282">
         <v>210</v>
@@ -10760,22 +11360,22 @@
         <v>413</v>
       </c>
       <c r="I283" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="J283" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="K283" s="3" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="R283" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S283" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="T283" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="V283">
         <v>1</v>
@@ -10798,16 +11398,16 @@
         <v>343</v>
       </c>
       <c r="I284" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="J284" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="K284" s="3" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="R284" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S284">
         <v>149</v>
@@ -10836,16 +11436,16 @@
         <v>414</v>
       </c>
       <c r="I285" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="J285" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="K285" s="3" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="R285" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S285">
         <v>365</v>
@@ -10874,16 +11474,16 @@
         <v>415</v>
       </c>
       <c r="I298" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="J298" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="K298" s="3" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="R298" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="V298">
         <v>2</v>
@@ -10906,13 +11506,13 @@
         <v>337</v>
       </c>
       <c r="I306" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="K306" s="3" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="R306" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S306">
         <v>116</v>
@@ -10941,16 +11541,16 @@
         <v>391</v>
       </c>
       <c r="I310" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="J310" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="K310" s="3" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="R310" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S310">
         <v>107</v>
@@ -10979,16 +11579,16 @@
         <v>416</v>
       </c>
       <c r="I311" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="J311" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="K311" s="3" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="R311" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="S311">
         <v>500</v>
@@ -11017,16 +11617,16 @@
         <v>355</v>
       </c>
       <c r="I312" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="J312" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="K312" s="3" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="R312" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S312">
         <v>82</v>
@@ -11052,16 +11652,16 @@
         <v>417</v>
       </c>
       <c r="I322" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="J322" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="K322" s="3" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="R322" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="T322">
         <v>700</v>
@@ -11087,16 +11687,16 @@
         <v>418</v>
       </c>
       <c r="I330" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="J330" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="K330" s="3" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="R330" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="V330">
         <v>3</v>
@@ -11119,13 +11719,13 @@
         <v>376</v>
       </c>
       <c r="I334" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="K334" s="3" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="R334" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S334">
         <v>115</v>
@@ -11154,13 +11754,13 @@
         <v>419</v>
       </c>
       <c r="I338" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="K338" s="3" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="R338" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S338">
         <v>42</v>
@@ -11189,13 +11789,13 @@
         <v>420</v>
       </c>
       <c r="I342" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="K342" s="3" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="R342" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S342">
         <v>32</v>
@@ -11224,16 +11824,16 @@
         <v>356</v>
       </c>
       <c r="I346" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="J346" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="K346" s="3" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="R346" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S346">
         <v>85</v>
@@ -11262,16 +11862,16 @@
         <v>421</v>
       </c>
       <c r="I350" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="J350" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="K350" s="3" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="R350" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="S350">
         <v>301</v>
@@ -11300,16 +11900,16 @@
         <v>404</v>
       </c>
       <c r="I354" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="J354" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="K354" s="3" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="R354" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S354">
         <v>118</v>
@@ -11341,13 +11941,13 @@
         <v>530</v>
       </c>
       <c r="J355" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="K355" s="3" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="R355" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S355">
         <v>245</v>
@@ -11376,16 +11976,16 @@
         <v>350</v>
       </c>
       <c r="I356" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="J356" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="K356" s="3" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="R356" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S356">
         <v>119</v>
@@ -11414,16 +12014,16 @@
         <v>340</v>
       </c>
       <c r="I365" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="J365" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="K365" s="3" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="R365" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S365">
         <v>206</v>
@@ -11452,16 +12052,16 @@
         <v>355</v>
       </c>
       <c r="I366" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="J366" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="K366" s="3" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="R366" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S366">
         <v>677</v>
@@ -11490,16 +12090,16 @@
         <v>359</v>
       </c>
       <c r="I367" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="J367" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="K367" s="3" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="R367" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="S367">
         <v>555</v>
@@ -11641,102 +12241,116 @@
     <hyperlink ref="K113" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
     <hyperlink ref="K114" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
     <hyperlink ref="K115" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="K124" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="K128" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="K132" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="K133" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="K136" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="K140" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="K141" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="K142" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="K143" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="K144" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="K145" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="K149" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="K153" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="K157" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="K158" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="K159" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="K160" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="K161" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="K163" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="K167" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="K171" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="K175" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="K179" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="K180" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="K181" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="K182" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="K183" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="K184" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="K185" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="K186" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="K187" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="K188" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="K189" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="K193" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="K197" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="K201" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="K205" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="K208" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="K212" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="K216" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="K220" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="K221" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="K222" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="K223" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="K224" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="K225" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="K229" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="K230" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="K233" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="K237" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="K238" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="K239" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="K241" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="K242" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="K243" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="K244" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="K245" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="K249" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="K253" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="K257" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="K261" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="K265" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="K269" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="K273" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="K277" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="K281" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="K282" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="K283" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="K284" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="K285" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="K298" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="K306" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="K310" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="K311" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="K312" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="K322" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="K330" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="K334" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="K338" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="K342" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="K346" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="K350" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="K354" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="K355" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="K356" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="K365" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="K366" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="K367" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="K116" r:id="rId217" xr:uid="{02662092-E6C0-454A-8489-C97E5956E980}"/>
-    <hyperlink ref="K117" r:id="rId218" xr:uid="{FE70B001-8889-4AB8-9D4D-839ABB365E11}"/>
-    <hyperlink ref="K118" r:id="rId219" xr:uid="{66ED02C8-B796-4F9B-AC1C-81DC93F9F63E}"/>
-    <hyperlink ref="K119" r:id="rId220" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Jean_Clouet_-_Homme_au_P%C3%A9trarque_-_Royal_Collection.jpg/960px-Jean_Clouet_-_Homme_au_P%C3%A9trarque_-_Royal_Collection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9FEF5F6E-A8F1-45AC-95BC-DF3E82B41AB8}"/>
-    <hyperlink ref="K120" r:id="rId221" xr:uid="{E91CBA31-66A1-42A0-B75D-026F69F47838}"/>
-    <hyperlink ref="K121" r:id="rId222" xr:uid="{6F6B6D57-B58A-4E2A-80AF-D4A48207B5E8}"/>
-    <hyperlink ref="K122" r:id="rId223" xr:uid="{C16EBAE4-5B88-42A7-9D43-716CE6FA6944}"/>
-    <hyperlink ref="K123" r:id="rId224" xr:uid="{DB845F8C-A74D-4614-9577-F6D44008AC95}"/>
+    <hyperlink ref="K140" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="K141" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="K142" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="K143" r:id="rId132" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="K144" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="K145" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="K149" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="K153" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="K157" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="K158" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="K159" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="K160" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="K161" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="K163" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="K167" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="K171" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="K175" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="K179" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="K180" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="K181" r:id="rId148" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="K182" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="K183" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="K184" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="K185" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="K186" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="K187" r:id="rId154" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="K188" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="K189" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="K193" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="K197" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="K201" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="K205" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="K208" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="K212" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="K216" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="K220" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="K221" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="K222" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="K223" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="K224" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="K225" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="K229" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="K230" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="K233" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="K237" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="K238" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="K239" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="K241" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="K242" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="K243" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="K244" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="K245" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="K249" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="K253" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="K257" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="K261" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="K265" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="K269" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="K273" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="K277" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="K281" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="K282" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="K283" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="K284" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="K285" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="K298" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="K306" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="K310" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="K311" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="K312" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="K322" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="K330" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="K334" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="K338" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="K342" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="K346" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="K350" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="K354" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="K355" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="K356" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="K365" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="K366" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="K367" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="K116" r:id="rId212" xr:uid="{02662092-E6C0-454A-8489-C97E5956E980}"/>
+    <hyperlink ref="K117" r:id="rId213" xr:uid="{FE70B001-8889-4AB8-9D4D-839ABB365E11}"/>
+    <hyperlink ref="K118" r:id="rId214" xr:uid="{66ED02C8-B796-4F9B-AC1C-81DC93F9F63E}"/>
+    <hyperlink ref="K119" r:id="rId215" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Jean_Clouet_-_Homme_au_P%C3%A9trarque_-_Royal_Collection.jpg/960px-Jean_Clouet_-_Homme_au_P%C3%A9trarque_-_Royal_Collection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9FEF5F6E-A8F1-45AC-95BC-DF3E82B41AB8}"/>
+    <hyperlink ref="K120" r:id="rId216" xr:uid="{E91CBA31-66A1-42A0-B75D-026F69F47838}"/>
+    <hyperlink ref="K121" r:id="rId217" xr:uid="{6F6B6D57-B58A-4E2A-80AF-D4A48207B5E8}"/>
+    <hyperlink ref="K122" r:id="rId218" xr:uid="{C16EBAE4-5B88-42A7-9D43-716CE6FA6944}"/>
+    <hyperlink ref="K123" r:id="rId219" xr:uid="{DB845F8C-A74D-4614-9577-F6D44008AC95}"/>
+    <hyperlink ref="K124" r:id="rId220" xr:uid="{92549383-27C3-4F61-A9DB-B3470EC9C7BB}"/>
+    <hyperlink ref="K125" r:id="rId221" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Lucas_Cranach_d.%C3%84._-_Drei_Grazien%2C_1531_%28Mus%C3%A9e_du_Louvre%29.jpg/960px-Lucas_Cranach_d.%C3%84._-_Drei_Grazien%2C_1531_%28Mus%C3%A9e_du_Louvre%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BA392A0D-A372-4452-B4F0-446BE48BF915}"/>
+    <hyperlink ref="K126" r:id="rId222" xr:uid="{A26CAA22-30CC-49F9-8A79-BF0616655E6A}"/>
+    <hyperlink ref="M127" r:id="rId223" xr:uid="{D8816BFE-C9EA-4A20-B9E3-168A8072DE0C}"/>
+    <hyperlink ref="O127" r:id="rId224" xr:uid="{0ABE8A7B-1146-44AD-A4C2-809A18C5F922}"/>
+    <hyperlink ref="K127" r:id="rId225" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/Lucas_Cranach_d.%C3%84._-_Reformationsaltar%2C_St._Marien_zu_Wittenberg%2C_Mitteltafel.jpg/1280px-Lucas_Cranach_d.%C3%84._-_Reformationsaltar%2C_St._Marien_zu_Wittenberg%2C_Mitteltafel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CFC5ADDC-3DE3-4F3A-830C-50BCAFB9387E}"/>
+    <hyperlink ref="K128" r:id="rId226" xr:uid="{AFB28BBD-2AE3-4A4B-B6E3-16B51831D1E0}"/>
+    <hyperlink ref="M129" r:id="rId227" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/04/Weimar_-_Altar_in_St._Peter_und_Paul%2C_Weimar_by_Cranachs_-_Central_piece.jpg/1280px-Weimar_-_Altar_in_St._Peter_und_Paul%2C_Weimar_by_Cranachs_-_Central_piece.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0FF39A6F-DB2C-4A0F-A026-E0DC6B29B9C5}"/>
+    <hyperlink ref="K129" r:id="rId228" xr:uid="{A5655B2E-9461-46DC-906C-986678462AB9}"/>
+    <hyperlink ref="K130" r:id="rId229" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9a/Cranach_the_Younger%2C_Lucas_-_Christ_and_the_adulteress.jpg/1280px-Cranach_the_Younger%2C_Lucas_-_Christ_and_the_adulteress.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{20501BF6-5553-4FF4-83B7-1C44D78B7395}"/>
+    <hyperlink ref="K131" r:id="rId230" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Lucas_Cranach_the_Younger_-_Prince_Elector_Moritz_of_Saxony_-_Google_Art_Project.jpg/960px-Lucas_Cranach_the_Younger_-_Prince_Elector_Moritz_of_Saxony_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2A38A1E4-BADE-4B55-B19D-74F39A6EB955}"/>
+    <hyperlink ref="K132" r:id="rId231" xr:uid="{99D941CE-18C5-4C46-A37E-C357A87E55CA}"/>
+    <hyperlink ref="K133" r:id="rId232" xr:uid="{33E2761B-FD91-42EF-A344-D48F8FAD69C5}"/>
+    <hyperlink ref="K134" r:id="rId233" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Antonio_Allegri%2C_called_Correggio_-_Jupiter_and_Io_-_Google_Art_Project.jpg/500px-Antonio_Allegri%2C_called_Correggio_-_Jupiter_and_Io_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A974AF6C-8C43-4842-B137-FD08EF68FE9B}"/>
+    <hyperlink ref="K135" r:id="rId234" xr:uid="{71DF1715-70D1-4D44-9851-AB0EF86AC473}"/>
+    <hyperlink ref="K136" r:id="rId235" xr:uid="{7F6733B0-AD5E-4F26-8851-7B6246C790A8}"/>
+    <hyperlink ref="K137" r:id="rId236" xr:uid="{71D663C2-7F30-4928-87F0-CD9CF31008D3}"/>
+    <hyperlink ref="K138" r:id="rId237" xr:uid="{F3FD869E-7EFF-4F18-946E-44B80BFB9D47}"/>
+    <hyperlink ref="K139" r:id="rId238" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/David_and_Goliath_by_Daniele_da_Volterra_%28Louvre_INV_566%29_verso_02.jpg/1280px-David_and_Goliath_by_Daniele_da_Volterra_%28Louvre_INV_566%29_verso_02.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{53E930F4-DA77-41E2-93AF-DDEC287F81CB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B254099A-BA68-471D-8BF0-48CBE9D7A587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AF687E-ECC7-44C9-ACFD-C6EF5378E96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3881,9 +3881,6 @@
     <t>1552-1553</t>
   </si>
   <si>
-    <t>Accademia Carrara</t>
-  </si>
-  <si>
     <t>Portrait d'Isotta Brembati</t>
   </si>
   <si>
@@ -5112,6 +5109,9 @@
   </si>
   <si>
     <t>Décoration de plafond</t>
+  </si>
+  <si>
+    <t>Académie Carrara</t>
   </si>
 </sst>
 </file>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="10" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>367</v>
@@ -10519,7 +10519,7 @@
         <v>514</v>
       </c>
       <c r="L96" s="13" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
@@ -19162,19 +19162,19 @@
         <v>1112</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>1282</v>
+        <v>1692</v>
       </c>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
       <c r="I267" s="2"/>
       <c r="J267" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="K267" s="2" t="s">
         <v>1283</v>
       </c>
-      <c r="K267" s="2" t="s">
+      <c r="L267" s="4" t="s">
         <v>1284</v>
-      </c>
-      <c r="L267" s="4" t="s">
-        <v>1285</v>
       </c>
       <c r="M267" s="2"/>
       <c r="N267" s="2"/>
@@ -19188,7 +19188,7 @@
         <v>32</v>
       </c>
       <c r="T267" s="10" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="U267" s="10" t="s">
         <v>1275</v>
@@ -19203,29 +19203,29 @@
         <v>380</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="10" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
       <c r="I268" s="2"/>
       <c r="J268" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="K268" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="K268" s="2" t="s">
+      <c r="L268" s="4" t="s">
         <v>1291</v>
-      </c>
-      <c r="L268" s="4" t="s">
-        <v>1292</v>
       </c>
       <c r="M268" s="2"/>
       <c r="N268" s="2"/>
@@ -19233,16 +19233,16 @@
       <c r="P268" s="2"/>
       <c r="Q268" s="2"/>
       <c r="R268" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="S268" s="2" t="s">
         <v>117</v>
       </c>
       <c r="T268" s="10" t="s">
+        <v>1293</v>
+      </c>
+      <c r="U268" s="10" t="s">
         <v>1294</v>
-      </c>
-      <c r="U268" s="10" t="s">
-        <v>1295</v>
       </c>
       <c r="V268" s="10"/>
       <c r="W268" s="10">
@@ -19254,11 +19254,11 @@
         <v>380</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="10" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>305</v>
@@ -19270,13 +19270,13 @@
       <c r="H269" s="2"/>
       <c r="I269" s="2"/>
       <c r="J269" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="K269" s="2" t="s">
         <v>1297</v>
       </c>
-      <c r="K269" s="2" t="s">
+      <c r="L269" s="4" t="s">
         <v>1298</v>
-      </c>
-      <c r="L269" s="4" t="s">
-        <v>1299</v>
       </c>
       <c r="M269" s="2"/>
       <c r="N269" s="2"/>
@@ -19290,7 +19290,7 @@
         <v>117</v>
       </c>
       <c r="T269" s="10" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="U269" s="10" t="s">
         <v>1275</v>
@@ -19305,11 +19305,11 @@
         <v>380</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="10" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>295</v>
@@ -19327,7 +19327,7 @@
         <v>608</v>
       </c>
       <c r="L270" s="4" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="M270" s="2"/>
       <c r="N270" s="2"/>
@@ -19356,29 +19356,29 @@
         <v>380</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="10" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E271" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F271" s="2" t="s">
         <v>1303</v>
-      </c>
-      <c r="F271" s="2" t="s">
-        <v>1304</v>
       </c>
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
       <c r="I271" s="2"/>
       <c r="J271" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="K271" s="2" t="s">
         <v>1305</v>
       </c>
-      <c r="K271" s="2" t="s">
+      <c r="L271" s="4" t="s">
         <v>1306</v>
-      </c>
-      <c r="L271" s="4" t="s">
-        <v>1307</v>
       </c>
       <c r="M271" s="2"/>
       <c r="N271" s="2"/>
@@ -19392,10 +19392,10 @@
         <v>32</v>
       </c>
       <c r="T271" s="10" t="s">
+        <v>1307</v>
+      </c>
+      <c r="U271" s="10" t="s">
         <v>1308</v>
-      </c>
-      <c r="U271" s="10" t="s">
-        <v>1309</v>
       </c>
       <c r="V271" s="10"/>
       <c r="W271" s="10">
@@ -19407,11 +19407,11 @@
         <v>466</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="10" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>26</v>
@@ -19423,13 +19423,13 @@
       <c r="H272" s="2"/>
       <c r="I272" s="2"/>
       <c r="J272" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="K272" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="K272" s="2" t="s">
+      <c r="L272" s="4" t="s">
         <v>1313</v>
-      </c>
-      <c r="L272" s="4" t="s">
-        <v>1314</v>
       </c>
       <c r="M272" s="2"/>
       <c r="N272" s="2"/>
@@ -19458,7 +19458,7 @@
         <v>466</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="10" t="s">
@@ -19468,19 +19468,19 @@
         <v>213</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G273" s="2"/>
       <c r="H273" s="2"/>
       <c r="I273" s="2"/>
       <c r="J273" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K273" s="2" t="s">
         <v>1316</v>
       </c>
-      <c r="K273" s="2" t="s">
+      <c r="L273" s="4" t="s">
         <v>1317</v>
-      </c>
-      <c r="L273" s="4" t="s">
-        <v>1318</v>
       </c>
       <c r="M273" s="2"/>
       <c r="N273" s="2"/>
@@ -19494,7 +19494,7 @@
         <v>117</v>
       </c>
       <c r="T273" s="10" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="U273" s="10" t="s">
         <v>1269</v>
@@ -19509,11 +19509,11 @@
         <v>466</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="10" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>26</v>
@@ -19528,10 +19528,10 @@
         <v>188</v>
       </c>
       <c r="K274" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="L274" s="4" t="s">
         <v>1321</v>
-      </c>
-      <c r="L274" s="4" t="s">
-        <v>1322</v>
       </c>
       <c r="M274" s="2"/>
       <c r="N274" s="2"/>
@@ -19545,10 +19545,10 @@
         <v>117</v>
       </c>
       <c r="T274" s="10" t="s">
+        <v>1322</v>
+      </c>
+      <c r="U274" s="10" t="s">
         <v>1323</v>
-      </c>
-      <c r="U274" s="10" t="s">
-        <v>1324</v>
       </c>
       <c r="V274" s="10"/>
       <c r="W274" s="10">
@@ -19560,11 +19560,11 @@
         <v>466</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="10" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>46</v>
@@ -19579,10 +19579,10 @@
         <v>704</v>
       </c>
       <c r="K275" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="L275" s="4" t="s">
         <v>1326</v>
-      </c>
-      <c r="L275" s="4" t="s">
-        <v>1327</v>
       </c>
       <c r="M275" s="2"/>
       <c r="N275" s="2"/>
@@ -19596,10 +19596,10 @@
         <v>117</v>
       </c>
       <c r="T275" s="10" t="s">
+        <v>1327</v>
+      </c>
+      <c r="U275" s="10" t="s">
         <v>1328</v>
-      </c>
-      <c r="U275" s="10" t="s">
-        <v>1329</v>
       </c>
       <c r="V275" s="10"/>
       <c r="W275" s="10">
@@ -19611,11 +19611,11 @@
         <v>466</v>
       </c>
       <c r="B276" s="14" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C276" s="14"/>
       <c r="D276" s="15" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="E276" s="14" t="s">
         <v>1238</v>
@@ -19630,10 +19630,10 @@
         <v>399</v>
       </c>
       <c r="K276" s="14" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L276" s="16" t="s">
         <v>1331</v>
-      </c>
-      <c r="L276" s="16" t="s">
-        <v>1332</v>
       </c>
       <c r="M276" s="14"/>
       <c r="N276" s="14"/>
@@ -19662,11 +19662,11 @@
         <v>466</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" s="10" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>529</v>
@@ -19678,13 +19678,13 @@
       <c r="H277" s="2"/>
       <c r="I277" s="2"/>
       <c r="J277" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="K277" s="2" t="s">
         <v>1334</v>
       </c>
-      <c r="K277" s="2" t="s">
+      <c r="L277" s="4" t="s">
         <v>1335</v>
-      </c>
-      <c r="L277" s="4" t="s">
-        <v>1336</v>
       </c>
       <c r="M277" s="2"/>
       <c r="N277" s="2"/>
@@ -19698,10 +19698,10 @@
         <v>117</v>
       </c>
       <c r="T277" s="10" t="s">
+        <v>1336</v>
+      </c>
+      <c r="U277" s="10" t="s">
         <v>1337</v>
-      </c>
-      <c r="U277" s="10" t="s">
-        <v>1338</v>
       </c>
       <c r="V277" s="10"/>
       <c r="W277" s="10">
@@ -19713,11 +19713,11 @@
         <v>466</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" s="10" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>234</v>
@@ -19729,13 +19729,13 @@
       <c r="H278" s="2"/>
       <c r="I278" s="2"/>
       <c r="J278" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K278" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="L278" s="4" t="s">
         <v>1339</v>
-      </c>
-      <c r="K278" s="2" t="s">
-        <v>1339</v>
-      </c>
-      <c r="L278" s="4" t="s">
-        <v>1340</v>
       </c>
       <c r="M278" s="2"/>
       <c r="N278" s="2"/>
@@ -19749,7 +19749,7 @@
         <v>117</v>
       </c>
       <c r="T278" s="10" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="U278" s="10" t="s">
         <v>854</v>
@@ -19764,11 +19764,11 @@
         <v>466</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" s="10" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>75</v>
@@ -19780,13 +19780,13 @@
       <c r="H279" s="2"/>
       <c r="I279" s="2"/>
       <c r="J279" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="K279" s="2" t="s">
         <v>1343</v>
       </c>
-      <c r="K279" s="2" t="s">
+      <c r="L279" s="4" t="s">
         <v>1344</v>
-      </c>
-      <c r="L279" s="4" t="s">
-        <v>1345</v>
       </c>
       <c r="M279" s="2"/>
       <c r="N279" s="2"/>
@@ -19800,10 +19800,10 @@
         <v>117</v>
       </c>
       <c r="T279" s="10" t="s">
+        <v>1345</v>
+      </c>
+      <c r="U279" s="10" t="s">
         <v>1346</v>
-      </c>
-      <c r="U279" s="10" t="s">
-        <v>1347</v>
       </c>
       <c r="V279" s="10"/>
       <c r="W279" s="10">
@@ -19815,17 +19815,17 @@
         <v>380</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" s="10" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>142</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G280" s="2"/>
       <c r="H280" s="2"/>
@@ -19837,7 +19837,7 @@
         <v>332</v>
       </c>
       <c r="L280" s="8" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="M280" s="2"/>
       <c r="N280" s="2"/>
@@ -19866,29 +19866,29 @@
         <v>380</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" s="10" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E281" s="2" t="s">
         <v>1352</v>
       </c>
-      <c r="E281" s="2" t="s">
+      <c r="F281" s="2" t="s">
         <v>1353</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>1354</v>
       </c>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
       <c r="I281" s="2"/>
       <c r="J281" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="K281" s="2" t="s">
         <v>1355</v>
       </c>
-      <c r="K281" s="2" t="s">
+      <c r="L281" s="4" t="s">
         <v>1356</v>
-      </c>
-      <c r="L281" s="4" t="s">
-        <v>1357</v>
       </c>
       <c r="M281" s="2"/>
       <c r="N281" s="2"/>
@@ -19917,29 +19917,29 @@
         <v>380</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" s="10" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E282" s="2" t="s">
         <v>1358</v>
       </c>
-      <c r="E282" s="2" t="s">
+      <c r="F282" s="2" t="s">
         <v>1359</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>1360</v>
       </c>
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
       <c r="I282" s="2"/>
       <c r="J282" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="K282" s="2" t="s">
         <v>1361</v>
       </c>
-      <c r="K282" s="2" t="s">
+      <c r="L282" s="4" t="s">
         <v>1362</v>
-      </c>
-      <c r="L282" s="4" t="s">
-        <v>1363</v>
       </c>
       <c r="M282" s="2"/>
       <c r="N282" s="2"/>
@@ -19950,7 +19950,7 @@
         <v>173</v>
       </c>
       <c r="S282" s="2" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="T282" s="10">
         <v>461</v>
@@ -19968,29 +19968,29 @@
         <v>380</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" s="10" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E283" s="2" t="s">
         <v>1365</v>
       </c>
-      <c r="E283" s="2" t="s">
+      <c r="F283" s="2" t="s">
         <v>1366</v>
-      </c>
-      <c r="F283" s="2" t="s">
-        <v>1367</v>
       </c>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
       <c r="I283" s="2"/>
       <c r="J283" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="K283" s="2" t="s">
         <v>1368</v>
       </c>
-      <c r="K283" s="2" t="s">
+      <c r="L283" s="4" t="s">
         <v>1369</v>
-      </c>
-      <c r="L283" s="4" t="s">
-        <v>1370</v>
       </c>
       <c r="M283" s="2"/>
       <c r="N283" s="2"/>
@@ -20019,11 +20019,11 @@
         <v>380</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" s="10" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>142</v>
@@ -20035,13 +20035,13 @@
       <c r="H284" s="2"/>
       <c r="I284" s="2"/>
       <c r="J284" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="K284" s="2" t="s">
         <v>1372</v>
       </c>
-      <c r="K284" s="2" t="s">
+      <c r="L284" s="4" t="s">
         <v>1373</v>
-      </c>
-      <c r="L284" s="4" t="s">
-        <v>1374</v>
       </c>
       <c r="M284" s="2"/>
       <c r="N284" s="2"/>
@@ -20070,11 +20070,11 @@
         <v>380</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" s="10" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>893</v>
@@ -20086,13 +20086,13 @@
       <c r="H285" s="2"/>
       <c r="I285" s="2"/>
       <c r="J285" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="K285" s="2" t="s">
         <v>1376</v>
       </c>
-      <c r="K285" s="2" t="s">
+      <c r="L285" s="4" t="s">
         <v>1377</v>
-      </c>
-      <c r="L285" s="4" t="s">
-        <v>1378</v>
       </c>
       <c r="M285" s="2"/>
       <c r="N285" s="2"/>
@@ -20103,7 +20103,7 @@
         <v>31</v>
       </c>
       <c r="S285" s="2" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="T285" s="10">
         <v>92</v>
@@ -20121,7 +20121,7 @@
         <v>380</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" s="10" t="s">
@@ -20140,10 +20140,10 @@
         <v>1114</v>
       </c>
       <c r="K286" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="L286" s="4" t="s">
         <v>1380</v>
-      </c>
-      <c r="L286" s="4" t="s">
-        <v>1381</v>
       </c>
       <c r="M286" s="2"/>
       <c r="N286" s="2"/>
@@ -20151,7 +20151,7 @@
       <c r="P286" s="2"/>
       <c r="Q286" s="2"/>
       <c r="R286" s="2" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="S286" s="2" t="s">
         <v>117</v>
@@ -20172,29 +20172,29 @@
         <v>380</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" s="10" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>142</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
       <c r="I287" s="2"/>
       <c r="J287" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="K287" s="2" t="s">
         <v>1385</v>
       </c>
-      <c r="K287" s="2" t="s">
+      <c r="L287" s="4" t="s">
         <v>1386</v>
-      </c>
-      <c r="L287" s="4" t="s">
-        <v>1387</v>
       </c>
       <c r="M287" s="2"/>
       <c r="N287" s="2"/>
@@ -20223,27 +20223,27 @@
         <v>1162</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" s="10" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E288" s="2"/>
       <c r="F288" s="2" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="G288" s="2"/>
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
       <c r="J288" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="K288" s="2" t="s">
         <v>1391</v>
       </c>
-      <c r="K288" s="2" t="s">
+      <c r="L288" s="4" t="s">
         <v>1392</v>
-      </c>
-      <c r="L288" s="4" t="s">
-        <v>1393</v>
       </c>
       <c r="M288" s="2"/>
       <c r="N288" s="2"/>
@@ -20254,7 +20254,7 @@
         <v>173</v>
       </c>
       <c r="S288" s="2" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="T288" s="10"/>
       <c r="U288" s="10"/>
@@ -20268,15 +20268,15 @@
         <v>1162</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" s="10" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E289" s="2"/>
       <c r="F289" s="2" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
@@ -20288,7 +20288,7 @@
         <v>357</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="M289" s="2"/>
       <c r="N289" s="2"/>
@@ -20299,7 +20299,7 @@
         <v>173</v>
       </c>
       <c r="S289" s="2" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="T289" s="10"/>
       <c r="U289" s="10"/>
@@ -20313,29 +20313,29 @@
         <v>1162</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" s="10" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E290" s="2" t="s">
         <v>1397</v>
       </c>
-      <c r="E290" s="2" t="s">
+      <c r="F290" s="2" t="s">
         <v>1398</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>1399</v>
       </c>
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
       <c r="I290" s="2"/>
       <c r="J290" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K290" s="2" t="s">
         <v>1400</v>
       </c>
-      <c r="K290" s="2" t="s">
+      <c r="L290" s="4" t="s">
         <v>1401</v>
-      </c>
-      <c r="L290" s="4" t="s">
-        <v>1402</v>
       </c>
       <c r="M290" s="2"/>
       <c r="N290" s="2"/>
@@ -20349,10 +20349,10 @@
         <v>32</v>
       </c>
       <c r="T290" s="10" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="U290" s="10" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="V290" s="10"/>
       <c r="W290" s="10">
@@ -20364,11 +20364,11 @@
         <v>1162</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" s="10" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>719</v>
@@ -20380,13 +20380,13 @@
       <c r="H291" s="2"/>
       <c r="I291" s="2"/>
       <c r="J291" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="K291" s="2" t="s">
         <v>1405</v>
       </c>
-      <c r="K291" s="2" t="s">
+      <c r="L291" s="4" t="s">
         <v>1406</v>
-      </c>
-      <c r="L291" s="4" t="s">
-        <v>1407</v>
       </c>
       <c r="M291" s="2"/>
       <c r="N291" s="2"/>
@@ -20403,7 +20403,7 @@
         <v>43</v>
       </c>
       <c r="U291" s="10" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="V291" s="10"/>
       <c r="W291" s="10">
@@ -20415,11 +20415,11 @@
         <v>380</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" s="10" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>295</v>
@@ -20431,13 +20431,13 @@
       <c r="H292" s="2"/>
       <c r="I292" s="2"/>
       <c r="J292" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="K292" s="2" t="s">
         <v>1411</v>
       </c>
-      <c r="K292" s="2" t="s">
+      <c r="L292" s="9" t="s">
         <v>1412</v>
-      </c>
-      <c r="L292" s="9" t="s">
-        <v>1413</v>
       </c>
       <c r="M292" s="2"/>
       <c r="N292" s="2"/>
@@ -20466,11 +20466,11 @@
         <v>380</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" s="10" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>26</v>
@@ -20482,13 +20482,13 @@
       <c r="H293" s="2"/>
       <c r="I293" s="2"/>
       <c r="J293" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="K293" s="2" t="s">
         <v>1415</v>
       </c>
-      <c r="K293" s="2" t="s">
+      <c r="L293" s="9" t="s">
         <v>1416</v>
-      </c>
-      <c r="L293" s="9" t="s">
-        <v>1417</v>
       </c>
       <c r="M293" s="2"/>
       <c r="N293" s="2"/>
@@ -20517,7 +20517,7 @@
         <v>380</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" s="10" t="s">
@@ -20527,19 +20527,19 @@
         <v>295</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
       <c r="I294" s="2"/>
       <c r="J294" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="K294" s="2" t="s">
         <v>1419</v>
       </c>
-      <c r="K294" s="2" t="s">
+      <c r="L294" s="9" t="s">
         <v>1420</v>
-      </c>
-      <c r="L294" s="9" t="s">
-        <v>1421</v>
       </c>
       <c r="M294" s="2"/>
       <c r="N294" s="2"/>
@@ -20568,11 +20568,11 @@
         <v>380</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" s="10" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>75</v>
@@ -20584,13 +20584,13 @@
       <c r="H295" s="2"/>
       <c r="I295" s="2"/>
       <c r="J295" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="K295" s="2" t="s">
         <v>1423</v>
       </c>
-      <c r="K295" s="2" t="s">
+      <c r="L295" s="9" t="s">
         <v>1424</v>
-      </c>
-      <c r="L295" s="9" t="s">
-        <v>1425</v>
       </c>
       <c r="M295" s="2"/>
       <c r="N295" s="2"/>
@@ -20619,29 +20619,29 @@
         <v>380</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" s="10" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="G296" s="2"/>
       <c r="H296" s="2"/>
       <c r="I296" s="2"/>
       <c r="J296" s="2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="K296" s="2" t="s">
         <v>390</v>
       </c>
       <c r="L296" s="9" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="M296" s="2"/>
       <c r="N296" s="2"/>
@@ -20670,29 +20670,29 @@
         <v>380</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" s="10" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="G297" s="2"/>
       <c r="H297" s="2"/>
       <c r="I297" s="2"/>
       <c r="J297" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="K297" s="2" t="s">
         <v>1432</v>
       </c>
-      <c r="K297" s="2" t="s">
+      <c r="L297" s="9" t="s">
         <v>1433</v>
-      </c>
-      <c r="L297" s="9" t="s">
-        <v>1434</v>
       </c>
       <c r="M297" s="2"/>
       <c r="N297" s="2"/>
@@ -20721,7 +20721,7 @@
         <v>380</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" s="10">
@@ -20743,7 +20743,7 @@
         <v>1109</v>
       </c>
       <c r="L298" s="9" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="M298" s="2"/>
       <c r="N298" s="2"/>
@@ -20772,29 +20772,29 @@
         <v>380</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" s="10" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="G299" s="2"/>
       <c r="H299" s="2"/>
       <c r="I299" s="2"/>
       <c r="J299" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="K299" s="2" t="s">
         <v>1438</v>
       </c>
-      <c r="K299" s="2" t="s">
+      <c r="L299" s="9" t="s">
         <v>1439</v>
-      </c>
-      <c r="L299" s="9" t="s">
-        <v>1440</v>
       </c>
       <c r="M299" s="2"/>
       <c r="N299" s="2"/>
@@ -20823,11 +20823,11 @@
         <v>380</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" s="10" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>295</v>
@@ -20839,13 +20839,13 @@
       <c r="H300" s="2"/>
       <c r="I300" s="2"/>
       <c r="J300" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="K300" s="2" t="s">
         <v>1442</v>
       </c>
-      <c r="K300" s="2" t="s">
+      <c r="L300" s="9" t="s">
         <v>1443</v>
-      </c>
-      <c r="L300" s="9" t="s">
-        <v>1444</v>
       </c>
       <c r="M300" s="2"/>
       <c r="N300" s="2"/>
@@ -20874,7 +20874,7 @@
         <v>380</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" s="10">
@@ -20890,13 +20890,13 @@
       <c r="H301" s="2"/>
       <c r="I301" s="2"/>
       <c r="J301" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="K301" s="2" t="s">
         <v>1445</v>
       </c>
-      <c r="K301" s="2" t="s">
+      <c r="L301" s="9" t="s">
         <v>1446</v>
-      </c>
-      <c r="L301" s="9" t="s">
-        <v>1447</v>
       </c>
       <c r="M301" s="2"/>
       <c r="N301" s="2"/>
@@ -20925,11 +20925,11 @@
         <v>380</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" s="10" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>70</v>
@@ -20941,13 +20941,13 @@
       <c r="H302" s="2"/>
       <c r="I302" s="2"/>
       <c r="J302" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K302" s="2" t="s">
         <v>1449</v>
       </c>
-      <c r="K302" s="2" t="s">
+      <c r="L302" s="9" t="s">
         <v>1450</v>
-      </c>
-      <c r="L302" s="9" t="s">
-        <v>1451</v>
       </c>
       <c r="M302" s="2"/>
       <c r="N302" s="2"/>
@@ -20958,7 +20958,7 @@
         <v>31</v>
       </c>
       <c r="S302" s="2" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="T302" s="10">
         <v>117</v>
@@ -20976,11 +20976,11 @@
         <v>380</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" s="10" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>75</v>
@@ -20992,13 +20992,13 @@
       <c r="H303" s="2"/>
       <c r="I303" s="2"/>
       <c r="J303" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="K303" s="2" t="s">
         <v>1454</v>
       </c>
-      <c r="K303" s="2" t="s">
+      <c r="L303" s="4" t="s">
         <v>1455</v>
-      </c>
-      <c r="L303" s="4" t="s">
-        <v>1456</v>
       </c>
       <c r="M303" s="2"/>
       <c r="N303" s="2"/>
@@ -21024,32 +21024,32 @@
     </row>
     <row r="304" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B304" s="2" t="s">
         <v>1457</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>1458</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" s="10" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E304" s="2" t="s">
         <v>1459</v>
       </c>
-      <c r="E304" s="2" t="s">
+      <c r="F304" s="2" t="s">
         <v>1460</v>
-      </c>
-      <c r="F304" s="2" t="s">
-        <v>1461</v>
       </c>
       <c r="G304" s="2"/>
       <c r="H304" s="2"/>
       <c r="I304" s="2"/>
       <c r="J304" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="K304" s="2" t="s">
         <v>1462</v>
       </c>
-      <c r="K304" s="2" t="s">
+      <c r="L304" s="4" t="s">
         <v>1463</v>
-      </c>
-      <c r="L304" s="4" t="s">
-        <v>1464</v>
       </c>
       <c r="M304" s="2"/>
       <c r="N304" s="2"/>
@@ -21071,32 +21071,32 @@
     </row>
     <row r="305" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B305" s="2" t="s">
         <v>1457</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>1458</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" s="10" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="E305" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F305" s="2" t="s">
         <v>1460</v>
-      </c>
-      <c r="F305" s="2" t="s">
-        <v>1461</v>
       </c>
       <c r="G305" s="2"/>
       <c r="H305" s="2"/>
       <c r="I305" s="2"/>
       <c r="J305" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="K305" s="2" t="s">
         <v>1465</v>
       </c>
-      <c r="K305" s="2" t="s">
+      <c r="L305" s="4" t="s">
         <v>1466</v>
-      </c>
-      <c r="L305" s="4" t="s">
-        <v>1467</v>
       </c>
       <c r="M305" s="2"/>
       <c r="N305" s="2"/>
@@ -21118,32 +21118,32 @@
     </row>
     <row r="306" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B306" s="2" t="s">
         <v>1457</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>1458</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" s="10" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
       <c r="I306" s="2"/>
       <c r="J306" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="K306" s="2" t="s">
         <v>1469</v>
       </c>
-      <c r="K306" s="2" t="s">
+      <c r="L306" s="4" t="s">
         <v>1470</v>
-      </c>
-      <c r="L306" s="4" t="s">
-        <v>1471</v>
       </c>
       <c r="M306" s="2"/>
       <c r="N306" s="2"/>
@@ -21165,10 +21165,10 @@
     </row>
     <row r="307" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B307" s="2" t="s">
         <v>1457</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>1458</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" s="10" t="s">
@@ -21184,13 +21184,13 @@
       <c r="H307" s="2"/>
       <c r="I307" s="2"/>
       <c r="J307" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="K307" s="2" t="s">
         <v>1472</v>
       </c>
-      <c r="K307" s="2" t="s">
+      <c r="L307" s="4" t="s">
         <v>1473</v>
-      </c>
-      <c r="L307" s="4" t="s">
-        <v>1474</v>
       </c>
       <c r="M307" s="2"/>
       <c r="N307" s="2"/>
@@ -21207,7 +21207,7 @@
         <v>616</v>
       </c>
       <c r="U307" s="10" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="V307" s="10"/>
       <c r="W307" s="10" t="s">
@@ -21216,14 +21216,14 @@
     </row>
     <row r="308" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B308" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" s="10" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>142</v>
@@ -21235,13 +21235,13 @@
       <c r="H308" s="2"/>
       <c r="I308" s="2"/>
       <c r="J308" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K308" s="2" t="s">
         <v>1479</v>
       </c>
-      <c r="K308" s="2" t="s">
+      <c r="L308" s="9" t="s">
         <v>1480</v>
-      </c>
-      <c r="L308" s="9" t="s">
-        <v>1481</v>
       </c>
       <c r="M308" s="2"/>
       <c r="N308" s="2"/>
@@ -21267,32 +21267,32 @@
     </row>
     <row r="309" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B309" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C309" s="2"/>
       <c r="D309" s="10" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>581</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="G309" s="2"/>
       <c r="H309" s="2"/>
       <c r="I309" s="2"/>
       <c r="J309" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="K309" s="2" t="s">
         <v>1484</v>
       </c>
-      <c r="K309" s="2" t="s">
+      <c r="L309" s="9" t="s">
         <v>1485</v>
-      </c>
-      <c r="L309" s="9" t="s">
-        <v>1486</v>
       </c>
       <c r="M309" s="2"/>
       <c r="N309" s="2"/>
@@ -21318,10 +21318,10 @@
     </row>
     <row r="310" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B310" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" s="10" t="s">
@@ -21337,13 +21337,13 @@
       <c r="H310" s="2"/>
       <c r="I310" s="2"/>
       <c r="J310" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="K310" s="2" t="s">
         <v>1487</v>
       </c>
-      <c r="K310" s="2" t="s">
+      <c r="L310" s="9" t="s">
         <v>1488</v>
-      </c>
-      <c r="L310" s="9" t="s">
-        <v>1489</v>
       </c>
       <c r="M310" s="2"/>
       <c r="N310" s="2"/>
@@ -21369,10 +21369,10 @@
     </row>
     <row r="311" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B311" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C311" s="2"/>
       <c r="D311" s="10" t="s">
@@ -21394,7 +21394,7 @@
         <v>891</v>
       </c>
       <c r="L311" s="4" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="M311" s="2"/>
       <c r="N311" s="2"/>
@@ -21420,14 +21420,14 @@
     </row>
     <row r="312" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B312" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" s="10" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>305</v>
@@ -21439,13 +21439,13 @@
       <c r="H312" s="2"/>
       <c r="I312" s="2"/>
       <c r="J312" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="K312" s="2" t="s">
         <v>1492</v>
       </c>
-      <c r="K312" s="2" t="s">
+      <c r="L312" s="4" t="s">
         <v>1493</v>
-      </c>
-      <c r="L312" s="4" t="s">
-        <v>1494</v>
       </c>
       <c r="M312" s="2"/>
       <c r="N312" s="2"/>
@@ -21471,32 +21471,32 @@
     </row>
     <row r="313" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B313" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" s="10" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>581</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
       <c r="I313" s="2"/>
       <c r="J313" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="K313" s="2" t="s">
         <v>1497</v>
       </c>
-      <c r="K313" s="2" t="s">
+      <c r="L313" s="4" t="s">
         <v>1498</v>
-      </c>
-      <c r="L313" s="4" t="s">
-        <v>1499</v>
       </c>
       <c r="M313" s="2"/>
       <c r="N313" s="2"/>
@@ -21522,10 +21522,10 @@
     </row>
     <row r="314" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B314" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" s="10" t="s">
@@ -21541,13 +21541,13 @@
       <c r="H314" s="2"/>
       <c r="I314" s="2"/>
       <c r="J314" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="K314" s="2" t="s">
         <v>1500</v>
       </c>
-      <c r="K314" s="2" t="s">
+      <c r="L314" s="4" t="s">
         <v>1501</v>
-      </c>
-      <c r="L314" s="4" t="s">
-        <v>1502</v>
       </c>
       <c r="M314" s="2"/>
       <c r="N314" s="2"/>
@@ -21573,14 +21573,14 @@
     </row>
     <row r="315" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B315" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" s="10" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>96</v>
@@ -21595,10 +21595,10 @@
         <v>884</v>
       </c>
       <c r="K315" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="L315" s="4" t="s">
         <v>1504</v>
-      </c>
-      <c r="L315" s="4" t="s">
-        <v>1505</v>
       </c>
       <c r="M315" s="2"/>
       <c r="N315" s="2"/>
@@ -21624,14 +21624,14 @@
     </row>
     <row r="316" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B316" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" s="10" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>142</v>
@@ -21643,13 +21643,13 @@
       <c r="H316" s="2"/>
       <c r="I316" s="2"/>
       <c r="J316" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="K316" s="2" t="s">
         <v>1507</v>
       </c>
-      <c r="K316" s="2" t="s">
+      <c r="L316" s="4" t="s">
         <v>1508</v>
-      </c>
-      <c r="L316" s="4" t="s">
-        <v>1509</v>
       </c>
       <c r="M316" s="2"/>
       <c r="N316" s="2"/>
@@ -21675,14 +21675,14 @@
     </row>
     <row r="317" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B317" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" s="10" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>234</v>
@@ -21694,13 +21694,13 @@
       <c r="H317" s="2"/>
       <c r="I317" s="2"/>
       <c r="J317" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="K317" s="2" t="s">
         <v>1511</v>
       </c>
-      <c r="K317" s="2" t="s">
+      <c r="L317" s="4" t="s">
         <v>1512</v>
-      </c>
-      <c r="L317" s="4" t="s">
-        <v>1513</v>
       </c>
       <c r="M317" s="2"/>
       <c r="N317" s="2"/>
@@ -21726,10 +21726,10 @@
     </row>
     <row r="318" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B318" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" s="10" t="s">
@@ -21745,13 +21745,13 @@
       <c r="H318" s="2"/>
       <c r="I318" s="2"/>
       <c r="J318" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="K318" s="2" t="s">
         <v>1514</v>
       </c>
-      <c r="K318" s="2" t="s">
+      <c r="L318" s="4" t="s">
         <v>1515</v>
-      </c>
-      <c r="L318" s="4" t="s">
-        <v>1516</v>
       </c>
       <c r="M318" s="2"/>
       <c r="N318" s="2"/>
@@ -21777,14 +21777,14 @@
     </row>
     <row r="319" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B319" s="2" t="s">
         <v>1476</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>1477</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" s="10" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>142</v>
@@ -21796,13 +21796,13 @@
       <c r="H319" s="2"/>
       <c r="I319" s="2"/>
       <c r="J319" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="K319" s="2" t="s">
         <v>1518</v>
       </c>
-      <c r="K319" s="2" t="s">
+      <c r="L319" s="4" t="s">
         <v>1519</v>
-      </c>
-      <c r="L319" s="4" t="s">
-        <v>1520</v>
       </c>
       <c r="M319" s="2"/>
       <c r="N319" s="2"/>
@@ -21828,17 +21828,17 @@
     </row>
     <row r="320" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B320" s="2" t="s">
         <v>1521</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>1522</v>
       </c>
       <c r="C320" s="2"/>
       <c r="D320" s="10" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E320" s="2" t="s">
         <v>1523</v>
-      </c>
-      <c r="E320" s="2" t="s">
-        <v>1524</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>731</v>
@@ -21847,13 +21847,13 @@
       <c r="H320" s="2"/>
       <c r="I320" s="2"/>
       <c r="J320" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K320" s="2" t="s">
         <v>1525</v>
       </c>
-      <c r="K320" s="2" t="s">
+      <c r="L320" s="4" t="s">
         <v>1526</v>
-      </c>
-      <c r="L320" s="4" t="s">
-        <v>1527</v>
       </c>
       <c r="M320" s="2"/>
       <c r="N320" s="2"/>
@@ -21867,7 +21867,7 @@
         <v>173</v>
       </c>
       <c r="T320" s="10" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="U320" s="10"/>
       <c r="V320" s="10"/>
@@ -21877,20 +21877,20 @@
     </row>
     <row r="321" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>1521</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>1522</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" s="10" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E321" s="2" t="s">
         <v>1529</v>
       </c>
-      <c r="E321" s="2" t="s">
+      <c r="F321" s="2" t="s">
         <v>1530</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>1531</v>
       </c>
       <c r="G321" s="2"/>
       <c r="H321" s="2"/>
@@ -21902,7 +21902,7 @@
         <v>973</v>
       </c>
       <c r="L321" s="4" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="M321" s="2"/>
       <c r="N321" s="2"/>
@@ -21916,10 +21916,10 @@
         <v>1034</v>
       </c>
       <c r="T321" s="10" t="s">
+        <v>1532</v>
+      </c>
+      <c r="U321" s="10" t="s">
         <v>1533</v>
-      </c>
-      <c r="U321" s="10" t="s">
-        <v>1534</v>
       </c>
       <c r="V321" s="10"/>
       <c r="W321" s="10" t="s">
@@ -21928,32 +21928,32 @@
     </row>
     <row r="322" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B322" s="2" t="s">
         <v>1521</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>1522</v>
       </c>
       <c r="C322" s="2"/>
       <c r="D322" s="10" t="s">
         <v>1059</v>
       </c>
       <c r="E322" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F322" s="2" t="s">
         <v>1530</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>1531</v>
       </c>
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
       <c r="I322" s="2"/>
       <c r="J322" s="2" t="s">
+        <v>1534</v>
+      </c>
+      <c r="K322" s="2" t="s">
         <v>1535</v>
       </c>
-      <c r="K322" s="2" t="s">
+      <c r="L322" s="4" t="s">
         <v>1536</v>
-      </c>
-      <c r="L322" s="4" t="s">
-        <v>1537</v>
       </c>
       <c r="M322" s="2"/>
       <c r="N322" s="2"/>
@@ -21967,7 +21967,7 @@
         <v>117</v>
       </c>
       <c r="T322" s="10" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="U322" s="10" t="s">
         <v>1280</v>
@@ -21979,32 +21979,32 @@
     </row>
     <row r="323" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B323" s="2" t="s">
         <v>1521</v>
-      </c>
-      <c r="B323" s="2" t="s">
-        <v>1522</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" s="10" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="E323" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F323" s="2" t="s">
         <v>1539</v>
-      </c>
-      <c r="F323" s="2" t="s">
-        <v>1540</v>
       </c>
       <c r="G323" s="2"/>
       <c r="H323" s="2"/>
       <c r="I323" s="2"/>
       <c r="J323" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="K323" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="L323" s="4" t="s">
         <v>1541</v>
-      </c>
-      <c r="K323" s="2" t="s">
-        <v>1433</v>
-      </c>
-      <c r="L323" s="4" t="s">
-        <v>1542</v>
       </c>
       <c r="M323" s="2"/>
       <c r="N323" s="2"/>
@@ -22021,7 +22021,7 @@
         <v>850</v>
       </c>
       <c r="U323" s="10" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="V323" s="10"/>
       <c r="W323" s="10" t="s">
@@ -22030,30 +22030,30 @@
     </row>
     <row r="324" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B324" s="2" t="s">
         <v>1544</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>1545</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" s="10" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F324" s="2" t="s">
         <v>1546</v>
-      </c>
-      <c r="E324" s="2" t="s">
-        <v>1303</v>
-      </c>
-      <c r="F324" s="2" t="s">
-        <v>1547</v>
       </c>
       <c r="G324" s="2"/>
       <c r="H324" s="2"/>
       <c r="I324" s="2"/>
       <c r="J324" s="2" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="K324" s="2"/>
       <c r="L324" s="11" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="M324" s="3"/>
       <c r="N324" s="2"/>
@@ -22079,42 +22079,42 @@
     </row>
     <row r="325" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B325" s="2" t="s">
         <v>1544</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>1545</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" s="10" t="s">
         <v>734</v>
       </c>
       <c r="E325" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F325" s="2" t="s">
         <v>1550</v>
-      </c>
-      <c r="F325" s="2" t="s">
-        <v>1551</v>
       </c>
       <c r="G325" s="2"/>
       <c r="H325" s="2"/>
       <c r="I325" s="2"/>
       <c r="J325" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="K325" s="2" t="s">
         <v>1552</v>
       </c>
-      <c r="K325" s="2" t="s">
+      <c r="L325" s="4" t="s">
         <v>1553</v>
       </c>
-      <c r="L325" s="4" t="s">
+      <c r="M325" s="3" t="s">
         <v>1554</v>
       </c>
-      <c r="M325" s="3" t="s">
+      <c r="N325" s="7" t="s">
         <v>1555</v>
-      </c>
-      <c r="N325" s="7" t="s">
-        <v>1556</v>
       </c>
       <c r="O325" s="2"/>
       <c r="P325" s="7" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="Q325" s="2"/>
       <c r="R325" s="2" t="s">
@@ -22136,14 +22136,14 @@
     </row>
     <row r="326" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B326" s="2" t="s">
         <v>1544</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>1545</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" s="10" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>213</v>
@@ -22155,13 +22155,13 @@
       <c r="H326" s="2"/>
       <c r="I326" s="2"/>
       <c r="J326" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="K326" s="2" t="s">
         <v>1559</v>
       </c>
-      <c r="K326" s="2" t="s">
+      <c r="L326" s="4" t="s">
         <v>1560</v>
-      </c>
-      <c r="L326" s="4" t="s">
-        <v>1561</v>
       </c>
       <c r="M326" s="3"/>
       <c r="N326" s="2"/>
@@ -22187,32 +22187,32 @@
     </row>
     <row r="327" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B327" s="2" t="s">
         <v>1544</v>
-      </c>
-      <c r="B327" s="2" t="s">
-        <v>1545</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" s="10" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E327" s="2" t="s">
         <v>1562</v>
       </c>
-      <c r="E327" s="2" t="s">
+      <c r="F327" s="2" t="s">
         <v>1563</v>
-      </c>
-      <c r="F327" s="2" t="s">
-        <v>1564</v>
       </c>
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
       <c r="I327" s="2"/>
       <c r="J327" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="K327" s="2" t="s">
         <v>1565</v>
       </c>
-      <c r="K327" s="2" t="s">
+      <c r="L327" s="4" t="s">
         <v>1566</v>
-      </c>
-      <c r="L327" s="4" t="s">
-        <v>1567</v>
       </c>
       <c r="M327" s="3"/>
       <c r="N327" s="2"/>
@@ -22241,29 +22241,29 @@
         <v>672</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" s="10" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E328" s="2" t="s">
         <v>1569</v>
       </c>
-      <c r="E328" s="2" t="s">
+      <c r="F328" s="2" t="s">
         <v>1570</v>
-      </c>
-      <c r="F328" s="2" t="s">
-        <v>1571</v>
       </c>
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
       <c r="I328" s="2"/>
       <c r="J328" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="K328" s="2" t="s">
         <v>1572</v>
       </c>
-      <c r="K328" s="2" t="s">
+      <c r="L328" s="4" t="s">
         <v>1573</v>
-      </c>
-      <c r="L328" s="4" t="s">
-        <v>1574</v>
       </c>
       <c r="M328" s="2"/>
       <c r="N328" s="2"/>
@@ -22292,7 +22292,7 @@
         <v>672</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="C329" s="2"/>
       <c r="D329" s="10" t="s">
@@ -22308,13 +22308,13 @@
       <c r="H329" s="2"/>
       <c r="I329" s="2"/>
       <c r="J329" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="K329" s="2" t="s">
         <v>1575</v>
       </c>
-      <c r="K329" s="2" t="s">
+      <c r="L329" s="4" t="s">
         <v>1576</v>
-      </c>
-      <c r="L329" s="4" t="s">
-        <v>1577</v>
       </c>
       <c r="M329" s="2"/>
       <c r="N329" s="2"/>
@@ -22343,7 +22343,7 @@
         <v>672</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="C330" s="2"/>
       <c r="D330" s="10" t="s">
@@ -22359,13 +22359,13 @@
       <c r="H330" s="2"/>
       <c r="I330" s="2"/>
       <c r="J330" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="K330" s="2" t="s">
         <v>1578</v>
       </c>
-      <c r="K330" s="2" t="s">
+      <c r="L330" s="4" t="s">
         <v>1579</v>
-      </c>
-      <c r="L330" s="4" t="s">
-        <v>1580</v>
       </c>
       <c r="M330" s="2"/>
       <c r="N330" s="2"/>
@@ -22394,7 +22394,7 @@
         <v>672</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" s="10" t="s">
@@ -22410,13 +22410,13 @@
       <c r="H331" s="2"/>
       <c r="I331" s="2"/>
       <c r="J331" s="2" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K331" s="2" t="s">
         <v>1581</v>
       </c>
-      <c r="K331" s="2" t="s">
+      <c r="L331" s="4" t="s">
         <v>1582</v>
-      </c>
-      <c r="L331" s="4" t="s">
-        <v>1583</v>
       </c>
       <c r="M331" s="2"/>
       <c r="N331" s="2"/>
@@ -22445,11 +22445,11 @@
         <v>292</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" s="10" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>142</v>
@@ -22461,13 +22461,13 @@
       <c r="H332" s="2"/>
       <c r="I332" s="2"/>
       <c r="J332" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="K332" s="2" t="s">
         <v>1586</v>
       </c>
-      <c r="K332" s="2" t="s">
+      <c r="L332" s="4" t="s">
         <v>1587</v>
-      </c>
-      <c r="L332" s="4" t="s">
-        <v>1588</v>
       </c>
       <c r="M332" s="2"/>
       <c r="N332" s="2"/>
@@ -22496,7 +22496,7 @@
         <v>292</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="C333" s="2"/>
       <c r="D333" s="10" t="s">
@@ -22512,13 +22512,13 @@
       <c r="H333" s="2"/>
       <c r="I333" s="2"/>
       <c r="J333" s="2" t="s">
+        <v>1588</v>
+      </c>
+      <c r="K333" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="L333" s="4" t="s">
         <v>1589</v>
-      </c>
-      <c r="K333" s="2" t="s">
-        <v>1369</v>
-      </c>
-      <c r="L333" s="4" t="s">
-        <v>1590</v>
       </c>
       <c r="M333" s="2"/>
       <c r="N333" s="2"/>
@@ -22547,11 +22547,11 @@
         <v>292</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="C334" s="2"/>
       <c r="D334" s="10" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>295</v>
@@ -22563,13 +22563,13 @@
       <c r="H334" s="2"/>
       <c r="I334" s="2"/>
       <c r="J334" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="K334" s="2" t="s">
         <v>1592</v>
       </c>
-      <c r="K334" s="2" t="s">
+      <c r="L334" s="4" t="s">
         <v>1593</v>
-      </c>
-      <c r="L334" s="4" t="s">
-        <v>1594</v>
       </c>
       <c r="M334" s="2"/>
       <c r="N334" s="2"/>
@@ -22580,7 +22580,7 @@
         <v>31</v>
       </c>
       <c r="S334" s="2" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="T334" s="10">
         <v>202</v>
@@ -22598,11 +22598,11 @@
         <v>292</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" s="10" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>142</v>
@@ -22614,13 +22614,13 @@
       <c r="H335" s="2"/>
       <c r="I335" s="2"/>
       <c r="J335" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K335" s="2" t="s">
         <v>1597</v>
       </c>
-      <c r="K335" s="2" t="s">
+      <c r="L335" s="4" t="s">
         <v>1598</v>
-      </c>
-      <c r="L335" s="4" t="s">
-        <v>1599</v>
       </c>
       <c r="M335" s="2"/>
       <c r="N335" s="2"/>
@@ -22649,11 +22649,11 @@
         <v>292</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="C336" s="2"/>
       <c r="D336" s="10" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>234</v>
@@ -22671,7 +22671,7 @@
         <v>357</v>
       </c>
       <c r="L336" s="4" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="M336" s="2"/>
       <c r="N336" s="2"/>
@@ -22700,29 +22700,29 @@
         <v>292</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" s="10" t="s">
+        <v>1601</v>
+      </c>
+      <c r="E337" s="2" t="s">
         <v>1602</v>
       </c>
-      <c r="E337" s="2" t="s">
+      <c r="F337" s="2" t="s">
         <v>1603</v>
-      </c>
-      <c r="F337" s="2" t="s">
-        <v>1604</v>
       </c>
       <c r="G337" s="2"/>
       <c r="H337" s="2"/>
       <c r="I337" s="2"/>
       <c r="J337" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K337" s="2" t="s">
         <v>1605</v>
       </c>
-      <c r="K337" s="2" t="s">
+      <c r="L337" s="4" t="s">
         <v>1606</v>
-      </c>
-      <c r="L337" s="4" t="s">
-        <v>1607</v>
       </c>
       <c r="M337" s="2"/>
       <c r="N337" s="2"/>
@@ -22733,7 +22733,7 @@
         <v>31</v>
       </c>
       <c r="S337" s="2" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="T337" s="10">
         <v>305</v>
@@ -22751,29 +22751,29 @@
         <v>292</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="C338" s="2"/>
       <c r="D338" s="10" t="s">
         <v>212</v>
       </c>
       <c r="E338" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F338" s="2" t="s">
         <v>1608</v>
-      </c>
-      <c r="F338" s="2" t="s">
-        <v>1609</v>
       </c>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
       <c r="I338" s="2"/>
       <c r="J338" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="K338" s="2" t="s">
         <v>1610</v>
       </c>
-      <c r="K338" s="2" t="s">
+      <c r="L338" s="4" t="s">
         <v>1611</v>
-      </c>
-      <c r="L338" s="4" t="s">
-        <v>1612</v>
       </c>
       <c r="M338" s="2"/>
       <c r="N338" s="2"/>
@@ -22784,7 +22784,7 @@
         <v>31</v>
       </c>
       <c r="S338" s="2" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="T338" s="10">
         <v>118</v>
@@ -22799,10 +22799,10 @@
     </row>
     <row r="339" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B339" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B339" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" s="10" t="s">
@@ -22818,13 +22818,13 @@
       <c r="H339" s="2"/>
       <c r="I339" s="2"/>
       <c r="J339" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="K339" s="2" t="s">
         <v>1615</v>
       </c>
-      <c r="K339" s="2" t="s">
+      <c r="L339" s="4" t="s">
         <v>1616</v>
-      </c>
-      <c r="L339" s="4" t="s">
-        <v>1617</v>
       </c>
       <c r="M339" s="2"/>
       <c r="N339" s="2"/>
@@ -22850,20 +22850,20 @@
     </row>
     <row r="340" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B340" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B340" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C340" s="2"/>
       <c r="D340" s="10" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
@@ -22875,7 +22875,7 @@
         <v>608</v>
       </c>
       <c r="L340" s="4" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="M340" s="2"/>
       <c r="N340" s="2"/>
@@ -22901,10 +22901,10 @@
     </row>
     <row r="341" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B341" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C341" s="2"/>
       <c r="D341" s="10" t="s">
@@ -22920,13 +22920,13 @@
       <c r="H341" s="2"/>
       <c r="I341" s="2"/>
       <c r="J341" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="K341" s="2" t="s">
         <v>1621</v>
       </c>
-      <c r="K341" s="2" t="s">
+      <c r="L341" s="4" t="s">
         <v>1622</v>
-      </c>
-      <c r="L341" s="4" t="s">
-        <v>1623</v>
       </c>
       <c r="M341" s="2"/>
       <c r="N341" s="2"/>
@@ -22952,14 +22952,14 @@
     </row>
     <row r="342" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B342" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B342" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C342" s="2"/>
       <c r="D342" s="10" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>75</v>
@@ -22971,13 +22971,13 @@
       <c r="H342" s="2"/>
       <c r="I342" s="2"/>
       <c r="J342" s="2" t="s">
+        <v>1624</v>
+      </c>
+      <c r="K342" s="2" t="s">
         <v>1625</v>
       </c>
-      <c r="K342" s="2" t="s">
+      <c r="L342" s="4" t="s">
         <v>1626</v>
-      </c>
-      <c r="L342" s="4" t="s">
-        <v>1627</v>
       </c>
       <c r="M342" s="2"/>
       <c r="N342" s="2"/>
@@ -23003,14 +23003,14 @@
     </row>
     <row r="343" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B343" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B343" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" s="10" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>26</v>
@@ -23022,13 +23022,13 @@
       <c r="H343" s="2"/>
       <c r="I343" s="2"/>
       <c r="J343" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="K343" s="2" t="s">
         <v>1628</v>
       </c>
-      <c r="K343" s="2" t="s">
+      <c r="L343" s="4" t="s">
         <v>1629</v>
-      </c>
-      <c r="L343" s="4" t="s">
-        <v>1630</v>
       </c>
       <c r="M343" s="2"/>
       <c r="N343" s="2"/>
@@ -23054,20 +23054,20 @@
     </row>
     <row r="344" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B344" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B344" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C344" s="2"/>
       <c r="D344" s="10" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="G344" s="2"/>
       <c r="H344" s="2"/>
@@ -23076,10 +23076,10 @@
         <v>428</v>
       </c>
       <c r="K344" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="L344" s="4" t="s">
         <v>1632</v>
-      </c>
-      <c r="L344" s="4" t="s">
-        <v>1633</v>
       </c>
       <c r="M344" s="2"/>
       <c r="N344" s="2"/>
@@ -23087,7 +23087,7 @@
       <c r="P344" s="2"/>
       <c r="Q344" s="2"/>
       <c r="R344" s="2" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="S344" s="2" t="s">
         <v>32</v>
@@ -23105,10 +23105,10 @@
     </row>
     <row r="345" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B345" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B345" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" s="10" t="s">
@@ -23118,19 +23118,19 @@
         <v>1170</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="G345" s="2"/>
       <c r="H345" s="2"/>
       <c r="I345" s="2"/>
       <c r="J345" s="2" t="s">
+        <v>1635</v>
+      </c>
+      <c r="K345" s="2" t="s">
         <v>1636</v>
       </c>
-      <c r="K345" s="2" t="s">
+      <c r="L345" s="4" t="s">
         <v>1637</v>
-      </c>
-      <c r="L345" s="4" t="s">
-        <v>1638</v>
       </c>
       <c r="M345" s="2"/>
       <c r="N345" s="2"/>
@@ -23156,14 +23156,14 @@
     </row>
     <row r="346" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B346" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B346" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C346" s="2"/>
       <c r="D346" s="10" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>26</v>
@@ -23175,13 +23175,13 @@
       <c r="H346" s="2"/>
       <c r="I346" s="2"/>
       <c r="J346" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="K346" s="2" t="s">
         <v>1640</v>
       </c>
-      <c r="K346" s="2" t="s">
+      <c r="L346" s="4" t="s">
         <v>1641</v>
-      </c>
-      <c r="L346" s="4" t="s">
-        <v>1642</v>
       </c>
       <c r="M346" s="2"/>
       <c r="N346" s="2"/>
@@ -23207,10 +23207,10 @@
     </row>
     <row r="347" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B347" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B347" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C347" s="2"/>
       <c r="D347" s="10" t="s">
@@ -23226,13 +23226,13 @@
       <c r="H347" s="2"/>
       <c r="I347" s="2"/>
       <c r="J347" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K347" s="2" t="s">
         <v>1643</v>
       </c>
-      <c r="K347" s="2" t="s">
+      <c r="L347" s="4" t="s">
         <v>1644</v>
-      </c>
-      <c r="L347" s="4" t="s">
-        <v>1645</v>
       </c>
       <c r="M347" s="2"/>
       <c r="N347" s="2"/>
@@ -23258,14 +23258,14 @@
     </row>
     <row r="348" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B348" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C348" s="2"/>
       <c r="D348" s="10" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>234</v>
@@ -23277,13 +23277,13 @@
       <c r="H348" s="2"/>
       <c r="I348" s="2"/>
       <c r="J348" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="K348" s="2" t="s">
         <v>1647</v>
       </c>
-      <c r="K348" s="2" t="s">
+      <c r="L348" s="4" t="s">
         <v>1648</v>
-      </c>
-      <c r="L348" s="4" t="s">
-        <v>1649</v>
       </c>
       <c r="M348" s="2"/>
       <c r="N348" s="2"/>
@@ -23309,32 +23309,32 @@
     </row>
     <row r="349" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B349" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B349" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C349" s="2"/>
       <c r="D349" s="10" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="G349" s="2"/>
       <c r="H349" s="2"/>
       <c r="I349" s="2"/>
       <c r="J349" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="K349" s="2" t="s">
         <v>1651</v>
       </c>
-      <c r="K349" s="2" t="s">
+      <c r="L349" s="4" t="s">
         <v>1652</v>
-      </c>
-      <c r="L349" s="4" t="s">
-        <v>1653</v>
       </c>
       <c r="M349" s="2"/>
       <c r="N349" s="2"/>
@@ -23360,14 +23360,14 @@
     </row>
     <row r="350" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B350" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B350" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" s="10" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>295</v>
@@ -23385,7 +23385,7 @@
         <v>903</v>
       </c>
       <c r="L350" s="4" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="M350" s="2"/>
       <c r="N350" s="2"/>
@@ -23411,10 +23411,10 @@
     </row>
     <row r="351" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B351" s="2" t="s">
         <v>1656</v>
-      </c>
-      <c r="B351" s="2" t="s">
-        <v>1657</v>
       </c>
       <c r="C351" s="2"/>
       <c r="D351" s="10" t="s">
@@ -23430,13 +23430,13 @@
       <c r="H351" s="2"/>
       <c r="I351" s="2"/>
       <c r="J351" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="K351" s="2" t="s">
         <v>1658</v>
       </c>
-      <c r="K351" s="2" t="s">
+      <c r="L351" s="4" t="s">
         <v>1659</v>
-      </c>
-      <c r="L351" s="4" t="s">
-        <v>1660</v>
       </c>
       <c r="M351" s="2"/>
       <c r="N351" s="2"/>
@@ -23450,10 +23450,10 @@
         <v>32</v>
       </c>
       <c r="T351" s="10" t="s">
+        <v>1660</v>
+      </c>
+      <c r="U351" s="10" t="s">
         <v>1661</v>
-      </c>
-      <c r="U351" s="10" t="s">
-        <v>1662</v>
       </c>
       <c r="V351" s="10"/>
       <c r="W351" s="10" t="s">
@@ -23462,10 +23462,10 @@
     </row>
     <row r="352" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B352" s="2" t="s">
         <v>1656</v>
-      </c>
-      <c r="B352" s="2" t="s">
-        <v>1657</v>
       </c>
       <c r="C352" s="2"/>
       <c r="D352" s="10" t="s">
@@ -23481,13 +23481,13 @@
       <c r="H352" s="2"/>
       <c r="I352" s="2"/>
       <c r="J352" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="K352" s="2" t="s">
         <v>1663</v>
       </c>
-      <c r="K352" s="2" t="s">
+      <c r="L352" s="4" t="s">
         <v>1664</v>
-      </c>
-      <c r="L352" s="4" t="s">
-        <v>1665</v>
       </c>
       <c r="M352" s="2"/>
       <c r="N352" s="2"/>
@@ -23501,10 +23501,10 @@
         <v>32</v>
       </c>
       <c r="T352" s="10" t="s">
+        <v>1665</v>
+      </c>
+      <c r="U352" s="10" t="s">
         <v>1666</v>
-      </c>
-      <c r="U352" s="10" t="s">
-        <v>1667</v>
       </c>
       <c r="V352" s="10"/>
       <c r="W352" s="10" t="s">
@@ -23513,10 +23513,10 @@
     </row>
     <row r="353" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B353" s="2" t="s">
         <v>1656</v>
-      </c>
-      <c r="B353" s="2" t="s">
-        <v>1657</v>
       </c>
       <c r="C353" s="2"/>
       <c r="D353" s="10" t="s">
@@ -23532,13 +23532,13 @@
       <c r="H353" s="2"/>
       <c r="I353" s="2"/>
       <c r="J353" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="K353" s="2" t="s">
         <v>1668</v>
       </c>
-      <c r="K353" s="2" t="s">
+      <c r="L353" s="4" t="s">
         <v>1669</v>
-      </c>
-      <c r="L353" s="4" t="s">
-        <v>1670</v>
       </c>
       <c r="M353" s="2"/>
       <c r="N353" s="2"/>
@@ -23552,10 +23552,10 @@
         <v>32</v>
       </c>
       <c r="T353" s="10" t="s">
+        <v>1670</v>
+      </c>
+      <c r="U353" s="10" t="s">
         <v>1671</v>
-      </c>
-      <c r="U353" s="10" t="s">
-        <v>1672</v>
       </c>
       <c r="V353" s="10"/>
       <c r="W353" s="10" t="s">
@@ -23564,10 +23564,10 @@
     </row>
     <row r="354" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B354" s="2" t="s">
         <v>1656</v>
-      </c>
-      <c r="B354" s="2" t="s">
-        <v>1657</v>
       </c>
       <c r="C354" s="2"/>
       <c r="D354" s="10" t="s">
@@ -23583,11 +23583,11 @@
       <c r="H354" s="2"/>
       <c r="I354" s="2"/>
       <c r="J354" s="2" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="K354" s="2"/>
       <c r="L354" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="M354" s="2"/>
       <c r="N354" s="2"/>
@@ -23601,10 +23601,10 @@
         <v>32</v>
       </c>
       <c r="T354" s="10" t="s">
+        <v>1674</v>
+      </c>
+      <c r="U354" s="10" t="s">
         <v>1675</v>
-      </c>
-      <c r="U354" s="10" t="s">
-        <v>1676</v>
       </c>
       <c r="V354" s="10"/>
       <c r="W354" s="10" t="s">
@@ -23613,30 +23613,30 @@
     </row>
     <row r="355" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B355" s="2" t="s">
         <v>1656</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>1657</v>
       </c>
       <c r="C355" s="2"/>
       <c r="D355" s="10" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="G355" s="2"/>
       <c r="H355" s="2"/>
       <c r="I355" s="2"/>
       <c r="J355" s="2" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="K355" s="2"/>
       <c r="L355" s="4" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M355" s="2"/>
       <c r="N355" s="2"/>
@@ -23662,30 +23662,30 @@
     </row>
     <row r="356" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B356" s="2" t="s">
         <v>1656</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>1657</v>
       </c>
       <c r="C356" s="2"/>
       <c r="D356" s="10" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="G356" s="2"/>
       <c r="H356" s="2"/>
       <c r="I356" s="2"/>
       <c r="J356" s="2" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="K356" s="2"/>
       <c r="L356" s="4" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="M356" s="2"/>
       <c r="N356" s="2"/>
@@ -23693,16 +23693,16 @@
       <c r="P356" s="2"/>
       <c r="Q356" s="2"/>
       <c r="R356" s="2" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="S356" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T356" s="10" t="s">
+        <v>1681</v>
+      </c>
+      <c r="U356" s="10" t="s">
         <v>1682</v>
-      </c>
-      <c r="U356" s="10" t="s">
-        <v>1683</v>
       </c>
       <c r="V356" s="10"/>
       <c r="W356" s="10" t="s">
@@ -23711,30 +23711,30 @@
     </row>
     <row r="357" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B357" s="2" t="s">
         <v>1656</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>1657</v>
       </c>
       <c r="C357" s="2"/>
       <c r="D357" s="10" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E357" s="2" t="s">
         <v>1684</v>
       </c>
-      <c r="E357" s="2" t="s">
+      <c r="F357" s="2" t="s">
         <v>1685</v>
-      </c>
-      <c r="F357" s="2" t="s">
-        <v>1686</v>
       </c>
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
       <c r="I357" s="2"/>
       <c r="J357" s="2" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="K357" s="2"/>
       <c r="L357" s="4" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="M357" s="2"/>
       <c r="N357" s="2"/>
@@ -23742,10 +23742,10 @@
       <c r="P357" s="2"/>
       <c r="Q357" s="2"/>
       <c r="R357" s="2" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="S357" s="2" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="T357" s="10"/>
       <c r="U357" s="10"/>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AF687E-ECC7-44C9-ACFD-C6EF5378E96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3FC9AC-2ECE-4C01-A6C7-42A11BA0694F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3673" uniqueCount="1693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3673" uniqueCount="1692">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -4434,9 +4434,6 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Sud-parete_banchetto_sposi.jpg/1280px-Sud-parete_banchetto_sposi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Musée du Vatican</t>
   </si>
   <si>
     <t>La Bataille du pont Milvius</t>
@@ -9740,7 +9737,7 @@
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="10" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>367</v>
@@ -10519,7 +10516,7 @@
         <v>514</v>
       </c>
       <c r="L96" s="13" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
@@ -19162,7 +19159,7 @@
         <v>1112</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
@@ -21131,19 +21128,19 @@
         <v>96</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>1467</v>
+        <v>1494</v>
       </c>
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
       <c r="I306" s="2"/>
       <c r="J306" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="K306" s="2" t="s">
         <v>1468</v>
       </c>
-      <c r="K306" s="2" t="s">
+      <c r="L306" s="4" t="s">
         <v>1469</v>
-      </c>
-      <c r="L306" s="4" t="s">
-        <v>1470</v>
       </c>
       <c r="M306" s="2"/>
       <c r="N306" s="2"/>
@@ -21184,13 +21181,13 @@
       <c r="H307" s="2"/>
       <c r="I307" s="2"/>
       <c r="J307" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="K307" s="2" t="s">
         <v>1471</v>
       </c>
-      <c r="K307" s="2" t="s">
+      <c r="L307" s="4" t="s">
         <v>1472</v>
-      </c>
-      <c r="L307" s="4" t="s">
-        <v>1473</v>
       </c>
       <c r="M307" s="2"/>
       <c r="N307" s="2"/>
@@ -21207,7 +21204,7 @@
         <v>616</v>
       </c>
       <c r="U307" s="10" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="V307" s="10"/>
       <c r="W307" s="10" t="s">
@@ -21216,14 +21213,14 @@
     </row>
     <row r="308" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B308" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" s="10" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>142</v>
@@ -21235,13 +21232,13 @@
       <c r="H308" s="2"/>
       <c r="I308" s="2"/>
       <c r="J308" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="K308" s="2" t="s">
         <v>1478</v>
       </c>
-      <c r="K308" s="2" t="s">
+      <c r="L308" s="9" t="s">
         <v>1479</v>
-      </c>
-      <c r="L308" s="9" t="s">
-        <v>1480</v>
       </c>
       <c r="M308" s="2"/>
       <c r="N308" s="2"/>
@@ -21267,32 +21264,32 @@
     </row>
     <row r="309" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B309" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C309" s="2"/>
       <c r="D309" s="10" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>581</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="G309" s="2"/>
       <c r="H309" s="2"/>
       <c r="I309" s="2"/>
       <c r="J309" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="K309" s="2" t="s">
         <v>1483</v>
       </c>
-      <c r="K309" s="2" t="s">
+      <c r="L309" s="9" t="s">
         <v>1484</v>
-      </c>
-      <c r="L309" s="9" t="s">
-        <v>1485</v>
       </c>
       <c r="M309" s="2"/>
       <c r="N309" s="2"/>
@@ -21318,10 +21315,10 @@
     </row>
     <row r="310" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B310" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" s="10" t="s">
@@ -21337,13 +21334,13 @@
       <c r="H310" s="2"/>
       <c r="I310" s="2"/>
       <c r="J310" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="K310" s="2" t="s">
         <v>1486</v>
       </c>
-      <c r="K310" s="2" t="s">
+      <c r="L310" s="9" t="s">
         <v>1487</v>
-      </c>
-      <c r="L310" s="9" t="s">
-        <v>1488</v>
       </c>
       <c r="M310" s="2"/>
       <c r="N310" s="2"/>
@@ -21369,10 +21366,10 @@
     </row>
     <row r="311" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B311" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C311" s="2"/>
       <c r="D311" s="10" t="s">
@@ -21394,7 +21391,7 @@
         <v>891</v>
       </c>
       <c r="L311" s="4" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="M311" s="2"/>
       <c r="N311" s="2"/>
@@ -21420,14 +21417,14 @@
     </row>
     <row r="312" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B312" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" s="10" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>305</v>
@@ -21439,13 +21436,13 @@
       <c r="H312" s="2"/>
       <c r="I312" s="2"/>
       <c r="J312" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="K312" s="2" t="s">
         <v>1491</v>
       </c>
-      <c r="K312" s="2" t="s">
+      <c r="L312" s="4" t="s">
         <v>1492</v>
-      </c>
-      <c r="L312" s="4" t="s">
-        <v>1493</v>
       </c>
       <c r="M312" s="2"/>
       <c r="N312" s="2"/>
@@ -21471,32 +21468,32 @@
     </row>
     <row r="313" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B313" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" s="10" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>581</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
       <c r="I313" s="2"/>
       <c r="J313" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="K313" s="2" t="s">
         <v>1496</v>
       </c>
-      <c r="K313" s="2" t="s">
+      <c r="L313" s="4" t="s">
         <v>1497</v>
-      </c>
-      <c r="L313" s="4" t="s">
-        <v>1498</v>
       </c>
       <c r="M313" s="2"/>
       <c r="N313" s="2"/>
@@ -21522,10 +21519,10 @@
     </row>
     <row r="314" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B314" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" s="10" t="s">
@@ -21541,13 +21538,13 @@
       <c r="H314" s="2"/>
       <c r="I314" s="2"/>
       <c r="J314" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="K314" s="2" t="s">
         <v>1499</v>
       </c>
-      <c r="K314" s="2" t="s">
+      <c r="L314" s="4" t="s">
         <v>1500</v>
-      </c>
-      <c r="L314" s="4" t="s">
-        <v>1501</v>
       </c>
       <c r="M314" s="2"/>
       <c r="N314" s="2"/>
@@ -21573,14 +21570,14 @@
     </row>
     <row r="315" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B315" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" s="10" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>96</v>
@@ -21595,10 +21592,10 @@
         <v>884</v>
       </c>
       <c r="K315" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="L315" s="4" t="s">
         <v>1503</v>
-      </c>
-      <c r="L315" s="4" t="s">
-        <v>1504</v>
       </c>
       <c r="M315" s="2"/>
       <c r="N315" s="2"/>
@@ -21624,14 +21621,14 @@
     </row>
     <row r="316" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B316" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" s="10" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>142</v>
@@ -21643,13 +21640,13 @@
       <c r="H316" s="2"/>
       <c r="I316" s="2"/>
       <c r="J316" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="K316" s="2" t="s">
         <v>1506</v>
       </c>
-      <c r="K316" s="2" t="s">
+      <c r="L316" s="4" t="s">
         <v>1507</v>
-      </c>
-      <c r="L316" s="4" t="s">
-        <v>1508</v>
       </c>
       <c r="M316" s="2"/>
       <c r="N316" s="2"/>
@@ -21675,14 +21672,14 @@
     </row>
     <row r="317" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B317" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" s="10" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>234</v>
@@ -21694,13 +21691,13 @@
       <c r="H317" s="2"/>
       <c r="I317" s="2"/>
       <c r="J317" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="K317" s="2" t="s">
         <v>1510</v>
       </c>
-      <c r="K317" s="2" t="s">
+      <c r="L317" s="4" t="s">
         <v>1511</v>
-      </c>
-      <c r="L317" s="4" t="s">
-        <v>1512</v>
       </c>
       <c r="M317" s="2"/>
       <c r="N317" s="2"/>
@@ -21726,10 +21723,10 @@
     </row>
     <row r="318" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B318" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" s="10" t="s">
@@ -21745,13 +21742,13 @@
       <c r="H318" s="2"/>
       <c r="I318" s="2"/>
       <c r="J318" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K318" s="2" t="s">
         <v>1513</v>
       </c>
-      <c r="K318" s="2" t="s">
+      <c r="L318" s="4" t="s">
         <v>1514</v>
-      </c>
-      <c r="L318" s="4" t="s">
-        <v>1515</v>
       </c>
       <c r="M318" s="2"/>
       <c r="N318" s="2"/>
@@ -21777,14 +21774,14 @@
     </row>
     <row r="319" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B319" s="2" t="s">
         <v>1475</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" s="10" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>142</v>
@@ -21796,13 +21793,13 @@
       <c r="H319" s="2"/>
       <c r="I319" s="2"/>
       <c r="J319" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="K319" s="2" t="s">
         <v>1517</v>
       </c>
-      <c r="K319" s="2" t="s">
+      <c r="L319" s="4" t="s">
         <v>1518</v>
-      </c>
-      <c r="L319" s="4" t="s">
-        <v>1519</v>
       </c>
       <c r="M319" s="2"/>
       <c r="N319" s="2"/>
@@ -21828,17 +21825,17 @@
     </row>
     <row r="320" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B320" s="2" t="s">
         <v>1520</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>1521</v>
       </c>
       <c r="C320" s="2"/>
       <c r="D320" s="10" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E320" s="2" t="s">
         <v>1522</v>
-      </c>
-      <c r="E320" s="2" t="s">
-        <v>1523</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>731</v>
@@ -21847,13 +21844,13 @@
       <c r="H320" s="2"/>
       <c r="I320" s="2"/>
       <c r="J320" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="K320" s="2" t="s">
         <v>1524</v>
       </c>
-      <c r="K320" s="2" t="s">
+      <c r="L320" s="4" t="s">
         <v>1525</v>
-      </c>
-      <c r="L320" s="4" t="s">
-        <v>1526</v>
       </c>
       <c r="M320" s="2"/>
       <c r="N320" s="2"/>
@@ -21867,7 +21864,7 @@
         <v>173</v>
       </c>
       <c r="T320" s="10" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="U320" s="10"/>
       <c r="V320" s="10"/>
@@ -21877,20 +21874,20 @@
     </row>
     <row r="321" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>1520</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>1521</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" s="10" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E321" s="2" t="s">
         <v>1528</v>
       </c>
-      <c r="E321" s="2" t="s">
+      <c r="F321" s="2" t="s">
         <v>1529</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>1530</v>
       </c>
       <c r="G321" s="2"/>
       <c r="H321" s="2"/>
@@ -21902,7 +21899,7 @@
         <v>973</v>
       </c>
       <c r="L321" s="4" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="M321" s="2"/>
       <c r="N321" s="2"/>
@@ -21916,10 +21913,10 @@
         <v>1034</v>
       </c>
       <c r="T321" s="10" t="s">
+        <v>1531</v>
+      </c>
+      <c r="U321" s="10" t="s">
         <v>1532</v>
-      </c>
-      <c r="U321" s="10" t="s">
-        <v>1533</v>
       </c>
       <c r="V321" s="10"/>
       <c r="W321" s="10" t="s">
@@ -21928,32 +21925,32 @@
     </row>
     <row r="322" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B322" s="2" t="s">
         <v>1520</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>1521</v>
       </c>
       <c r="C322" s="2"/>
       <c r="D322" s="10" t="s">
         <v>1059</v>
       </c>
       <c r="E322" s="2" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F322" s="2" t="s">
         <v>1529</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>1530</v>
       </c>
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
       <c r="I322" s="2"/>
       <c r="J322" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="K322" s="2" t="s">
         <v>1534</v>
       </c>
-      <c r="K322" s="2" t="s">
+      <c r="L322" s="4" t="s">
         <v>1535</v>
-      </c>
-      <c r="L322" s="4" t="s">
-        <v>1536</v>
       </c>
       <c r="M322" s="2"/>
       <c r="N322" s="2"/>
@@ -21967,7 +21964,7 @@
         <v>117</v>
       </c>
       <c r="T322" s="10" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="U322" s="10" t="s">
         <v>1280</v>
@@ -21979,32 +21976,32 @@
     </row>
     <row r="323" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B323" s="2" t="s">
         <v>1520</v>
-      </c>
-      <c r="B323" s="2" t="s">
-        <v>1521</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" s="10" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="E323" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="F323" s="2" t="s">
         <v>1538</v>
-      </c>
-      <c r="F323" s="2" t="s">
-        <v>1539</v>
       </c>
       <c r="G323" s="2"/>
       <c r="H323" s="2"/>
       <c r="I323" s="2"/>
       <c r="J323" s="2" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="K323" s="2" t="s">
         <v>1432</v>
       </c>
       <c r="L323" s="4" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="M323" s="2"/>
       <c r="N323" s="2"/>
@@ -22021,7 +22018,7 @@
         <v>850</v>
       </c>
       <c r="U323" s="10" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="V323" s="10"/>
       <c r="W323" s="10" t="s">
@@ -22030,30 +22027,30 @@
     </row>
     <row r="324" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B324" s="2" t="s">
         <v>1543</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>1544</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" s="10" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>1302</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="G324" s="2"/>
       <c r="H324" s="2"/>
       <c r="I324" s="2"/>
       <c r="J324" s="2" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="K324" s="2"/>
       <c r="L324" s="11" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="M324" s="3"/>
       <c r="N324" s="2"/>
@@ -22079,42 +22076,42 @@
     </row>
     <row r="325" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B325" s="2" t="s">
         <v>1543</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>1544</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" s="10" t="s">
         <v>734</v>
       </c>
       <c r="E325" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F325" s="2" t="s">
         <v>1549</v>
-      </c>
-      <c r="F325" s="2" t="s">
-        <v>1550</v>
       </c>
       <c r="G325" s="2"/>
       <c r="H325" s="2"/>
       <c r="I325" s="2"/>
       <c r="J325" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="K325" s="2" t="s">
         <v>1551</v>
       </c>
-      <c r="K325" s="2" t="s">
+      <c r="L325" s="4" t="s">
         <v>1552</v>
       </c>
-      <c r="L325" s="4" t="s">
+      <c r="M325" s="3" t="s">
         <v>1553</v>
       </c>
-      <c r="M325" s="3" t="s">
+      <c r="N325" s="7" t="s">
         <v>1554</v>
-      </c>
-      <c r="N325" s="7" t="s">
-        <v>1555</v>
       </c>
       <c r="O325" s="2"/>
       <c r="P325" s="7" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="Q325" s="2"/>
       <c r="R325" s="2" t="s">
@@ -22136,14 +22133,14 @@
     </row>
     <row r="326" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B326" s="2" t="s">
         <v>1543</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>1544</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" s="10" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>213</v>
@@ -22155,13 +22152,13 @@
       <c r="H326" s="2"/>
       <c r="I326" s="2"/>
       <c r="J326" s="2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="K326" s="2" t="s">
         <v>1558</v>
       </c>
-      <c r="K326" s="2" t="s">
+      <c r="L326" s="4" t="s">
         <v>1559</v>
-      </c>
-      <c r="L326" s="4" t="s">
-        <v>1560</v>
       </c>
       <c r="M326" s="3"/>
       <c r="N326" s="2"/>
@@ -22187,32 +22184,32 @@
     </row>
     <row r="327" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B327" s="2" t="s">
         <v>1543</v>
-      </c>
-      <c r="B327" s="2" t="s">
-        <v>1544</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" s="10" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E327" s="2" t="s">
         <v>1561</v>
       </c>
-      <c r="E327" s="2" t="s">
+      <c r="F327" s="2" t="s">
         <v>1562</v>
-      </c>
-      <c r="F327" s="2" t="s">
-        <v>1563</v>
       </c>
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
       <c r="I327" s="2"/>
       <c r="J327" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="K327" s="2" t="s">
         <v>1564</v>
       </c>
-      <c r="K327" s="2" t="s">
+      <c r="L327" s="4" t="s">
         <v>1565</v>
-      </c>
-      <c r="L327" s="4" t="s">
-        <v>1566</v>
       </c>
       <c r="M327" s="3"/>
       <c r="N327" s="2"/>
@@ -22241,29 +22238,29 @@
         <v>672</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" s="10" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E328" s="2" t="s">
         <v>1568</v>
       </c>
-      <c r="E328" s="2" t="s">
+      <c r="F328" s="2" t="s">
         <v>1569</v>
-      </c>
-      <c r="F328" s="2" t="s">
-        <v>1570</v>
       </c>
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
       <c r="I328" s="2"/>
       <c r="J328" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="K328" s="2" t="s">
         <v>1571</v>
       </c>
-      <c r="K328" s="2" t="s">
+      <c r="L328" s="4" t="s">
         <v>1572</v>
-      </c>
-      <c r="L328" s="4" t="s">
-        <v>1573</v>
       </c>
       <c r="M328" s="2"/>
       <c r="N328" s="2"/>
@@ -22292,7 +22289,7 @@
         <v>672</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="C329" s="2"/>
       <c r="D329" s="10" t="s">
@@ -22308,13 +22305,13 @@
       <c r="H329" s="2"/>
       <c r="I329" s="2"/>
       <c r="J329" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="K329" s="2" t="s">
         <v>1574</v>
       </c>
-      <c r="K329" s="2" t="s">
+      <c r="L329" s="4" t="s">
         <v>1575</v>
-      </c>
-      <c r="L329" s="4" t="s">
-        <v>1576</v>
       </c>
       <c r="M329" s="2"/>
       <c r="N329" s="2"/>
@@ -22343,7 +22340,7 @@
         <v>672</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="C330" s="2"/>
       <c r="D330" s="10" t="s">
@@ -22359,13 +22356,13 @@
       <c r="H330" s="2"/>
       <c r="I330" s="2"/>
       <c r="J330" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="K330" s="2" t="s">
         <v>1577</v>
       </c>
-      <c r="K330" s="2" t="s">
+      <c r="L330" s="4" t="s">
         <v>1578</v>
-      </c>
-      <c r="L330" s="4" t="s">
-        <v>1579</v>
       </c>
       <c r="M330" s="2"/>
       <c r="N330" s="2"/>
@@ -22394,7 +22391,7 @@
         <v>672</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" s="10" t="s">
@@ -22410,13 +22407,13 @@
       <c r="H331" s="2"/>
       <c r="I331" s="2"/>
       <c r="J331" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="K331" s="2" t="s">
         <v>1580</v>
       </c>
-      <c r="K331" s="2" t="s">
+      <c r="L331" s="4" t="s">
         <v>1581</v>
-      </c>
-      <c r="L331" s="4" t="s">
-        <v>1582</v>
       </c>
       <c r="M331" s="2"/>
       <c r="N331" s="2"/>
@@ -22445,11 +22442,11 @@
         <v>292</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" s="10" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>142</v>
@@ -22461,13 +22458,13 @@
       <c r="H332" s="2"/>
       <c r="I332" s="2"/>
       <c r="J332" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="K332" s="2" t="s">
         <v>1585</v>
       </c>
-      <c r="K332" s="2" t="s">
+      <c r="L332" s="4" t="s">
         <v>1586</v>
-      </c>
-      <c r="L332" s="4" t="s">
-        <v>1587</v>
       </c>
       <c r="M332" s="2"/>
       <c r="N332" s="2"/>
@@ -22496,7 +22493,7 @@
         <v>292</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="C333" s="2"/>
       <c r="D333" s="10" t="s">
@@ -22512,13 +22509,13 @@
       <c r="H333" s="2"/>
       <c r="I333" s="2"/>
       <c r="J333" s="2" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="K333" s="2" t="s">
         <v>1368</v>
       </c>
       <c r="L333" s="4" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="M333" s="2"/>
       <c r="N333" s="2"/>
@@ -22547,11 +22544,11 @@
         <v>292</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="C334" s="2"/>
       <c r="D334" s="10" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>295</v>
@@ -22563,13 +22560,13 @@
       <c r="H334" s="2"/>
       <c r="I334" s="2"/>
       <c r="J334" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="K334" s="2" t="s">
         <v>1591</v>
       </c>
-      <c r="K334" s="2" t="s">
+      <c r="L334" s="4" t="s">
         <v>1592</v>
-      </c>
-      <c r="L334" s="4" t="s">
-        <v>1593</v>
       </c>
       <c r="M334" s="2"/>
       <c r="N334" s="2"/>
@@ -22580,7 +22577,7 @@
         <v>31</v>
       </c>
       <c r="S334" s="2" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="T334" s="10">
         <v>202</v>
@@ -22598,11 +22595,11 @@
         <v>292</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" s="10" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>142</v>
@@ -22614,13 +22611,13 @@
       <c r="H335" s="2"/>
       <c r="I335" s="2"/>
       <c r="J335" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="K335" s="2" t="s">
         <v>1596</v>
       </c>
-      <c r="K335" s="2" t="s">
+      <c r="L335" s="4" t="s">
         <v>1597</v>
-      </c>
-      <c r="L335" s="4" t="s">
-        <v>1598</v>
       </c>
       <c r="M335" s="2"/>
       <c r="N335" s="2"/>
@@ -22649,11 +22646,11 @@
         <v>292</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="C336" s="2"/>
       <c r="D336" s="10" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>234</v>
@@ -22671,7 +22668,7 @@
         <v>357</v>
       </c>
       <c r="L336" s="4" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="M336" s="2"/>
       <c r="N336" s="2"/>
@@ -22700,29 +22697,29 @@
         <v>292</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" s="10" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E337" s="2" t="s">
         <v>1601</v>
       </c>
-      <c r="E337" s="2" t="s">
+      <c r="F337" s="2" t="s">
         <v>1602</v>
-      </c>
-      <c r="F337" s="2" t="s">
-        <v>1603</v>
       </c>
       <c r="G337" s="2"/>
       <c r="H337" s="2"/>
       <c r="I337" s="2"/>
       <c r="J337" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="K337" s="2" t="s">
         <v>1604</v>
       </c>
-      <c r="K337" s="2" t="s">
+      <c r="L337" s="4" t="s">
         <v>1605</v>
-      </c>
-      <c r="L337" s="4" t="s">
-        <v>1606</v>
       </c>
       <c r="M337" s="2"/>
       <c r="N337" s="2"/>
@@ -22733,7 +22730,7 @@
         <v>31</v>
       </c>
       <c r="S337" s="2" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="T337" s="10">
         <v>305</v>
@@ -22751,29 +22748,29 @@
         <v>292</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="C338" s="2"/>
       <c r="D338" s="10" t="s">
         <v>212</v>
       </c>
       <c r="E338" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F338" s="2" t="s">
         <v>1607</v>
-      </c>
-      <c r="F338" s="2" t="s">
-        <v>1608</v>
       </c>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
       <c r="I338" s="2"/>
       <c r="J338" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="K338" s="2" t="s">
         <v>1609</v>
       </c>
-      <c r="K338" s="2" t="s">
+      <c r="L338" s="4" t="s">
         <v>1610</v>
-      </c>
-      <c r="L338" s="4" t="s">
-        <v>1611</v>
       </c>
       <c r="M338" s="2"/>
       <c r="N338" s="2"/>
@@ -22784,7 +22781,7 @@
         <v>31</v>
       </c>
       <c r="S338" s="2" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="T338" s="10">
         <v>118</v>
@@ -22799,10 +22796,10 @@
     </row>
     <row r="339" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B339" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B339" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" s="10" t="s">
@@ -22818,13 +22815,13 @@
       <c r="H339" s="2"/>
       <c r="I339" s="2"/>
       <c r="J339" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="K339" s="2" t="s">
         <v>1614</v>
       </c>
-      <c r="K339" s="2" t="s">
+      <c r="L339" s="4" t="s">
         <v>1615</v>
-      </c>
-      <c r="L339" s="4" t="s">
-        <v>1616</v>
       </c>
       <c r="M339" s="2"/>
       <c r="N339" s="2"/>
@@ -22850,20 +22847,20 @@
     </row>
     <row r="340" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B340" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B340" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C340" s="2"/>
       <c r="D340" s="10" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
@@ -22875,7 +22872,7 @@
         <v>608</v>
       </c>
       <c r="L340" s="4" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="M340" s="2"/>
       <c r="N340" s="2"/>
@@ -22901,10 +22898,10 @@
     </row>
     <row r="341" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B341" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C341" s="2"/>
       <c r="D341" s="10" t="s">
@@ -22920,13 +22917,13 @@
       <c r="H341" s="2"/>
       <c r="I341" s="2"/>
       <c r="J341" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="K341" s="2" t="s">
         <v>1620</v>
       </c>
-      <c r="K341" s="2" t="s">
+      <c r="L341" s="4" t="s">
         <v>1621</v>
-      </c>
-      <c r="L341" s="4" t="s">
-        <v>1622</v>
       </c>
       <c r="M341" s="2"/>
       <c r="N341" s="2"/>
@@ -22952,14 +22949,14 @@
     </row>
     <row r="342" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B342" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B342" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C342" s="2"/>
       <c r="D342" s="10" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>75</v>
@@ -22971,13 +22968,13 @@
       <c r="H342" s="2"/>
       <c r="I342" s="2"/>
       <c r="J342" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="K342" s="2" t="s">
         <v>1624</v>
       </c>
-      <c r="K342" s="2" t="s">
+      <c r="L342" s="4" t="s">
         <v>1625</v>
-      </c>
-      <c r="L342" s="4" t="s">
-        <v>1626</v>
       </c>
       <c r="M342" s="2"/>
       <c r="N342" s="2"/>
@@ -23003,10 +23000,10 @@
     </row>
     <row r="343" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B343" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B343" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" s="10" t="s">
@@ -23022,13 +23019,13 @@
       <c r="H343" s="2"/>
       <c r="I343" s="2"/>
       <c r="J343" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="K343" s="2" t="s">
         <v>1627</v>
       </c>
-      <c r="K343" s="2" t="s">
+      <c r="L343" s="4" t="s">
         <v>1628</v>
-      </c>
-      <c r="L343" s="4" t="s">
-        <v>1629</v>
       </c>
       <c r="M343" s="2"/>
       <c r="N343" s="2"/>
@@ -23054,20 +23051,20 @@
     </row>
     <row r="344" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B344" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B344" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C344" s="2"/>
       <c r="D344" s="10" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="G344" s="2"/>
       <c r="H344" s="2"/>
@@ -23076,10 +23073,10 @@
         <v>428</v>
       </c>
       <c r="K344" s="2" t="s">
+        <v>1630</v>
+      </c>
+      <c r="L344" s="4" t="s">
         <v>1631</v>
-      </c>
-      <c r="L344" s="4" t="s">
-        <v>1632</v>
       </c>
       <c r="M344" s="2"/>
       <c r="N344" s="2"/>
@@ -23087,7 +23084,7 @@
       <c r="P344" s="2"/>
       <c r="Q344" s="2"/>
       <c r="R344" s="2" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="S344" s="2" t="s">
         <v>32</v>
@@ -23105,10 +23102,10 @@
     </row>
     <row r="345" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B345" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B345" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" s="10" t="s">
@@ -23118,19 +23115,19 @@
         <v>1170</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="G345" s="2"/>
       <c r="H345" s="2"/>
       <c r="I345" s="2"/>
       <c r="J345" s="2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="K345" s="2" t="s">
         <v>1635</v>
       </c>
-      <c r="K345" s="2" t="s">
+      <c r="L345" s="4" t="s">
         <v>1636</v>
-      </c>
-      <c r="L345" s="4" t="s">
-        <v>1637</v>
       </c>
       <c r="M345" s="2"/>
       <c r="N345" s="2"/>
@@ -23156,14 +23153,14 @@
     </row>
     <row r="346" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B346" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B346" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C346" s="2"/>
       <c r="D346" s="10" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>26</v>
@@ -23175,13 +23172,13 @@
       <c r="H346" s="2"/>
       <c r="I346" s="2"/>
       <c r="J346" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="K346" s="2" t="s">
         <v>1639</v>
       </c>
-      <c r="K346" s="2" t="s">
+      <c r="L346" s="4" t="s">
         <v>1640</v>
-      </c>
-      <c r="L346" s="4" t="s">
-        <v>1641</v>
       </c>
       <c r="M346" s="2"/>
       <c r="N346" s="2"/>
@@ -23207,10 +23204,10 @@
     </row>
     <row r="347" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B347" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B347" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C347" s="2"/>
       <c r="D347" s="10" t="s">
@@ -23226,13 +23223,13 @@
       <c r="H347" s="2"/>
       <c r="I347" s="2"/>
       <c r="J347" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K347" s="2" t="s">
         <v>1642</v>
       </c>
-      <c r="K347" s="2" t="s">
+      <c r="L347" s="4" t="s">
         <v>1643</v>
-      </c>
-      <c r="L347" s="4" t="s">
-        <v>1644</v>
       </c>
       <c r="M347" s="2"/>
       <c r="N347" s="2"/>
@@ -23258,14 +23255,14 @@
     </row>
     <row r="348" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B348" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C348" s="2"/>
       <c r="D348" s="10" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>234</v>
@@ -23277,13 +23274,13 @@
       <c r="H348" s="2"/>
       <c r="I348" s="2"/>
       <c r="J348" s="2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="K348" s="2" t="s">
         <v>1646</v>
       </c>
-      <c r="K348" s="2" t="s">
+      <c r="L348" s="4" t="s">
         <v>1647</v>
-      </c>
-      <c r="L348" s="4" t="s">
-        <v>1648</v>
       </c>
       <c r="M348" s="2"/>
       <c r="N348" s="2"/>
@@ -23309,32 +23306,32 @@
     </row>
     <row r="349" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B349" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B349" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C349" s="2"/>
       <c r="D349" s="10" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>1302</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="G349" s="2"/>
       <c r="H349" s="2"/>
       <c r="I349" s="2"/>
       <c r="J349" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="K349" s="2" t="s">
         <v>1650</v>
       </c>
-      <c r="K349" s="2" t="s">
+      <c r="L349" s="4" t="s">
         <v>1651</v>
-      </c>
-      <c r="L349" s="4" t="s">
-        <v>1652</v>
       </c>
       <c r="M349" s="2"/>
       <c r="N349" s="2"/>
@@ -23360,14 +23357,14 @@
     </row>
     <row r="350" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B350" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="B350" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" s="10" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>295</v>
@@ -23385,7 +23382,7 @@
         <v>903</v>
       </c>
       <c r="L350" s="4" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="M350" s="2"/>
       <c r="N350" s="2"/>
@@ -23411,10 +23408,10 @@
     </row>
     <row r="351" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B351" s="2" t="s">
         <v>1655</v>
-      </c>
-      <c r="B351" s="2" t="s">
-        <v>1656</v>
       </c>
       <c r="C351" s="2"/>
       <c r="D351" s="10" t="s">
@@ -23430,13 +23427,13 @@
       <c r="H351" s="2"/>
       <c r="I351" s="2"/>
       <c r="J351" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="K351" s="2" t="s">
         <v>1657</v>
       </c>
-      <c r="K351" s="2" t="s">
+      <c r="L351" s="4" t="s">
         <v>1658</v>
-      </c>
-      <c r="L351" s="4" t="s">
-        <v>1659</v>
       </c>
       <c r="M351" s="2"/>
       <c r="N351" s="2"/>
@@ -23450,10 +23447,10 @@
         <v>32</v>
       </c>
       <c r="T351" s="10" t="s">
+        <v>1659</v>
+      </c>
+      <c r="U351" s="10" t="s">
         <v>1660</v>
-      </c>
-      <c r="U351" s="10" t="s">
-        <v>1661</v>
       </c>
       <c r="V351" s="10"/>
       <c r="W351" s="10" t="s">
@@ -23462,10 +23459,10 @@
     </row>
     <row r="352" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B352" s="2" t="s">
         <v>1655</v>
-      </c>
-      <c r="B352" s="2" t="s">
-        <v>1656</v>
       </c>
       <c r="C352" s="2"/>
       <c r="D352" s="10" t="s">
@@ -23481,13 +23478,13 @@
       <c r="H352" s="2"/>
       <c r="I352" s="2"/>
       <c r="J352" s="2" t="s">
+        <v>1661</v>
+      </c>
+      <c r="K352" s="2" t="s">
         <v>1662</v>
       </c>
-      <c r="K352" s="2" t="s">
+      <c r="L352" s="4" t="s">
         <v>1663</v>
-      </c>
-      <c r="L352" s="4" t="s">
-        <v>1664</v>
       </c>
       <c r="M352" s="2"/>
       <c r="N352" s="2"/>
@@ -23501,10 +23498,10 @@
         <v>32</v>
       </c>
       <c r="T352" s="10" t="s">
+        <v>1664</v>
+      </c>
+      <c r="U352" s="10" t="s">
         <v>1665</v>
-      </c>
-      <c r="U352" s="10" t="s">
-        <v>1666</v>
       </c>
       <c r="V352" s="10"/>
       <c r="W352" s="10" t="s">
@@ -23513,10 +23510,10 @@
     </row>
     <row r="353" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B353" s="2" t="s">
         <v>1655</v>
-      </c>
-      <c r="B353" s="2" t="s">
-        <v>1656</v>
       </c>
       <c r="C353" s="2"/>
       <c r="D353" s="10" t="s">
@@ -23532,13 +23529,13 @@
       <c r="H353" s="2"/>
       <c r="I353" s="2"/>
       <c r="J353" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="K353" s="2" t="s">
         <v>1667</v>
       </c>
-      <c r="K353" s="2" t="s">
+      <c r="L353" s="4" t="s">
         <v>1668</v>
-      </c>
-      <c r="L353" s="4" t="s">
-        <v>1669</v>
       </c>
       <c r="M353" s="2"/>
       <c r="N353" s="2"/>
@@ -23552,10 +23549,10 @@
         <v>32</v>
       </c>
       <c r="T353" s="10" t="s">
+        <v>1669</v>
+      </c>
+      <c r="U353" s="10" t="s">
         <v>1670</v>
-      </c>
-      <c r="U353" s="10" t="s">
-        <v>1671</v>
       </c>
       <c r="V353" s="10"/>
       <c r="W353" s="10" t="s">
@@ -23564,10 +23561,10 @@
     </row>
     <row r="354" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B354" s="2" t="s">
         <v>1655</v>
-      </c>
-      <c r="B354" s="2" t="s">
-        <v>1656</v>
       </c>
       <c r="C354" s="2"/>
       <c r="D354" s="10" t="s">
@@ -23583,11 +23580,11 @@
       <c r="H354" s="2"/>
       <c r="I354" s="2"/>
       <c r="J354" s="2" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="K354" s="2"/>
       <c r="L354" s="4" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M354" s="2"/>
       <c r="N354" s="2"/>
@@ -23601,10 +23598,10 @@
         <v>32</v>
       </c>
       <c r="T354" s="10" t="s">
+        <v>1673</v>
+      </c>
+      <c r="U354" s="10" t="s">
         <v>1674</v>
-      </c>
-      <c r="U354" s="10" t="s">
-        <v>1675</v>
       </c>
       <c r="V354" s="10"/>
       <c r="W354" s="10" t="s">
@@ -23613,14 +23610,14 @@
     </row>
     <row r="355" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B355" s="2" t="s">
         <v>1655</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>1656</v>
       </c>
       <c r="C355" s="2"/>
       <c r="D355" s="10" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>295</v>
@@ -23632,11 +23629,11 @@
       <c r="H355" s="2"/>
       <c r="I355" s="2"/>
       <c r="J355" s="2" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="K355" s="2"/>
       <c r="L355" s="4" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="M355" s="2"/>
       <c r="N355" s="2"/>
@@ -23662,14 +23659,14 @@
     </row>
     <row r="356" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B356" s="2" t="s">
         <v>1655</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>1656</v>
       </c>
       <c r="C356" s="2"/>
       <c r="D356" s="10" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>295</v>
@@ -23681,11 +23678,11 @@
       <c r="H356" s="2"/>
       <c r="I356" s="2"/>
       <c r="J356" s="2" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="K356" s="2"/>
       <c r="L356" s="4" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="M356" s="2"/>
       <c r="N356" s="2"/>
@@ -23693,16 +23690,16 @@
       <c r="P356" s="2"/>
       <c r="Q356" s="2"/>
       <c r="R356" s="2" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="S356" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T356" s="10" t="s">
+        <v>1680</v>
+      </c>
+      <c r="U356" s="10" t="s">
         <v>1681</v>
-      </c>
-      <c r="U356" s="10" t="s">
-        <v>1682</v>
       </c>
       <c r="V356" s="10"/>
       <c r="W356" s="10" t="s">
@@ -23711,30 +23708,30 @@
     </row>
     <row r="357" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B357" s="2" t="s">
         <v>1655</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>1656</v>
       </c>
       <c r="C357" s="2"/>
       <c r="D357" s="10" t="s">
+        <v>1682</v>
+      </c>
+      <c r="E357" s="2" t="s">
         <v>1683</v>
       </c>
-      <c r="E357" s="2" t="s">
+      <c r="F357" s="2" t="s">
         <v>1684</v>
-      </c>
-      <c r="F357" s="2" t="s">
-        <v>1685</v>
       </c>
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
       <c r="I357" s="2"/>
       <c r="J357" s="2" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="K357" s="2"/>
       <c r="L357" s="4" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="M357" s="2"/>
       <c r="N357" s="2"/>
@@ -23742,10 +23739,10 @@
       <c r="P357" s="2"/>
       <c r="Q357" s="2"/>
       <c r="R357" s="2" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="S357" s="2" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="T357" s="10"/>
       <c r="U357" s="10"/>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1017B87-1D24-4805-A53A-4E67D4E7F2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EAA930-38A4-441D-9F6E-2D0447BE2178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3673" uniqueCount="1691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3662" uniqueCount="1687">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2864,18 +2864,6 @@
     <t>FONTANA</t>
   </si>
   <si>
-    <t>1613</t>
-  </si>
-  <si>
-    <t>Minerve s'habillant</t>
-  </si>
-  <si>
-    <t>Minerva che si abbiglia</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/74-_Lavinia_Fontana%2C_Minerva_in_atto_di_abbigliarsi%2C_1613_-FG74.jpg/1280px-74-_Lavinia_Fontana%2C_Minerva_in_atto_di_abbigliarsi%2C_1613_-FG74.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1584</t>
   </si>
   <si>
@@ -4124,12 +4112,6 @@
     <t xml:space="preserve"> 1534-1535</t>
   </si>
   <si>
-    <t>Lucca</t>
-  </si>
-  <si>
-    <t>Musée national du Palais Mansi</t>
-  </si>
-  <si>
     <t>Portrait d'Alessandro de' Medici</t>
   </si>
   <si>
@@ -5106,6 +5088,12 @@
   </si>
   <si>
     <t>Cathédrale San Lorenzo</t>
+  </si>
+  <si>
+    <t>Philadelphie</t>
+  </si>
+  <si>
+    <t>Musée Städel</t>
   </si>
 </sst>
 </file>
@@ -5562,7 +5550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X357"/>
+  <dimension ref="A1:X356"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -8669,7 +8657,7 @@
         <v>328</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>1690</v>
+        <v>1684</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -9734,7 +9722,7 @@
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="10" t="s">
-        <v>1686</v>
+        <v>1680</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>365</v>
@@ -10513,7 +10501,7 @@
         <v>512</v>
       </c>
       <c r="L96" s="13" t="s">
-        <v>1687</v>
+        <v>1681</v>
       </c>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
@@ -12605,54 +12593,54 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="2" t="s">
+    <row r="138" spans="1:23" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="C138" s="2"/>
-      <c r="D138" s="10" t="s">
-        <v>672</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G138" s="2"/>
-      <c r="H138" s="2"/>
-      <c r="I138" s="2"/>
-      <c r="J138" s="2" t="s">
+      <c r="C138" s="14"/>
+      <c r="D138" s="15">
+        <v>1533</v>
+      </c>
+      <c r="E138" s="14" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F138" s="14" t="s">
+        <v>1686</v>
+      </c>
+      <c r="G138" s="14"/>
+      <c r="H138" s="14"/>
+      <c r="I138" s="14"/>
+      <c r="J138" s="14" t="s">
         <v>694</v>
       </c>
-      <c r="K138" s="3" t="s">
+      <c r="K138" s="18" t="s">
         <v>695</v>
       </c>
-      <c r="L138" s="4" t="s">
+      <c r="L138" s="16" t="s">
         <v>696</v>
       </c>
-      <c r="M138" s="2"/>
-      <c r="N138" s="3"/>
-      <c r="O138" s="2"/>
-      <c r="P138" s="3"/>
-      <c r="Q138" s="2"/>
-      <c r="R138" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S138" s="2" t="s">
+      <c r="M138" s="14"/>
+      <c r="N138" s="18"/>
+      <c r="O138" s="14"/>
+      <c r="P138" s="18"/>
+      <c r="Q138" s="14"/>
+      <c r="R138" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="S138" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="T138" s="10">
+      <c r="T138" s="15">
         <v>80</v>
       </c>
-      <c r="U138" s="10">
-        <v>117</v>
-      </c>
-      <c r="V138" s="10"/>
-      <c r="W138" s="10">
+      <c r="U138" s="15">
+        <v>113</v>
+      </c>
+      <c r="V138" s="15"/>
+      <c r="W138" s="15">
         <v>2</v>
       </c>
     </row>
@@ -15596,22 +15584,22 @@
         <v>943</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>96</v>
+        <v>604</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>97</v>
+        <v>944</v>
       </c>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
       <c r="J197" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="K197" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="L197" s="4" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
@@ -15625,14 +15613,14 @@
         <v>32</v>
       </c>
       <c r="T197" s="10">
-        <v>133</v>
+        <v>253</v>
       </c>
       <c r="U197" s="10">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="V197" s="10"/>
       <c r="W197" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15644,13 +15632,13 @@
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="10" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>604</v>
+        <v>142</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>948</v>
+        <v>143</v>
       </c>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
@@ -15676,14 +15664,14 @@
         <v>32</v>
       </c>
       <c r="T198" s="10">
-        <v>253</v>
+        <v>27</v>
       </c>
       <c r="U198" s="10">
-        <v>191</v>
+        <v>24</v>
       </c>
       <c r="V198" s="10"/>
       <c r="W198" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15698,22 +15686,22 @@
         <v>952</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>142</v>
+        <v>26</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>143</v>
+        <v>953</v>
       </c>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
       <c r="J199" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="K199" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="L199" s="4" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="M199" s="2"/>
       <c r="N199" s="2"/>
@@ -15727,44 +15715,42 @@
         <v>32</v>
       </c>
       <c r="T199" s="10">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="U199" s="10">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="V199" s="10"/>
       <c r="W199" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>941</v>
+        <v>957</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>942</v>
+        <v>958</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="10" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>26</v>
+        <v>233</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>957</v>
+        <v>234</v>
       </c>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
       <c r="J200" s="2" t="s">
-        <v>958</v>
-      </c>
-      <c r="K200" s="2" t="s">
-        <v>959</v>
-      </c>
+        <v>960</v>
+      </c>
+      <c r="K200" s="3"/>
       <c r="L200" s="4" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
@@ -15775,29 +15761,29 @@
         <v>31</v>
       </c>
       <c r="S200" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="T200" s="10">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="U200" s="10">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="V200" s="10"/>
       <c r="W200" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" s="10" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>233</v>
@@ -15809,9 +15795,11 @@
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
       <c r="J201" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="K201" s="3" t="s">
         <v>964</v>
       </c>
-      <c r="K201" s="3"/>
       <c r="L201" s="4" t="s">
         <v>965</v>
       </c>
@@ -15827,10 +15815,10 @@
         <v>117</v>
       </c>
       <c r="T201" s="10">
-        <v>96</v>
+        <v>257</v>
       </c>
       <c r="U201" s="10">
-        <v>76</v>
+        <v>228</v>
       </c>
       <c r="V201" s="10"/>
       <c r="W201" s="10">
@@ -15839,32 +15827,32 @@
     </row>
     <row r="202" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" s="10" t="s">
-        <v>966</v>
+        <v>105</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>234</v>
+        <v>839</v>
       </c>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
-      <c r="I202" s="2"/>
+      <c r="I202" s="4"/>
       <c r="J202" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="K202" s="3" t="s">
         <v>967</v>
       </c>
-      <c r="K202" s="3" t="s">
+      <c r="L202" s="13" t="s">
         <v>968</v>
-      </c>
-      <c r="L202" s="4" t="s">
-        <v>969</v>
       </c>
       <c r="M202" s="2"/>
       <c r="N202" s="2"/>
@@ -15878,10 +15866,10 @@
         <v>117</v>
       </c>
       <c r="T202" s="10">
-        <v>257</v>
+        <v>158</v>
       </c>
       <c r="U202" s="10">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="V202" s="10"/>
       <c r="W202" s="10">
@@ -15890,31 +15878,31 @@
     </row>
     <row r="203" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C203" s="2"/>
-      <c r="D203" s="10" t="s">
-        <v>105</v>
+      <c r="D203" s="10">
+        <v>1498</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>142</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>839</v>
+        <v>969</v>
       </c>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
-      <c r="I203" s="4"/>
+      <c r="I203" s="2"/>
       <c r="J203" s="2" t="s">
         <v>970</v>
       </c>
       <c r="K203" s="3" t="s">
         <v>971</v>
       </c>
-      <c r="L203" s="13" t="s">
+      <c r="L203" s="4" t="s">
         <v>972</v>
       </c>
       <c r="M203" s="2"/>
@@ -15929,10 +15917,10 @@
         <v>117</v>
       </c>
       <c r="T203" s="10">
-        <v>158</v>
+        <v>47</v>
       </c>
       <c r="U203" s="10">
-        <v>199</v>
+        <v>31</v>
       </c>
       <c r="V203" s="10"/>
       <c r="W203" s="10">
@@ -15941,32 +15929,32 @@
     </row>
     <row r="204" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C204" s="2"/>
-      <c r="D204" s="10">
-        <v>1498</v>
+      <c r="D204" s="10" t="s">
+        <v>959</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>142</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
       <c r="J204" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="K204" s="3" t="s">
         <v>974</v>
       </c>
-      <c r="K204" s="3" t="s">
+      <c r="L204" s="4" t="s">
         <v>975</v>
-      </c>
-      <c r="L204" s="4" t="s">
-        <v>976</v>
       </c>
       <c r="M204" s="2"/>
       <c r="N204" s="2"/>
@@ -15977,98 +15965,98 @@
         <v>31</v>
       </c>
       <c r="S204" s="2" t="s">
-        <v>117</v>
+        <v>976</v>
       </c>
       <c r="T204" s="10">
-        <v>47</v>
+        <v>352</v>
       </c>
       <c r="U204" s="10">
-        <v>31</v>
+        <v>212</v>
       </c>
       <c r="V204" s="10"/>
       <c r="W204" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:23" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C205" s="2"/>
-      <c r="D205" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="E205" s="2" t="s">
+      <c r="D205" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="E205" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="F205" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2" t="s">
+      <c r="F205" s="14" t="s">
+        <v>839</v>
+      </c>
+      <c r="G205" s="14"/>
+      <c r="H205" s="14"/>
+      <c r="I205" s="14"/>
+      <c r="J205" s="14" t="s">
         <v>977</v>
       </c>
-      <c r="K205" s="3" t="s">
+      <c r="K205" s="18" t="s">
         <v>978</v>
       </c>
-      <c r="L205" s="4" t="s">
+      <c r="L205" s="16" t="s">
         <v>979</v>
       </c>
-      <c r="M205" s="2"/>
-      <c r="N205" s="2"/>
-      <c r="O205" s="2"/>
-      <c r="P205" s="2"/>
-      <c r="Q205" s="2"/>
-      <c r="R205" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S205" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="T205" s="10">
-        <v>352</v>
-      </c>
-      <c r="U205" s="10">
-        <v>212</v>
-      </c>
-      <c r="V205" s="10"/>
-      <c r="W205" s="10">
+      <c r="M205" s="14"/>
+      <c r="N205" s="14"/>
+      <c r="O205" s="14"/>
+      <c r="P205" s="14"/>
+      <c r="Q205" s="14"/>
+      <c r="R205" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="S205" s="14" t="s">
+        <v>976</v>
+      </c>
+      <c r="T205" s="15">
+        <v>283</v>
+      </c>
+      <c r="U205" s="15">
+        <v>201</v>
+      </c>
+      <c r="V205" s="15"/>
+      <c r="W205" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="206" spans="1:23" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" s="15" t="s">
-        <v>522</v>
+        <v>105</v>
       </c>
       <c r="E206" s="14" t="s">
-        <v>142</v>
+        <v>980</v>
       </c>
       <c r="F206" s="14" t="s">
-        <v>839</v>
+        <v>981</v>
       </c>
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="14"/>
       <c r="J206" s="14" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="K206" s="18" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="L206" s="16" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="M206" s="14"/>
       <c r="N206" s="14"/>
@@ -16079,116 +16067,118 @@
         <v>31</v>
       </c>
       <c r="S206" s="14" t="s">
-        <v>980</v>
+        <v>117</v>
       </c>
       <c r="T206" s="15">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="U206" s="15">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="V206" s="15"/>
       <c r="W206" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:23" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>961</v>
+        <v>985</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>962</v>
+        <v>986</v>
       </c>
       <c r="C207" s="2"/>
-      <c r="D207" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E207" s="14" t="s">
-        <v>984</v>
-      </c>
-      <c r="F207" s="14" t="s">
-        <v>985</v>
-      </c>
-      <c r="G207" s="14"/>
-      <c r="H207" s="14"/>
-      <c r="I207" s="14"/>
-      <c r="J207" s="14" t="s">
-        <v>986</v>
-      </c>
-      <c r="K207" s="18" t="s">
+      <c r="D207" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G207" s="2"/>
+      <c r="H207" s="2"/>
+      <c r="I207" s="2"/>
+      <c r="J207" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="L207" s="16" t="s">
+      <c r="K207" s="2" t="s">
         <v>988</v>
       </c>
-      <c r="M207" s="14"/>
-      <c r="N207" s="14"/>
-      <c r="O207" s="14"/>
-      <c r="P207" s="14"/>
-      <c r="Q207" s="14"/>
-      <c r="R207" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="S207" s="14" t="s">
+      <c r="L207" s="3" t="str">
+        <f>HYPERLINK("https://upload.wikimedia.org/wikipedia/commons/8/8f/Jan_Gossaert_-_Neptune_and_Amphitrite_-_WGA9786.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled", "https://upload.wikimedia.org/wikipedia/commons/8/8f/Jan_Gossaert_-_Neptune_and_Amphitrite_-_WGA9786.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled")</f>
+        <v>https://upload.wikimedia.org/wikipedia/commons/8/8f/Jan_Gossaert_-_Neptune_and_Amphitrite_-_WGA9786.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</v>
+      </c>
+      <c r="M207" s="2"/>
+      <c r="N207" s="2"/>
+      <c r="O207" s="2"/>
+      <c r="P207" s="2"/>
+      <c r="Q207" s="2"/>
+      <c r="R207" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S207" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="T207" s="15">
-        <v>260</v>
-      </c>
-      <c r="U207" s="15">
-        <v>230</v>
-      </c>
-      <c r="V207" s="15"/>
-      <c r="W207" s="15">
-        <v>2</v>
+      <c r="T207" s="10">
+        <v>188</v>
+      </c>
+      <c r="U207" s="10">
+        <v>124</v>
+      </c>
+      <c r="V207" s="10"/>
+      <c r="W207" s="10">
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="10" t="s">
-        <v>522</v>
+        <v>284</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>112</v>
+        <v>233</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>113</v>
+        <v>234</v>
       </c>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
       <c r="J208" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="K208" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="L208" s="4" t="s">
         <v>991</v>
       </c>
-      <c r="K208" s="2" t="s">
+      <c r="M208" s="2"/>
+      <c r="N208" s="7" t="s">
         <v>992</v>
       </c>
-      <c r="L208" s="3" t="str">
-        <f>HYPERLINK("https://upload.wikimedia.org/wikipedia/commons/8/8f/Jan_Gossaert_-_Neptune_and_Amphitrite_-_WGA9786.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled", "https://upload.wikimedia.org/wikipedia/commons/8/8f/Jan_Gossaert_-_Neptune_and_Amphitrite_-_WGA9786.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled")</f>
-        <v>https://upload.wikimedia.org/wikipedia/commons/8/8f/Jan_Gossaert_-_Neptune_and_Amphitrite_-_WGA9786.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</v>
-      </c>
-      <c r="M208" s="2"/>
-      <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" s="2"/>
       <c r="Q208" s="2"/>
       <c r="R208" s="2" t="s">
-        <v>31</v>
+        <v>993</v>
       </c>
       <c r="S208" s="2" t="s">
         <v>117</v>
       </c>
       <c r="T208" s="10">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="U208" s="10">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="V208" s="10"/>
       <c r="W208" s="10">
@@ -16197,51 +16187,47 @@
     </row>
     <row r="209" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>233</v>
-      </c>
+        <v>994</v>
+      </c>
+      <c r="E209" s="2"/>
       <c r="F209" s="2" t="s">
-        <v>234</v>
+        <v>650</v>
       </c>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
       <c r="J209" s="2" t="s">
-        <v>993</v>
+        <v>674</v>
       </c>
       <c r="K209" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="L209" s="4" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M209" s="2"/>
-      <c r="N209" s="7" t="s">
-        <v>996</v>
-      </c>
+      <c r="N209" s="2"/>
       <c r="O209" s="2"/>
       <c r="P209" s="2"/>
       <c r="Q209" s="2"/>
       <c r="R209" s="2" t="s">
-        <v>997</v>
+        <v>31</v>
       </c>
       <c r="S209" s="2" t="s">
         <v>117</v>
       </c>
       <c r="T209" s="10">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="U209" s="10">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="V209" s="10"/>
       <c r="W209" s="10">
@@ -16250,24 +16236,26 @@
     </row>
     <row r="210" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="10" t="s">
-        <v>998</v>
-      </c>
-      <c r="E210" s="2"/>
+        <v>997</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="F210" s="2" t="s">
-        <v>650</v>
+        <v>76</v>
       </c>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
       <c r="J210" s="2" t="s">
-        <v>674</v>
+        <v>998</v>
       </c>
       <c r="K210" s="2" t="s">
         <v>999</v>
@@ -16287,10 +16275,10 @@
         <v>117</v>
       </c>
       <c r="T210" s="10">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="U210" s="10">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="V210" s="10"/>
       <c r="W210" s="10">
@@ -16299,32 +16287,30 @@
     </row>
     <row r="211" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" s="10" t="s">
-        <v>1001</v>
+        <v>959</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>75</v>
+        <v>1003</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>76</v>
+        <v>1004</v>
       </c>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
       <c r="J211" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="K211" s="2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="L211" s="4" t="s">
-        <v>1004</v>
+        <v>1005</v>
+      </c>
+      <c r="K211" s="2"/>
+      <c r="L211" s="11" t="s">
+        <v>1006</v>
       </c>
       <c r="M211" s="2"/>
       <c r="N211" s="2"/>
@@ -16332,48 +16318,50 @@
       <c r="P211" s="2"/>
       <c r="Q211" s="2"/>
       <c r="R211" s="2" t="s">
-        <v>31</v>
+        <v>1007</v>
       </c>
       <c r="S211" s="2" t="s">
-        <v>117</v>
+        <v>1008</v>
       </c>
       <c r="T211" s="10">
-        <v>177</v>
+        <v>376</v>
       </c>
       <c r="U211" s="10">
-        <v>162</v>
+        <v>534</v>
       </c>
       <c r="V211" s="10"/>
       <c r="W211" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" s="10" t="s">
-        <v>963</v>
+        <v>1009</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>1007</v>
+        <v>34</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>1008</v>
+        <v>35</v>
       </c>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
       <c r="J212" s="2" t="s">
-        <v>1009</v>
-      </c>
-      <c r="K212" s="2"/>
-      <c r="L212" s="11" t="s">
         <v>1010</v>
+      </c>
+      <c r="K212" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="L212" s="4" t="s">
+        <v>1012</v>
       </c>
       <c r="M212" s="2"/>
       <c r="N212" s="2"/>
@@ -16381,16 +16369,16 @@
       <c r="P212" s="2"/>
       <c r="Q212" s="2"/>
       <c r="R212" s="2" t="s">
-        <v>1011</v>
+        <v>31</v>
       </c>
       <c r="S212" s="2" t="s">
-        <v>1012</v>
+        <v>117</v>
       </c>
       <c r="T212" s="10">
-        <v>376</v>
+        <v>109</v>
       </c>
       <c r="U212" s="10">
-        <v>534</v>
+        <v>74</v>
       </c>
       <c r="V212" s="10"/>
       <c r="W212" s="10">
@@ -16399,32 +16387,32 @@
     </row>
     <row r="213" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C213" s="2"/>
-      <c r="D213" s="10" t="s">
-        <v>1013</v>
+      <c r="D213" s="10">
+        <v>1505</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>34</v>
+        <v>285</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>35</v>
+        <v>286</v>
       </c>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
       <c r="I213" s="2"/>
       <c r="J213" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K213" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="K213" s="2" t="s">
+      <c r="L213" s="4" t="s">
         <v>1015</v>
-      </c>
-      <c r="L213" s="4" t="s">
-        <v>1016</v>
       </c>
       <c r="M213" s="2"/>
       <c r="N213" s="2"/>
@@ -16438,123 +16426,123 @@
         <v>117</v>
       </c>
       <c r="T213" s="10">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="U213" s="10">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="V213" s="10"/>
       <c r="W213" s="10">
         <v>2</v>
       </c>
+      <c r="X213" s="2"/>
     </row>
     <row r="214" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C214" s="2"/>
-      <c r="D214" s="10">
-        <v>1505</v>
+      <c r="D214" s="10" t="s">
+        <v>1016</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>285</v>
+        <v>1017</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>286</v>
+        <v>1018</v>
       </c>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
       <c r="I214" s="2"/>
       <c r="J214" s="2" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="K214" s="2" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="L214" s="4" t="s">
-        <v>1019</v>
-      </c>
-      <c r="M214" s="2"/>
-      <c r="N214" s="2"/>
-      <c r="O214" s="2"/>
-      <c r="P214" s="2"/>
-      <c r="Q214" s="2"/>
+        <v>1021</v>
+      </c>
+      <c r="M214" s="7" t="s">
+        <v>1022</v>
+      </c>
+      <c r="N214" s="7" t="s">
+        <v>1023</v>
+      </c>
+      <c r="O214" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="P214" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="Q214" s="2" t="s">
+        <v>1026</v>
+      </c>
       <c r="R214" s="2" t="s">
-        <v>31</v>
+        <v>1027</v>
       </c>
       <c r="S214" s="2" t="s">
-        <v>117</v>
+        <v>1028</v>
       </c>
       <c r="T214" s="10">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="U214" s="10">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="V214" s="10"/>
       <c r="W214" s="10">
         <v>2</v>
       </c>
-      <c r="X214" s="2"/>
     </row>
     <row r="215" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" s="10" t="s">
-        <v>1020</v>
+        <v>1029</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>1021</v>
+        <v>70</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>1022</v>
+        <v>71</v>
       </c>
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
       <c r="I215" s="2"/>
       <c r="J215" s="2" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="L215" s="4" t="s">
-        <v>1025</v>
-      </c>
-      <c r="M215" s="7" t="s">
-        <v>1026</v>
-      </c>
-      <c r="N215" s="7" t="s">
-        <v>1027</v>
-      </c>
-      <c r="O215" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="P215" s="7" t="s">
-        <v>1029</v>
-      </c>
-      <c r="Q215" s="2" t="s">
-        <v>1030</v>
-      </c>
+        <v>1032</v>
+      </c>
+      <c r="M215" s="2"/>
+      <c r="N215" s="2"/>
+      <c r="O215" s="2"/>
+      <c r="P215" s="2"/>
+      <c r="Q215" s="2"/>
       <c r="R215" s="2" t="s">
-        <v>1031</v>
+        <v>31</v>
       </c>
       <c r="S215" s="2" t="s">
-        <v>1032</v>
+        <v>117</v>
       </c>
       <c r="T215" s="10">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="U215" s="10">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V215" s="10"/>
       <c r="W215" s="10">
@@ -16563,20 +16551,20 @@
     </row>
     <row r="216" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F216" s="2" t="s">
         <v>1033</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
@@ -16590,7 +16578,9 @@
       <c r="L216" s="4" t="s">
         <v>1036</v>
       </c>
-      <c r="M216" s="2"/>
+      <c r="M216" s="2" t="s">
+        <v>1037</v>
+      </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
       <c r="P216" s="2"/>
@@ -16602,10 +16592,10 @@
         <v>117</v>
       </c>
       <c r="T216" s="10">
-        <v>62</v>
+        <v>179</v>
       </c>
       <c r="U216" s="10">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="V216" s="10"/>
       <c r="W216" s="10">
@@ -16614,36 +16604,34 @@
     </row>
     <row r="217" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" s="10" t="s">
         <v>816</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>276</v>
+        <v>1038</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
       <c r="J217" s="2" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="K217" s="2" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="L217" s="4" t="s">
-        <v>1040</v>
-      </c>
-      <c r="M217" s="2" t="s">
-        <v>1041</v>
-      </c>
+        <v>1042</v>
+      </c>
+      <c r="M217" s="2"/>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
       <c r="P217" s="2"/>
@@ -16652,13 +16640,13 @@
         <v>31</v>
       </c>
       <c r="S217" s="2" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="T217" s="10">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U217" s="10">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="V217" s="10"/>
       <c r="W217" s="10">
@@ -16667,20 +16655,20 @@
     </row>
     <row r="218" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" s="10" t="s">
-        <v>816</v>
+        <v>1043</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>1042</v>
+        <v>34</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>1043</v>
+        <v>35</v>
       </c>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
@@ -16703,13 +16691,13 @@
         <v>31</v>
       </c>
       <c r="S218" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="T218" s="10">
-        <v>186</v>
+        <v>226</v>
       </c>
       <c r="U218" s="10">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="V218" s="10"/>
       <c r="W218" s="10">
@@ -16718,32 +16706,32 @@
     </row>
     <row r="219" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>1005</v>
+        <v>262</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>1006</v>
+        <v>1047</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" s="10" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>34</v>
+        <v>285</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>35</v>
+        <v>286</v>
       </c>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
       <c r="J219" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="K219" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="L219" s="4" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="M219" s="2"/>
       <c r="N219" s="2"/>
@@ -16754,17 +16742,17 @@
         <v>31</v>
       </c>
       <c r="S219" s="2" t="s">
-        <v>117</v>
+        <v>1052</v>
       </c>
       <c r="T219" s="10">
-        <v>226</v>
+        <v>31</v>
       </c>
       <c r="U219" s="10">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="V219" s="10"/>
       <c r="W219" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16772,11 +16760,11 @@
         <v>262</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" s="10" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>285</v>
@@ -16788,13 +16776,13 @@
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
       <c r="J220" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="K220" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="L220" s="4" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="M220" s="2"/>
       <c r="N220" s="2"/>
@@ -16805,13 +16793,13 @@
         <v>31</v>
       </c>
       <c r="S220" s="2" t="s">
-        <v>1056</v>
+        <v>117</v>
       </c>
       <c r="T220" s="10">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="U220" s="10">
-        <v>200</v>
+        <v>33</v>
       </c>
       <c r="V220" s="10"/>
       <c r="W220" s="10">
@@ -16823,17 +16811,17 @@
         <v>262</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" s="10" t="s">
         <v>1057</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>285</v>
+        <v>75</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>286</v>
+        <v>76</v>
       </c>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
@@ -16856,13 +16844,13 @@
         <v>31</v>
       </c>
       <c r="S221" s="2" t="s">
-        <v>117</v>
+        <v>1061</v>
       </c>
       <c r="T221" s="10">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="U221" s="10">
-        <v>33</v>
+        <v>210</v>
       </c>
       <c r="V221" s="10"/>
       <c r="W221" s="10">
@@ -16874,29 +16862,29 @@
         <v>262</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="10" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>75</v>
+        <v>212</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
       <c r="J222" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="L222" s="4" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="M222" s="2"/>
       <c r="N222" s="2"/>
@@ -16907,13 +16895,13 @@
         <v>31</v>
       </c>
       <c r="S222" s="2" t="s">
-        <v>1065</v>
+        <v>117</v>
       </c>
       <c r="T222" s="10">
-        <v>207</v>
+        <v>65</v>
       </c>
       <c r="U222" s="10">
-        <v>210</v>
+        <v>41</v>
       </c>
       <c r="V222" s="10"/>
       <c r="W222" s="10">
@@ -16925,29 +16913,29 @@
         <v>262</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" s="10" t="s">
         <v>1066</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>212</v>
+        <v>1067</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>213</v>
+        <v>1068</v>
       </c>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
       <c r="J223" s="2" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="K223" s="2" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="L223" s="4" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="M223" s="2"/>
       <c r="N223" s="2"/>
@@ -16961,10 +16949,10 @@
         <v>117</v>
       </c>
       <c r="T223" s="10">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="U223" s="10">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="V223" s="10"/>
       <c r="W223" s="10">
@@ -16976,29 +16964,27 @@
         <v>262</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" s="10" t="s">
-        <v>1070</v>
+        <v>863</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>1071</v>
+        <v>46</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>1072</v>
+        <v>148</v>
       </c>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
       <c r="J224" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="K224" s="2"/>
+      <c r="L224" s="4" t="s">
         <v>1073</v>
-      </c>
-      <c r="K224" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="L224" s="4" t="s">
-        <v>1075</v>
       </c>
       <c r="M224" s="2"/>
       <c r="N224" s="2"/>
@@ -17012,10 +16998,10 @@
         <v>117</v>
       </c>
       <c r="T224" s="10">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="U224" s="10">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="V224" s="10"/>
       <c r="W224" s="10">
@@ -17027,27 +17013,27 @@
         <v>262</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" s="10" t="s">
-        <v>863</v>
+        <v>1074</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>46</v>
+        <v>1075</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>148</v>
+        <v>1076</v>
       </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="2"/>
       <c r="J225" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="K225" s="2"/>
       <c r="L225" s="4" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="M225" s="2"/>
       <c r="N225" s="2"/>
@@ -17061,10 +17047,10 @@
         <v>117</v>
       </c>
       <c r="T225" s="10">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="U225" s="10">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="V225" s="10"/>
       <c r="W225" s="10">
@@ -17076,27 +17062,27 @@
         <v>262</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" s="10" t="s">
-        <v>1078</v>
+        <v>678</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>1079</v>
+        <v>233</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>1080</v>
+        <v>234</v>
       </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
       <c r="I226" s="2"/>
       <c r="J226" s="2" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="K226" s="2"/>
       <c r="L226" s="4" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="M226" s="2"/>
       <c r="N226" s="2"/>
@@ -17110,10 +17096,10 @@
         <v>117</v>
       </c>
       <c r="T226" s="10">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="U226" s="10">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="V226" s="10"/>
       <c r="W226" s="10">
@@ -17125,27 +17111,27 @@
         <v>262</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" s="10" t="s">
-        <v>678</v>
+        <v>732</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>233</v>
+        <v>112</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>234</v>
+        <v>113</v>
       </c>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
       <c r="I227" s="2"/>
       <c r="J227" s="2" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="K227" s="2"/>
       <c r="L227" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="M227" s="2"/>
       <c r="N227" s="2"/>
@@ -17159,10 +17145,10 @@
         <v>117</v>
       </c>
       <c r="T227" s="10">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="U227" s="10">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="V227" s="10"/>
       <c r="W227" s="10">
@@ -17174,17 +17160,17 @@
         <v>262</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" s="10" t="s">
-        <v>732</v>
+        <v>1057</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>112</v>
+        <v>1083</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>113</v>
+        <v>1084</v>
       </c>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
@@ -17208,10 +17194,10 @@
         <v>117</v>
       </c>
       <c r="T228" s="10">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="U228" s="10">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="V228" s="10"/>
       <c r="W228" s="10">
@@ -17223,27 +17209,27 @@
         <v>262</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" s="10" t="s">
-        <v>1061</v>
+        <v>1087</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>1087</v>
+        <v>304</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>1088</v>
+        <v>305</v>
       </c>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
       <c r="J229" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="K229" s="2"/>
       <c r="L229" s="4" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="M229" s="2"/>
       <c r="N229" s="2"/>
@@ -17257,10 +17243,10 @@
         <v>117</v>
       </c>
       <c r="T229" s="10">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="U229" s="10">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="V229" s="10"/>
       <c r="W229" s="10">
@@ -17272,27 +17258,27 @@
         <v>262</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="10" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>304</v>
+        <v>75</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>305</v>
+        <v>76</v>
       </c>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
       <c r="J230" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="K230" s="2"/>
       <c r="L230" s="4" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="M230" s="2"/>
       <c r="N230" s="2"/>
@@ -17306,10 +17292,10 @@
         <v>117</v>
       </c>
       <c r="T230" s="10">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="U230" s="10">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="V230" s="10"/>
       <c r="W230" s="10">
@@ -17318,30 +17304,32 @@
     </row>
     <row r="231" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>262</v>
+        <v>1093</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>1051</v>
+        <v>1094</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" s="10" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
       <c r="J231" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="K231" s="2"/>
-      <c r="L231" s="4" t="s">
         <v>1096</v>
+      </c>
+      <c r="K231" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="L231" s="3" t="s">
+        <v>1098</v>
       </c>
       <c r="M231" s="2"/>
       <c r="N231" s="2"/>
@@ -17352,47 +17340,47 @@
         <v>31</v>
       </c>
       <c r="S231" s="2" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="T231" s="10">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="U231" s="10">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="V231" s="10"/>
       <c r="W231" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" s="10" t="s">
         <v>1099</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>70</v>
+        <v>1100</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>71</v>
+        <v>1101</v>
       </c>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
       <c r="J232" s="2" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="K232" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="L232" s="3" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="M232" s="2"/>
       <c r="N232" s="2"/>
@@ -17403,13 +17391,13 @@
         <v>31</v>
       </c>
       <c r="S232" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="T232" s="10">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="U232" s="10">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="V232" s="10"/>
       <c r="W232" s="10">
@@ -17418,32 +17406,32 @@
     </row>
     <row r="233" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
       <c r="J233" s="2" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="K233" s="2" t="s">
-        <v>1107</v>
-      </c>
-      <c r="L233" s="3" t="s">
-        <v>1108</v>
+        <v>1109</v>
+      </c>
+      <c r="L233" s="4" t="s">
+        <v>1110</v>
       </c>
       <c r="M233" s="2"/>
       <c r="N233" s="2"/>
@@ -17451,16 +17439,16 @@
       <c r="P233" s="2"/>
       <c r="Q233" s="2"/>
       <c r="R233" s="2" t="s">
-        <v>31</v>
+        <v>315</v>
       </c>
       <c r="S233" s="2" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="T233" s="10">
-        <v>66</v>
+        <v>287</v>
       </c>
       <c r="U233" s="10">
-        <v>50</v>
+        <v>267</v>
       </c>
       <c r="V233" s="10"/>
       <c r="W233" s="10">
@@ -17469,32 +17457,32 @@
     </row>
     <row r="234" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" s="10" t="s">
-        <v>1109</v>
+        <v>701</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
       <c r="J234" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="K234" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="L234" s="4" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="M234" s="2"/>
       <c r="N234" s="2"/>
@@ -17505,13 +17493,13 @@
         <v>315</v>
       </c>
       <c r="S234" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="T234" s="10">
-        <v>287</v>
+        <v>175</v>
       </c>
       <c r="U234" s="10">
-        <v>267</v>
+        <v>162</v>
       </c>
       <c r="V234" s="10"/>
       <c r="W234" s="10">
@@ -17520,32 +17508,32 @@
     </row>
     <row r="235" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C235" s="2"/>
-      <c r="D235" s="10" t="s">
-        <v>701</v>
+      <c r="D235" s="10">
+        <v>1515</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>1115</v>
+        <v>212</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>1116</v>
+        <v>213</v>
       </c>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
       <c r="J235" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K235" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="K235" s="2" t="s">
+      <c r="L235" s="4" t="s">
         <v>1118</v>
-      </c>
-      <c r="L235" s="4" t="s">
-        <v>1119</v>
       </c>
       <c r="M235" s="2"/>
       <c r="N235" s="2"/>
@@ -17553,16 +17541,16 @@
       <c r="P235" s="2"/>
       <c r="Q235" s="2"/>
       <c r="R235" s="2" t="s">
-        <v>315</v>
+        <v>31</v>
       </c>
       <c r="S235" s="2" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="T235" s="10">
-        <v>175</v>
+        <v>96</v>
       </c>
       <c r="U235" s="10">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="V235" s="10"/>
       <c r="W235" s="10">
@@ -17571,20 +17559,20 @@
     </row>
     <row r="236" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C236" s="2"/>
-      <c r="D236" s="10">
-        <v>1515</v>
+      <c r="D236" s="10" t="s">
+        <v>863</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>212</v>
+        <v>294</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>213</v>
+        <v>1119</v>
       </c>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
@@ -17610,10 +17598,10 @@
         <v>32</v>
       </c>
       <c r="T236" s="10">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="U236" s="10">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="V236" s="10"/>
       <c r="W236" s="10">
@@ -17622,32 +17610,32 @@
     </row>
     <row r="237" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" s="10" t="s">
-        <v>863</v>
+        <v>270</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>294</v>
+        <v>1123</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
       <c r="J237" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="K237" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="L237" s="4" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="M237" s="2"/>
       <c r="N237" s="2"/>
@@ -17661,10 +17649,10 @@
         <v>32</v>
       </c>
       <c r="T237" s="10">
-        <v>98</v>
+        <v>384</v>
       </c>
       <c r="U237" s="10">
-        <v>116</v>
+        <v>264</v>
       </c>
       <c r="V237" s="10"/>
       <c r="W237" s="10">
@@ -17673,32 +17661,32 @@
     </row>
     <row r="238" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" s="10" t="s">
-        <v>270</v>
+        <v>1128</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
       <c r="J238" s="2" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="K238" s="2" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="L238" s="4" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="M238" s="2"/>
       <c r="N238" s="2"/>
@@ -17706,16 +17694,16 @@
       <c r="P238" s="2"/>
       <c r="Q238" s="2"/>
       <c r="R238" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="S238" s="2" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="T238" s="10">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="U238" s="10">
-        <v>264</v>
+        <v>1000</v>
       </c>
       <c r="V238" s="10"/>
       <c r="W238" s="10">
@@ -17724,32 +17712,32 @@
     </row>
     <row r="239" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>1097</v>
+        <v>1134</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>1098</v>
+        <v>1135</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="10" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>1133</v>
+        <v>96</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>1134</v>
+        <v>97</v>
       </c>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
       <c r="I239" s="2"/>
       <c r="J239" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="K239" s="2" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="M239" s="2"/>
       <c r="N239" s="2"/>
@@ -17757,50 +17745,50 @@
       <c r="P239" s="2"/>
       <c r="Q239" s="2"/>
       <c r="R239" s="2" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="S239" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="T239" s="10">
-        <v>400</v>
-      </c>
-      <c r="U239" s="10">
-        <v>1000</v>
+        <v>117</v>
+      </c>
+      <c r="T239" s="10" t="s">
+        <v>1140</v>
+      </c>
+      <c r="U239" s="10" t="s">
+        <v>1141</v>
       </c>
       <c r="V239" s="10"/>
-      <c r="W239" s="10">
-        <v>2</v>
+      <c r="W239" s="10" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="240" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" s="10" t="s">
-        <v>1140</v>
+        <v>406</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>96</v>
+        <v>1142</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>97</v>
+        <v>1143</v>
       </c>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
       <c r="I240" s="2"/>
       <c r="J240" s="2" t="s">
-        <v>1141</v>
+        <v>888</v>
       </c>
       <c r="K240" s="2" t="s">
-        <v>1142</v>
+        <v>889</v>
       </c>
       <c r="L240" s="4" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="M240" s="2"/>
       <c r="N240" s="2"/>
@@ -17808,17 +17796,13 @@
       <c r="P240" s="2"/>
       <c r="Q240" s="2"/>
       <c r="R240" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="S240" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T240" s="10" t="s">
-        <v>1144</v>
-      </c>
-      <c r="U240" s="10" t="s">
-        <v>1145</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="T240" s="10"/>
+      <c r="U240" s="10"/>
       <c r="V240" s="10"/>
       <c r="W240" s="10" t="s">
         <v>616</v>
@@ -17826,14 +17810,14 @@
     </row>
     <row r="241" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" s="10" t="s">
-        <v>406</v>
+        <v>1145</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>1146</v>
@@ -17845,13 +17829,13 @@
       <c r="H241" s="2"/>
       <c r="I241" s="2"/>
       <c r="J241" s="2" t="s">
-        <v>888</v>
+        <v>1148</v>
       </c>
       <c r="K241" s="2" t="s">
-        <v>889</v>
+        <v>1149</v>
       </c>
       <c r="L241" s="4" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="M241" s="2"/>
       <c r="N241" s="2"/>
@@ -17873,32 +17857,32 @@
     </row>
     <row r="242" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="10" t="s">
-        <v>1149</v>
+        <v>792</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>1150</v>
+        <v>233</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>1151</v>
+        <v>234</v>
       </c>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
       <c r="I242" s="2"/>
       <c r="J242" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K242" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="K242" s="2" t="s">
+      <c r="L242" s="4" t="s">
         <v>1153</v>
-      </c>
-      <c r="L242" s="4" t="s">
-        <v>1154</v>
       </c>
       <c r="M242" s="2"/>
       <c r="N242" s="2"/>
@@ -17906,13 +17890,17 @@
       <c r="P242" s="2"/>
       <c r="Q242" s="2"/>
       <c r="R242" s="2" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="S242" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="T242" s="10"/>
-      <c r="U242" s="10"/>
+        <v>117</v>
+      </c>
+      <c r="T242" s="10" t="s">
+        <v>1154</v>
+      </c>
+      <c r="U242" s="10" t="s">
+        <v>1155</v>
+      </c>
       <c r="V242" s="10"/>
       <c r="W242" s="10" t="s">
         <v>616</v>
@@ -17920,32 +17908,32 @@
     </row>
     <row r="243" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>1138</v>
+        <v>1156</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>1139</v>
+        <v>1157</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="10" t="s">
-        <v>792</v>
+        <v>1158</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
       <c r="J243" s="2" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="K243" s="2" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="L243" s="4" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="M243" s="2"/>
       <c r="N243" s="2"/>
@@ -17956,47 +17944,47 @@
         <v>31</v>
       </c>
       <c r="S243" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T243" s="10" t="s">
-        <v>1158</v>
-      </c>
-      <c r="U243" s="10" t="s">
-        <v>1159</v>
+        <v>1162</v>
+      </c>
+      <c r="T243" s="10">
+        <v>24</v>
+      </c>
+      <c r="U243" s="10">
+        <v>24</v>
       </c>
       <c r="V243" s="10"/>
-      <c r="W243" s="10" t="s">
-        <v>616</v>
+      <c r="W243" s="10">
+        <v>2</v>
       </c>
     </row>
     <row r="244" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" s="10" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>212</v>
+        <v>1164</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>213</v>
+        <v>1165</v>
       </c>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
       <c r="I244" s="2"/>
       <c r="J244" s="2" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="K244" s="2" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="L244" s="4" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="M244" s="2"/>
       <c r="N244" s="2"/>
@@ -18007,13 +17995,13 @@
         <v>31</v>
       </c>
       <c r="S244" s="2" t="s">
-        <v>1166</v>
+        <v>32</v>
       </c>
       <c r="T244" s="10">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="U244" s="10">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="V244" s="10"/>
       <c r="W244" s="10">
@@ -18022,26 +18010,26 @@
     </row>
     <row r="245" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" s="10" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>1168</v>
+        <v>142</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>1169</v>
+        <v>143</v>
       </c>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
       <c r="I245" s="2"/>
       <c r="J245" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="K245" s="2" t="s">
         <v>1170</v>
@@ -18058,13 +18046,13 @@
         <v>31</v>
       </c>
       <c r="S245" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="T245" s="10">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="U245" s="10">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="V245" s="10"/>
       <c r="W245" s="10">
@@ -18073,49 +18061,48 @@
     </row>
     <row r="246" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="10" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E246" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="E246" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="F246" s="2" t="s">
-        <v>143</v>
+        <v>1173</v>
       </c>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
       <c r="J246" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="K246" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="L246" s="4" t="s">
-        <v>1175</v>
-      </c>
-      <c r="M246" s="2"/>
+        <v>1176</v>
+      </c>
       <c r="N246" s="2"/>
       <c r="O246" s="2"/>
       <c r="P246" s="2"/>
       <c r="Q246" s="2"/>
       <c r="R246" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="S246" s="2" t="s">
-        <v>117</v>
+        <v>1177</v>
       </c>
       <c r="T246" s="10">
-        <v>216</v>
+        <v>435</v>
       </c>
       <c r="U246" s="10">
-        <v>132</v>
+        <v>350</v>
       </c>
       <c r="V246" s="10"/>
       <c r="W246" s="10">
@@ -18124,20 +18111,20 @@
     </row>
     <row r="247" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="10" t="s">
-        <v>1132</v>
+        <v>863</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>1176</v>
+        <v>75</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>1177</v>
+        <v>76</v>
       </c>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
@@ -18151,21 +18138,22 @@
       <c r="L247" s="4" t="s">
         <v>1180</v>
       </c>
+      <c r="M247" s="2"/>
       <c r="N247" s="2"/>
       <c r="O247" s="2"/>
       <c r="P247" s="2"/>
       <c r="Q247" s="2"/>
       <c r="R247" s="2" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="S247" s="2" t="s">
-        <v>1181</v>
+        <v>117</v>
       </c>
       <c r="T247" s="10">
-        <v>435</v>
+        <v>343</v>
       </c>
       <c r="U247" s="10">
-        <v>350</v>
+        <v>149</v>
       </c>
       <c r="V247" s="10"/>
       <c r="W247" s="10">
@@ -18174,32 +18162,32 @@
     </row>
     <row r="248" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" s="10" t="s">
-        <v>863</v>
+        <v>1053</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
       <c r="I248" s="2"/>
       <c r="J248" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="K248" s="2" t="s">
         <v>1182</v>
       </c>
-      <c r="K248" s="2" t="s">
+      <c r="L248" s="4" t="s">
         <v>1183</v>
-      </c>
-      <c r="L248" s="4" t="s">
-        <v>1184</v>
       </c>
       <c r="M248" s="2"/>
       <c r="N248" s="2"/>
@@ -18213,10 +18201,10 @@
         <v>117</v>
       </c>
       <c r="T248" s="10">
-        <v>343</v>
+        <v>108</v>
       </c>
       <c r="U248" s="10">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="V248" s="10"/>
       <c r="W248" s="10">
@@ -18225,32 +18213,32 @@
     </row>
     <row r="249" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" s="10" t="s">
-        <v>1057</v>
+        <v>1184</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>26</v>
+        <v>728</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>27</v>
+        <v>1185</v>
       </c>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
       <c r="I249" s="2"/>
       <c r="J249" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="K249" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="M249" s="2"/>
       <c r="N249" s="2"/>
@@ -18258,16 +18246,16 @@
       <c r="P249" s="2"/>
       <c r="Q249" s="2"/>
       <c r="R249" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="S249" s="2" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="T249" s="10">
-        <v>108</v>
+        <v>600</v>
       </c>
       <c r="U249" s="10">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="V249" s="10"/>
       <c r="W249" s="10">
@@ -18276,20 +18264,20 @@
     </row>
     <row r="250" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" s="10" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>728</v>
+        <v>26</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>1189</v>
+        <v>27</v>
       </c>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
@@ -18309,16 +18297,16 @@
       <c r="P250" s="2"/>
       <c r="Q250" s="2"/>
       <c r="R250" s="2" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="S250" s="2" t="s">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="T250" s="10">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="U250" s="10">
-        <v>800</v>
+        <v>89</v>
       </c>
       <c r="V250" s="10"/>
       <c r="W250" s="10">
@@ -18327,32 +18315,32 @@
     </row>
     <row r="251" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>1160</v>
+        <v>572</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>1161</v>
+        <v>1193</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" s="10" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>27</v>
+        <v>1195</v>
       </c>
       <c r="G251" s="2"/>
-      <c r="H251" s="2"/>
+      <c r="H251" s="3"/>
       <c r="I251" s="2"/>
       <c r="J251" s="2" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="K251" s="2" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="L251" s="4" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="M251" s="2"/>
       <c r="N251" s="2"/>
@@ -18363,17 +18351,17 @@
         <v>31</v>
       </c>
       <c r="S251" s="2" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="T251" s="10">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="U251" s="10">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="V251" s="10"/>
       <c r="W251" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18381,29 +18369,29 @@
         <v>572</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" s="10" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>96</v>
+        <v>1199</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="G252" s="2"/>
       <c r="H252" s="3"/>
       <c r="I252" s="2"/>
       <c r="J252" s="2" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="K252" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="L252" s="4" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="M252" s="2"/>
       <c r="N252" s="2"/>
@@ -18417,7 +18405,7 @@
         <v>32</v>
       </c>
       <c r="T252" s="10">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="U252" s="10">
         <v>131</v>
@@ -18432,29 +18420,29 @@
         <v>572</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" s="10" t="s">
-        <v>1198</v>
+        <v>340</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>1203</v>
+        <v>142</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>1204</v>
+        <v>143</v>
       </c>
       <c r="G253" s="2"/>
       <c r="H253" s="3"/>
       <c r="I253" s="2"/>
       <c r="J253" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="K253" s="2" t="s">
         <v>1205</v>
       </c>
-      <c r="K253" s="2" t="s">
+      <c r="L253" s="4" t="s">
         <v>1206</v>
-      </c>
-      <c r="L253" s="4" t="s">
-        <v>1207</v>
       </c>
       <c r="M253" s="2"/>
       <c r="N253" s="2"/>
@@ -18468,10 +18456,10 @@
         <v>32</v>
       </c>
       <c r="T253" s="10">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="U253" s="10">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="V253" s="10"/>
       <c r="W253" s="10">
@@ -18483,29 +18471,29 @@
         <v>572</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" s="10" t="s">
-        <v>340</v>
+        <v>1207</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>143</v>
+        <v>1208</v>
       </c>
       <c r="G254" s="2"/>
       <c r="H254" s="3"/>
       <c r="I254" s="2"/>
       <c r="J254" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="K254" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="L254" s="4" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="M254" s="2"/>
       <c r="N254" s="2"/>
@@ -18519,10 +18507,10 @@
         <v>32</v>
       </c>
       <c r="T254" s="10">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="U254" s="10">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="V254" s="10"/>
       <c r="W254" s="10">
@@ -18531,32 +18519,32 @@
     </row>
     <row r="255" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>572</v>
+        <v>1212</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>1197</v>
+        <v>1213</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" s="10" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>1212</v>
+        <v>234</v>
       </c>
       <c r="G255" s="2"/>
-      <c r="H255" s="3"/>
+      <c r="H255" s="2"/>
       <c r="I255" s="2"/>
       <c r="J255" s="2" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="K255" s="2" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="L255" s="4" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="M255" s="2"/>
       <c r="N255" s="2"/>
@@ -18567,47 +18555,47 @@
         <v>31</v>
       </c>
       <c r="S255" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T255" s="10">
-        <v>145</v>
-      </c>
-      <c r="U255" s="10">
-        <v>195</v>
+        <v>117</v>
+      </c>
+      <c r="T255" s="10" t="s">
+        <v>1218</v>
+      </c>
+      <c r="U255" s="10" t="s">
+        <v>1219</v>
       </c>
       <c r="V255" s="10"/>
       <c r="W255" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" s="10" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>233</v>
+        <v>75</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>234</v>
+        <v>76</v>
       </c>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
       <c r="I256" s="2"/>
       <c r="J256" s="2" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="K256" s="2" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="L256" s="4" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="M256" s="2"/>
       <c r="N256" s="2"/>
@@ -18621,10 +18609,10 @@
         <v>117</v>
       </c>
       <c r="T256" s="10" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="U256" s="10" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="V256" s="10"/>
       <c r="W256" s="10">
@@ -18633,32 +18621,32 @@
     </row>
     <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" s="10" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>75</v>
+        <v>550</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>76</v>
+        <v>551</v>
       </c>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
       <c r="I257" s="2"/>
       <c r="J257" s="2" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="K257" s="2" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="L257" s="4" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="M257" s="2"/>
       <c r="N257" s="2"/>
@@ -18666,16 +18654,16 @@
       <c r="P257" s="2"/>
       <c r="Q257" s="2"/>
       <c r="R257" s="2" t="s">
-        <v>31</v>
+        <v>315</v>
       </c>
       <c r="S257" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="T257" s="10" t="s">
-        <v>1228</v>
+      <c r="T257" s="10">
+        <v>224</v>
       </c>
       <c r="U257" s="10" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="V257" s="10"/>
       <c r="W257" s="10">
@@ -18684,32 +18672,32 @@
     </row>
     <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" s="10" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>550</v>
+        <v>1232</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>551</v>
+        <v>1233</v>
       </c>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
       <c r="I258" s="2"/>
       <c r="J258" s="2" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="K258" s="2" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="L258" s="4" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="M258" s="2"/>
       <c r="N258" s="2"/>
@@ -18722,11 +18710,11 @@
       <c r="S258" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="T258" s="10">
-        <v>224</v>
+      <c r="T258" s="10" t="s">
+        <v>1237</v>
       </c>
       <c r="U258" s="10" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="V258" s="10"/>
       <c r="W258" s="10">
@@ -18735,26 +18723,26 @@
     </row>
     <row r="259" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" s="10" t="s">
-        <v>1235</v>
+        <v>284</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>1236</v>
+        <v>75</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>1237</v>
+        <v>76</v>
       </c>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
       <c r="I259" s="2"/>
       <c r="J259" s="2" t="s">
-        <v>1238</v>
+        <v>1054</v>
       </c>
       <c r="K259" s="2" t="s">
         <v>1239</v>
@@ -18768,7 +18756,7 @@
       <c r="P259" s="2"/>
       <c r="Q259" s="2"/>
       <c r="R259" s="2" t="s">
-        <v>315</v>
+        <v>31</v>
       </c>
       <c r="S259" s="2" t="s">
         <v>117</v>
@@ -18786,32 +18774,32 @@
     </row>
     <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" s="10" t="s">
         <v>284</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>75</v>
+        <v>1243</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>76</v>
+        <v>1244</v>
       </c>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
       <c r="I260" s="2"/>
       <c r="J260" s="2" t="s">
-        <v>1058</v>
+        <v>1245</v>
       </c>
       <c r="K260" s="2" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="L260" s="4" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="M260" s="2"/>
       <c r="N260" s="2"/>
@@ -18825,10 +18813,10 @@
         <v>117</v>
       </c>
       <c r="T260" s="10" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="U260" s="10" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="V260" s="10"/>
       <c r="W260" s="10">
@@ -18837,20 +18825,20 @@
     </row>
     <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="10" t="s">
-        <v>284</v>
+        <v>1248</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>1247</v>
+        <v>70</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>1248</v>
+        <v>71</v>
       </c>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
@@ -18876,10 +18864,10 @@
         <v>117</v>
       </c>
       <c r="T261" s="10" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="U261" s="10" t="s">
-        <v>1246</v>
+        <v>1140</v>
       </c>
       <c r="V261" s="10"/>
       <c r="W261" s="10">
@@ -18888,32 +18876,32 @@
     </row>
     <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="10" t="s">
-        <v>1252</v>
+        <v>672</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
       <c r="I262" s="2"/>
       <c r="J262" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="K262" s="2" t="s">
         <v>1253</v>
       </c>
-      <c r="K262" s="2" t="s">
+      <c r="L262" s="4" t="s">
         <v>1254</v>
-      </c>
-      <c r="L262" s="4" t="s">
-        <v>1255</v>
       </c>
       <c r="M262" s="2"/>
       <c r="N262" s="2"/>
@@ -18927,10 +18915,10 @@
         <v>117</v>
       </c>
       <c r="T262" s="10" t="s">
+        <v>1255</v>
+      </c>
+      <c r="U262" s="10" t="s">
         <v>1256</v>
-      </c>
-      <c r="U262" s="10" t="s">
-        <v>1144</v>
       </c>
       <c r="V262" s="10"/>
       <c r="W262" s="10">
@@ -18939,32 +18927,32 @@
     </row>
     <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>1216</v>
+        <v>875</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>1217</v>
+        <v>1257</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="10" t="s">
-        <v>672</v>
+        <v>1258</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
       <c r="I263" s="2"/>
       <c r="J263" s="2" t="s">
-        <v>383</v>
+        <v>1259</v>
       </c>
       <c r="K263" s="2" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="L263" s="4" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="M263" s="2"/>
       <c r="N263" s="2"/>
@@ -18975,17 +18963,17 @@
         <v>31</v>
       </c>
       <c r="S263" s="2" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="T263" s="10" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="U263" s="10" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="V263" s="10"/>
       <c r="W263" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18993,29 +18981,29 @@
         <v>875</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="10" t="s">
-        <v>1262</v>
+        <v>545</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>75</v>
+        <v>1106</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>76</v>
+        <v>1264</v>
       </c>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
       <c r="I264" s="2"/>
       <c r="J264" s="2" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="K264" s="2" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="L264" s="4" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="M264" s="2"/>
       <c r="N264" s="2"/>
@@ -19029,10 +19017,10 @@
         <v>32</v>
       </c>
       <c r="T264" s="10" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="U264" s="10" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="V264" s="10"/>
       <c r="W264" s="10">
@@ -19044,29 +19032,29 @@
         <v>875</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" s="10" t="s">
-        <v>545</v>
+        <v>111</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>1110</v>
+        <v>365</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
       <c r="I265" s="2"/>
       <c r="J265" s="2" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="K265" s="2" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="L265" s="4" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="M265" s="2"/>
       <c r="N265" s="2"/>
@@ -19080,10 +19068,10 @@
         <v>32</v>
       </c>
       <c r="T265" s="10" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="U265" s="10" t="s">
-        <v>1273</v>
+        <v>1154</v>
       </c>
       <c r="V265" s="10"/>
       <c r="W265" s="10">
@@ -19095,29 +19083,29 @@
         <v>875</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="10" t="s">
-        <v>111</v>
+        <v>1275</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>365</v>
+        <v>1106</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>1274</v>
+        <v>1683</v>
       </c>
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
       <c r="I266" s="2"/>
       <c r="J266" s="2" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="K266" s="2" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="L266" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="M266" s="2"/>
       <c r="N266" s="2"/>
@@ -19131,10 +19119,10 @@
         <v>32</v>
       </c>
       <c r="T266" s="10" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="U266" s="10" t="s">
-        <v>1158</v>
+        <v>1269</v>
       </c>
       <c r="V266" s="10"/>
       <c r="W266" s="10">
@@ -19143,32 +19131,32 @@
     </row>
     <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>875</v>
+        <v>378</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>1261</v>
+        <v>1280</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="10" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>1110</v>
+        <v>294</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>1689</v>
+        <v>1282</v>
       </c>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
       <c r="I267" s="2"/>
       <c r="J267" s="2" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="K267" s="2" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="L267" s="4" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="M267" s="2"/>
       <c r="N267" s="2"/>
@@ -19176,16 +19164,16 @@
       <c r="P267" s="2"/>
       <c r="Q267" s="2"/>
       <c r="R267" s="2" t="s">
-        <v>31</v>
+        <v>1286</v>
       </c>
       <c r="S267" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="T267" s="10" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="U267" s="10" t="s">
-        <v>1273</v>
+        <v>1288</v>
       </c>
       <c r="V267" s="10"/>
       <c r="W267" s="10">
@@ -19197,29 +19185,29 @@
         <v>378</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="10" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>1286</v>
+        <v>305</v>
       </c>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
       <c r="I268" s="2"/>
       <c r="J268" s="2" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="K268" s="2" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="L268" s="4" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="M268" s="2"/>
       <c r="N268" s="2"/>
@@ -19227,16 +19215,16 @@
       <c r="P268" s="2"/>
       <c r="Q268" s="2"/>
       <c r="R268" s="2" t="s">
-        <v>1290</v>
+        <v>31</v>
       </c>
       <c r="S268" s="2" t="s">
         <v>117</v>
       </c>
       <c r="T268" s="10" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="U268" s="10" t="s">
-        <v>1292</v>
+        <v>1269</v>
       </c>
       <c r="V268" s="10"/>
       <c r="W268" s="10">
@@ -19248,29 +19236,29 @@
         <v>378</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="10" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>305</v>
+        <v>1119</v>
       </c>
       <c r="G269" s="2"/>
       <c r="H269" s="2"/>
       <c r="I269" s="2"/>
       <c r="J269" s="2" t="s">
-        <v>1294</v>
+        <v>605</v>
       </c>
       <c r="K269" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="L269" s="4" t="s">
         <v>1295</v>
-      </c>
-      <c r="L269" s="4" t="s">
-        <v>1296</v>
       </c>
       <c r="M269" s="2"/>
       <c r="N269" s="2"/>
@@ -19284,10 +19272,10 @@
         <v>117</v>
       </c>
       <c r="T269" s="10" t="s">
-        <v>1297</v>
+        <v>873</v>
       </c>
       <c r="U269" s="10" t="s">
-        <v>1273</v>
+        <v>852</v>
       </c>
       <c r="V269" s="10"/>
       <c r="W269" s="10">
@@ -19299,29 +19287,29 @@
         <v>378</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="10" t="s">
-        <v>1298</v>
+        <v>1289</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>294</v>
+        <v>1296</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>1123</v>
+        <v>1297</v>
       </c>
       <c r="G270" s="2"/>
       <c r="H270" s="2"/>
       <c r="I270" s="2"/>
       <c r="J270" s="2" t="s">
-        <v>605</v>
+        <v>1298</v>
       </c>
       <c r="K270" s="2" t="s">
-        <v>606</v>
+        <v>1299</v>
       </c>
       <c r="L270" s="4" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="M270" s="2"/>
       <c r="N270" s="2"/>
@@ -19332,13 +19320,13 @@
         <v>31</v>
       </c>
       <c r="S270" s="2" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="T270" s="10" t="s">
-        <v>873</v>
+        <v>1301</v>
       </c>
       <c r="U270" s="10" t="s">
-        <v>852</v>
+        <v>1302</v>
       </c>
       <c r="V270" s="10"/>
       <c r="W270" s="10">
@@ -19347,32 +19335,32 @@
     </row>
     <row r="271" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>378</v>
+        <v>464</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>1284</v>
+        <v>1303</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="10" t="s">
-        <v>1293</v>
+        <v>1304</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>1300</v>
+        <v>26</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>1301</v>
+        <v>27</v>
       </c>
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
       <c r="I271" s="2"/>
       <c r="J271" s="2" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="K271" s="2" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="L271" s="4" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="M271" s="2"/>
       <c r="N271" s="2"/>
@@ -19383,17 +19371,17 @@
         <v>31</v>
       </c>
       <c r="S271" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="T271" s="10" t="s">
-        <v>1305</v>
+        <v>1224</v>
       </c>
       <c r="U271" s="10" t="s">
-        <v>1306</v>
+        <v>1255</v>
       </c>
       <c r="V271" s="10"/>
       <c r="W271" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19401,17 +19389,17 @@
         <v>464</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="10" t="s">
+        <v>959</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F272" s="2" t="s">
         <v>1308</v>
-      </c>
-      <c r="E272" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F272" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
@@ -19437,10 +19425,10 @@
         <v>117</v>
       </c>
       <c r="T272" s="10" t="s">
-        <v>1228</v>
+        <v>1312</v>
       </c>
       <c r="U272" s="10" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="V272" s="10"/>
       <c r="W272" s="10">
@@ -19452,23 +19440,23 @@
         <v>464</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="10" t="s">
-        <v>963</v>
+        <v>1313</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>212</v>
+        <v>26</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>1312</v>
+        <v>27</v>
       </c>
       <c r="G273" s="2"/>
       <c r="H273" s="2"/>
       <c r="I273" s="2"/>
       <c r="J273" s="2" t="s">
-        <v>1313</v>
+        <v>187</v>
       </c>
       <c r="K273" s="2" t="s">
         <v>1314</v>
@@ -19491,7 +19479,7 @@
         <v>1316</v>
       </c>
       <c r="U273" s="10" t="s">
-        <v>1267</v>
+        <v>1317</v>
       </c>
       <c r="V273" s="10"/>
       <c r="W273" s="10">
@@ -19503,29 +19491,29 @@
         <v>464</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="10" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
       <c r="I274" s="2"/>
       <c r="J274" s="2" t="s">
-        <v>187</v>
+        <v>702</v>
       </c>
       <c r="K274" s="2" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="L274" s="4" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="M274" s="2"/>
       <c r="N274" s="2"/>
@@ -19539,115 +19527,115 @@
         <v>117</v>
       </c>
       <c r="T274" s="10" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="U274" s="10" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="V274" s="10"/>
       <c r="W274" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A275" s="2" t="s">
+    <row r="275" spans="1:23" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A275" s="14" t="s">
         <v>464</v>
       </c>
-      <c r="B275" s="2" t="s">
-        <v>1307</v>
-      </c>
-      <c r="C275" s="2"/>
-      <c r="D275" s="10" t="s">
-        <v>1322</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G275" s="2"/>
-      <c r="H275" s="2"/>
-      <c r="I275" s="2"/>
-      <c r="J275" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="K275" s="2" t="s">
+      <c r="B275" s="14" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C275" s="14"/>
+      <c r="D275" s="15" t="s">
         <v>1323</v>
       </c>
-      <c r="L275" s="4" t="s">
+      <c r="E275" s="14" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F275" s="14" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G275" s="14"/>
+      <c r="H275" s="14"/>
+      <c r="I275" s="14"/>
+      <c r="J275" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="K275" s="14" t="s">
         <v>1324</v>
       </c>
-      <c r="M275" s="2"/>
-      <c r="N275" s="2"/>
-      <c r="O275" s="2"/>
-      <c r="P275" s="2"/>
-      <c r="Q275" s="2"/>
-      <c r="R275" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S275" s="2" t="s">
+      <c r="L275" s="16" t="s">
+        <v>1325</v>
+      </c>
+      <c r="M275" s="14"/>
+      <c r="N275" s="14"/>
+      <c r="O275" s="14"/>
+      <c r="P275" s="14"/>
+      <c r="Q275" s="14"/>
+      <c r="R275" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="S275" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="T275" s="10" t="s">
-        <v>1325</v>
-      </c>
-      <c r="U275" s="10" t="s">
+      <c r="T275" s="15">
+        <v>17</v>
+      </c>
+      <c r="U275" s="15">
+        <v>21</v>
+      </c>
+      <c r="V275" s="15"/>
+      <c r="W275" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C276" s="2"/>
+      <c r="D276" s="10" t="s">
         <v>1326</v>
       </c>
-      <c r="V275" s="10"/>
-      <c r="W275" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="276" spans="1:23" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A276" s="14" t="s">
-        <v>464</v>
-      </c>
-      <c r="B276" s="14" t="s">
-        <v>1307</v>
-      </c>
-      <c r="C276" s="14"/>
-      <c r="D276" s="15" t="s">
+      <c r="E276" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F276" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="G276" s="2"/>
+      <c r="H276" s="2"/>
+      <c r="I276" s="2"/>
+      <c r="J276" s="2" t="s">
         <v>1327</v>
       </c>
-      <c r="E276" s="14" t="s">
-        <v>1236</v>
-      </c>
-      <c r="F276" s="14" t="s">
-        <v>1237</v>
-      </c>
-      <c r="G276" s="14"/>
-      <c r="H276" s="14"/>
-      <c r="I276" s="14"/>
-      <c r="J276" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="K276" s="14" t="s">
+      <c r="K276" s="2" t="s">
         <v>1328</v>
       </c>
-      <c r="L276" s="16" t="s">
+      <c r="L276" s="4" t="s">
         <v>1329</v>
       </c>
-      <c r="M276" s="14"/>
-      <c r="N276" s="14"/>
-      <c r="O276" s="14"/>
-      <c r="P276" s="14"/>
-      <c r="Q276" s="14"/>
-      <c r="R276" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="S276" s="14" t="s">
+      <c r="M276" s="2"/>
+      <c r="N276" s="2"/>
+      <c r="O276" s="2"/>
+      <c r="P276" s="2"/>
+      <c r="Q276" s="2"/>
+      <c r="R276" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S276" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="T276" s="15">
-        <v>17</v>
-      </c>
-      <c r="U276" s="15">
-        <v>21</v>
-      </c>
-      <c r="V276" s="15"/>
-      <c r="W276" s="15">
+      <c r="T276" s="10" t="s">
+        <v>1330</v>
+      </c>
+      <c r="U276" s="10" t="s">
+        <v>1331</v>
+      </c>
+      <c r="V276" s="10"/>
+      <c r="W276" s="10">
         <v>2</v>
       </c>
     </row>
@@ -19656,23 +19644,23 @@
         <v>464</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" s="10" t="s">
-        <v>1330</v>
+        <v>1313</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>527</v>
+        <v>233</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>528</v>
+        <v>234</v>
       </c>
       <c r="G277" s="2"/>
       <c r="H277" s="2"/>
       <c r="I277" s="2"/>
       <c r="J277" s="2" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="K277" s="2" t="s">
         <v>1332</v>
@@ -19695,7 +19683,7 @@
         <v>1334</v>
       </c>
       <c r="U277" s="10" t="s">
-        <v>1335</v>
+        <v>852</v>
       </c>
       <c r="V277" s="10"/>
       <c r="W277" s="10">
@@ -19707,17 +19695,17 @@
         <v>464</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" s="10" t="s">
-        <v>1317</v>
+        <v>1335</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>233</v>
+        <v>75</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>234</v>
+        <v>76</v>
       </c>
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
@@ -19726,10 +19714,10 @@
         <v>1336</v>
       </c>
       <c r="K278" s="2" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="L278" s="4" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="M278" s="2"/>
       <c r="N278" s="2"/>
@@ -19743,10 +19731,10 @@
         <v>117</v>
       </c>
       <c r="T278" s="10" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="U278" s="10" t="s">
-        <v>852</v>
+        <v>1340</v>
       </c>
       <c r="V278" s="10"/>
       <c r="W278" s="10">
@@ -19755,32 +19743,32 @@
     </row>
     <row r="279" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>464</v>
+        <v>378</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>1307</v>
+        <v>1341</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" s="10" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>76</v>
+        <v>1343</v>
       </c>
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
       <c r="I279" s="2"/>
       <c r="J279" s="2" t="s">
-        <v>1340</v>
+        <v>329</v>
       </c>
       <c r="K279" s="2" t="s">
-        <v>1341</v>
-      </c>
-      <c r="L279" s="4" t="s">
-        <v>1342</v>
+        <v>330</v>
+      </c>
+      <c r="L279" s="8" t="s">
+        <v>1344</v>
       </c>
       <c r="M279" s="2"/>
       <c r="N279" s="2"/>
@@ -19793,11 +19781,11 @@
       <c r="S279" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="T279" s="10" t="s">
-        <v>1343</v>
-      </c>
-      <c r="U279" s="10" t="s">
-        <v>1344</v>
+      <c r="T279" s="10">
+        <v>313</v>
+      </c>
+      <c r="U279" s="10">
+        <v>192</v>
       </c>
       <c r="V279" s="10"/>
       <c r="W279" s="10">
@@ -19809,14 +19797,14 @@
         <v>378</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" s="10" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E280" s="2" t="s">
         <v>1346</v>
-      </c>
-      <c r="E280" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>1347</v>
@@ -19825,13 +19813,13 @@
       <c r="H280" s="2"/>
       <c r="I280" s="2"/>
       <c r="J280" s="2" t="s">
-        <v>329</v>
+        <v>1348</v>
       </c>
       <c r="K280" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="L280" s="8" t="s">
-        <v>1348</v>
+        <v>1349</v>
+      </c>
+      <c r="L280" s="4" t="s">
+        <v>1350</v>
       </c>
       <c r="M280" s="2"/>
       <c r="N280" s="2"/>
@@ -19845,10 +19833,10 @@
         <v>117</v>
       </c>
       <c r="T280" s="10">
-        <v>313</v>
+        <v>202</v>
       </c>
       <c r="U280" s="10">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="V280" s="10"/>
       <c r="W280" s="10">
@@ -19860,29 +19848,29 @@
         <v>378</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" s="10" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
       <c r="I281" s="2"/>
       <c r="J281" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="K281" s="2" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="L281" s="4" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="M281" s="2"/>
       <c r="N281" s="2"/>
@@ -19890,70 +19878,70 @@
       <c r="P281" s="2"/>
       <c r="Q281" s="2"/>
       <c r="R281" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="S281" s="2" t="s">
-        <v>117</v>
+        <v>1357</v>
       </c>
       <c r="T281" s="10">
-        <v>202</v>
+        <v>461</v>
       </c>
       <c r="U281" s="10">
-        <v>156</v>
+        <v>990</v>
       </c>
       <c r="V281" s="10"/>
       <c r="W281" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A282" s="2" t="s">
+    <row r="282" spans="1:23" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A282" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="B282" s="2" t="s">
-        <v>1345</v>
-      </c>
-      <c r="C282" s="2"/>
-      <c r="D282" s="10" t="s">
-        <v>1355</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>1356</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>1357</v>
-      </c>
-      <c r="G282" s="2"/>
-      <c r="H282" s="2"/>
-      <c r="I282" s="2"/>
-      <c r="J282" s="2" t="s">
+      <c r="B282" s="14" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C282" s="14"/>
+      <c r="D282" s="15" t="s">
         <v>1358</v>
       </c>
-      <c r="K282" s="2" t="s">
+      <c r="E282" s="14" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F282" s="14" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G282" s="14"/>
+      <c r="H282" s="14"/>
+      <c r="I282" s="14"/>
+      <c r="J282" s="14" t="s">
         <v>1359</v>
       </c>
-      <c r="L282" s="4" t="s">
+      <c r="K282" s="14" t="s">
         <v>1360</v>
       </c>
-      <c r="M282" s="2"/>
-      <c r="N282" s="2"/>
-      <c r="O282" s="2"/>
-      <c r="P282" s="2"/>
-      <c r="Q282" s="2"/>
-      <c r="R282" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="S282" s="2" t="s">
+      <c r="L282" s="16" t="s">
         <v>1361</v>
       </c>
-      <c r="T282" s="10">
-        <v>461</v>
-      </c>
-      <c r="U282" s="10">
-        <v>990</v>
-      </c>
-      <c r="V282" s="10"/>
-      <c r="W282" s="10">
+      <c r="M282" s="14"/>
+      <c r="N282" s="14"/>
+      <c r="O282" s="14"/>
+      <c r="P282" s="14"/>
+      <c r="Q282" s="14"/>
+      <c r="R282" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="S282" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="T282" s="15">
+        <v>100</v>
+      </c>
+      <c r="U282" s="15">
+        <v>81</v>
+      </c>
+      <c r="V282" s="15"/>
+      <c r="W282" s="15">
         <v>2</v>
       </c>
     </row>
@@ -19962,29 +19950,29 @@
         <v>378</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" s="10" t="s">
         <v>1362</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>1363</v>
+        <v>142</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>1364</v>
+        <v>143</v>
       </c>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
       <c r="I283" s="2"/>
       <c r="J283" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="K283" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L283" s="4" t="s">
         <v>1365</v>
-      </c>
-      <c r="K283" s="2" t="s">
-        <v>1366</v>
-      </c>
-      <c r="L283" s="4" t="s">
-        <v>1367</v>
       </c>
       <c r="M283" s="2"/>
       <c r="N283" s="2"/>
@@ -19998,10 +19986,10 @@
         <v>117</v>
       </c>
       <c r="T283" s="10">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="U283" s="10">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="V283" s="10"/>
       <c r="W283" s="10">
@@ -20013,29 +20001,29 @@
         <v>378</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" s="10" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>142</v>
+        <v>891</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>143</v>
+        <v>892</v>
       </c>
       <c r="G284" s="2"/>
       <c r="H284" s="2"/>
       <c r="I284" s="2"/>
       <c r="J284" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="K284" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="L284" s="4" t="s">
         <v>1369</v>
-      </c>
-      <c r="K284" s="2" t="s">
-        <v>1370</v>
-      </c>
-      <c r="L284" s="4" t="s">
-        <v>1371</v>
       </c>
       <c r="M284" s="2"/>
       <c r="N284" s="2"/>
@@ -20046,13 +20034,13 @@
         <v>31</v>
       </c>
       <c r="S284" s="2" t="s">
-        <v>117</v>
+        <v>1370</v>
       </c>
       <c r="T284" s="10">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="U284" s="10">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="V284" s="10"/>
       <c r="W284" s="10">
@@ -20064,29 +20052,29 @@
         <v>378</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" s="10" t="s">
-        <v>1372</v>
+        <v>849</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>891</v>
+        <v>142</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>892</v>
+        <v>143</v>
       </c>
       <c r="G285" s="2"/>
       <c r="H285" s="2"/>
       <c r="I285" s="2"/>
       <c r="J285" s="2" t="s">
-        <v>1373</v>
+        <v>1108</v>
       </c>
       <c r="K285" s="2" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="L285" s="4" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="M285" s="2"/>
       <c r="N285" s="2"/>
@@ -20094,16 +20082,16 @@
       <c r="P285" s="2"/>
       <c r="Q285" s="2"/>
       <c r="R285" s="2" t="s">
-        <v>31</v>
+        <v>1373</v>
       </c>
       <c r="S285" s="2" t="s">
-        <v>1376</v>
+        <v>117</v>
       </c>
       <c r="T285" s="10">
-        <v>92</v>
+        <v>214</v>
       </c>
       <c r="U285" s="10">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="V285" s="10"/>
       <c r="W285" s="10">
@@ -20115,23 +20103,23 @@
         <v>378</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" s="10" t="s">
-        <v>849</v>
+        <v>1374</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>142</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>143</v>
+        <v>1375</v>
       </c>
       <c r="G286" s="2"/>
       <c r="H286" s="2"/>
       <c r="I286" s="2"/>
       <c r="J286" s="2" t="s">
-        <v>1112</v>
+        <v>1376</v>
       </c>
       <c r="K286" s="2" t="s">
         <v>1377</v>
@@ -20145,16 +20133,16 @@
       <c r="P286" s="2"/>
       <c r="Q286" s="2"/>
       <c r="R286" s="2" t="s">
-        <v>1379</v>
+        <v>172</v>
       </c>
       <c r="S286" s="2" t="s">
-        <v>117</v>
+        <v>1177</v>
       </c>
       <c r="T286" s="10">
-        <v>214</v>
+        <v>300</v>
       </c>
       <c r="U286" s="10">
-        <v>185</v>
+        <v>290</v>
       </c>
       <c r="V286" s="10"/>
       <c r="W286" s="10">
@@ -20163,18 +20151,16 @@
     </row>
     <row r="287" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>378</v>
+        <v>1156</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>1345</v>
+        <v>1379</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" s="10" t="s">
         <v>1380</v>
       </c>
-      <c r="E287" s="2" t="s">
-        <v>142</v>
-      </c>
+      <c r="E287" s="2"/>
       <c r="F287" s="2" t="s">
         <v>1381</v>
       </c>
@@ -20199,45 +20185,41 @@
         <v>172</v>
       </c>
       <c r="S287" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="T287" s="10">
-        <v>300</v>
-      </c>
-      <c r="U287" s="10">
-        <v>290</v>
-      </c>
+        <v>1385</v>
+      </c>
+      <c r="T287" s="10"/>
+      <c r="U287" s="10"/>
       <c r="V287" s="10"/>
       <c r="W287" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" s="10" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="E288" s="2"/>
       <c r="F288" s="2" t="s">
-        <v>1387</v>
+        <v>1381</v>
       </c>
       <c r="G288" s="2"/>
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
       <c r="J288" s="2" t="s">
-        <v>1388</v>
+        <v>354</v>
       </c>
       <c r="K288" s="2" t="s">
-        <v>1389</v>
+        <v>355</v>
       </c>
       <c r="L288" s="4" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="M288" s="2"/>
       <c r="N288" s="2"/>
@@ -20248,7 +20230,7 @@
         <v>172</v>
       </c>
       <c r="S288" s="2" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="T288" s="10"/>
       <c r="U288" s="10"/>
@@ -20259,30 +20241,32 @@
     </row>
     <row r="289" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" s="10" t="s">
-        <v>1386</v>
-      </c>
-      <c r="E289" s="2"/>
+        <v>1388</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>1389</v>
+      </c>
       <c r="F289" s="2" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
       <c r="I289" s="2"/>
       <c r="J289" s="2" t="s">
-        <v>354</v>
+        <v>1391</v>
       </c>
       <c r="K289" s="2" t="s">
-        <v>355</v>
+        <v>1392</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="M289" s="2"/>
       <c r="N289" s="2"/>
@@ -20290,13 +20274,17 @@
       <c r="P289" s="2"/>
       <c r="Q289" s="2"/>
       <c r="R289" s="2" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="S289" s="2" t="s">
-        <v>1393</v>
-      </c>
-      <c r="T289" s="10"/>
-      <c r="U289" s="10"/>
+        <v>32</v>
+      </c>
+      <c r="T289" s="10" t="s">
+        <v>1394</v>
+      </c>
+      <c r="U289" s="10" t="s">
+        <v>1293</v>
+      </c>
       <c r="V289" s="10"/>
       <c r="W289" s="10">
         <v>3</v>
@@ -20304,32 +20292,32 @@
     </row>
     <row r="290" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" s="10" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>1395</v>
+        <v>717</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>1396</v>
+        <v>718</v>
       </c>
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
       <c r="I290" s="2"/>
       <c r="J290" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="K290" s="2" t="s">
         <v>1397</v>
       </c>
-      <c r="K290" s="2" t="s">
+      <c r="L290" s="4" t="s">
         <v>1398</v>
-      </c>
-      <c r="L290" s="4" t="s">
-        <v>1399</v>
       </c>
       <c r="M290" s="2"/>
       <c r="N290" s="2"/>
@@ -20342,11 +20330,11 @@
       <c r="S290" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T290" s="10" t="s">
-        <v>1400</v>
+      <c r="T290" s="10">
+        <v>43</v>
       </c>
       <c r="U290" s="10" t="s">
-        <v>1297</v>
+        <v>1399</v>
       </c>
       <c r="V290" s="10"/>
       <c r="W290" s="10">
@@ -20355,20 +20343,20 @@
     </row>
     <row r="291" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>1160</v>
+        <v>378</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>1385</v>
+        <v>1400</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" s="10" t="s">
         <v>1401</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>717</v>
+        <v>294</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>718</v>
+        <v>1119</v>
       </c>
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
@@ -20379,7 +20367,7 @@
       <c r="K291" s="2" t="s">
         <v>1403</v>
       </c>
-      <c r="L291" s="4" t="s">
+      <c r="L291" s="9" t="s">
         <v>1404</v>
       </c>
       <c r="M291" s="2"/>
@@ -20394,14 +20382,14 @@
         <v>32</v>
       </c>
       <c r="T291" s="10">
-        <v>43</v>
-      </c>
-      <c r="U291" s="10" t="s">
-        <v>1405</v>
+        <v>416</v>
+      </c>
+      <c r="U291" s="10">
+        <v>544</v>
       </c>
       <c r="V291" s="10"/>
       <c r="W291" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20409,29 +20397,29 @@
         <v>378</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" s="10" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>294</v>
+        <v>26</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>1123</v>
+        <v>27</v>
       </c>
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
       <c r="I292" s="2"/>
       <c r="J292" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K292" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="L292" s="9" t="s">
         <v>1408</v>
-      </c>
-      <c r="K292" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="L292" s="9" t="s">
-        <v>1410</v>
       </c>
       <c r="M292" s="2"/>
       <c r="N292" s="2"/>
@@ -20445,10 +20433,10 @@
         <v>32</v>
       </c>
       <c r="T292" s="10">
-        <v>416</v>
+        <v>210</v>
       </c>
       <c r="U292" s="10">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="V292" s="10"/>
       <c r="W292" s="10">
@@ -20460,29 +20448,29 @@
         <v>378</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" s="10" t="s">
-        <v>1411</v>
+        <v>240</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>26</v>
+        <v>294</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>27</v>
+        <v>1409</v>
       </c>
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
       <c r="I293" s="2"/>
       <c r="J293" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="K293" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="L293" s="9" t="s">
         <v>1412</v>
-      </c>
-      <c r="K293" s="2" t="s">
-        <v>1413</v>
-      </c>
-      <c r="L293" s="9" t="s">
-        <v>1414</v>
       </c>
       <c r="M293" s="2"/>
       <c r="N293" s="2"/>
@@ -20496,10 +20484,10 @@
         <v>32</v>
       </c>
       <c r="T293" s="10">
-        <v>210</v>
+        <v>1450</v>
       </c>
       <c r="U293" s="10">
-        <v>533</v>
+        <v>590</v>
       </c>
       <c r="V293" s="10"/>
       <c r="W293" s="10">
@@ -20511,29 +20499,29 @@
         <v>378</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" s="10" t="s">
-        <v>240</v>
+        <v>1413</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>294</v>
+        <v>75</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>1415</v>
+        <v>76</v>
       </c>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
       <c r="I294" s="2"/>
       <c r="J294" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="K294" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="L294" s="9" t="s">
         <v>1416</v>
-      </c>
-      <c r="K294" s="2" t="s">
-        <v>1417</v>
-      </c>
-      <c r="L294" s="9" t="s">
-        <v>1418</v>
       </c>
       <c r="M294" s="2"/>
       <c r="N294" s="2"/>
@@ -20547,10 +20535,10 @@
         <v>32</v>
       </c>
       <c r="T294" s="10">
-        <v>1450</v>
+        <v>149</v>
       </c>
       <c r="U294" s="10">
-        <v>590</v>
+        <v>168</v>
       </c>
       <c r="V294" s="10"/>
       <c r="W294" s="10">
@@ -20562,29 +20550,29 @@
         <v>378</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" s="10" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>75</v>
+        <v>294</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>76</v>
+        <v>1418</v>
       </c>
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
       <c r="I295" s="2"/>
       <c r="J295" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="K295" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="L295" s="9" t="s">
         <v>1420</v>
-      </c>
-      <c r="K295" s="2" t="s">
-        <v>1421</v>
-      </c>
-      <c r="L295" s="9" t="s">
-        <v>1422</v>
       </c>
       <c r="M295" s="2"/>
       <c r="N295" s="2"/>
@@ -20598,10 +20586,10 @@
         <v>32</v>
       </c>
       <c r="T295" s="10">
-        <v>149</v>
+        <v>365</v>
       </c>
       <c r="U295" s="10">
-        <v>168</v>
+        <v>568</v>
       </c>
       <c r="V295" s="10"/>
       <c r="W295" s="10">
@@ -20613,29 +20601,29 @@
         <v>378</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" s="10" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>294</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="G296" s="2"/>
       <c r="H296" s="2"/>
       <c r="I296" s="2"/>
       <c r="J296" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="K296" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="L296" s="9" t="s">
         <v>1425</v>
-      </c>
-      <c r="K296" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="L296" s="9" t="s">
-        <v>1426</v>
       </c>
       <c r="M296" s="2"/>
       <c r="N296" s="2"/>
@@ -20649,10 +20637,10 @@
         <v>32</v>
       </c>
       <c r="T296" s="10">
-        <v>365</v>
+        <v>518</v>
       </c>
       <c r="U296" s="10">
-        <v>568</v>
+        <v>1224</v>
       </c>
       <c r="V296" s="10"/>
       <c r="W296" s="10">
@@ -20664,29 +20652,29 @@
         <v>378</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="C297" s="2"/>
-      <c r="D297" s="10" t="s">
-        <v>1427</v>
+      <c r="D297" s="10">
+        <v>1555</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>294</v>
+        <v>212</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>1428</v>
+        <v>213</v>
       </c>
       <c r="G297" s="2"/>
       <c r="H297" s="2"/>
       <c r="I297" s="2"/>
       <c r="J297" s="2" t="s">
-        <v>1429</v>
+        <v>665</v>
       </c>
       <c r="K297" s="2" t="s">
-        <v>1430</v>
+        <v>1103</v>
       </c>
       <c r="L297" s="9" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="M297" s="2"/>
       <c r="N297" s="2"/>
@@ -20700,10 +20688,10 @@
         <v>32</v>
       </c>
       <c r="T297" s="10">
-        <v>518</v>
+        <v>146</v>
       </c>
       <c r="U297" s="10">
-        <v>1224</v>
+        <v>193</v>
       </c>
       <c r="V297" s="10"/>
       <c r="W297" s="10">
@@ -20715,29 +20703,29 @@
         <v>378</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="C298" s="2"/>
-      <c r="D298" s="10">
-        <v>1555</v>
+      <c r="D298" s="10" t="s">
+        <v>1427</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>212</v>
+        <v>294</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>213</v>
+        <v>1428</v>
       </c>
       <c r="G298" s="2"/>
       <c r="H298" s="2"/>
       <c r="I298" s="2"/>
       <c r="J298" s="2" t="s">
-        <v>665</v>
+        <v>1429</v>
       </c>
       <c r="K298" s="2" t="s">
-        <v>1107</v>
+        <v>1430</v>
       </c>
       <c r="L298" s="9" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="M298" s="2"/>
       <c r="N298" s="2"/>
@@ -20751,10 +20739,10 @@
         <v>32</v>
       </c>
       <c r="T298" s="10">
-        <v>146</v>
+        <v>910</v>
       </c>
       <c r="U298" s="10">
-        <v>193</v>
+        <v>2260</v>
       </c>
       <c r="V298" s="10"/>
       <c r="W298" s="10">
@@ -20766,29 +20754,29 @@
         <v>378</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" s="10" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>294</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>1434</v>
+        <v>1119</v>
       </c>
       <c r="G299" s="2"/>
       <c r="H299" s="2"/>
       <c r="I299" s="2"/>
       <c r="J299" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="K299" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="L299" s="9" t="s">
         <v>1435</v>
-      </c>
-      <c r="K299" s="2" t="s">
-        <v>1436</v>
-      </c>
-      <c r="L299" s="9" t="s">
-        <v>1437</v>
       </c>
       <c r="M299" s="2"/>
       <c r="N299" s="2"/>
@@ -20802,10 +20790,10 @@
         <v>32</v>
       </c>
       <c r="T299" s="10">
-        <v>910</v>
+        <v>151</v>
       </c>
       <c r="U299" s="10">
-        <v>2260</v>
+        <v>258</v>
       </c>
       <c r="V299" s="10"/>
       <c r="W299" s="10">
@@ -20817,29 +20805,29 @@
         <v>378</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="C300" s="2"/>
-      <c r="D300" s="10" t="s">
-        <v>1438</v>
+      <c r="D300" s="10">
+        <v>1570</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>294</v>
+        <v>233</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>1123</v>
+        <v>234</v>
       </c>
       <c r="G300" s="2"/>
       <c r="H300" s="2"/>
       <c r="I300" s="2"/>
       <c r="J300" s="2" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="K300" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="L300" s="9" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="M300" s="2"/>
       <c r="N300" s="2"/>
@@ -20853,10 +20841,10 @@
         <v>32</v>
       </c>
       <c r="T300" s="10">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="U300" s="10">
-        <v>258</v>
+        <v>362</v>
       </c>
       <c r="V300" s="10"/>
       <c r="W300" s="10">
@@ -20868,29 +20856,29 @@
         <v>378</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="C301" s="2"/>
-      <c r="D301" s="10">
-        <v>1570</v>
+      <c r="D301" s="10" t="s">
+        <v>1439</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>233</v>
+        <v>70</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>234</v>
+        <v>71</v>
       </c>
       <c r="G301" s="2"/>
       <c r="H301" s="2"/>
       <c r="I301" s="2"/>
       <c r="J301" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="K301" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L301" s="9" t="s">
         <v>1442</v>
-      </c>
-      <c r="K301" s="2" t="s">
-        <v>1443</v>
-      </c>
-      <c r="L301" s="9" t="s">
-        <v>1444</v>
       </c>
       <c r="M301" s="2"/>
       <c r="N301" s="2"/>
@@ -20901,13 +20889,13 @@
         <v>31</v>
       </c>
       <c r="S301" s="2" t="s">
-        <v>32</v>
+        <v>1443</v>
       </c>
       <c r="T301" s="10">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="U301" s="10">
-        <v>362</v>
+        <v>168</v>
       </c>
       <c r="V301" s="10"/>
       <c r="W301" s="10">
@@ -20919,29 +20907,29 @@
         <v>378</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" s="10" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G302" s="2"/>
       <c r="H302" s="2"/>
       <c r="I302" s="2"/>
       <c r="J302" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="K302" s="2" t="s">
         <v>1446</v>
       </c>
-      <c r="K302" s="2" t="s">
+      <c r="L302" s="4" t="s">
         <v>1447</v>
-      </c>
-      <c r="L302" s="9" t="s">
-        <v>1448</v>
       </c>
       <c r="M302" s="2"/>
       <c r="N302" s="2"/>
@@ -20952,13 +20940,13 @@
         <v>31</v>
       </c>
       <c r="S302" s="2" t="s">
-        <v>1449</v>
+        <v>32</v>
       </c>
       <c r="T302" s="10">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="U302" s="10">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="V302" s="10"/>
       <c r="W302" s="10">
@@ -20967,32 +20955,32 @@
     </row>
     <row r="303" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>378</v>
+        <v>1448</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>1406</v>
+        <v>1449</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" s="10" t="s">
         <v>1450</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>75</v>
+        <v>1451</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>76</v>
+        <v>1452</v>
       </c>
       <c r="G303" s="2"/>
       <c r="H303" s="2"/>
       <c r="I303" s="2"/>
       <c r="J303" s="2" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="K303" s="2" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="L303" s="4" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="M303" s="2"/>
       <c r="N303" s="2"/>
@@ -21000,50 +20988,46 @@
       <c r="P303" s="2"/>
       <c r="Q303" s="2"/>
       <c r="R303" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="S303" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T303" s="10">
-        <v>157</v>
-      </c>
-      <c r="U303" s="10">
-        <v>100</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="T303" s="10"/>
+      <c r="U303" s="10"/>
       <c r="V303" s="10"/>
-      <c r="W303" s="10">
-        <v>1</v>
+      <c r="W303" s="10" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="304" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>1454</v>
+        <v>1448</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>1455</v>
+        <v>1449</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" s="10" t="s">
-        <v>1456</v>
+        <v>1281</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="G304" s="2"/>
       <c r="H304" s="2"/>
       <c r="I304" s="2"/>
       <c r="J304" s="2" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="K304" s="2" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="L304" s="4" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="M304" s="2"/>
       <c r="N304" s="2"/>
@@ -21065,32 +21049,32 @@
     </row>
     <row r="305" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>1454</v>
+        <v>1448</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>1455</v>
+        <v>1449</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" s="10" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>1457</v>
+        <v>96</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>1458</v>
+        <v>1486</v>
       </c>
       <c r="G305" s="2"/>
       <c r="H305" s="2"/>
       <c r="I305" s="2"/>
       <c r="J305" s="2" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="K305" s="2" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="L305" s="4" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="M305" s="2"/>
       <c r="N305" s="2"/>
@@ -21112,32 +21096,32 @@
     </row>
     <row r="306" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>1454</v>
+        <v>1448</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>1455</v>
+        <v>1449</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" s="10" t="s">
-        <v>1293</v>
+        <v>1053</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>1492</v>
+        <v>234</v>
       </c>
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
       <c r="I306" s="2"/>
       <c r="J306" s="2" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="K306" s="2" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="L306" s="4" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="M306" s="2"/>
       <c r="N306" s="2"/>
@@ -21145,13 +21129,17 @@
       <c r="P306" s="2"/>
       <c r="Q306" s="2"/>
       <c r="R306" s="2" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="S306" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="T306" s="10"/>
-      <c r="U306" s="10"/>
+        <v>117</v>
+      </c>
+      <c r="T306" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="U306" s="10" t="s">
+        <v>1465</v>
+      </c>
       <c r="V306" s="10"/>
       <c r="W306" s="10" t="s">
         <v>616</v>
@@ -21159,32 +21147,32 @@
     </row>
     <row r="307" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>1454</v>
+        <v>1466</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>1455</v>
+        <v>1467</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" s="10" t="s">
-        <v>1057</v>
+        <v>1468</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>234</v>
+        <v>143</v>
       </c>
       <c r="G307" s="2"/>
       <c r="H307" s="2"/>
       <c r="I307" s="2"/>
       <c r="J307" s="2" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="K307" s="2" t="s">
-        <v>1469</v>
-      </c>
-      <c r="L307" s="4" t="s">
         <v>1470</v>
+      </c>
+      <c r="L307" s="9" t="s">
+        <v>1471</v>
       </c>
       <c r="M307" s="2"/>
       <c r="N307" s="2"/>
@@ -21197,45 +21185,45 @@
       <c r="S307" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="T307" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="U307" s="10" t="s">
-        <v>1471</v>
+      <c r="T307" s="10">
+        <v>107</v>
+      </c>
+      <c r="U307" s="10">
+        <v>77</v>
       </c>
       <c r="V307" s="10"/>
-      <c r="W307" s="10" t="s">
-        <v>616</v>
+      <c r="W307" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" s="10" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>142</v>
+        <v>579</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>143</v>
+        <v>1473</v>
       </c>
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
       <c r="I308" s="2"/>
       <c r="J308" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="K308" s="2" t="s">
         <v>1475</v>
       </c>
-      <c r="K308" s="2" t="s">
+      <c r="L308" s="9" t="s">
         <v>1476</v>
-      </c>
-      <c r="L308" s="9" t="s">
-        <v>1477</v>
       </c>
       <c r="M308" s="2"/>
       <c r="N308" s="2"/>
@@ -21243,16 +21231,16 @@
       <c r="P308" s="2"/>
       <c r="Q308" s="2"/>
       <c r="R308" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="S308" s="2" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="T308" s="10">
-        <v>107</v>
+        <v>500</v>
       </c>
       <c r="U308" s="10">
-        <v>77</v>
+        <v>770</v>
       </c>
       <c r="V308" s="10"/>
       <c r="W308" s="10">
@@ -21261,32 +21249,32 @@
     </row>
     <row r="309" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C309" s="2"/>
       <c r="D309" s="10" t="s">
-        <v>1478</v>
+        <v>959</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>579</v>
+        <v>233</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>1479</v>
+        <v>234</v>
       </c>
       <c r="G309" s="2"/>
       <c r="H309" s="2"/>
       <c r="I309" s="2"/>
       <c r="J309" s="2" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="K309" s="2" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="L309" s="9" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="M309" s="2"/>
       <c r="N309" s="2"/>
@@ -21294,16 +21282,16 @@
       <c r="P309" s="2"/>
       <c r="Q309" s="2"/>
       <c r="R309" s="2" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="S309" s="2" t="s">
-        <v>172</v>
+        <v>32</v>
       </c>
       <c r="T309" s="10">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="U309" s="10">
-        <v>770</v>
+        <v>67</v>
       </c>
       <c r="V309" s="10"/>
       <c r="W309" s="10">
@@ -21312,32 +21300,32 @@
     </row>
     <row r="310" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" s="10" t="s">
-        <v>963</v>
+        <v>912</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>233</v>
+        <v>365</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>234</v>
+        <v>366</v>
       </c>
       <c r="G310" s="2"/>
       <c r="H310" s="2"/>
       <c r="I310" s="2"/>
       <c r="J310" s="2" t="s">
-        <v>1483</v>
+        <v>888</v>
       </c>
       <c r="K310" s="2" t="s">
-        <v>1484</v>
-      </c>
-      <c r="L310" s="9" t="s">
-        <v>1485</v>
+        <v>889</v>
+      </c>
+      <c r="L310" s="4" t="s">
+        <v>1480</v>
       </c>
       <c r="M310" s="2"/>
       <c r="N310" s="2"/>
@@ -21348,13 +21336,13 @@
         <v>31</v>
       </c>
       <c r="S310" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="T310" s="10">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="U310" s="10">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="V310" s="10"/>
       <c r="W310" s="10">
@@ -21363,32 +21351,32 @@
     </row>
     <row r="311" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C311" s="2"/>
       <c r="D311" s="10" t="s">
-        <v>912</v>
+        <v>1481</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>365</v>
+        <v>304</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>366</v>
+        <v>305</v>
       </c>
       <c r="G311" s="2"/>
       <c r="H311" s="2"/>
       <c r="I311" s="2"/>
       <c r="J311" s="2" t="s">
-        <v>888</v>
+        <v>1482</v>
       </c>
       <c r="K311" s="2" t="s">
-        <v>889</v>
+        <v>1483</v>
       </c>
       <c r="L311" s="4" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="M311" s="2"/>
       <c r="N311" s="2"/>
@@ -21399,13 +21387,13 @@
         <v>31</v>
       </c>
       <c r="S311" s="2" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="T311" s="10">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="U311" s="10">
-        <v>117</v>
+        <v>201</v>
       </c>
       <c r="V311" s="10"/>
       <c r="W311" s="10">
@@ -21414,32 +21402,32 @@
     </row>
     <row r="312" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" s="10" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>304</v>
+        <v>579</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>305</v>
+        <v>1486</v>
       </c>
       <c r="G312" s="2"/>
       <c r="H312" s="2"/>
       <c r="I312" s="2"/>
       <c r="J312" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="K312" s="2" t="s">
         <v>1488</v>
       </c>
-      <c r="K312" s="2" t="s">
+      <c r="L312" s="4" t="s">
         <v>1489</v>
-      </c>
-      <c r="L312" s="4" t="s">
-        <v>1490</v>
       </c>
       <c r="M312" s="2"/>
       <c r="N312" s="2"/>
@@ -21450,13 +21438,13 @@
         <v>31</v>
       </c>
       <c r="S312" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="T312" s="10">
-        <v>270</v>
+        <v>410</v>
       </c>
       <c r="U312" s="10">
-        <v>201</v>
+        <v>279</v>
       </c>
       <c r="V312" s="10"/>
       <c r="W312" s="10">
@@ -21465,32 +21453,32 @@
     </row>
     <row r="313" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" s="10" t="s">
-        <v>1491</v>
+        <v>105</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>579</v>
+        <v>96</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>1492</v>
+        <v>412</v>
       </c>
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
       <c r="I313" s="2"/>
       <c r="J313" s="2" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="K313" s="2" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="L313" s="4" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="M313" s="2"/>
       <c r="N313" s="2"/>
@@ -21498,16 +21486,16 @@
       <c r="P313" s="2"/>
       <c r="Q313" s="2"/>
       <c r="R313" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="S313" s="2" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="T313" s="10">
-        <v>410</v>
+        <v>295</v>
       </c>
       <c r="U313" s="10">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="V313" s="10"/>
       <c r="W313" s="10">
@@ -21516,32 +21504,32 @@
     </row>
     <row r="314" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" s="10" t="s">
-        <v>105</v>
+        <v>1493</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>412</v>
+        <v>97</v>
       </c>
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
       <c r="I314" s="2"/>
       <c r="J314" s="2" t="s">
-        <v>1496</v>
+        <v>882</v>
       </c>
       <c r="K314" s="2" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="L314" s="4" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="M314" s="2"/>
       <c r="N314" s="2"/>
@@ -21549,16 +21537,16 @@
       <c r="P314" s="2"/>
       <c r="Q314" s="2"/>
       <c r="R314" s="2" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="S314" s="2" t="s">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="T314" s="10">
-        <v>295</v>
+        <v>174</v>
       </c>
       <c r="U314" s="10">
-        <v>225</v>
+        <v>178</v>
       </c>
       <c r="V314" s="10"/>
       <c r="W314" s="10">
@@ -21567,32 +21555,32 @@
     </row>
     <row r="315" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" s="10" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>97</v>
+        <v>839</v>
       </c>
       <c r="G315" s="2"/>
       <c r="H315" s="2"/>
       <c r="I315" s="2"/>
       <c r="J315" s="2" t="s">
-        <v>882</v>
+        <v>1497</v>
       </c>
       <c r="K315" s="2" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="L315" s="4" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="M315" s="2"/>
       <c r="N315" s="2"/>
@@ -21603,13 +21591,13 @@
         <v>31</v>
       </c>
       <c r="S315" s="2" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="T315" s="10">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="U315" s="10">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="V315" s="10"/>
       <c r="W315" s="10">
@@ -21618,32 +21606,32 @@
     </row>
     <row r="316" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" s="10" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>142</v>
+        <v>233</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>839</v>
+        <v>234</v>
       </c>
       <c r="G316" s="2"/>
       <c r="H316" s="2"/>
       <c r="I316" s="2"/>
       <c r="J316" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K316" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="L316" s="4" t="s">
         <v>1503</v>
-      </c>
-      <c r="K316" s="2" t="s">
-        <v>1504</v>
-      </c>
-      <c r="L316" s="4" t="s">
-        <v>1505</v>
       </c>
       <c r="M316" s="2"/>
       <c r="N316" s="2"/>
@@ -21654,13 +21642,13 @@
         <v>31</v>
       </c>
       <c r="S316" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="T316" s="10">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="U316" s="10">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="V316" s="10"/>
       <c r="W316" s="10">
@@ -21669,14 +21657,14 @@
     </row>
     <row r="317" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" s="10" t="s">
-        <v>1506</v>
+        <v>849</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>233</v>
@@ -21688,13 +21676,13 @@
       <c r="H317" s="2"/>
       <c r="I317" s="2"/>
       <c r="J317" s="2" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="K317" s="2" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="L317" s="4" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="M317" s="2"/>
       <c r="N317" s="2"/>
@@ -21708,10 +21696,10 @@
         <v>117</v>
       </c>
       <c r="T317" s="10">
-        <v>122</v>
+        <v>268</v>
       </c>
       <c r="U317" s="10">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="V317" s="10"/>
       <c r="W317" s="10">
@@ -21720,32 +21708,32 @@
     </row>
     <row r="318" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" s="10" t="s">
-        <v>849</v>
+        <v>1507</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>234</v>
+        <v>839</v>
       </c>
       <c r="G318" s="2"/>
       <c r="H318" s="2"/>
       <c r="I318" s="2"/>
       <c r="J318" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="K318" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="L318" s="4" t="s">
         <v>1510</v>
-      </c>
-      <c r="K318" s="2" t="s">
-        <v>1511</v>
-      </c>
-      <c r="L318" s="4" t="s">
-        <v>1512</v>
       </c>
       <c r="M318" s="2"/>
       <c r="N318" s="2"/>
@@ -21759,10 +21747,10 @@
         <v>117</v>
       </c>
       <c r="T318" s="10">
-        <v>268</v>
+        <v>71</v>
       </c>
       <c r="U318" s="10">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="V318" s="10"/>
       <c r="W318" s="10">
@@ -21771,32 +21759,32 @@
     </row>
     <row r="319" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>1472</v>
+        <v>1511</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>1473</v>
+        <v>1512</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" s="10" t="s">
         <v>1513</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>142</v>
+        <v>1514</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>839</v>
+        <v>729</v>
       </c>
       <c r="G319" s="2"/>
       <c r="H319" s="2"/>
       <c r="I319" s="2"/>
       <c r="J319" s="2" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="K319" s="2" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="L319" s="4" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="M319" s="2"/>
       <c r="N319" s="2"/>
@@ -21804,28 +21792,26 @@
       <c r="P319" s="2"/>
       <c r="Q319" s="2"/>
       <c r="R319" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="S319" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T319" s="10">
-        <v>71</v>
-      </c>
-      <c r="U319" s="10">
-        <v>71</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="T319" s="10" t="s">
+        <v>1518</v>
+      </c>
+      <c r="U319" s="10"/>
       <c r="V319" s="10"/>
-      <c r="W319" s="10">
-        <v>1</v>
+      <c r="W319" s="10" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="320" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>1517</v>
+        <v>1511</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>1518</v>
+        <v>1512</v>
       </c>
       <c r="C320" s="2"/>
       <c r="D320" s="10" t="s">
@@ -21835,19 +21821,19 @@
         <v>1520</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>729</v>
+        <v>1521</v>
       </c>
       <c r="G320" s="2"/>
       <c r="H320" s="2"/>
       <c r="I320" s="2"/>
       <c r="J320" s="2" t="s">
-        <v>1521</v>
+        <v>966</v>
       </c>
       <c r="K320" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="L320" s="4" t="s">
         <v>1522</v>
-      </c>
-      <c r="L320" s="4" t="s">
-        <v>1523</v>
       </c>
       <c r="M320" s="2"/>
       <c r="N320" s="2"/>
@@ -21855,15 +21841,17 @@
       <c r="P320" s="2"/>
       <c r="Q320" s="2"/>
       <c r="R320" s="2" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="S320" s="2" t="s">
-        <v>172</v>
+        <v>1028</v>
       </c>
       <c r="T320" s="10" t="s">
+        <v>1523</v>
+      </c>
+      <c r="U320" s="10" t="s">
         <v>1524</v>
       </c>
-      <c r="U320" s="10"/>
       <c r="V320" s="10"/>
       <c r="W320" s="10" t="s">
         <v>838</v>
@@ -21871,32 +21859,32 @@
     </row>
     <row r="321" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>1517</v>
+        <v>1511</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>1518</v>
+        <v>1512</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" s="10" t="s">
-        <v>1525</v>
+        <v>1053</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="G321" s="2"/>
       <c r="H321" s="2"/>
       <c r="I321" s="2"/>
       <c r="J321" s="2" t="s">
-        <v>970</v>
+        <v>1525</v>
       </c>
       <c r="K321" s="2" t="s">
-        <v>971</v>
+        <v>1526</v>
       </c>
       <c r="L321" s="4" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="M321" s="2"/>
       <c r="N321" s="2"/>
@@ -21907,13 +21895,13 @@
         <v>31</v>
       </c>
       <c r="S321" s="2" t="s">
-        <v>1032</v>
+        <v>117</v>
       </c>
       <c r="T321" s="10" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="U321" s="10" t="s">
-        <v>1530</v>
+        <v>1274</v>
       </c>
       <c r="V321" s="10"/>
       <c r="W321" s="10" t="s">
@@ -21922,20 +21910,20 @@
     </row>
     <row r="322" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>1517</v>
+        <v>1511</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>1518</v>
+        <v>1512</v>
       </c>
       <c r="C322" s="2"/>
       <c r="D322" s="10" t="s">
-        <v>1057</v>
+        <v>1493</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
@@ -21944,10 +21932,10 @@
         <v>1531</v>
       </c>
       <c r="K322" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="L322" s="4" t="s">
         <v>1532</v>
-      </c>
-      <c r="L322" s="4" t="s">
-        <v>1533</v>
       </c>
       <c r="M322" s="2"/>
       <c r="N322" s="2"/>
@@ -21961,10 +21949,10 @@
         <v>117</v>
       </c>
       <c r="T322" s="10" t="s">
-        <v>1534</v>
+        <v>848</v>
       </c>
       <c r="U322" s="10" t="s">
-        <v>1278</v>
+        <v>1533</v>
       </c>
       <c r="V322" s="10"/>
       <c r="W322" s="10" t="s">
@@ -21973,34 +21961,32 @@
     </row>
     <row r="323" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>1517</v>
+        <v>1534</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>1518</v>
+        <v>1535</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" s="10" t="s">
-        <v>1499</v>
+        <v>1536</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>1535</v>
+        <v>1296</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="G323" s="2"/>
       <c r="H323" s="2"/>
       <c r="I323" s="2"/>
       <c r="J323" s="2" t="s">
-        <v>1537</v>
-      </c>
-      <c r="K323" s="2" t="s">
-        <v>1430</v>
-      </c>
-      <c r="L323" s="4" t="s">
         <v>1538</v>
       </c>
-      <c r="M323" s="2"/>
+      <c r="K323" s="2"/>
+      <c r="L323" s="11" t="s">
+        <v>1539</v>
+      </c>
+      <c r="M323" s="3"/>
       <c r="N323" s="2"/>
       <c r="O323" s="2"/>
       <c r="P323" s="2"/>
@@ -22011,48 +21997,56 @@
       <c r="S323" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="T323" s="10" t="s">
-        <v>848</v>
-      </c>
-      <c r="U323" s="10" t="s">
-        <v>1539</v>
+      <c r="T323" s="10">
+        <v>42</v>
+      </c>
+      <c r="U323" s="10">
+        <v>54</v>
       </c>
       <c r="V323" s="10"/>
-      <c r="W323" s="10" t="s">
-        <v>838</v>
+      <c r="W323" s="10">
+        <v>3</v>
       </c>
     </row>
     <row r="324" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>1540</v>
+        <v>1534</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" s="10" t="s">
-        <v>1542</v>
+        <v>732</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>1300</v>
+        <v>1540</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="G324" s="2"/>
       <c r="H324" s="2"/>
       <c r="I324" s="2"/>
       <c r="J324" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="K324" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="L324" s="4" t="s">
         <v>1544</v>
       </c>
-      <c r="K324" s="2"/>
-      <c r="L324" s="11" t="s">
+      <c r="M324" s="3" t="s">
         <v>1545</v>
       </c>
-      <c r="M324" s="3"/>
-      <c r="N324" s="2"/>
+      <c r="N324" s="7" t="s">
+        <v>1546</v>
+      </c>
       <c r="O324" s="2"/>
-      <c r="P324" s="2"/>
+      <c r="P324" s="7" t="s">
+        <v>1547</v>
+      </c>
       <c r="Q324" s="2"/>
       <c r="R324" s="2" t="s">
         <v>31</v>
@@ -22061,10 +22055,10 @@
         <v>117</v>
       </c>
       <c r="T324" s="10">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="U324" s="10">
-        <v>54</v>
+        <v>259</v>
       </c>
       <c r="V324" s="10"/>
       <c r="W324" s="10">
@@ -22073,43 +22067,37 @@
     </row>
     <row r="325" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>1540</v>
+        <v>1534</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" s="10" t="s">
-        <v>732</v>
+        <v>1548</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>1546</v>
+        <v>212</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>1547</v>
+        <v>213</v>
       </c>
       <c r="G325" s="2"/>
       <c r="H325" s="2"/>
       <c r="I325" s="2"/>
       <c r="J325" s="2" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="K325" s="2" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="L325" s="4" t="s">
-        <v>1550</v>
-      </c>
-      <c r="M325" s="3" t="s">
         <v>1551</v>
       </c>
-      <c r="N325" s="7" t="s">
-        <v>1552</v>
-      </c>
+      <c r="M325" s="3"/>
+      <c r="N325" s="2"/>
       <c r="O325" s="2"/>
-      <c r="P325" s="7" t="s">
-        <v>1553</v>
-      </c>
+      <c r="P325" s="2"/>
       <c r="Q325" s="2"/>
       <c r="R325" s="2" t="s">
         <v>31</v>
@@ -22118,10 +22106,10 @@
         <v>117</v>
       </c>
       <c r="T325" s="10">
-        <v>192</v>
+        <v>56</v>
       </c>
       <c r="U325" s="10">
-        <v>259</v>
+        <v>106</v>
       </c>
       <c r="V325" s="10"/>
       <c r="W325" s="10">
@@ -22130,20 +22118,20 @@
     </row>
     <row r="326" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>1540</v>
+        <v>1534</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" s="10" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F326" s="2" t="s">
         <v>1554</v>
-      </c>
-      <c r="E326" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="G326" s="2"/>
       <c r="H326" s="2"/>
@@ -22163,16 +22151,16 @@
       <c r="P326" s="2"/>
       <c r="Q326" s="2"/>
       <c r="R326" s="2" t="s">
-        <v>31</v>
+        <v>520</v>
       </c>
       <c r="S326" s="2" t="s">
         <v>117</v>
       </c>
       <c r="T326" s="10">
-        <v>56</v>
+        <v>219</v>
       </c>
       <c r="U326" s="10">
-        <v>106</v>
+        <v>584</v>
       </c>
       <c r="V326" s="10"/>
       <c r="W326" s="10">
@@ -22181,49 +22169,49 @@
     </row>
     <row r="327" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>1540</v>
+        <v>670</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>1541</v>
+        <v>1558</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" s="10" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
       <c r="I327" s="2"/>
       <c r="J327" s="2" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K327" s="2" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="L327" s="4" t="s">
-        <v>1563</v>
-      </c>
-      <c r="M327" s="3"/>
+        <v>1564</v>
+      </c>
+      <c r="M327" s="2"/>
       <c r="N327" s="2"/>
       <c r="O327" s="2"/>
       <c r="P327" s="2"/>
       <c r="Q327" s="2"/>
       <c r="R327" s="2" t="s">
-        <v>520</v>
+        <v>31</v>
       </c>
       <c r="S327" s="2" t="s">
         <v>117</v>
       </c>
       <c r="T327" s="10">
-        <v>219</v>
+        <v>301</v>
       </c>
       <c r="U327" s="10">
-        <v>584</v>
+        <v>441</v>
       </c>
       <c r="V327" s="10"/>
       <c r="W327" s="10">
@@ -22235,29 +22223,29 @@
         <v>670</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" s="10" t="s">
-        <v>1565</v>
+        <v>303</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1566</v>
+        <v>70</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>1567</v>
+        <v>71</v>
       </c>
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
       <c r="I328" s="2"/>
       <c r="J328" s="2" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="K328" s="2" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="L328" s="4" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="M328" s="2"/>
       <c r="N328" s="2"/>
@@ -22271,10 +22259,10 @@
         <v>117</v>
       </c>
       <c r="T328" s="10">
-        <v>301</v>
+        <v>56</v>
       </c>
       <c r="U328" s="10">
-        <v>441</v>
+        <v>70</v>
       </c>
       <c r="V328" s="10"/>
       <c r="W328" s="10">
@@ -22286,29 +22274,29 @@
         <v>670</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="C329" s="2"/>
       <c r="D329" s="10" t="s">
         <v>303</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>71</v>
+        <v>905</v>
       </c>
       <c r="G329" s="2"/>
       <c r="H329" s="2"/>
       <c r="I329" s="2"/>
       <c r="J329" s="2" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="K329" s="2" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="L329" s="4" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="M329" s="2"/>
       <c r="N329" s="2"/>
@@ -22322,10 +22310,10 @@
         <v>117</v>
       </c>
       <c r="T329" s="10">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="U329" s="10">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="V329" s="10"/>
       <c r="W329" s="10">
@@ -22337,29 +22325,29 @@
         <v>670</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="C330" s="2"/>
       <c r="D330" s="10" t="s">
-        <v>303</v>
+        <v>824</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>112</v>
+        <v>233</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>905</v>
+        <v>234</v>
       </c>
       <c r="G330" s="2"/>
       <c r="H330" s="2"/>
       <c r="I330" s="2"/>
       <c r="J330" s="2" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="K330" s="2" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="L330" s="4" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="M330" s="2"/>
       <c r="N330" s="2"/>
@@ -22373,10 +22361,10 @@
         <v>117</v>
       </c>
       <c r="T330" s="10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="U330" s="10">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="V330" s="10"/>
       <c r="W330" s="10">
@@ -22385,32 +22373,32 @@
     </row>
     <row r="331" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>670</v>
+        <v>291</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>1564</v>
+        <v>1574</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" s="10" t="s">
-        <v>824</v>
+        <v>1575</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>234</v>
+        <v>143</v>
       </c>
       <c r="G331" s="2"/>
       <c r="H331" s="2"/>
       <c r="I331" s="2"/>
       <c r="J331" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="K331" s="2" t="s">
         <v>1577</v>
       </c>
-      <c r="K331" s="2" t="s">
+      <c r="L331" s="4" t="s">
         <v>1578</v>
-      </c>
-      <c r="L331" s="4" t="s">
-        <v>1579</v>
       </c>
       <c r="M331" s="2"/>
       <c r="N331" s="2"/>
@@ -22424,14 +22412,14 @@
         <v>117</v>
       </c>
       <c r="T331" s="10">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="U331" s="10">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="V331" s="10"/>
       <c r="W331" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22439,11 +22427,11 @@
         <v>291</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" s="10" t="s">
-        <v>1581</v>
+        <v>697</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>142</v>
@@ -22455,13 +22443,13 @@
       <c r="H332" s="2"/>
       <c r="I332" s="2"/>
       <c r="J332" s="2" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="K332" s="2" t="s">
-        <v>1583</v>
+        <v>1360</v>
       </c>
       <c r="L332" s="4" t="s">
-        <v>1584</v>
+        <v>1580</v>
       </c>
       <c r="M332" s="2"/>
       <c r="N332" s="2"/>
@@ -22475,10 +22463,10 @@
         <v>117</v>
       </c>
       <c r="T332" s="10">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="U332" s="10">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="V332" s="10"/>
       <c r="W332" s="10">
@@ -22490,29 +22478,29 @@
         <v>291</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="C333" s="2"/>
       <c r="D333" s="10" t="s">
-        <v>697</v>
+        <v>1581</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>142</v>
+        <v>294</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>143</v>
+        <v>1119</v>
       </c>
       <c r="G333" s="2"/>
       <c r="H333" s="2"/>
       <c r="I333" s="2"/>
       <c r="J333" s="2" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="K333" s="2" t="s">
-        <v>1366</v>
+        <v>1583</v>
       </c>
       <c r="L333" s="4" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="M333" s="2"/>
       <c r="N333" s="2"/>
@@ -22523,13 +22511,13 @@
         <v>31</v>
       </c>
       <c r="S333" s="2" t="s">
-        <v>117</v>
+        <v>1585</v>
       </c>
       <c r="T333" s="10">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="U333" s="10">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="V333" s="10"/>
       <c r="W333" s="10">
@@ -22541,29 +22529,29 @@
         <v>291</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="C334" s="2"/>
       <c r="D334" s="10" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>294</v>
+        <v>142</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>1123</v>
+        <v>143</v>
       </c>
       <c r="G334" s="2"/>
       <c r="H334" s="2"/>
       <c r="I334" s="2"/>
       <c r="J334" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="K334" s="2" t="s">
         <v>1588</v>
       </c>
-      <c r="K334" s="2" t="s">
+      <c r="L334" s="4" t="s">
         <v>1589</v>
-      </c>
-      <c r="L334" s="4" t="s">
-        <v>1590</v>
       </c>
       <c r="M334" s="2"/>
       <c r="N334" s="2"/>
@@ -22574,13 +22562,13 @@
         <v>31</v>
       </c>
       <c r="S334" s="2" t="s">
-        <v>1591</v>
+        <v>117</v>
       </c>
       <c r="T334" s="10">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="U334" s="10">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="V334" s="10"/>
       <c r="W334" s="10">
@@ -22592,29 +22580,29 @@
         <v>291</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" s="10" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>142</v>
+        <v>233</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="G335" s="2"/>
       <c r="H335" s="2"/>
       <c r="I335" s="2"/>
       <c r="J335" s="2" t="s">
-        <v>1593</v>
+        <v>354</v>
       </c>
       <c r="K335" s="2" t="s">
-        <v>1594</v>
+        <v>355</v>
       </c>
       <c r="L335" s="4" t="s">
-        <v>1595</v>
+        <v>1591</v>
       </c>
       <c r="M335" s="2"/>
       <c r="N335" s="2"/>
@@ -22628,10 +22616,10 @@
         <v>117</v>
       </c>
       <c r="T335" s="10">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="U335" s="10">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="V335" s="10"/>
       <c r="W335" s="10">
@@ -22643,26 +22631,26 @@
         <v>291</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="C336" s="2"/>
       <c r="D336" s="10" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>233</v>
+        <v>1593</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>234</v>
+        <v>1594</v>
       </c>
       <c r="G336" s="2"/>
       <c r="H336" s="2"/>
       <c r="I336" s="2"/>
       <c r="J336" s="2" t="s">
-        <v>354</v>
+        <v>1595</v>
       </c>
       <c r="K336" s="2" t="s">
-        <v>355</v>
+        <v>1596</v>
       </c>
       <c r="L336" s="4" t="s">
         <v>1597</v>
@@ -22676,13 +22664,13 @@
         <v>31</v>
       </c>
       <c r="S336" s="2" t="s">
-        <v>117</v>
+        <v>1585</v>
       </c>
       <c r="T336" s="10">
-        <v>216</v>
+        <v>305</v>
       </c>
       <c r="U336" s="10">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="V336" s="10"/>
       <c r="W336" s="10">
@@ -22694,29 +22682,29 @@
         <v>291</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E337" s="2" t="s">
         <v>1598</v>
       </c>
-      <c r="E337" s="2" t="s">
+      <c r="F337" s="2" t="s">
         <v>1599</v>
-      </c>
-      <c r="F337" s="2" t="s">
-        <v>1600</v>
       </c>
       <c r="G337" s="2"/>
       <c r="H337" s="2"/>
       <c r="I337" s="2"/>
       <c r="J337" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="K337" s="2" t="s">
         <v>1601</v>
       </c>
-      <c r="K337" s="2" t="s">
+      <c r="L337" s="4" t="s">
         <v>1602</v>
-      </c>
-      <c r="L337" s="4" t="s">
-        <v>1603</v>
       </c>
       <c r="M337" s="2"/>
       <c r="N337" s="2"/>
@@ -22727,13 +22715,13 @@
         <v>31</v>
       </c>
       <c r="S337" s="2" t="s">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="T337" s="10">
-        <v>305</v>
+        <v>118</v>
       </c>
       <c r="U337" s="10">
-        <v>204</v>
+        <v>94</v>
       </c>
       <c r="V337" s="10"/>
       <c r="W337" s="10">
@@ -22742,32 +22730,32 @@
     </row>
     <row r="338" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>291</v>
+        <v>1603</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>1580</v>
+        <v>1604</v>
       </c>
       <c r="C338" s="2"/>
       <c r="D338" s="10" t="s">
-        <v>211</v>
+        <v>1214</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>1604</v>
+        <v>96</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>1605</v>
+        <v>97</v>
       </c>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
       <c r="I338" s="2"/>
       <c r="J338" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="K338" s="2" t="s">
         <v>1606</v>
       </c>
-      <c r="K338" s="2" t="s">
+      <c r="L338" s="4" t="s">
         <v>1607</v>
-      </c>
-      <c r="L338" s="4" t="s">
-        <v>1608</v>
       </c>
       <c r="M338" s="2"/>
       <c r="N338" s="2"/>
@@ -22778,13 +22766,13 @@
         <v>31</v>
       </c>
       <c r="S338" s="2" t="s">
-        <v>1591</v>
+        <v>32</v>
       </c>
       <c r="T338" s="10">
         <v>118</v>
       </c>
       <c r="U338" s="10">
-        <v>94</v>
+        <v>279</v>
       </c>
       <c r="V338" s="10"/>
       <c r="W338" s="10">
@@ -22793,32 +22781,32 @@
     </row>
     <row r="339" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" s="10" t="s">
-        <v>1218</v>
+        <v>1608</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>96</v>
+        <v>294</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>97</v>
+        <v>1609</v>
       </c>
       <c r="G339" s="2"/>
       <c r="H339" s="2"/>
       <c r="I339" s="2"/>
       <c r="J339" s="2" t="s">
-        <v>1611</v>
+        <v>605</v>
       </c>
       <c r="K339" s="2" t="s">
-        <v>1612</v>
+        <v>606</v>
       </c>
       <c r="L339" s="4" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="M339" s="2"/>
       <c r="N339" s="2"/>
@@ -22832,10 +22820,10 @@
         <v>32</v>
       </c>
       <c r="T339" s="10">
-        <v>118</v>
+        <v>690</v>
       </c>
       <c r="U339" s="10">
-        <v>279</v>
+        <v>360</v>
       </c>
       <c r="V339" s="10"/>
       <c r="W339" s="10">
@@ -22844,32 +22832,32 @@
     </row>
     <row r="340" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C340" s="2"/>
       <c r="D340" s="10" t="s">
-        <v>1614</v>
+        <v>1090</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>294</v>
+        <v>142</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>1615</v>
+        <v>143</v>
       </c>
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
       <c r="I340" s="2"/>
       <c r="J340" s="2" t="s">
-        <v>605</v>
+        <v>1611</v>
       </c>
       <c r="K340" s="2" t="s">
-        <v>606</v>
+        <v>1612</v>
       </c>
       <c r="L340" s="4" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="M340" s="2"/>
       <c r="N340" s="2"/>
@@ -22883,10 +22871,10 @@
         <v>32</v>
       </c>
       <c r="T340" s="10">
-        <v>690</v>
+        <v>119</v>
       </c>
       <c r="U340" s="10">
-        <v>360</v>
+        <v>165</v>
       </c>
       <c r="V340" s="10"/>
       <c r="W340" s="10">
@@ -22895,32 +22883,32 @@
     </row>
     <row r="341" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C341" s="2"/>
       <c r="D341" s="10" t="s">
-        <v>1094</v>
+        <v>1614</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="G341" s="2"/>
       <c r="H341" s="2"/>
       <c r="I341" s="2"/>
       <c r="J341" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="K341" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="L341" s="4" t="s">
         <v>1617</v>
-      </c>
-      <c r="K341" s="2" t="s">
-        <v>1618</v>
-      </c>
-      <c r="L341" s="4" t="s">
-        <v>1619</v>
       </c>
       <c r="M341" s="2"/>
       <c r="N341" s="2"/>
@@ -22934,10 +22922,10 @@
         <v>32</v>
       </c>
       <c r="T341" s="10">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="U341" s="10">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="V341" s="10"/>
       <c r="W341" s="10">
@@ -22946,32 +22934,32 @@
     </row>
     <row r="342" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C342" s="2"/>
       <c r="D342" s="10" t="s">
-        <v>1620</v>
+        <v>1401</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="G342" s="2"/>
       <c r="H342" s="2"/>
       <c r="I342" s="2"/>
       <c r="J342" s="2" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="K342" s="2" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="L342" s="4" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="M342" s="2"/>
       <c r="N342" s="2"/>
@@ -22985,10 +22973,10 @@
         <v>32</v>
       </c>
       <c r="T342" s="10">
-        <v>176</v>
+        <v>335</v>
       </c>
       <c r="U342" s="10">
-        <v>191</v>
+        <v>283</v>
       </c>
       <c r="V342" s="10"/>
       <c r="W342" s="10">
@@ -22997,32 +22985,32 @@
     </row>
     <row r="343" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" s="10" t="s">
-        <v>1407</v>
+        <v>1621</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>26</v>
+        <v>294</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>27</v>
+        <v>1609</v>
       </c>
       <c r="G343" s="2"/>
       <c r="H343" s="2"/>
       <c r="I343" s="2"/>
       <c r="J343" s="2" t="s">
-        <v>1624</v>
+        <v>426</v>
       </c>
       <c r="K343" s="2" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="L343" s="4" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="M343" s="2"/>
       <c r="N343" s="2"/>
@@ -23030,16 +23018,16 @@
       <c r="P343" s="2"/>
       <c r="Q343" s="2"/>
       <c r="R343" s="2" t="s">
-        <v>31</v>
+        <v>1624</v>
       </c>
       <c r="S343" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T343" s="10">
-        <v>335</v>
+        <v>478</v>
       </c>
       <c r="U343" s="10">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="V343" s="10"/>
       <c r="W343" s="10">
@@ -23048,32 +23036,32 @@
     </row>
     <row r="344" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C344" s="2"/>
       <c r="D344" s="10" t="s">
-        <v>1627</v>
+        <v>162</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>294</v>
+        <v>1164</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>1615</v>
+        <v>1625</v>
       </c>
       <c r="G344" s="2"/>
       <c r="H344" s="2"/>
       <c r="I344" s="2"/>
       <c r="J344" s="2" t="s">
-        <v>426</v>
+        <v>1626</v>
       </c>
       <c r="K344" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="L344" s="4" t="s">
         <v>1628</v>
-      </c>
-      <c r="L344" s="4" t="s">
-        <v>1629</v>
       </c>
       <c r="M344" s="2"/>
       <c r="N344" s="2"/>
@@ -23081,16 +23069,16 @@
       <c r="P344" s="2"/>
       <c r="Q344" s="2"/>
       <c r="R344" s="2" t="s">
-        <v>1630</v>
+        <v>31</v>
       </c>
       <c r="S344" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T344" s="10">
-        <v>478</v>
+        <v>120</v>
       </c>
       <c r="U344" s="10">
-        <v>268</v>
+        <v>172</v>
       </c>
       <c r="V344" s="10"/>
       <c r="W344" s="10">
@@ -23099,32 +23087,32 @@
     </row>
     <row r="345" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" s="10" t="s">
-        <v>162</v>
+        <v>1629</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>1168</v>
+        <v>26</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>1631</v>
+        <v>27</v>
       </c>
       <c r="G345" s="2"/>
       <c r="H345" s="2"/>
       <c r="I345" s="2"/>
       <c r="J345" s="2" t="s">
+        <v>1630</v>
+      </c>
+      <c r="K345" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="L345" s="4" t="s">
         <v>1632</v>
-      </c>
-      <c r="K345" s="2" t="s">
-        <v>1633</v>
-      </c>
-      <c r="L345" s="4" t="s">
-        <v>1634</v>
       </c>
       <c r="M345" s="2"/>
       <c r="N345" s="2"/>
@@ -23138,10 +23126,10 @@
         <v>32</v>
       </c>
       <c r="T345" s="10">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="U345" s="10">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="V345" s="10"/>
       <c r="W345" s="10">
@@ -23150,14 +23138,14 @@
     </row>
     <row r="346" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C346" s="2"/>
       <c r="D346" s="10" t="s">
-        <v>1635</v>
+        <v>118</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>26</v>
@@ -23169,13 +23157,13 @@
       <c r="H346" s="2"/>
       <c r="I346" s="2"/>
       <c r="J346" s="2" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="K346" s="2" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="L346" s="4" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="M346" s="2"/>
       <c r="N346" s="2"/>
@@ -23189,7 +23177,7 @@
         <v>32</v>
       </c>
       <c r="T346" s="10">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U346" s="10">
         <v>111</v>
@@ -23201,32 +23189,32 @@
     </row>
     <row r="347" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C347" s="2"/>
       <c r="D347" s="10" t="s">
-        <v>118</v>
+        <v>1636</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>26</v>
+        <v>233</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>27</v>
+        <v>234</v>
       </c>
       <c r="G347" s="2"/>
       <c r="H347" s="2"/>
       <c r="I347" s="2"/>
       <c r="J347" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="K347" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="L347" s="4" t="s">
         <v>1639</v>
-      </c>
-      <c r="K347" s="2" t="s">
-        <v>1640</v>
-      </c>
-      <c r="L347" s="4" t="s">
-        <v>1641</v>
       </c>
       <c r="M347" s="2"/>
       <c r="N347" s="2"/>
@@ -23240,10 +23228,10 @@
         <v>32</v>
       </c>
       <c r="T347" s="10">
-        <v>193</v>
+        <v>303</v>
       </c>
       <c r="U347" s="10">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="V347" s="10"/>
       <c r="W347" s="10">
@@ -23252,32 +23240,32 @@
     </row>
     <row r="348" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C348" s="2"/>
       <c r="D348" s="10" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>233</v>
+        <v>1296</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>234</v>
+        <v>1537</v>
       </c>
       <c r="G348" s="2"/>
       <c r="H348" s="2"/>
       <c r="I348" s="2"/>
       <c r="J348" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K348" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="L348" s="4" t="s">
         <v>1643</v>
-      </c>
-      <c r="K348" s="2" t="s">
-        <v>1644</v>
-      </c>
-      <c r="L348" s="4" t="s">
-        <v>1645</v>
       </c>
       <c r="M348" s="2"/>
       <c r="N348" s="2"/>
@@ -23291,10 +23279,10 @@
         <v>32</v>
       </c>
       <c r="T348" s="10">
-        <v>303</v>
+        <v>189</v>
       </c>
       <c r="U348" s="10">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="V348" s="10"/>
       <c r="W348" s="10">
@@ -23303,32 +23291,32 @@
     </row>
     <row r="349" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C349" s="2"/>
       <c r="D349" s="10" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>1300</v>
+        <v>294</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>1543</v>
+        <v>1119</v>
       </c>
       <c r="G349" s="2"/>
       <c r="H349" s="2"/>
       <c r="I349" s="2"/>
       <c r="J349" s="2" t="s">
-        <v>1647</v>
+        <v>900</v>
       </c>
       <c r="K349" s="2" t="s">
-        <v>1648</v>
+        <v>901</v>
       </c>
       <c r="L349" s="4" t="s">
-        <v>1649</v>
+        <v>1645</v>
       </c>
       <c r="M349" s="2"/>
       <c r="N349" s="2"/>
@@ -23342,10 +23330,10 @@
         <v>32</v>
       </c>
       <c r="T349" s="10">
-        <v>189</v>
+        <v>351</v>
       </c>
       <c r="U349" s="10">
-        <v>145</v>
+        <v>389</v>
       </c>
       <c r="V349" s="10"/>
       <c r="W349" s="10">
@@ -23354,32 +23342,32 @@
     </row>
     <row r="350" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>1609</v>
+        <v>1646</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>1610</v>
+        <v>1647</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" s="10" t="s">
-        <v>1650</v>
+        <v>545</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>294</v>
+        <v>46</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>1123</v>
+        <v>47</v>
       </c>
       <c r="G350" s="2"/>
       <c r="H350" s="2"/>
       <c r="I350" s="2"/>
       <c r="J350" s="2" t="s">
-        <v>900</v>
+        <v>1648</v>
       </c>
       <c r="K350" s="2" t="s">
-        <v>901</v>
+        <v>1649</v>
       </c>
       <c r="L350" s="4" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="M350" s="2"/>
       <c r="N350" s="2"/>
@@ -23392,45 +23380,45 @@
       <c r="S350" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T350" s="10">
-        <v>351</v>
-      </c>
-      <c r="U350" s="10">
-        <v>389</v>
+      <c r="T350" s="10" t="s">
+        <v>1651</v>
+      </c>
+      <c r="U350" s="10" t="s">
+        <v>1652</v>
       </c>
       <c r="V350" s="10"/>
-      <c r="W350" s="10">
-        <v>1</v>
+      <c r="W350" s="10" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="351" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>1652</v>
+        <v>1646</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="C351" s="2"/>
       <c r="D351" s="10" t="s">
-        <v>545</v>
+        <v>240</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>46</v>
+        <v>233</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>47</v>
+        <v>234</v>
       </c>
       <c r="G351" s="2"/>
       <c r="H351" s="2"/>
       <c r="I351" s="2"/>
       <c r="J351" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="K351" s="2" t="s">
         <v>1654</v>
       </c>
-      <c r="K351" s="2" t="s">
+      <c r="L351" s="4" t="s">
         <v>1655</v>
-      </c>
-      <c r="L351" s="4" t="s">
-        <v>1656</v>
       </c>
       <c r="M351" s="2"/>
       <c r="N351" s="2"/>
@@ -23444,10 +23432,10 @@
         <v>32</v>
       </c>
       <c r="T351" s="10" t="s">
+        <v>1656</v>
+      </c>
+      <c r="U351" s="10" t="s">
         <v>1657</v>
-      </c>
-      <c r="U351" s="10" t="s">
-        <v>1658</v>
       </c>
       <c r="V351" s="10"/>
       <c r="W351" s="10" t="s">
@@ -23456,32 +23444,32 @@
     </row>
     <row r="352" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>1652</v>
+        <v>1646</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="C352" s="2"/>
       <c r="D352" s="10" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="G352" s="2"/>
       <c r="H352" s="2"/>
       <c r="I352" s="2"/>
       <c r="J352" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="K352" s="2" t="s">
         <v>1659</v>
       </c>
-      <c r="K352" s="2" t="s">
+      <c r="L352" s="4" t="s">
         <v>1660</v>
-      </c>
-      <c r="L352" s="4" t="s">
-        <v>1661</v>
       </c>
       <c r="M352" s="2"/>
       <c r="N352" s="2"/>
@@ -23495,10 +23483,10 @@
         <v>32</v>
       </c>
       <c r="T352" s="10" t="s">
+        <v>1661</v>
+      </c>
+      <c r="U352" s="10" t="s">
         <v>1662</v>
-      </c>
-      <c r="U352" s="10" t="s">
-        <v>1663</v>
       </c>
       <c r="V352" s="10"/>
       <c r="W352" s="10" t="s">
@@ -23507,32 +23495,30 @@
     </row>
     <row r="353" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>1652</v>
+        <v>1646</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="C353" s="2"/>
       <c r="D353" s="10" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>294</v>
+        <v>75</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>295</v>
+        <v>76</v>
       </c>
       <c r="G353" s="2"/>
       <c r="H353" s="2"/>
       <c r="I353" s="2"/>
       <c r="J353" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K353" s="2"/>
+      <c r="L353" s="4" t="s">
         <v>1664</v>
-      </c>
-      <c r="K353" s="2" t="s">
-        <v>1665</v>
-      </c>
-      <c r="L353" s="4" t="s">
-        <v>1666</v>
       </c>
       <c r="M353" s="2"/>
       <c r="N353" s="2"/>
@@ -23546,10 +23532,10 @@
         <v>32</v>
       </c>
       <c r="T353" s="10" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="U353" s="10" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="V353" s="10"/>
       <c r="W353" s="10" t="s">
@@ -23558,30 +23544,30 @@
     </row>
     <row r="354" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>1652</v>
+        <v>1646</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="C354" s="2"/>
       <c r="D354" s="10" t="s">
-        <v>207</v>
+        <v>1536</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>75</v>
+        <v>294</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>76</v>
+        <v>1428</v>
       </c>
       <c r="G354" s="2"/>
       <c r="H354" s="2"/>
       <c r="I354" s="2"/>
       <c r="J354" s="2" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="K354" s="2"/>
       <c r="L354" s="4" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="M354" s="2"/>
       <c r="N354" s="2"/>
@@ -23594,11 +23580,11 @@
       <c r="S354" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T354" s="10" t="s">
-        <v>1671</v>
-      </c>
-      <c r="U354" s="10" t="s">
-        <v>1672</v>
+      <c r="T354" s="10">
+        <v>365</v>
+      </c>
+      <c r="U354" s="10">
+        <v>147</v>
       </c>
       <c r="V354" s="10"/>
       <c r="W354" s="10" t="s">
@@ -23607,30 +23593,30 @@
     </row>
     <row r="355" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>1652</v>
+        <v>1646</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="C355" s="2"/>
       <c r="D355" s="10" t="s">
-        <v>1542</v>
+        <v>1669</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>294</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="G355" s="2"/>
       <c r="H355" s="2"/>
       <c r="I355" s="2"/>
       <c r="J355" s="2" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="K355" s="2"/>
       <c r="L355" s="4" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="M355" s="2"/>
       <c r="N355" s="2"/>
@@ -23638,16 +23624,16 @@
       <c r="P355" s="2"/>
       <c r="Q355" s="2"/>
       <c r="R355" s="2" t="s">
-        <v>31</v>
+        <v>1682</v>
       </c>
       <c r="S355" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T355" s="10">
-        <v>365</v>
-      </c>
-      <c r="U355" s="10">
-        <v>147</v>
+      <c r="T355" s="10" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U355" s="10" t="s">
+        <v>1673</v>
       </c>
       <c r="V355" s="10"/>
       <c r="W355" s="10" t="s">
@@ -23656,30 +23642,30 @@
     </row>
     <row r="356" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>1652</v>
+        <v>1646</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="C356" s="2"/>
       <c r="D356" s="10" t="s">
+        <v>1674</v>
+      </c>
+      <c r="E356" s="2" t="s">
         <v>1675</v>
       </c>
-      <c r="E356" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="F356" s="2" t="s">
-        <v>1434</v>
+        <v>1676</v>
       </c>
       <c r="G356" s="2"/>
       <c r="H356" s="2"/>
       <c r="I356" s="2"/>
       <c r="J356" s="2" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="K356" s="2"/>
       <c r="L356" s="4" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="M356" s="2"/>
       <c r="N356" s="2"/>
@@ -23687,64 +23673,15 @@
       <c r="P356" s="2"/>
       <c r="Q356" s="2"/>
       <c r="R356" s="2" t="s">
-        <v>1688</v>
+        <v>1682</v>
       </c>
       <c r="S356" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T356" s="10" t="s">
-        <v>1678</v>
-      </c>
-      <c r="U356" s="10" t="s">
         <v>1679</v>
       </c>
+      <c r="T356" s="10"/>
+      <c r="U356" s="10"/>
       <c r="V356" s="10"/>
       <c r="W356" s="10" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="357" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A357" s="2" t="s">
-        <v>1652</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>1653</v>
-      </c>
-      <c r="C357" s="2"/>
-      <c r="D357" s="10" t="s">
-        <v>1680</v>
-      </c>
-      <c r="E357" s="2" t="s">
-        <v>1681</v>
-      </c>
-      <c r="F357" s="2" t="s">
-        <v>1682</v>
-      </c>
-      <c r="G357" s="2"/>
-      <c r="H357" s="2"/>
-      <c r="I357" s="2"/>
-      <c r="J357" s="2" t="s">
-        <v>1683</v>
-      </c>
-      <c r="K357" s="2"/>
-      <c r="L357" s="4" t="s">
-        <v>1684</v>
-      </c>
-      <c r="M357" s="2"/>
-      <c r="N357" s="2"/>
-      <c r="O357" s="2"/>
-      <c r="P357" s="2"/>
-      <c r="Q357" s="2"/>
-      <c r="R357" s="2" t="s">
-        <v>1688</v>
-      </c>
-      <c r="S357" s="2" t="s">
-        <v>1685</v>
-      </c>
-      <c r="T357" s="10"/>
-      <c r="U357" s="10"/>
-      <c r="V357" s="10"/>
-      <c r="W357" s="10" t="s">
         <v>838</v>
       </c>
     </row>
@@ -23960,171 +23897,170 @@
     <hyperlink ref="L194" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
     <hyperlink ref="L195" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
     <hyperlink ref="L196" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="L197" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="L198" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="L199" r:id="rId213" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/Self-portrait_at_the_Clavichord_with_a_Servant_by_Lavinia_Fontana.jpg/960px-Self-portrait_at_the_Clavichord_with_a_Servant_by_Lavinia_Fontana.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="L200" r:id="rId214" display="https://upload.wikimedia.org/wikipedia/commons/b/ba/%27Christ_with_the_Symbols_of_the_Passion%27%2C_oil_on_canvas_painting_by_Lavinia_Fontana%2C_1576%2C_El_Paso_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="L201" r:id="rId215" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/03/L%27Incarnation_du_Christ_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_96_%3B_MR_223.jpg/960px-L%27Incarnation_du_Christ_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_96_%3B_MR_223.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="L202" r:id="rId216" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Le_Mariage_mystique_de_sainte_Catherine_de_Sienne_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_97.jpg/960px-Le_Mariage_mystique_de_sainte_Catherine_de_Sienne_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_97.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="L203" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="L204" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="L205" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="L206" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="L207" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="L209" r:id="rId222" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Diptyque_de_Jean_Carondelet_%E2%80%93_Jan_Mabuse_%E2%80%93_Mus%C3%A9e_du_Louvre%2C_INV_1442%2C_INV_1443_%E2%80%93_Q27051640.jpg/1280px-Diptyque_de_Jean_Carondelet_%E2%80%93_Jan_Mabuse_%E2%80%93_Mus%C3%A9e_du_Louvre%2C_INV_1442%2C_INV_1443_%E2%80%93_Q27051640.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="N209" r:id="rId223" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Gossaert%2C_Jan_-_Diptyque_Carondelet_La_Vierge_%C3%A0_l%27Enfant%2C_1517%2C_INV_1443%2C_0000385324_OG.jpg/1280px-Gossaert%2C_Jan_-_Diptyque_Carondelet_La_Vierge_%C3%A0_l%27Enfant%2C_1517%2C_INV_1443%2C_0000385324_OG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="L210" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="L211" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="L212" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="L213" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="L214" r:id="rId228" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Matthias_Gr%C3%BCnewald_-_Die_Kreuzigung_Christi_%28Kunstmuseum_Basel%29.jpg/960px-Matthias_Gr%C3%BCnewald_-_Die_Kreuzigung_Christi_%28Kunstmuseum_Basel%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="L215" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="M215" r:id="rId230" display="Le Retable d'Heller " xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="N215" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="P215" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="L216" r:id="rId233" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Matthias_Gr%C3%BCnewald%2C_The_Small_Crucifixion%2C_c._1511-1520%2C_NGA_46118.jpg/960px-Matthias_Gr%C3%BCnewald%2C_The_Small_Crucifixion%2C_c._1511-1520%2C_NGA_46118.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="L217" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="L218" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="L219" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="L220" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="L221" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="L222" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="L223" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="L224" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="L225" r:id="rId242" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Hans_Holbein%2C_the_Younger_-_Sir_Thomas_More_-_Google_Art_Project.jpg/960px-Hans_Holbein%2C_the_Younger_-_Sir_Thomas_More_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="L226" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="L227" r:id="rId244" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Portrait_of_Nicholas_Kratzer_%281528%29_Hans_Holbein_d._J._%28Louvre_Museum%29.jpg/960px-Portrait_of_Nicholas_Kratzer_%281528%29_Hans_Holbein_d._J._%28Louvre_Museum%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="L228" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="L229" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="L230" r:id="rId247" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Hans_Holbein_the_Younger_-_Charles_de_Solier%2C_Sieur_de_Morette_-_Google_Art_Project.jpg/960px-Hans_Holbein_the_Younger_-_Charles_de_Solier%2C_Sieur_de_Morette_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="L231" r:id="rId248" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c6/Hans_the_Younger_Holbein_-_Christina_of_Denmark%2C_Duchess_of_Milan_-_Google_Art_Project.jpg/500px-Hans_the_Younger_Holbein_-_Christina_of_Denmark%2C_Duchess_of_Milan_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="L234" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="L235" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="L236" r:id="rId251" display="https://upload.wikimedia.org/wikipedia/commons/a/a2/Lorenzo_Lotto%2C_%2C_Kunsthistorisches_Museum_Wien%2C_Gem%C3%A4ldegalerie_-_Bildnis_eines_Mannes_mit_einer_goldenen_Tierpranke_%28Leonino_Brembate%5E%29_-_GG_265_-_Kunsthistorisches_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=it" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="L237" r:id="rId252" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Accademia_-_Ritratto_di_giovane_gentiluomo_nel_suo_studio_-_Lorenzo_Lotto_cat.912.jpg/1280px-Accademia_-_Ritratto_di_giovane_gentiluomo_nel_suo_studio_-_Lorenzo_Lotto_cat.912.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="L238" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="L239" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="L240" r:id="rId255" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="L241" r:id="rId256" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="L242" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="L243" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="L244" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="L245" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="L246" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="L247" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="L248" r:id="rId263" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Parmigianino_-_The_Madonna_and_Child_with_Saints_%28The_Vision_of_St_Jerome%29.jpg/500px-Parmigianino_-_The_Madonna_and_Child_with_Saints_%28The_Vision_of_St_Jerome%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="L249" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="L250" r:id="rId265" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="L251" r:id="rId266" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="L252" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="L253" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="L254" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="L255" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="L256" r:id="rId271" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="L257" r:id="rId272" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="L258" r:id="rId273" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/Quinten_Metsys_-_Triptyque_de_la_confr%C3%A9rie_de_Sainte-Anne_%C3%A0_Louvain.jpg/1280px-Quinten_Metsys_-_Triptyque_de_la_confr%C3%A9rie_de_Sainte-Anne_%C3%A0_Louvain.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="L259" r:id="rId274" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/Altaarstuk_van_het_schrijnwerkerambacht%2C_Quinten_Massijs%2C_%281511%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_245-248.jpg/1280px-Altaarstuk_van_het_schrijnwerkerambacht%2C_Quinten_Massijs%2C_%281511%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_245-248.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="L260" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="L261" r:id="rId276" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Quentin_Metsys%2C_Portrait_of_Pieter_Gillis_%281517%29_Longford_Castle%2C_Wiltshire%2C_England.jpg/960px-Quentin_Metsys%2C_Portrait_of_Pieter_Gillis_%281517%29_Longford_Castle%2C_Wiltshire%2C_England.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="L262" r:id="rId277" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d9/Quentin_Massys_-_Ill-Matched_Lovers%2C_c._1520-25.jpg/1280px-Quentin_Massys_-_Ill-Matched_Lovers%2C_c._1520-25.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="L263" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="L264" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="L265" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="L266" r:id="rId281" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Giovanni_Battista_Moroni_-_The_Knight_in_Black_-_Google_Art_Project.jpg/960px-Giovanni_Battista_Moroni_-_The_Knight_in_Black_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="L267" r:id="rId282" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="L268" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="L269" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="L270" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="L271" r:id="rId286" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Jacopo_Palma_il_vecchio_%28c.1480-1528%29_-_Venus_and_Cupid_-_109_-_Fitzwilliam_Museum.jpg/960px-Jacopo_Palma_il_vecchio_%28c.1480-1528%29_-_Venus_and_Cupid_-_109_-_Fitzwilliam_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="L272" r:id="rId287" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="L273" r:id="rId288" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="L274" r:id="rId289" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Joachim_Patinir_-_Rest_during_the_Flight_to_Egypt%2C_Museo_del_Prado.jpg/1280px-Joachim_Patinir_-_Rest_during_the_Flight_to_Egypt%2C_Museo_del_Prado.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="L275" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="L276" r:id="rId291" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Landschap_met_de_vlucht_naar_Egypte%2C_Joachim_Patinir%2C_%281516-1517%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_64.jpg/1280px-Landschap_met_de_vlucht_naar_Egypte%2C_Joachim_Patinir%2C_%281516-1517%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_64.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="L277" r:id="rId292" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/56/Joachim_Patinir_-_Landscape_with_the_Destruction_of_Sodom_and_Gomorrah_-_Google_Art_Project.jpg/1280px-Joachim_Patinir_-_Landscape_with_the_Destruction_of_Sodom_and_Gomorrah_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="L278" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="L279" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="L280" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="L281" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="L282" r:id="rId297" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="L283" r:id="rId298" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="L284" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="L285" r:id="rId300" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Pontormo_%28Jacopo_Carucci%29_%28Italian%2C_Florentine%29_-_Portrait_of_a_Halberdier_%28Francesco_Guardi%3F%29_-_Google_Art_Project.jpg/960px-Pontormo_%28Jacopo_Carucci%29_%28Italian%2C_Florentine%29_-_Portrait_of_a_Halberdier_%28Francesco_Guardi%3F%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="L286" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="L287" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="L288" r:id="rId303" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="L289" r:id="rId304" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="L290" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="L291" r:id="rId306" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Francesco_Primaticcio_-_The_Holy_Family_with_Sts_Elisabeth_and_John_the_Baptist_-_WGA18410.jpg/960px-Francesco_Primaticcio_-_The_Holy_Family_with_Sts_Elisabeth_and_John_the_Baptist_-_WGA18410.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="L292" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="L293" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="L294" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="L295" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="L296" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="L297" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="L298" r:id="rId313" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="L299" r:id="rId314" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="L300" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="L301" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="L302" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="L303" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="L304" r:id="rId319" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="L305" r:id="rId320" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="L306" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="L307" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="L308" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="L309" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="L310" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="L311" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="L312" r:id="rId327" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Raphael_-_The_Sistine_Madonna_-_Google_Arts_%26_Culture.jpg/960px-Raphael_-_The_Sistine_Madonna_-_Google_Arts_%26_Culture.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="L313" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="L314" r:id="rId329" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="L315" r:id="rId330" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="L316" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="L317" r:id="rId332" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/La_Vierge_%C3%A0_l%27Enfant_avec_le_petit_saint_Jean_Baptiste_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_602_%3B_MR_433.jpg/960px-La_Vierge_%C3%A0_l%27Enfant_avec_le_petit_saint_Jean_Baptiste_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_602_%3B_MR_433.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=it" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="L318" r:id="rId333" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Saint_Michel_et_le_Dragon_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_608_%3B_MR_439.jpg/960px-Saint_Michel_et_le_Dragon_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_608_%3B_MR_439.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="L319" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="L320" r:id="rId335" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="L321" r:id="rId336" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Luca_Signorelli_-_Compianto_sul_Cristo_morto_%28Museo_Diocesano%2C_Cortona%29.jpg/960px-Luca_Signorelli_-_Compianto_sul_Cristo_morto_%28Museo_Diocesano%2C_Cortona%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="L322" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="L323" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="L324" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="L325" r:id="rId340" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/09/Maarten_van_Heemskerck_-_St_Luke_Painting_the_Virgin_%281532_Haarlem%29.jpg/1280px-Maarten_van_Heemskerck_-_St_Luke_Painting_the_Virgin_%281532_Haarlem%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="N325" r:id="rId341" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/De_heilige_Lucas_schildert_de_Madonna_-_Maarten_van_Heemskerck-1532.JPG/1280px-De_heilige_Lucas_schildert_de_Madonna_-_Maarten_van_Heemskerck-1532.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="P325" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="L326" r:id="rId343" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7f/Maerten_van_Heemskerck_-_The_Triumphal_Procession_of_Bacchus_-_Google_Art_Project.jpg/1280px-Maerten_van_Heemskerck_-_The_Triumphal_Procession_of_Bacchus_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="L327" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="L328" r:id="rId345" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="L329" r:id="rId346" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="L330" r:id="rId347" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Lucas_Hugensz._van_Leyden_-_Die_Schachpartie%2C_1500_-_1520%2C_574A.jpg/1280px-Lucas_Hugensz._van_Leyden_-_Die_Schachpartie%2C_1500_-_1520%2C_574A.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="L331" r:id="rId348" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b5/La_Tireuse_de_cartes_-_Lucas_van_Leyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1962_17.jpg/1280px-La_Tireuse_de_cartes_-_Lucas_van_Leyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1962_17.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="L332" r:id="rId349" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Portrait_of_Lorenzo_de%27_Medici%2C_the_Magnificent_%281449%E2%80%931492%29%2C_by_Giorgio_Vasari_-_Uffizi_Gallery.jpg/960px-Portrait_of_Lorenzo_de%27_Medici%2C_the_Magnificent_%281449%E2%80%931492%29%2C_by_Giorgio_Vasari_-_Uffizi_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="L333" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="L334" r:id="rId351" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/78/Giorgio_Vasari_-_Allegory_of_Justice_and_Truth_%281543%29_-_Google_Arts_and_Culture.jpg/960px-Giorgio_Vasari_-_Allegory_of_Justice_and_Truth_%281543%29_-_Google_Arts_and_Culture.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="L335" r:id="rId352" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="L336" r:id="rId353" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/L%27Annonciation_-_Giorgio_Vasari_-_Mus%C3%A9e_du_Louvre_Peintures_INV_732_%3B_MR_536.jpg/960px-L%27Annonciation_-_Giorgio_Vasari_-_Mus%C3%A9e_du_Louvre_Peintures_INV_732_%3B_MR_536.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="L337" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="L338" r:id="rId355" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fb/Giorgio_Vasari_-_Judith_and_Holofernes_-_2-1982_-_Saint_Louis_Art_Museum.jpg/960px-Giorgio_Vasari_-_Judith_and_Holofernes_-_2-1982_-_Saint_Louis_Art_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="L339" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="L340" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="L341" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="L342" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="L343" r:id="rId360" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Carlos_V_en_M%C3%BChlberg%2C_by_Titian%2C_from_Prado_in_Google_Earth.jpg/960px-Carlos_V_en_M%C3%BChlberg%2C_by_Titian%2C_from_Prado_in_Google_Earth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="L344" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="L345" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="L346" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="L347" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="L348" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="L349" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="L350" r:id="rId367" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="L351" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="L352" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="L353" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="L354" r:id="rId371" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/The_Family_of_Darius_before_Alexander_by_Paolo_Veronese_1570.jpg/1280px-The_Family_of_Darius_before_Alexander_by_Paolo_Veronese_1570.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="L355" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="L356" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="L357" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="L96" r:id="rId375" xr:uid="{C962C132-A78E-4C23-A7FC-642370B7FFCC}"/>
+    <hyperlink ref="L197" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="L198" r:id="rId212" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/Self-portrait_at_the_Clavichord_with_a_Servant_by_Lavinia_Fontana.jpg/960px-Self-portrait_at_the_Clavichord_with_a_Servant_by_Lavinia_Fontana.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="L199" r:id="rId213" display="https://upload.wikimedia.org/wikipedia/commons/b/ba/%27Christ_with_the_Symbols_of_the_Passion%27%2C_oil_on_canvas_painting_by_Lavinia_Fontana%2C_1576%2C_El_Paso_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="L200" r:id="rId214" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/03/L%27Incarnation_du_Christ_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_96_%3B_MR_223.jpg/960px-L%27Incarnation_du_Christ_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_96_%3B_MR_223.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="L201" r:id="rId215" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Le_Mariage_mystique_de_sainte_Catherine_de_Sienne_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_97.jpg/960px-Le_Mariage_mystique_de_sainte_Catherine_de_Sienne_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_97.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="L202" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="L203" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="L204" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="L205" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="L206" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="L208" r:id="rId221" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Diptyque_de_Jean_Carondelet_%E2%80%93_Jan_Mabuse_%E2%80%93_Mus%C3%A9e_du_Louvre%2C_INV_1442%2C_INV_1443_%E2%80%93_Q27051640.jpg/1280px-Diptyque_de_Jean_Carondelet_%E2%80%93_Jan_Mabuse_%E2%80%93_Mus%C3%A9e_du_Louvre%2C_INV_1442%2C_INV_1443_%E2%80%93_Q27051640.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="N208" r:id="rId222" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Gossaert%2C_Jan_-_Diptyque_Carondelet_La_Vierge_%C3%A0_l%27Enfant%2C_1517%2C_INV_1443%2C_0000385324_OG.jpg/1280px-Gossaert%2C_Jan_-_Diptyque_Carondelet_La_Vierge_%C3%A0_l%27Enfant%2C_1517%2C_INV_1443%2C_0000385324_OG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="L209" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="L210" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="L211" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="L212" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="L213" r:id="rId227" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Matthias_Gr%C3%BCnewald_-_Die_Kreuzigung_Christi_%28Kunstmuseum_Basel%29.jpg/960px-Matthias_Gr%C3%BCnewald_-_Die_Kreuzigung_Christi_%28Kunstmuseum_Basel%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="L214" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="M214" r:id="rId229" display="Le Retable d'Heller " xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="N214" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="P214" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="L215" r:id="rId232" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Matthias_Gr%C3%BCnewald%2C_The_Small_Crucifixion%2C_c._1511-1520%2C_NGA_46118.jpg/960px-Matthias_Gr%C3%BCnewald%2C_The_Small_Crucifixion%2C_c._1511-1520%2C_NGA_46118.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="L216" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="L217" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="L218" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="L219" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="L220" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="L221" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="L222" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="L223" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="L224" r:id="rId241" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Hans_Holbein%2C_the_Younger_-_Sir_Thomas_More_-_Google_Art_Project.jpg/960px-Hans_Holbein%2C_the_Younger_-_Sir_Thomas_More_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="L225" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="L226" r:id="rId243" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Portrait_of_Nicholas_Kratzer_%281528%29_Hans_Holbein_d._J._%28Louvre_Museum%29.jpg/960px-Portrait_of_Nicholas_Kratzer_%281528%29_Hans_Holbein_d._J._%28Louvre_Museum%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="L227" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="L228" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="L229" r:id="rId246" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Hans_Holbein_the_Younger_-_Charles_de_Solier%2C_Sieur_de_Morette_-_Google_Art_Project.jpg/960px-Hans_Holbein_the_Younger_-_Charles_de_Solier%2C_Sieur_de_Morette_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="L230" r:id="rId247" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c6/Hans_the_Younger_Holbein_-_Christina_of_Denmark%2C_Duchess_of_Milan_-_Google_Art_Project.jpg/500px-Hans_the_Younger_Holbein_-_Christina_of_Denmark%2C_Duchess_of_Milan_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="L233" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="L234" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="L235" r:id="rId250" display="https://upload.wikimedia.org/wikipedia/commons/a/a2/Lorenzo_Lotto%2C_%2C_Kunsthistorisches_Museum_Wien%2C_Gem%C3%A4ldegalerie_-_Bildnis_eines_Mannes_mit_einer_goldenen_Tierpranke_%28Leonino_Brembate%5E%29_-_GG_265_-_Kunsthistorisches_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=it" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="L236" r:id="rId251" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Accademia_-_Ritratto_di_giovane_gentiluomo_nel_suo_studio_-_Lorenzo_Lotto_cat.912.jpg/1280px-Accademia_-_Ritratto_di_giovane_gentiluomo_nel_suo_studio_-_Lorenzo_Lotto_cat.912.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="L237" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="L238" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="L239" r:id="rId254" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="L240" r:id="rId255" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="L241" r:id="rId256" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="L242" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="L243" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="L244" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="L245" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="L246" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="L247" r:id="rId262" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Parmigianino_-_The_Madonna_and_Child_with_Saints_%28The_Vision_of_St_Jerome%29.jpg/500px-Parmigianino_-_The_Madonna_and_Child_with_Saints_%28The_Vision_of_St_Jerome%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="L248" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="L249" r:id="rId264" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="L250" r:id="rId265" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="L251" r:id="rId266" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="L252" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="L253" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="L254" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="L255" r:id="rId270" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="L256" r:id="rId271" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="L257" r:id="rId272" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/Quinten_Metsys_-_Triptyque_de_la_confr%C3%A9rie_de_Sainte-Anne_%C3%A0_Louvain.jpg/1280px-Quinten_Metsys_-_Triptyque_de_la_confr%C3%A9rie_de_Sainte-Anne_%C3%A0_Louvain.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="L258" r:id="rId273" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/Altaarstuk_van_het_schrijnwerkerambacht%2C_Quinten_Massijs%2C_%281511%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_245-248.jpg/1280px-Altaarstuk_van_het_schrijnwerkerambacht%2C_Quinten_Massijs%2C_%281511%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_245-248.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="L259" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="L260" r:id="rId275" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Quentin_Metsys%2C_Portrait_of_Pieter_Gillis_%281517%29_Longford_Castle%2C_Wiltshire%2C_England.jpg/960px-Quentin_Metsys%2C_Portrait_of_Pieter_Gillis_%281517%29_Longford_Castle%2C_Wiltshire%2C_England.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="L261" r:id="rId276" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d9/Quentin_Massys_-_Ill-Matched_Lovers%2C_c._1520-25.jpg/1280px-Quentin_Massys_-_Ill-Matched_Lovers%2C_c._1520-25.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="L262" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="L263" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="L264" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="L265" r:id="rId280" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Giovanni_Battista_Moroni_-_The_Knight_in_Black_-_Google_Art_Project.jpg/960px-Giovanni_Battista_Moroni_-_The_Knight_in_Black_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="L266" r:id="rId281" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="L267" r:id="rId282" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="L268" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="L269" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="L270" r:id="rId285" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Jacopo_Palma_il_vecchio_%28c.1480-1528%29_-_Venus_and_Cupid_-_109_-_Fitzwilliam_Museum.jpg/960px-Jacopo_Palma_il_vecchio_%28c.1480-1528%29_-_Venus_and_Cupid_-_109_-_Fitzwilliam_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="L271" r:id="rId286" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="L272" r:id="rId287" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="L273" r:id="rId288" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Joachim_Patinir_-_Rest_during_the_Flight_to_Egypt%2C_Museo_del_Prado.jpg/1280px-Joachim_Patinir_-_Rest_during_the_Flight_to_Egypt%2C_Museo_del_Prado.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="L274" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="L275" r:id="rId290" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Landschap_met_de_vlucht_naar_Egypte%2C_Joachim_Patinir%2C_%281516-1517%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_64.jpg/1280px-Landschap_met_de_vlucht_naar_Egypte%2C_Joachim_Patinir%2C_%281516-1517%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_64.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="L276" r:id="rId291" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/56/Joachim_Patinir_-_Landscape_with_the_Destruction_of_Sodom_and_Gomorrah_-_Google_Art_Project.jpg/1280px-Joachim_Patinir_-_Landscape_with_the_Destruction_of_Sodom_and_Gomorrah_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="L277" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="L278" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="L279" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="L280" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="L281" r:id="rId296" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="L282" r:id="rId297" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="L283" r:id="rId298" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="L284" r:id="rId299" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Pontormo_%28Jacopo_Carucci%29_%28Italian%2C_Florentine%29_-_Portrait_of_a_Halberdier_%28Francesco_Guardi%3F%29_-_Google_Art_Project.jpg/960px-Pontormo_%28Jacopo_Carucci%29_%28Italian%2C_Florentine%29_-_Portrait_of_a_Halberdier_%28Francesco_Guardi%3F%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="L285" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="L286" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="L287" r:id="rId302" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="L288" r:id="rId303" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="L289" r:id="rId304" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="L290" r:id="rId305" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Francesco_Primaticcio_-_The_Holy_Family_with_Sts_Elisabeth_and_John_the_Baptist_-_WGA18410.jpg/960px-Francesco_Primaticcio_-_The_Holy_Family_with_Sts_Elisabeth_and_John_the_Baptist_-_WGA18410.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="L291" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="L292" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="L293" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="L294" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="L295" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="L296" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="L297" r:id="rId312" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="L298" r:id="rId313" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="L299" r:id="rId314" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="L300" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="L301" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="L302" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="L303" r:id="rId318" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="L304" r:id="rId319" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="L305" r:id="rId320" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="L306" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="L307" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="L308" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="L309" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="L310" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="L311" r:id="rId326" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Raphael_-_The_Sistine_Madonna_-_Google_Arts_%26_Culture.jpg/960px-Raphael_-_The_Sistine_Madonna_-_Google_Arts_%26_Culture.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="L312" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="L313" r:id="rId328" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="L314" r:id="rId329" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="L315" r:id="rId330" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="L316" r:id="rId331" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/La_Vierge_%C3%A0_l%27Enfant_avec_le_petit_saint_Jean_Baptiste_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_602_%3B_MR_433.jpg/960px-La_Vierge_%C3%A0_l%27Enfant_avec_le_petit_saint_Jean_Baptiste_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_602_%3B_MR_433.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=it" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="L317" r:id="rId332" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Saint_Michel_et_le_Dragon_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_608_%3B_MR_439.jpg/960px-Saint_Michel_et_le_Dragon_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_608_%3B_MR_439.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="L318" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="L319" r:id="rId334" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="L320" r:id="rId335" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Luca_Signorelli_-_Compianto_sul_Cristo_morto_%28Museo_Diocesano%2C_Cortona%29.jpg/960px-Luca_Signorelli_-_Compianto_sul_Cristo_morto_%28Museo_Diocesano%2C_Cortona%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="L321" r:id="rId336" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="L322" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="L323" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="L324" r:id="rId339" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/09/Maarten_van_Heemskerck_-_St_Luke_Painting_the_Virgin_%281532_Haarlem%29.jpg/1280px-Maarten_van_Heemskerck_-_St_Luke_Painting_the_Virgin_%281532_Haarlem%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="N324" r:id="rId340" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/De_heilige_Lucas_schildert_de_Madonna_-_Maarten_van_Heemskerck-1532.JPG/1280px-De_heilige_Lucas_schildert_de_Madonna_-_Maarten_van_Heemskerck-1532.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="P324" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="L325" r:id="rId342" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7f/Maerten_van_Heemskerck_-_The_Triumphal_Procession_of_Bacchus_-_Google_Art_Project.jpg/1280px-Maerten_van_Heemskerck_-_The_Triumphal_Procession_of_Bacchus_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="L326" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="L327" r:id="rId344" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="L328" r:id="rId345" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="L329" r:id="rId346" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Lucas_Hugensz._van_Leyden_-_Die_Schachpartie%2C_1500_-_1520%2C_574A.jpg/1280px-Lucas_Hugensz._van_Leyden_-_Die_Schachpartie%2C_1500_-_1520%2C_574A.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="L330" r:id="rId347" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b5/La_Tireuse_de_cartes_-_Lucas_van_Leyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1962_17.jpg/1280px-La_Tireuse_de_cartes_-_Lucas_van_Leyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1962_17.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="L331" r:id="rId348" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Portrait_of_Lorenzo_de%27_Medici%2C_the_Magnificent_%281449%E2%80%931492%29%2C_by_Giorgio_Vasari_-_Uffizi_Gallery.jpg/960px-Portrait_of_Lorenzo_de%27_Medici%2C_the_Magnificent_%281449%E2%80%931492%29%2C_by_Giorgio_Vasari_-_Uffizi_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="L332" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="L333" r:id="rId350" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/78/Giorgio_Vasari_-_Allegory_of_Justice_and_Truth_%281543%29_-_Google_Arts_and_Culture.jpg/960px-Giorgio_Vasari_-_Allegory_of_Justice_and_Truth_%281543%29_-_Google_Arts_and_Culture.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="L334" r:id="rId351" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="L335" r:id="rId352" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/L%27Annonciation_-_Giorgio_Vasari_-_Mus%C3%A9e_du_Louvre_Peintures_INV_732_%3B_MR_536.jpg/960px-L%27Annonciation_-_Giorgio_Vasari_-_Mus%C3%A9e_du_Louvre_Peintures_INV_732_%3B_MR_536.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="L336" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="L337" r:id="rId354" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fb/Giorgio_Vasari_-_Judith_and_Holofernes_-_2-1982_-_Saint_Louis_Art_Museum.jpg/960px-Giorgio_Vasari_-_Judith_and_Holofernes_-_2-1982_-_Saint_Louis_Art_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="L338" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="L339" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="L340" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="L341" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="L342" r:id="rId359" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Carlos_V_en_M%C3%BChlberg%2C_by_Titian%2C_from_Prado_in_Google_Earth.jpg/960px-Carlos_V_en_M%C3%BChlberg%2C_by_Titian%2C_from_Prado_in_Google_Earth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="L343" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="L344" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="L345" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="L346" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="L347" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="L348" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="L349" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="L350" r:id="rId367" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="L351" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="L352" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="L353" r:id="rId370" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/The_Family_of_Darius_before_Alexander_by_Paolo_Veronese_1570.jpg/1280px-The_Family_of_Darius_before_Alexander_by_Paolo_Veronese_1570.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="L354" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="L355" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="L356" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="L96" r:id="rId374" xr:uid="{C962C132-A78E-4C23-A7FC-642370B7FFCC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -1537,12 +1537,12 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Giovanni di Niccolò</t>
+          <t>Giovanni di Niccolò de</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>de Lutero</t>
+          <t>Lutero</t>
         </is>
       </c>
       <c r="C14" s="2" t="n"/>
@@ -1608,12 +1608,12 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Giovanni di Niccolò</t>
+          <t>Giovanni di Niccolò de</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>de Lutero</t>
+          <t>Lutero</t>
         </is>
       </c>
       <c r="C15" s="2" t="n"/>
@@ -1679,12 +1679,12 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Giovanni di Niccolò</t>
+          <t>Giovanni di Niccolò de</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>de Lutero</t>
+          <t>Lutero</t>
         </is>
       </c>
       <c r="C16" s="2" t="n"/>
@@ -1750,12 +1750,12 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Giovanni di Niccolò</t>
+          <t>Giovanni di Niccolò de</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>de Lutero</t>
+          <t>Lutero</t>
         </is>
       </c>
       <c r="C17" s="2" t="n"/>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>DÜRER</t>
+          <t>DURER</t>
         </is>
       </c>
       <c r="C194" s="2" t="n"/>
@@ -14480,7 +14480,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>DÜRER</t>
+          <t>DURER</t>
         </is>
       </c>
       <c r="C195" s="2" t="n"/>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>DÜRER</t>
+          <t>DURER</t>
         </is>
       </c>
       <c r="C196" s="2" t="n"/>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>DÜRER</t>
+          <t>DURER</t>
         </is>
       </c>
       <c r="C197" s="2" t="n"/>
@@ -14685,7 +14685,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>DÜRER</t>
+          <t>DURER</t>
         </is>
       </c>
       <c r="C198" s="2" t="n"/>
@@ -14754,7 +14754,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>DÜRER</t>
+          <t>DURER</t>
         </is>
       </c>
       <c r="C199" s="2" t="n"/>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>DÜRER</t>
+          <t>DURER</t>
         </is>
       </c>
       <c r="C200" s="2" t="n"/>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>DÜRER</t>
+          <t>DURER</t>
         </is>
       </c>
       <c r="C201" s="2" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>DÜRER</t>
+          <t>DURER</t>
         </is>
       </c>
       <c r="C202" s="2" t="n"/>
@@ -26771,8 +26771,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a3/Painting_-_Portrait_of_Bartolomeo_Panciatichi_by_Bronzino.jpg/960px-Painting_-_Portrait_of_Bartolomeo_Panciatichi_by_Bronzino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Bronzino_%28Agnolo_di_Cosimo_di_Mariano%29_-_Portrait_of_a_Young_Man_-_The_Metropolitan_Museum_of_Art.jpg/960px-Bronzino_%28Agnolo_di_Cosimo_di_Mariano%29_-_Portrait_of_a_Young_Man_-_The_Metropolitan_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
@@ -26818,14 +26818,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ea/Giorgione_-_Adoration_of_the_Shepherds_-_National_Gallery_of_Art.jpg/1280px-Giorgione_-_Adoration_of_the_Shepherds_-_National_Gallery_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/51/Barocci_-_Il_martirio_di_San_Vitale%2C_1580_-_1583%2C_401.jpg/960px-Barocci_-_Il_martirio_di_San_Vitale%2C_1580_-_1583%2C_401.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId82"/>
@@ -26860,7 +26860,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Jheronimus_Bosch_-_De_hooiwagen_%28c.1516%2C_Prado%29.jpg/1280px-Jheronimus_Bosch_-_De_hooiwagen_%28c.1516%2C_Prado%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId117"/>
@@ -26882,10 +26882,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/87/Assumption_of_Mary_-_Cerasi_Chapel_-_Santa_Maria_del_Popolo_-_Rome_2015.jpg/960px-Assumption_of_Mary_-_Cerasi_Chapel_-_Santa_Maria_del_Popolo_-_Rome_2015.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Madonna_Enthroned_with_Saint_Matthew%2C_Annibale_Carracci%2C_1588.png/960px-Madonna_Enthroned_with_Saint_Matthew%2C_Annibale_Carracci%2C_1588.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId142"/>
@@ -26893,38 +26893,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Jean_Clouet_-_Homme_au_P%C3%A9trarque_-_Royal_Collection.jpg/960px-Jean_Clouet_-_Homme_au_P%C3%A9trarque_-_Royal_Collection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Lucas_Cranach_d.%C3%84._-_Drei_Grazien%2C_1531_%28Mus%C3%A9e_du_Louvre%29.jpg/960px-Lucas_Cranach_d.%C3%84._-_Drei_Grazien%2C_1531_%28Mus%C3%A9e_du_Louvre%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/Lucas_Cranach_d.%C3%84._-_Reformationsaltar%2C_St._Marien_zu_Wittenberg%2C_Mitteltafel.jpg/1280px-Lucas_Cranach_d.%C3%84._-_Reformationsaltar%2C_St._Marien_zu_Wittenberg%2C_Mitteltafel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N142" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d7/Lucas_Cranach_d.%C3%84._-_Das_Goldene_Zeitalter_%28Alte_Pinakothek%29.jpg/1280px-Lucas_Cranach_d.%C3%84._-_Das_Goldene_Zeitalter_%28Alte_Pinakothek%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/78/Lucas_Cranach_d.%C3%84._-_Gastmahl_des_Herodes_%28St%C3%A4delsches_Kunstinstitut%29.jpg/1280px-Lucas_Cranach_d.%C3%84._-_Gastmahl_des_Herodes_%28St%C3%A4delsches_Kunstinstitut%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b5/Lucas_Cranach_-_Der_Jungbrunnen_%28Gem%C3%A4ldegalerie_Berlin%29.jpg/1280px-Lucas_Cranach_-_Der_Jungbrunnen_%28Gem%C3%A4ldegalerie_Berlin%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/35/Lucas_Cranach_d.%C3%84._-_Das_Martyrium_der_heiligen_Katarina_%28R%C3%A1day_Library%2C_Budapest%29.jpg/960px-Lucas_Cranach_d.%C3%84._-_Das_Martyrium_der_heiligen_Katarina_%28R%C3%A1day_Library%2C_Budapest%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N148" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/04/Weimar_-_Altar_in_St._Peter_und_Paul%2C_Weimar_by_Cranachs_-_Central_piece.jpg/1280px-Weimar_-_Altar_in_St._Peter_und_Paul%2C_Weimar_by_Cranachs_-_Central_piece.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9a/Cranach_the_Younger%2C_Lucas_-_Christ_and_the_adulteress.jpg/1280px-Cranach_the_Younger%2C_Lucas_-_Christ_and_the_adulteress.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Lucas_Cranach_the_Younger_-_Prince_Elector_Moritz_of_Saxony_-_Google_Art_Project.jpg/960px-Lucas_Cranach_the_Younger_-_Prince_Elector_Moritz_of_Saxony_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N148" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Antonio_Allegri%2C_called_Correggio_-_Jupiter_and_Io_-_Google_Art_Project.jpg/500px-Antonio_Allegri%2C_called_Correggio_-_Jupiter_and_Io_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/14/Le_Mariage_mystique_de_sainte_Catherine_d%27Alexandrie_en_pr%C3%A9sence_de_saint_S%C3%A9bastien_-_Le_Corr%C3%A8ge_-_Mus%C3%A9e_du_Louvre_Peintures_INV_41.jpg/1280px-Le_Mariage_mystique_de_sainte_Catherine_d%27Alexandrie_en_pr%C3%A9sence_de_saint_S%C3%A9bastien_-_Le_Corr%C3%A8ge_-_Mus%C3%A9e_du_Louvre_Peintures_INV_41.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Antonio_Allegri%2C_called_Correggio_-_The_Abduction_of_Ganymede_-_Google_Art_Project.jpg/500px-Antonio_Allegri%2C_called_Correggio_-_The_Abduction_of_Ganymede_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/David_and_Goliath_by_Daniele_da_Volterra_%28Louvre_INV_566%29_verso_02.jpg/1280px-David_and_Goliath_by_Daniele_da_Volterra_%28Louvre_INV_566%29_verso_02.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId181"/>
@@ -26943,8 +26943,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/19/La_Charit%C3%A9_-_Andrea_del_Sarto_-_Mus%C3%A9e_du_Louvre_Peintures_INV_712.jpg/960px-La_Charit%C3%A9_-_Andrea_del_Sarto_-_Mus%C3%A9e_du_Louvre_Peintures_INV_712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Andrea_del_Sarto_-_Disputation_on_the_Trinity_-_WGA0397.jpg/960px-Andrea_del_Sarto_-_Disputation_on_the_Trinity_-_WGA0397.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId201"/>
@@ -26955,7 +26955,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="rId207"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/24/Rosso_Fiorentino_%28Giovanni_Battista_di_Jacopo%29_%281495_-_1540%29_-_Portrait_of_a_Young_Man_-_245A_-_Gem%C3%A4ldegalerie.jpg/960px-Rosso_Fiorentino_%28Giovanni_Battista_di_Jacopo%29_%281495_-_1540%29_-_Portrait_of_a_Young_Man_-_245A_-_Gem%C3%A4ldegalerie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId209"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId211"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId212"/>
@@ -26966,28 +26966,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/Self-portrait_at_the_Clavichord_with_a_Servant_by_Lavinia_Fontana.jpg/960px-Self-portrait_at_the_Clavichord_with_a_Servant_by_Lavinia_Fontana.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" display="https://upload.wikimedia.org/wikipedia/commons/b/ba/%27Christ_with_the_Symbols_of_the_Passion%27%2C_oil_on_canvas_painting_by_Lavinia_Fontana%2C_1576%2C_El_Paso_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/03/L%27Incarnation_du_Christ_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_96_%3B_MR_223.jpg/960px-L%27Incarnation_du_Christ_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_96_%3B_MR_223.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Le_Mariage_mystique_de_sainte_Catherine_de_Sienne_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_97.jpg/960px-Le_Mariage_mystique_de_sainte_Catherine_de_Sienne_-_Fra_Bartolomeo_-_Mus%C3%A9e_du_Louvre_Peintures_INV_97.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId223"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId227"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Diptyque_de_Jean_Carondelet_%E2%80%93_Jan_Mabuse_%E2%80%93_Mus%C3%A9e_du_Louvre%2C_INV_1442%2C_INV_1443_%E2%80%93_Q27051640.jpg/1280px-Diptyque_de_Jean_Carondelet_%E2%80%93_Jan_Mabuse_%E2%80%93_Mus%C3%A9e_du_Louvre%2C_INV_1442%2C_INV_1443_%E2%80%93_Q27051640.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N215" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Gossaert%2C_Jan_-_Diptyque_Carondelet_La_Vierge_%C3%A0_l%27Enfant%2C_1517%2C_INV_1443%2C_0000385324_OG.jpg/1280px-Gossaert%2C_Jan_-_Diptyque_Carondelet_La_Vierge_%C3%A0_l%27Enfant%2C_1517%2C_INV_1443%2C_0000385324_OG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L220" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Matthias_Gr%C3%BCnewald_-_Die_Kreuzigung_Christi_%28Kunstmuseum_Basel%29.jpg/960px-Matthias_Gr%C3%BCnewald_-_Die_Kreuzigung_Christi_%28Kunstmuseum_Basel%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M221" display="Le Retable d'Heller " r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N215" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L220" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N221" r:id="rId239"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P221" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Matthias_Gr%C3%BCnewald%2C_The_Small_Crucifixion%2C_c._1511-1520%2C_NGA_46118.jpg/960px-Matthias_Gr%C3%BCnewald%2C_The_Small_Crucifixion%2C_c._1511-1520%2C_NGA_46118.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L223" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" r:id="rId243"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L225" r:id="rId244"/>
@@ -26996,141 +26996,143 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="rId247"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Hans_Holbein%2C_the_Younger_-_Sir_Thomas_More_-_Google_Art_Project.jpg/960px-Hans_Holbein%2C_the_Younger_-_Sir_Thomas_More_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L232" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Portrait_of_Nicholas_Kratzer_%281528%29_Hans_Holbein_d._J._%28Louvre_Museum%29.jpg/960px-Portrait_of_Nicholas_Kratzer_%281528%29_Hans_Holbein_d._J._%28Louvre_Museum%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Hans_Holbein_the_Younger_-_Charles_de_Solier%2C_Sieur_de_Morette_-_Google_Art_Project.jpg/960px-Hans_Holbein_the_Younger_-_Charles_de_Solier%2C_Sieur_de_Morette_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c6/Hans_the_Younger_Holbein_-_Christina_of_Denmark%2C_Duchess_of_Milan_-_Google_Art_Project.jpg/500px-Hans_the_Younger_Holbein_-_Christina_of_Denmark%2C_Duchess_of_Milan_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L242" display="https://upload.wikimedia.org/wikipedia/commons/a/a2/Lorenzo_Lotto%2C_%2C_Kunsthistorisches_Museum_Wien%2C_Gem%C3%A4ldegalerie_-_Bildnis_eines_Mannes_mit_einer_goldenen_Tierpranke_%28Leonino_Brembate%5E%29_-_GG_265_-_Kunsthistorisches_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=it" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L243" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Accademia_-_Ritratto_di_giovane_gentiluomo_nel_suo_studio_-_Lorenzo_Lotto_cat.912.jpg/1280px-Accademia_-_Ritratto_di_giovane_gentiluomo_nel_suo_studio_-_Lorenzo_Lotto_cat.912.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L244" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L245" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L246" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L247" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L248" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L249" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L251" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L252" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L253" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L254" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Parmigianino_-_The_Madonna_and_Child_with_Saints_%28The_Vision_of_St_Jerome%29.jpg/500px-Parmigianino_-_The_Madonna_and_Child_with_Saints_%28The_Vision_of_St_Jerome%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L255" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L256" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L257" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L258" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L259" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L260" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L261" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L262" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L263" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L264" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/Quinten_Metsys_-_Triptyque_de_la_confr%C3%A9rie_de_Sainte-Anne_%C3%A0_Louvain.jpg/1280px-Quinten_Metsys_-_Triptyque_de_la_confr%C3%A9rie_de_Sainte-Anne_%C3%A0_Louvain.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L265" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/Altaarstuk_van_het_schrijnwerkerambacht%2C_Quinten_Massijs%2C_%281511%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_245-248.jpg/1280px-Altaarstuk_van_het_schrijnwerkerambacht%2C_Quinten_Massijs%2C_%281511%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_245-248.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L266" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L267" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Quentin_Metsys%2C_Portrait_of_Pieter_Gillis_%281517%29_Longford_Castle%2C_Wiltshire%2C_England.jpg/960px-Quentin_Metsys%2C_Portrait_of_Pieter_Gillis_%281517%29_Longford_Castle%2C_Wiltshire%2C_England.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L268" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d9/Quentin_Massys_-_Ill-Matched_Lovers%2C_c._1520-25.jpg/1280px-Quentin_Massys_-_Ill-Matched_Lovers%2C_c._1520-25.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L269" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L270" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L271" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L272" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Giovanni_Battista_Moroni_-_The_Knight_in_Black_-_Google_Art_Project.jpg/960px-Giovanni_Battista_Moroni_-_The_Knight_in_Black_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L273" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L274" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L275" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L276" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L277" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Jacopo_Palma_il_vecchio_%28c.1480-1528%29_-_Venus_and_Cupid_-_109_-_Fitzwilliam_Museum.jpg/960px-Jacopo_Palma_il_vecchio_%28c.1480-1528%29_-_Venus_and_Cupid_-_109_-_Fitzwilliam_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L278" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L279" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L280" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Joachim_Patinir_-_Rest_during_the_Flight_to_Egypt%2C_Museo_del_Prado.jpg/1280px-Joachim_Patinir_-_Rest_during_the_Flight_to_Egypt%2C_Museo_del_Prado.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L281" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L282" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Landschap_met_de_vlucht_naar_Egypte%2C_Joachim_Patinir%2C_%281516-1517%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_64.jpg/1280px-Landschap_met_de_vlucht_naar_Egypte%2C_Joachim_Patinir%2C_%281516-1517%29%2C_Koninklijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_64.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L283" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/56/Joachim_Patinir_-_Landscape_with_the_Destruction_of_Sodom_and_Gomorrah_-_Google_Art_Project.jpg/1280px-Joachim_Patinir_-_Landscape_with_the_Destruction_of_Sodom_and_Gomorrah_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L284" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L285" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L286" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L287" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L288" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L289" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L290" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L291" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Pontormo_%28Jacopo_Carucci%29_%28Italian%2C_Florentine%29_-_Portrait_of_a_Halberdier_%28Francesco_Guardi%3F%29_-_Google_Art_Project.jpg/960px-Pontormo_%28Jacopo_Carucci%29_%28Italian%2C_Florentine%29_-_Portrait_of_a_Halberdier_%28Francesco_Guardi%3F%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L292" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L293" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L294" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L295" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L296" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L297" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Francesco_Primaticcio_-_The_Holy_Family_with_Sts_Elisabeth_and_John_the_Baptist_-_WGA18410.jpg/960px-Francesco_Primaticcio_-_The_Holy_Family_with_Sts_Elisabeth_and_John_the_Baptist_-_WGA18410.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L298" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L299" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L300" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L301" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L302" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L303" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L304" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L305" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L306" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L307" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L308" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L309" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L310" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L311" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L312" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L313" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L314" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L315" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L316" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L317" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L318" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Raphael_-_The_Sistine_Madonna_-_Google_Arts_%26_Culture.jpg/960px-Raphael_-_The_Sistine_Madonna_-_Google_Arts_%26_Culture.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L319" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L320" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L321" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L322" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L323" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/La_Vierge_%C3%A0_l%27Enfant_avec_le_petit_saint_Jean_Baptiste_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_602_%3B_MR_433.jpg/960px-La_Vierge_%C3%A0_l%27Enfant_avec_le_petit_saint_Jean_Baptiste_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_602_%3B_MR_433.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=it" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L324" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Saint_Michel_et_le_Dragon_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_608_%3B_MR_439.jpg/960px-Saint_Michel_et_le_Dragon_-_Rapha%C3%ABl_-_Mus%C3%A9e_du_Louvre_Peintures_INV_608_%3B_MR_439.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L325" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L326" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L327" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Luca_Signorelli_-_Compianto_sul_Cristo_morto_%28Museo_Diocesano%2C_Cortona%29.jpg/960px-Luca_Signorelli_-_Compianto_sul_Cristo_morto_%28Museo_Diocesano%2C_Cortona%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L328" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L329" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L330" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L331" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/09/Maarten_van_Heemskerck_-_St_Luke_Painting_the_Virgin_%281532_Haarlem%29.jpg/1280px-Maarten_van_Heemskerck_-_St_Luke_Painting_the_Virgin_%281532_Haarlem%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N331" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/De_heilige_Lucas_schildert_de_Madonna_-_Maarten_van_Heemskerck-1532.JPG/1280px-De_heilige_Lucas_schildert_de_Madonna_-_Maarten_van_Heemskerck-1532.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P331" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L332" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7f/Maerten_van_Heemskerck_-_The_Triumphal_Procession_of_Bacchus_-_Google_Art_Project.jpg/1280px-Maerten_van_Heemskerck_-_The_Triumphal_Procession_of_Bacchus_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L333" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L334" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L335" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L336" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Lucas_Hugensz._van_Leyden_-_Die_Schachpartie%2C_1500_-_1520%2C_574A.jpg/1280px-Lucas_Hugensz._van_Leyden_-_Die_Schachpartie%2C_1500_-_1520%2C_574A.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L337" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b5/La_Tireuse_de_cartes_-_Lucas_van_Leyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1962_17.jpg/1280px-La_Tireuse_de_cartes_-_Lucas_van_Leyden_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1962_17.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L338" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Portrait_of_Lorenzo_de%27_Medici%2C_the_Magnificent_%281449%E2%80%931492%29%2C_by_Giorgio_Vasari_-_Uffizi_Gallery.jpg/960px-Portrait_of_Lorenzo_de%27_Medici%2C_the_Magnificent_%281449%E2%80%931492%29%2C_by_Giorgio_Vasari_-_Uffizi_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L339" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L340" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/78/Giorgio_Vasari_-_Allegory_of_Justice_and_Truth_%281543%29_-_Google_Arts_and_Culture.jpg/960px-Giorgio_Vasari_-_Allegory_of_Justice_and_Truth_%281543%29_-_Google_Arts_and_Culture.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L341" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L342" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/L%27Annonciation_-_Giorgio_Vasari_-_Mus%C3%A9e_du_Louvre_Peintures_INV_732_%3B_MR_536.jpg/960px-L%27Annonciation_-_Giorgio_Vasari_-_Mus%C3%A9e_du_Louvre_Peintures_INV_732_%3B_MR_536.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L343" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L344" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fb/Giorgio_Vasari_-_Judith_and_Holofernes_-_2-1982_-_Saint_Louis_Art_Museum.jpg/960px-Giorgio_Vasari_-_Judith_and_Holofernes_-_2-1982_-_Saint_Louis_Art_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L345" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L346" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L347" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L348" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L349" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L350" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Carlos_V_en_M%C3%BChlberg%2C_by_Titian%2C_from_Prado_in_Google_Earth.jpg/960px-Carlos_V_en_M%C3%BChlberg%2C_by_Titian%2C_from_Prado_in_Google_Earth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L351" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L352" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L353" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L354" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L355" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L356" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L357" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L358" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L359" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L360" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L361" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/The_Family_of_Darius_before_Alexander_by_Paolo_Veronese_1570.jpg/1280px-The_Family_of_Darius_before_Alexander_by_Paolo_Veronese_1570.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L362" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L363" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L364" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L365" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L238" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L242" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L243" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L244" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L245" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L246" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L247" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L248" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L249" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L251" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L252" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L253" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L254" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L255" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L256" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L257" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L258" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L259" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L260" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L261" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L262" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L263" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L264" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L265" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L266" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L267" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L268" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L269" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L270" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L271" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L272" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L273" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L274" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L275" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L276" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L277" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L278" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L279" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L280" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L281" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L282" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L283" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L284" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L285" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L286" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L287" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L288" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L289" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L290" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L291" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L292" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L293" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L294" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L295" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L296" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L297" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L298" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L299" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L300" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L301" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L302" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L303" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L304" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L305" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L306" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L307" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L308" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L309" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L310" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L311" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L312" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L313" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L314" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L315" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L316" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L317" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L318" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L319" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L320" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L321" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L322" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L323" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L324" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L325" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L326" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L327" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L328" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L329" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L330" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L331" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N331" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P331" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L332" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L333" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L334" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L335" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L336" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L337" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L338" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L339" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L340" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L341" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L342" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L343" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L344" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L345" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L346" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L347" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L348" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L349" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L350" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L351" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L352" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L353" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L354" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L355" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L356" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L357" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L358" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L359" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L360" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L361" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L362" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L363" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L364" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L365" r:id="rId386"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -16305,11 +16305,15 @@
       <c r="D208" s="10" t="s">
         <v>945</v>
       </c>
-      <c r="E208" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>611</v>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>National Gallery</t>
+        </is>
       </c>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -5544,6 +5544,7 @@
     <col min="20" max="20" width="7.28515625" style="12" customWidth="1"/>
     <col min="21" max="22" width="7.42578125" style="12" customWidth="1"/>
     <col min="23" max="23" width="6.5703125" style="12" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5615,6 +5616,11 @@
       </c>
       <c r="W1" s="10" t="s">
         <v>22</v>
+      </c>
+      <c r="X1" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artiste associé</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
